--- a/documents/지표/주별활동지수.xlsx
+++ b/documents/지표/주별활동지수.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf1f1df607fbac1a/Desktop/Github/2026-QI/documents/지표/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{1F49EEAB-D64F-4024-878C-E43B7327B9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29211603-5565-4448-9EE9-EC5D5B8A0569}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{1F49EEAB-D64F-4024-878C-E43B7327B9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4BAC590-02B2-4D8E-BFFD-AECB49CEE05D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{0FC1208A-2CB8-4E1E-B9D0-F7D163D68827}"/>
   </bookViews>
@@ -39,28 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="46">
-  <si>
-    <t>92-CS</t>
-  </si>
-  <si>
-    <t>92-MC</t>
-  </si>
-  <si>
-    <t>131-ENT</t>
-  </si>
-  <si>
-    <t>131-URO</t>
-  </si>
-  <si>
-    <t>141-단기항암</t>
-  </si>
-  <si>
-    <t>141MH병동</t>
-  </si>
-  <si>
-    <t>142MH병동</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="48">
   <si>
     <t>1주차</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -180,24 +159,54 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>131 병동</t>
+    <t>92-CS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>92 병동</t>
+    <t>92-MC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>141 단기항암</t>
+    <t>131-ENT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>141 병동</t>
+    <t>131-URO</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>142 병동</t>
+    <t>141-단기항암</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>141-MH병동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>142-MH병동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6주차(6/25~7/1)</t>
+  </si>
+  <si>
+    <t>6주차(6/25~7/1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1주차(5/15~26)</t>
+  </si>
+  <si>
+    <t>2주차(5/27~6/3)</t>
+  </si>
+  <si>
+    <t>3주차(6/4~6/10)</t>
+  </si>
+  <si>
+    <t>4주차(6/11~6/17)</t>
+  </si>
+  <si>
+    <t>5주차(6/18~6/25)</t>
   </si>
 </sst>
 </file>
@@ -349,9 +358,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -376,6 +382,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -387,12 +402,6 @@
     </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1339,12 +1348,9 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="ko-KR"/>
-              <a:t>92</a:t>
+              <a:t>92-CS</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US"/>
-              <a:t> 병동</a:t>
-            </a:r>
+            <a:endParaRPr lang="ko-KR" altLang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1467,9 +1473,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$7</c:f>
+              <c:f>Sheet1!$A$3:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1484,16 +1490,19 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$B$7</c:f>
+              <c:f>Sheet1!$B$3:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -1508,6 +1517,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1601,9 +1613,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$7</c:f>
+              <c:f>Sheet1!$A$3:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1618,16 +1630,19 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$3:$C$7</c:f>
+              <c:f>Sheet1!$C$3:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -1642,6 +1657,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1735,9 +1753,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$7</c:f>
+              <c:f>Sheet1!$A$3:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1752,16 +1770,19 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$3:$D$7</c:f>
+              <c:f>Sheet1!$D$3:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1776,6 +1797,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1869,9 +1893,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$7</c:f>
+              <c:f>Sheet1!$A$3:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1886,16 +1910,19 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$3:$E$7</c:f>
+              <c:f>Sheet1!$E$3:$E$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1910,6 +1937,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2003,9 +2033,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$7</c:f>
+              <c:f>Sheet1!$A$3:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2020,16 +2050,19 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$3:$F$7</c:f>
+              <c:f>Sheet1!$F$3:$F$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2044,6 +2077,9 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2291,12 +2327,9 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="ko-KR"/>
-              <a:t>131</a:t>
+              <a:t>92-MC</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US"/>
-              <a:t> 병동</a:t>
-            </a:r>
+            <a:endParaRPr lang="ko-KR" altLang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -2419,9 +2452,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$7</c:f>
+              <c:f>Sheet1!$G$3:$G$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2436,30 +2469,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$3:$H$7</c:f>
+              <c:f>Sheet1!$H$3:$H$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>20</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55</c:v>
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2553,9 +2592,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$7</c:f>
+              <c:f>Sheet1!$G$3:$G$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2570,30 +2609,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$I$3:$I$7</c:f>
+              <c:f>Sheet1!$I$3:$I$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>32</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>52</c:v>
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2687,9 +2732,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$7</c:f>
+              <c:f>Sheet1!$G$3:$G$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2704,30 +2749,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$3:$J$7</c:f>
+              <c:f>Sheet1!$J$3:$J$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>31</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>51</c:v>
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2821,9 +2872,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$7</c:f>
+              <c:f>Sheet1!$G$3:$G$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2838,30 +2889,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$K$3:$K$7</c:f>
+              <c:f>Sheet1!$K$3:$K$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7</c:v>
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2955,9 +3012,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$7</c:f>
+              <c:f>Sheet1!$G$3:$G$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2972,16 +3029,19 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$3:$L$7</c:f>
+              <c:f>Sheet1!$L$3:$L$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -2989,13 +3049,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16</c:v>
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3243,12 +3306,9 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="ko-KR"/>
-              <a:t>141</a:t>
+              <a:t>131-ENT</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US"/>
-              <a:t> 병동</a:t>
-            </a:r>
+            <a:endParaRPr lang="ko-KR" altLang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -3372,9 +3432,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$7</c:f>
+              <c:f>Sheet1!$M$3:$M$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3389,30 +3449,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$N$3:$N$7</c:f>
+              <c:f>Sheet1!$N$3:$N$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>47</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17</c:v>
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>28</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3507,9 +3573,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$7</c:f>
+              <c:f>Sheet1!$M$3:$M$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3524,30 +3590,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$O$3:$O$7</c:f>
+              <c:f>Sheet1!$O$3:$O$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>43</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17</c:v>
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3642,9 +3714,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$7</c:f>
+              <c:f>Sheet1!$M$3:$M$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3659,30 +3731,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$P$3:$P$7</c:f>
+              <c:f>Sheet1!$P$3:$P$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>39</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16</c:v>
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3777,9 +3855,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$7</c:f>
+              <c:f>Sheet1!$M$3:$M$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3794,30 +3872,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Q$3:$Q$7</c:f>
+              <c:f>Sheet1!$Q$3:$Q$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2</c:v>
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3912,9 +3996,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$7</c:f>
+              <c:f>Sheet1!$M$3:$M$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3929,30 +4013,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$R$3:$R$7</c:f>
+              <c:f>Sheet1!$R$3:$R$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4</c:v>
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4201,12 +4291,9 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="ko-KR"/>
-              <a:t>141</a:t>
+              <a:t>131-URO</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US"/>
-              <a:t> 병동</a:t>
-            </a:r>
+            <a:endParaRPr lang="ko-KR" altLang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -4330,9 +4417,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$7</c:f>
+              <c:f>Sheet1!$S$3:$S$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4347,30 +4434,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$T$3:$T$7</c:f>
+              <c:f>Sheet1!$T$3:$T$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>27</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4465,9 +4558,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$7</c:f>
+              <c:f>Sheet1!$S$3:$S$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4482,30 +4575,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$U$3:$U$7</c:f>
+              <c:f>Sheet1!$U$3:$U$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>26</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4600,9 +4699,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$7</c:f>
+              <c:f>Sheet1!$S$3:$S$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4617,30 +4716,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$V$3:$V$7</c:f>
+              <c:f>Sheet1!$V$3:$V$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>22</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4735,9 +4840,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$7</c:f>
+              <c:f>Sheet1!$S$3:$S$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4752,30 +4857,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$W$3:$W$7</c:f>
+              <c:f>Sheet1!$W$3:$W$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4870,9 +4981,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$7</c:f>
+              <c:f>Sheet1!$S$3:$S$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4887,30 +4998,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$X$3:$X$7</c:f>
+              <c:f>Sheet1!$X$3:$X$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5159,11 +5276,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="ko-KR"/>
-              <a:t>142</a:t>
+              <a:t>141-</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="ko-KR" altLang="en-US"/>
-              <a:t> 병동</a:t>
+              <a:t>단기항암</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -5288,9 +5405,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$7</c:f>
+              <c:f>Sheet1!$Y$3:$Y$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5305,30 +5422,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Z$3:$Z$7</c:f>
+              <c:f>Sheet1!$Z$3:$Z$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>31</c:v>
+                  <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15</c:v>
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5423,9 +5546,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$7</c:f>
+              <c:f>Sheet1!$Y$3:$Y$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5440,30 +5563,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AA$3:$AA$7</c:f>
+              <c:f>Sheet1!$AA$3:$AA$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>30</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15</c:v>
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5558,9 +5687,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$7</c:f>
+              <c:f>Sheet1!$Y$3:$Y$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5575,30 +5704,36 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AB$3:$AB$7</c:f>
+              <c:f>Sheet1!$AB$3:$AB$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>27</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5693,9 +5828,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$7</c:f>
+              <c:f>Sheet1!$Y$3:$Y$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5710,29 +5845,35 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AC$3:$AC$7</c:f>
+              <c:f>Sheet1!$AC$3:$AC$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -5828,9 +5969,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$7</c:f>
+              <c:f>Sheet1!$Y$3:$Y$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5845,29 +5986,35 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AD$3:$AD$7</c:f>
+              <c:f>Sheet1!$AD$3:$AD$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -5996,6 +6143,1984 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1692466816"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR"/>
+              <a:t>141-MH</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>병동</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AF$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>요청</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$AE$3:$AE$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1주차(5/15~26)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2주차(5/27~6/3)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3주차(6/4~6/10)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4주차(6/11~6/17)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AF$3:$AF$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3E2E-4E5C-A845-81F34F113BFC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AG$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>실시간 피드백</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$AE$3:$AE$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1주차(5/15~26)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2주차(5/27~6/3)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3주차(6/4~6/10)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4주차(6/11~6/17)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AG$3:$AG$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3E2E-4E5C-A845-81F34F113BFC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AH$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>표준 프로토콜 준수</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$AE$3:$AE$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1주차(5/15~26)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2주차(5/27~6/3)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3주차(6/4~6/10)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4주차(6/11~6/17)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AH$3:$AH$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3E2E-4E5C-A845-81F34F113BFC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AI$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>재확인 호출</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$AE$3:$AE$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1주차(5/15~26)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2주차(5/27~6/3)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3주차(6/4~6/10)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4주차(6/11~6/17)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AI$3:$AI$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3E2E-4E5C-A845-81F34F113BFC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AJ$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>회진내용 공유</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$AE$3:$AE$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1주차(5/15~26)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2주차(5/27~6/3)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3주차(6/4~6/10)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4주차(6/11~6/17)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AJ$3:$AJ$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-3E2E-4E5C-A845-81F34F113BFC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="365924976"/>
+        <c:axId val="365920816"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="365924976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="365920816"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="365920816"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="365924976"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR"/>
+              <a:t>142-MH</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>병동</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AL$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>요청</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$AK$3:$AK$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1주차(5/15~26)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2주차(5/27~6/3)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3주차(6/4~6/10)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4주차(6/11~6/17)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AL$3:$AL$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7210-4774-B325-80E5948BDAB8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AM$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>실시간 피드백</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$AK$3:$AK$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1주차(5/15~26)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2주차(5/27~6/3)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3주차(6/4~6/10)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4주차(6/11~6/17)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AM$3:$AM$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7210-4774-B325-80E5948BDAB8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AN$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>표준 프로토콜 준수</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$AK$3:$AK$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1주차(5/15~26)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2주차(5/27~6/3)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3주차(6/4~6/10)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4주차(6/11~6/17)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AN$3:$AN$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7210-4774-B325-80E5948BDAB8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AO$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>재확인 호출</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$AK$3:$AK$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1주차(5/15~26)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2주차(5/27~6/3)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3주차(6/4~6/10)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4주차(6/11~6/17)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AO$3:$AO$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7210-4774-B325-80E5948BDAB8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AP$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>회진내용 공유</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$AK$3:$AK$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1주차(5/15~26)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2주차(5/27~6/3)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3주차(6/4~6/10)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4주차(6/11~6/17)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5주차(6/18~6/25)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AP$3:$AP$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-7210-4774-B325-80E5948BDAB8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="373627632"/>
+        <c:axId val="373616816"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="373627632"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="373616816"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="373616816"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="373627632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6322,6 +8447,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -8839,6 +11044,1012 @@
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -9393,8 +12604,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9429,8 +12640,8 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>119062</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>123265</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9465,8 +12676,8 @@
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>166687</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>134471</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9501,8 +12712,8 @@
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>109537</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9537,8 +12748,8 @@
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>185737</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>89648</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9558,6 +12769,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>409012</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>62752</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>201705</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>78442</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="차트 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C700F945-1390-4007-9133-7B57A341209A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>386602</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>40340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>168087</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>11205</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="차트 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C5C6A29-8567-4874-964B-F92310378738}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -9866,769 +13149,779 @@
   <dimension ref="A1:DB10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="5.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="18.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="13.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="107" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="13" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="107" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:106" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7" t="s">
+      <c r="B1" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="17"/>
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17"/>
+      <c r="AA1" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="17"/>
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="17"/>
+      <c r="AF1" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG1" s="17"/>
+      <c r="AH1" s="17"/>
+      <c r="AI1" s="17"/>
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL1" s="17"/>
+      <c r="AM1" s="17"/>
+      <c r="AN1" s="17"/>
+      <c r="AO1" s="17"/>
+      <c r="AP1" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ1" s="17"/>
+      <c r="AR1" s="17"/>
+      <c r="AS1" s="17"/>
+      <c r="AT1" s="17"/>
+      <c r="AU1" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AV1" s="17"/>
+      <c r="AW1" s="17"/>
+      <c r="AX1" s="17"/>
+      <c r="AY1" s="17"/>
+      <c r="AZ1" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="BA1" s="17"/>
+      <c r="BB1" s="17"/>
+      <c r="BC1" s="17"/>
+      <c r="BD1" s="17"/>
+      <c r="BE1" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="BF1" s="17"/>
+      <c r="BG1" s="17"/>
+      <c r="BH1" s="17"/>
+      <c r="BI1" s="17"/>
+      <c r="BJ1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="7"/>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="7" t="s">
+      <c r="BK1" s="17"/>
+      <c r="BL1" s="17"/>
+      <c r="BM1" s="17"/>
+      <c r="BN1" s="17"/>
+      <c r="BO1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="7"/>
-      <c r="AI1" s="7"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="7" t="s">
+      <c r="BP1" s="17"/>
+      <c r="BQ1" s="17"/>
+      <c r="BR1" s="17"/>
+      <c r="BS1" s="17"/>
+      <c r="BT1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="7"/>
-      <c r="AM1" s="7"/>
-      <c r="AN1" s="7"/>
-      <c r="AO1" s="7"/>
-      <c r="AP1" s="7" t="s">
+      <c r="BU1" s="17"/>
+      <c r="BV1" s="17"/>
+      <c r="BW1" s="17"/>
+      <c r="BX1" s="17"/>
+      <c r="BY1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AQ1" s="7"/>
-      <c r="AR1" s="7"/>
-      <c r="AS1" s="7"/>
-      <c r="AT1" s="7"/>
-      <c r="AU1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="AV1" s="7"/>
-      <c r="AW1" s="7"/>
-      <c r="AX1" s="7"/>
-      <c r="AY1" s="7"/>
-      <c r="AZ1" s="7" t="s">
+      <c r="BZ1" s="17"/>
+      <c r="CA1" s="17"/>
+      <c r="CB1" s="17"/>
+      <c r="CC1" s="17"/>
+      <c r="CD1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="BA1" s="7"/>
-      <c r="BB1" s="7"/>
-      <c r="BC1" s="7"/>
-      <c r="BD1" s="7"/>
-      <c r="BE1" s="7" t="s">
+      <c r="CE1" s="17"/>
+      <c r="CF1" s="17"/>
+      <c r="CG1" s="17"/>
+      <c r="CH1" s="17"/>
+      <c r="CI1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="BF1" s="7"/>
-      <c r="BG1" s="7"/>
-      <c r="BH1" s="7"/>
-      <c r="BI1" s="7"/>
-      <c r="BJ1" s="7" t="s">
+      <c r="CJ1" s="17"/>
+      <c r="CK1" s="17"/>
+      <c r="CL1" s="17"/>
+      <c r="CM1" s="17"/>
+      <c r="CN1" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="BK1" s="7"/>
-      <c r="BL1" s="7"/>
-      <c r="BM1" s="7"/>
-      <c r="BN1" s="7"/>
-      <c r="BO1" s="7" t="s">
+      <c r="CO1" s="17"/>
+      <c r="CP1" s="17"/>
+      <c r="CQ1" s="17"/>
+      <c r="CR1" s="17"/>
+      <c r="CS1" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="BP1" s="7"/>
-      <c r="BQ1" s="7"/>
-      <c r="BR1" s="7"/>
-      <c r="BS1" s="7"/>
-      <c r="BT1" s="7" t="s">
+      <c r="CT1" s="17"/>
+      <c r="CU1" s="17"/>
+      <c r="CV1" s="17"/>
+      <c r="CW1" s="17"/>
+      <c r="CX1" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="BU1" s="7"/>
-      <c r="BV1" s="7"/>
-      <c r="BW1" s="7"/>
-      <c r="BX1" s="7"/>
-      <c r="BY1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="BZ1" s="7"/>
-      <c r="CA1" s="7"/>
-      <c r="CB1" s="7"/>
-      <c r="CC1" s="7"/>
-      <c r="CD1" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="CE1" s="7"/>
-      <c r="CF1" s="7"/>
-      <c r="CG1" s="7"/>
-      <c r="CH1" s="7"/>
-      <c r="CI1" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="CJ1" s="7"/>
-      <c r="CK1" s="7"/>
-      <c r="CL1" s="7"/>
-      <c r="CM1" s="7"/>
-      <c r="CN1" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="CO1" s="7"/>
-      <c r="CP1" s="7"/>
-      <c r="CQ1" s="7"/>
-      <c r="CR1" s="7"/>
-      <c r="CS1" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="CT1" s="7"/>
-      <c r="CU1" s="7"/>
-      <c r="CV1" s="7"/>
-      <c r="CW1" s="7"/>
-      <c r="CX1" s="7" t="s">
+      <c r="CY1" s="17"/>
+      <c r="CZ1" s="17"/>
+      <c r="DA1" s="17"/>
+      <c r="DB1" s="17"/>
+    </row>
+    <row r="2" spans="1:106" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AT2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AU2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AY2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AZ2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="BA2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="BD2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="BE2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="BF2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BH2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="BI2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="BJ2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="BK2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BM2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="BN2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BR2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="BS2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="BT2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="BU2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="BX2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="BY2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="BZ2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="CA2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="CC2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="CD2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="CE2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="CF2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="CG2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="CH2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="CI2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="CJ2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="CK2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="CL2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="CM2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="CN2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="CO2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="CP2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="CQ2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="CR2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="CS2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="CT2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="CU2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="CV2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="CW2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="CX2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="CY2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="CZ2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="DA2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="DB2" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="CY1" s="7"/>
-      <c r="CZ1" s="7"/>
-      <c r="DA1" s="7"/>
-      <c r="DB1" s="7"/>
-    </row>
-    <row r="2" spans="1:106" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="B3" s="11">
         <v>10</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="C3" s="11">
+        <v>4</v>
+      </c>
+      <c r="D3" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="9" t="s">
+      <c r="E3" s="11">
+        <v>1</v>
+      </c>
+      <c r="F3" s="11">
+        <v>0</v>
+      </c>
+      <c r="G3" s="11">
+        <v>4</v>
+      </c>
+      <c r="H3" s="11">
+        <v>4</v>
+      </c>
+      <c r="I3" s="11">
+        <v>4</v>
+      </c>
+      <c r="J3" s="11">
+        <v>1</v>
+      </c>
+      <c r="K3" s="11">
+        <v>1</v>
+      </c>
+      <c r="L3" s="11">
+        <v>4</v>
+      </c>
+      <c r="M3" s="11">
+        <v>4</v>
+      </c>
+      <c r="N3" s="11">
+        <v>4</v>
+      </c>
+      <c r="O3" s="11">
+        <v>1</v>
+      </c>
+      <c r="P3" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="11">
         <v>13</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="9" t="s">
+      <c r="R3" s="11">
         <v>13</v>
       </c>
-      <c r="K2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" s="9" t="s">
+      <c r="S3" s="11">
         <v>13</v>
       </c>
-      <c r="P2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="R2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="S2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="T2" s="9" t="s">
+      <c r="T3" s="11">
+        <v>3</v>
+      </c>
+      <c r="U3" s="11">
+        <v>3</v>
+      </c>
+      <c r="V3" s="11">
+        <v>14</v>
+      </c>
+      <c r="W3" s="11">
+        <v>14</v>
+      </c>
+      <c r="X3" s="11">
         <v>13</v>
       </c>
-      <c r="U2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="W2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="X2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AG2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="AJ2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="AN2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="AO2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AP2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AQ2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="AR2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="AS2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="AT2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AU2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="AV2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="AW2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="AX2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="AY2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AZ2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="BA2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BB2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="BC2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="BD2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="BE2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="BF2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BG2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="BH2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="BI2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="BJ2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="BK2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BL2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="BM2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="BN2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="BO2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="BP2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BQ2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="BR2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="BS2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="BT2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="BU2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BV2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="BW2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="BX2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="BY2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="BZ2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="CA2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="CB2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="CC2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="CD2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="CE2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="CF2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="CG2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="CH2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="CI2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="CJ2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="CK2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="CL2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="CM2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="CN2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="CO2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="CP2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="CQ2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="CR2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="CS2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="CT2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="CU2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="CV2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="CW2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="CX2" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="CY2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="CZ2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="DA2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="DB2" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:106" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="12">
-        <v>10</v>
-      </c>
-      <c r="C3" s="12">
-        <v>4</v>
-      </c>
-      <c r="D3" s="12">
-        <v>8</v>
-      </c>
-      <c r="E3" s="12">
+      <c r="Y3" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="11">
+        <v>3</v>
+      </c>
+      <c r="AA3" s="11">
+        <v>6</v>
+      </c>
+      <c r="AB3" s="11">
+        <v>5</v>
+      </c>
+      <c r="AC3" s="11">
+        <v>5</v>
+      </c>
+      <c r="AD3" s="11">
         <v>1</v>
       </c>
-      <c r="F3" s="12">
-        <v>0</v>
-      </c>
-      <c r="G3" s="12">
-        <v>4</v>
-      </c>
-      <c r="H3" s="12">
-        <v>4</v>
-      </c>
-      <c r="I3" s="12">
-        <v>4</v>
-      </c>
-      <c r="J3" s="12">
+      <c r="AE3" s="11">
         <v>1</v>
       </c>
-      <c r="K3" s="12">
-        <v>1</v>
-      </c>
-      <c r="L3" s="12">
-        <v>4</v>
-      </c>
-      <c r="M3" s="12">
-        <v>4</v>
-      </c>
-      <c r="N3" s="12">
-        <v>4</v>
-      </c>
-      <c r="O3" s="12">
-        <v>1</v>
-      </c>
-      <c r="P3" s="12">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="12">
-        <v>13</v>
-      </c>
-      <c r="R3" s="12">
-        <v>13</v>
-      </c>
-      <c r="S3" s="12">
-        <v>13</v>
-      </c>
-      <c r="T3" s="12">
-        <v>3</v>
-      </c>
-      <c r="U3" s="12">
-        <v>3</v>
-      </c>
-      <c r="V3" s="12">
-        <v>14</v>
-      </c>
-      <c r="W3" s="12">
-        <v>14</v>
-      </c>
-      <c r="X3" s="12">
-        <v>13</v>
-      </c>
-      <c r="Y3" s="12">
-        <v>2</v>
-      </c>
-      <c r="Z3" s="12">
-        <v>3</v>
-      </c>
-      <c r="AA3" s="12"/>
-      <c r="AB3" s="12"/>
-      <c r="AC3" s="12"/>
-      <c r="AD3" s="12"/>
-      <c r="AE3" s="12"/>
-      <c r="AF3" s="12"/>
-      <c r="AG3" s="12"/>
-      <c r="AH3" s="12"/>
-      <c r="AI3" s="12"/>
-      <c r="AJ3" s="12"/>
-      <c r="AK3" s="12"/>
-      <c r="AL3" s="12"/>
-      <c r="AM3" s="12"/>
-      <c r="AN3" s="12"/>
-      <c r="AO3" s="12"/>
-      <c r="AP3" s="12"/>
-      <c r="AQ3" s="12"/>
-      <c r="AR3" s="12"/>
-      <c r="AS3" s="12"/>
-      <c r="AT3" s="12"/>
-      <c r="AU3" s="12"/>
-      <c r="AV3" s="12"/>
-      <c r="AW3" s="12"/>
-      <c r="AX3" s="12"/>
-      <c r="AY3" s="12"/>
-      <c r="AZ3" s="12"/>
-      <c r="BA3" s="12"/>
-      <c r="BB3" s="12"/>
-      <c r="BC3" s="12"/>
-      <c r="BD3" s="12"/>
-      <c r="BE3" s="12"/>
-      <c r="BF3" s="12"/>
-      <c r="BG3" s="12"/>
-      <c r="BH3" s="12"/>
-      <c r="BI3" s="12"/>
-      <c r="BJ3" s="12"/>
-      <c r="BK3" s="12"/>
-      <c r="BL3" s="12"/>
-      <c r="BM3" s="12"/>
-      <c r="BN3" s="12"/>
-      <c r="BO3" s="12"/>
-      <c r="BP3" s="12"/>
-      <c r="BQ3" s="12"/>
-      <c r="BR3" s="12"/>
-      <c r="BS3" s="12"/>
-      <c r="BT3" s="12"/>
-      <c r="BU3" s="12"/>
-      <c r="BV3" s="12"/>
-      <c r="BW3" s="12"/>
-      <c r="BX3" s="12"/>
-      <c r="BY3" s="12"/>
-      <c r="BZ3" s="12"/>
-      <c r="CA3" s="12"/>
-      <c r="CB3" s="12"/>
-      <c r="CC3" s="12"/>
-      <c r="CD3" s="12"/>
-      <c r="CE3" s="12"/>
-      <c r="CF3" s="12"/>
-      <c r="CG3" s="12"/>
-      <c r="CH3" s="12"/>
-      <c r="CI3" s="12"/>
-      <c r="CJ3" s="12"/>
-      <c r="CK3" s="12"/>
-      <c r="CL3" s="12"/>
-      <c r="CM3" s="12"/>
-      <c r="CN3" s="12"/>
-      <c r="CO3" s="12"/>
-      <c r="CP3" s="12"/>
-      <c r="CQ3" s="12"/>
-      <c r="CR3" s="12"/>
-      <c r="CS3" s="12"/>
-      <c r="CT3" s="12"/>
-      <c r="CU3" s="12"/>
-      <c r="CV3" s="12"/>
-      <c r="CW3" s="12"/>
-      <c r="CX3" s="12"/>
-      <c r="CY3" s="12"/>
-      <c r="CZ3" s="12"/>
-      <c r="DA3" s="12"/>
-      <c r="DB3" s="12"/>
+      <c r="AF3" s="11"/>
+      <c r="AG3" s="11"/>
+      <c r="AH3" s="11"/>
+      <c r="AI3" s="11"/>
+      <c r="AJ3" s="11"/>
+      <c r="AK3" s="11"/>
+      <c r="AL3" s="11"/>
+      <c r="AM3" s="11"/>
+      <c r="AN3" s="11"/>
+      <c r="AO3" s="11"/>
+      <c r="AP3" s="11"/>
+      <c r="AQ3" s="11"/>
+      <c r="AR3" s="11"/>
+      <c r="AS3" s="11"/>
+      <c r="AT3" s="11"/>
+      <c r="AU3" s="11"/>
+      <c r="AV3" s="11"/>
+      <c r="AW3" s="11"/>
+      <c r="AX3" s="11"/>
+      <c r="AY3" s="11"/>
+      <c r="AZ3" s="11"/>
+      <c r="BA3" s="11"/>
+      <c r="BB3" s="11"/>
+      <c r="BC3" s="11"/>
+      <c r="BD3" s="11"/>
+      <c r="BE3" s="11"/>
+      <c r="BF3" s="11"/>
+      <c r="BG3" s="11"/>
+      <c r="BH3" s="11"/>
+      <c r="BI3" s="11"/>
+      <c r="BJ3" s="11"/>
+      <c r="BK3" s="11"/>
+      <c r="BL3" s="11"/>
+      <c r="BM3" s="11"/>
+      <c r="BN3" s="11"/>
+      <c r="BO3" s="11"/>
+      <c r="BP3" s="11"/>
+      <c r="BQ3" s="11"/>
+      <c r="BR3" s="11"/>
+      <c r="BS3" s="11"/>
+      <c r="BT3" s="11"/>
+      <c r="BU3" s="11"/>
+      <c r="BV3" s="11"/>
+      <c r="BW3" s="11"/>
+      <c r="BX3" s="11"/>
+      <c r="BY3" s="11"/>
+      <c r="BZ3" s="11"/>
+      <c r="CA3" s="11"/>
+      <c r="CB3" s="11"/>
+      <c r="CC3" s="11"/>
+      <c r="CD3" s="11"/>
+      <c r="CE3" s="11"/>
+      <c r="CF3" s="11"/>
+      <c r="CG3" s="11"/>
+      <c r="CH3" s="11"/>
+      <c r="CI3" s="11"/>
+      <c r="CJ3" s="11"/>
+      <c r="CK3" s="11"/>
+      <c r="CL3" s="11"/>
+      <c r="CM3" s="11"/>
+      <c r="CN3" s="11"/>
+      <c r="CO3" s="11"/>
+      <c r="CP3" s="11"/>
+      <c r="CQ3" s="11"/>
+      <c r="CR3" s="11"/>
+      <c r="CS3" s="11"/>
+      <c r="CT3" s="11"/>
+      <c r="CU3" s="11"/>
+      <c r="CV3" s="11"/>
+      <c r="CW3" s="11"/>
+      <c r="CX3" s="11"/>
+      <c r="CY3" s="11"/>
+      <c r="CZ3" s="11"/>
+      <c r="DA3" s="11"/>
+      <c r="DB3" s="11"/>
     </row>
     <row r="4" spans="1:106" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B4" s="6">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6">
         <v>10</v>
-      </c>
-      <c r="C4" s="6">
-        <v>4</v>
-      </c>
-      <c r="D4" s="6">
-        <v>8</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
       </c>
       <c r="F4" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H4" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="6">
         <v>4</v>
@@ -10637,58 +13930,68 @@
         <v>1</v>
       </c>
       <c r="K4" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M4" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4" s="6">
         <v>4</v>
       </c>
       <c r="O4" s="6">
+        <v>2</v>
+      </c>
+      <c r="P4" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>15</v>
+      </c>
+      <c r="R4" s="6">
+        <v>14</v>
+      </c>
+      <c r="S4" s="6">
+        <v>10</v>
+      </c>
+      <c r="T4" s="6">
         <v>1</v>
       </c>
-      <c r="P4" s="6">
+      <c r="U4" s="6">
+        <v>2</v>
+      </c>
+      <c r="V4" s="6">
+        <v>10</v>
+      </c>
+      <c r="W4" s="6">
+        <v>9</v>
+      </c>
+      <c r="X4" s="6">
+        <v>8</v>
+      </c>
+      <c r="Y4" s="6">
         <v>1</v>
       </c>
-      <c r="Q4" s="6">
-        <v>13</v>
-      </c>
-      <c r="R4" s="6">
-        <v>13</v>
-      </c>
-      <c r="S4" s="6">
-        <v>13</v>
-      </c>
-      <c r="T4" s="6">
-        <v>3</v>
-      </c>
-      <c r="U4" s="6">
-        <v>3</v>
-      </c>
-      <c r="V4" s="6">
-        <v>14</v>
-      </c>
-      <c r="W4" s="6">
-        <v>14</v>
-      </c>
-      <c r="X4" s="6">
-        <v>13</v>
-      </c>
-      <c r="Y4" s="6">
-        <v>2</v>
-      </c>
       <c r="Z4" s="6">
-        <v>3</v>
-      </c>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>11</v>
+      </c>
+      <c r="AB4" s="6">
+        <v>10</v>
+      </c>
+      <c r="AC4" s="6">
+        <v>11</v>
+      </c>
+      <c r="AD4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="6">
+        <v>1</v>
+      </c>
       <c r="AF4" s="6"/>
       <c r="AG4" s="6"/>
       <c r="AH4" s="6"/>
@@ -10765,169 +14068,179 @@
       <c r="DA4" s="6"/>
       <c r="DB4" s="6"/>
     </row>
-    <row r="5" spans="1:106" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="11">
+        <v>6</v>
+      </c>
+      <c r="C5" s="11">
+        <v>5</v>
+      </c>
+      <c r="D5" s="11">
+        <v>3</v>
+      </c>
+      <c r="E5" s="11">
+        <v>1</v>
+      </c>
+      <c r="F5" s="11">
+        <v>1</v>
+      </c>
+      <c r="G5" s="11">
         <v>2</v>
       </c>
-      <c r="B5" s="12">
+      <c r="H5" s="11">
+        <v>2</v>
+      </c>
+      <c r="I5" s="11">
+        <v>2</v>
+      </c>
+      <c r="J5" s="11">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11">
+        <v>0</v>
+      </c>
+      <c r="L5" s="11">
+        <v>20</v>
+      </c>
+      <c r="M5" s="11">
+        <v>20</v>
+      </c>
+      <c r="N5" s="11">
+        <v>15</v>
+      </c>
+      <c r="O5" s="11">
+        <v>2</v>
+      </c>
+      <c r="P5" s="11">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>34</v>
+      </c>
+      <c r="R5" s="11">
+        <v>32</v>
+      </c>
+      <c r="S5" s="11">
+        <v>31</v>
+      </c>
+      <c r="T5" s="11">
         <v>6</v>
       </c>
-      <c r="C5" s="12">
-        <v>5</v>
-      </c>
-      <c r="D5" s="12">
-        <v>3</v>
-      </c>
-      <c r="E5" s="12">
-        <v>1</v>
-      </c>
-      <c r="F5" s="12">
-        <v>1</v>
-      </c>
-      <c r="G5" s="12">
-        <v>2</v>
-      </c>
-      <c r="H5" s="12">
-        <v>2</v>
-      </c>
-      <c r="I5" s="12">
-        <v>2</v>
-      </c>
-      <c r="J5" s="12">
-        <v>0</v>
-      </c>
-      <c r="K5" s="12">
-        <v>0</v>
-      </c>
-      <c r="L5" s="12">
-        <v>20</v>
-      </c>
-      <c r="M5" s="12">
-        <v>20</v>
-      </c>
-      <c r="N5" s="12">
-        <v>15</v>
-      </c>
-      <c r="O5" s="12">
-        <v>2</v>
-      </c>
-      <c r="P5" s="12">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>34</v>
-      </c>
-      <c r="R5" s="12">
-        <v>32</v>
-      </c>
-      <c r="S5" s="12">
-        <v>31</v>
-      </c>
-      <c r="T5" s="12">
-        <v>6</v>
-      </c>
-      <c r="U5" s="12">
+      <c r="U5" s="11">
         <v>11</v>
       </c>
-      <c r="V5" s="12">
+      <c r="V5" s="11">
         <v>55</v>
       </c>
-      <c r="W5" s="12">
+      <c r="W5" s="11">
         <v>52</v>
       </c>
-      <c r="X5" s="12">
+      <c r="X5" s="11">
         <v>51</v>
       </c>
-      <c r="Y5" s="12">
+      <c r="Y5" s="11">
         <v>7</v>
       </c>
-      <c r="Z5" s="12">
+      <c r="Z5" s="11">
         <v>16</v>
       </c>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="12"/>
-      <c r="AF5" s="12"/>
-      <c r="AG5" s="12"/>
-      <c r="AH5" s="12"/>
-      <c r="AI5" s="12"/>
-      <c r="AJ5" s="12"/>
-      <c r="AK5" s="12"/>
-      <c r="AL5" s="12"/>
-      <c r="AM5" s="12"/>
-      <c r="AN5" s="12"/>
-      <c r="AO5" s="12"/>
-      <c r="AP5" s="12"/>
-      <c r="AQ5" s="12"/>
-      <c r="AR5" s="12"/>
-      <c r="AS5" s="12"/>
-      <c r="AT5" s="12"/>
-      <c r="AU5" s="12"/>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="12"/>
-      <c r="AX5" s="12"/>
-      <c r="AY5" s="12"/>
-      <c r="AZ5" s="12"/>
-      <c r="BA5" s="12"/>
-      <c r="BB5" s="12"/>
-      <c r="BC5" s="12"/>
-      <c r="BD5" s="12"/>
-      <c r="BE5" s="12"/>
-      <c r="BF5" s="12"/>
-      <c r="BG5" s="12"/>
-      <c r="BH5" s="12"/>
-      <c r="BI5" s="12"/>
-      <c r="BJ5" s="12"/>
-      <c r="BK5" s="12"/>
-      <c r="BL5" s="12"/>
-      <c r="BM5" s="12"/>
-      <c r="BN5" s="12"/>
-      <c r="BO5" s="12"/>
-      <c r="BP5" s="12"/>
-      <c r="BQ5" s="12"/>
-      <c r="BR5" s="12"/>
-      <c r="BS5" s="12"/>
-      <c r="BT5" s="12"/>
-      <c r="BU5" s="12"/>
-      <c r="BV5" s="12"/>
-      <c r="BW5" s="12"/>
-      <c r="BX5" s="12"/>
-      <c r="BY5" s="12"/>
-      <c r="BZ5" s="12"/>
-      <c r="CA5" s="12"/>
-      <c r="CB5" s="12"/>
-      <c r="CC5" s="12"/>
-      <c r="CD5" s="12"/>
-      <c r="CE5" s="12"/>
-      <c r="CF5" s="12"/>
-      <c r="CG5" s="12"/>
-      <c r="CH5" s="12"/>
-      <c r="CI5" s="12"/>
-      <c r="CJ5" s="12"/>
-      <c r="CK5" s="12"/>
-      <c r="CL5" s="12"/>
-      <c r="CM5" s="12"/>
-      <c r="CN5" s="12"/>
-      <c r="CO5" s="12"/>
-      <c r="CP5" s="12"/>
-      <c r="CQ5" s="12"/>
-      <c r="CR5" s="12"/>
-      <c r="CS5" s="12"/>
-      <c r="CT5" s="12"/>
-      <c r="CU5" s="12"/>
-      <c r="CV5" s="12"/>
-      <c r="CW5" s="12"/>
-      <c r="CX5" s="12"/>
-      <c r="CY5" s="12"/>
-      <c r="CZ5" s="12"/>
-      <c r="DA5" s="12"/>
-      <c r="DB5" s="12"/>
+      <c r="AA5" s="11">
+        <v>28</v>
+      </c>
+      <c r="AB5" s="11">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="11">
+        <v>25</v>
+      </c>
+      <c r="AD5" s="11">
+        <v>4</v>
+      </c>
+      <c r="AE5" s="11">
+        <v>9</v>
+      </c>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+      <c r="BC5" s="11"/>
+      <c r="BD5" s="11"/>
+      <c r="BE5" s="11"/>
+      <c r="BF5" s="11"/>
+      <c r="BG5" s="11"/>
+      <c r="BH5" s="11"/>
+      <c r="BI5" s="11"/>
+      <c r="BJ5" s="11"/>
+      <c r="BK5" s="11"/>
+      <c r="BL5" s="11"/>
+      <c r="BM5" s="11"/>
+      <c r="BN5" s="11"/>
+      <c r="BO5" s="11"/>
+      <c r="BP5" s="11"/>
+      <c r="BQ5" s="11"/>
+      <c r="BR5" s="11"/>
+      <c r="BS5" s="11"/>
+      <c r="BT5" s="11"/>
+      <c r="BU5" s="11"/>
+      <c r="BV5" s="11"/>
+      <c r="BW5" s="11"/>
+      <c r="BX5" s="11"/>
+      <c r="BY5" s="11"/>
+      <c r="BZ5" s="11"/>
+      <c r="CA5" s="11"/>
+      <c r="CB5" s="11"/>
+      <c r="CC5" s="11"/>
+      <c r="CD5" s="11"/>
+      <c r="CE5" s="11"/>
+      <c r="CF5" s="11"/>
+      <c r="CG5" s="11"/>
+      <c r="CH5" s="11"/>
+      <c r="CI5" s="11"/>
+      <c r="CJ5" s="11"/>
+      <c r="CK5" s="11"/>
+      <c r="CL5" s="11"/>
+      <c r="CM5" s="11"/>
+      <c r="CN5" s="11"/>
+      <c r="CO5" s="11"/>
+      <c r="CP5" s="11"/>
+      <c r="CQ5" s="11"/>
+      <c r="CR5" s="11"/>
+      <c r="CS5" s="11"/>
+      <c r="CT5" s="11"/>
+      <c r="CU5" s="11"/>
+      <c r="CV5" s="11"/>
+      <c r="CW5" s="11"/>
+      <c r="CX5" s="11"/>
+      <c r="CY5" s="11"/>
+      <c r="CZ5" s="11"/>
+      <c r="DA5" s="11"/>
+      <c r="DB5" s="11"/>
     </row>
     <row r="6" spans="1:106" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="B6" s="6">
         <v>0</v>
@@ -10959,26 +14272,66 @@
       <c r="K6" s="6">
         <v>0</v>
       </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
+      <c r="L6" s="6">
+        <v>0</v>
+      </c>
+      <c r="M6" s="6">
+        <v>0</v>
+      </c>
+      <c r="N6" s="6">
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0</v>
+      </c>
+      <c r="X6" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0</v>
+      </c>
       <c r="AF6" s="6"/>
       <c r="AG6" s="6"/>
       <c r="AH6" s="6"/>
@@ -11055,501 +14408,531 @@
       <c r="DA6" s="6"/>
       <c r="DB6" s="6"/>
     </row>
-    <row r="7" spans="1:106" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="11">
+        <v>47</v>
+      </c>
+      <c r="C7" s="11">
+        <v>43</v>
+      </c>
+      <c r="D7" s="11">
+        <v>39</v>
+      </c>
+      <c r="E7" s="11">
+        <v>3</v>
+      </c>
+      <c r="F7" s="11">
+        <v>2</v>
+      </c>
+      <c r="G7" s="11">
+        <v>8</v>
+      </c>
+      <c r="H7" s="11">
+        <v>8</v>
+      </c>
+      <c r="I7" s="11">
+        <v>6</v>
+      </c>
+      <c r="J7" s="11">
+        <v>0</v>
+      </c>
+      <c r="K7" s="11">
+        <v>0</v>
+      </c>
+      <c r="L7" s="11">
+        <v>9</v>
+      </c>
+      <c r="M7" s="11">
+        <v>9</v>
+      </c>
+      <c r="N7" s="11">
+        <v>9</v>
+      </c>
+      <c r="O7" s="11">
+        <v>1</v>
+      </c>
+      <c r="P7" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>13</v>
+      </c>
+      <c r="R7" s="11">
+        <v>13</v>
+      </c>
+      <c r="S7" s="11">
+        <v>12</v>
+      </c>
+      <c r="T7" s="11">
+        <v>3</v>
+      </c>
+      <c r="U7" s="11">
         <v>4</v>
       </c>
-      <c r="B7" s="12">
-        <v>47</v>
-      </c>
-      <c r="C7" s="12">
-        <v>43</v>
-      </c>
-      <c r="D7" s="12">
+      <c r="V7" s="11">
+        <v>17</v>
+      </c>
+      <c r="W7" s="11">
+        <v>17</v>
+      </c>
+      <c r="X7" s="11">
+        <v>16</v>
+      </c>
+      <c r="Y7" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z7" s="11">
+        <v>4</v>
+      </c>
+      <c r="AA7" s="11">
+        <v>9</v>
+      </c>
+      <c r="AB7" s="11">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="11">
+        <v>8</v>
+      </c>
+      <c r="AD7" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="11">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="11"/>
+      <c r="AG7" s="11"/>
+      <c r="AH7" s="11"/>
+      <c r="AI7" s="11"/>
+      <c r="AJ7" s="11"/>
+      <c r="AK7" s="11"/>
+      <c r="AL7" s="11"/>
+      <c r="AM7" s="11"/>
+      <c r="AN7" s="11"/>
+      <c r="AO7" s="11"/>
+      <c r="AP7" s="11"/>
+      <c r="AQ7" s="11"/>
+      <c r="AR7" s="11"/>
+      <c r="AS7" s="11"/>
+      <c r="AT7" s="11"/>
+      <c r="AU7" s="11"/>
+      <c r="AV7" s="11"/>
+      <c r="AW7" s="11"/>
+      <c r="AX7" s="11"/>
+      <c r="AY7" s="11"/>
+      <c r="AZ7" s="11"/>
+      <c r="BA7" s="11"/>
+      <c r="BB7" s="11"/>
+      <c r="BC7" s="11"/>
+      <c r="BD7" s="11"/>
+      <c r="BE7" s="11"/>
+      <c r="BF7" s="11"/>
+      <c r="BG7" s="11"/>
+      <c r="BH7" s="11"/>
+      <c r="BI7" s="11"/>
+      <c r="BJ7" s="11"/>
+      <c r="BK7" s="11"/>
+      <c r="BL7" s="11"/>
+      <c r="BM7" s="11"/>
+      <c r="BN7" s="11"/>
+      <c r="BO7" s="11"/>
+      <c r="BP7" s="11"/>
+      <c r="BQ7" s="11"/>
+      <c r="BR7" s="11"/>
+      <c r="BS7" s="11"/>
+      <c r="BT7" s="11"/>
+      <c r="BU7" s="11"/>
+      <c r="BV7" s="11"/>
+      <c r="BW7" s="11"/>
+      <c r="BX7" s="11"/>
+      <c r="BY7" s="11"/>
+      <c r="BZ7" s="11"/>
+      <c r="CA7" s="11"/>
+      <c r="CB7" s="11"/>
+      <c r="CC7" s="11"/>
+      <c r="CD7" s="11"/>
+      <c r="CE7" s="11"/>
+      <c r="CF7" s="11"/>
+      <c r="CG7" s="11"/>
+      <c r="CH7" s="11"/>
+      <c r="CI7" s="11"/>
+      <c r="CJ7" s="11"/>
+      <c r="CK7" s="11"/>
+      <c r="CL7" s="11"/>
+      <c r="CM7" s="11"/>
+      <c r="CN7" s="11"/>
+      <c r="CO7" s="11"/>
+      <c r="CP7" s="11"/>
+      <c r="CQ7" s="11"/>
+      <c r="CR7" s="11"/>
+      <c r="CS7" s="11"/>
+      <c r="CT7" s="11"/>
+      <c r="CU7" s="11"/>
+      <c r="CV7" s="11"/>
+      <c r="CW7" s="11"/>
+      <c r="CX7" s="11"/>
+      <c r="CY7" s="11"/>
+      <c r="CZ7" s="11"/>
+      <c r="DA7" s="11"/>
+      <c r="DB7" s="11"/>
+    </row>
+    <row r="8" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="12">
-        <v>3</v>
-      </c>
-      <c r="F7" s="12">
+      <c r="B8" s="11">
+        <v>27</v>
+      </c>
+      <c r="C8" s="11">
+        <v>26</v>
+      </c>
+      <c r="D8" s="11">
+        <v>22</v>
+      </c>
+      <c r="E8" s="11">
         <v>2</v>
       </c>
-      <c r="G7" s="12">
+      <c r="F8" s="11">
+        <v>10</v>
+      </c>
+      <c r="G8" s="11">
+        <v>6</v>
+      </c>
+      <c r="H8" s="11">
+        <v>6</v>
+      </c>
+      <c r="I8" s="11">
+        <v>6</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0</v>
+      </c>
+      <c r="K8" s="11">
+        <v>2</v>
+      </c>
+      <c r="L8" s="11">
+        <v>10</v>
+      </c>
+      <c r="M8" s="11">
+        <v>10</v>
+      </c>
+      <c r="N8" s="11">
+        <v>9</v>
+      </c>
+      <c r="O8" s="11">
+        <v>1</v>
+      </c>
+      <c r="P8" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>12</v>
+      </c>
+      <c r="R8" s="11">
+        <v>11</v>
+      </c>
+      <c r="S8" s="11">
+        <v>11</v>
+      </c>
+      <c r="T8" s="11">
+        <v>2</v>
+      </c>
+      <c r="U8" s="11">
+        <v>2</v>
+      </c>
+      <c r="V8" s="11">
+        <v>12</v>
+      </c>
+      <c r="W8" s="11">
+        <v>11</v>
+      </c>
+      <c r="X8" s="11">
+        <v>11</v>
+      </c>
+      <c r="Y8" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="11">
+        <v>2</v>
+      </c>
+      <c r="AA8" s="11">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="11">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="11">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="11">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="11"/>
+      <c r="AG8" s="11"/>
+      <c r="AH8" s="11"/>
+      <c r="AI8" s="11"/>
+      <c r="AJ8" s="11"/>
+      <c r="AK8" s="11"/>
+      <c r="AL8" s="11"/>
+      <c r="AM8" s="11"/>
+      <c r="AN8" s="11"/>
+      <c r="AO8" s="11"/>
+      <c r="AP8" s="11"/>
+      <c r="AQ8" s="11"/>
+      <c r="AR8" s="11"/>
+      <c r="AS8" s="11"/>
+      <c r="AT8" s="11"/>
+      <c r="AU8" s="11"/>
+      <c r="AV8" s="11"/>
+      <c r="AW8" s="11"/>
+      <c r="AX8" s="11"/>
+      <c r="AY8" s="11"/>
+      <c r="AZ8" s="11"/>
+      <c r="BA8" s="11"/>
+      <c r="BB8" s="11"/>
+      <c r="BC8" s="11"/>
+      <c r="BD8" s="11"/>
+      <c r="BE8" s="11"/>
+      <c r="BF8" s="11"/>
+      <c r="BG8" s="11"/>
+      <c r="BH8" s="11"/>
+      <c r="BI8" s="11"/>
+      <c r="BJ8" s="11"/>
+      <c r="BK8" s="11"/>
+      <c r="BL8" s="11"/>
+      <c r="BM8" s="11"/>
+      <c r="BN8" s="11"/>
+      <c r="BO8" s="11"/>
+      <c r="BP8" s="11"/>
+      <c r="BQ8" s="11"/>
+      <c r="BR8" s="11"/>
+      <c r="BS8" s="11"/>
+      <c r="BT8" s="11"/>
+      <c r="BU8" s="11"/>
+      <c r="BV8" s="11"/>
+      <c r="BW8" s="11"/>
+      <c r="BX8" s="11"/>
+      <c r="BY8" s="11"/>
+      <c r="BZ8" s="11"/>
+      <c r="CA8" s="11"/>
+      <c r="CB8" s="11"/>
+      <c r="CC8" s="11"/>
+      <c r="CD8" s="11"/>
+      <c r="CE8" s="11"/>
+      <c r="CF8" s="11"/>
+      <c r="CG8" s="11"/>
+      <c r="CH8" s="11"/>
+      <c r="CI8" s="11"/>
+      <c r="CJ8" s="11"/>
+      <c r="CK8" s="11"/>
+      <c r="CL8" s="11"/>
+      <c r="CM8" s="11"/>
+      <c r="CN8" s="11"/>
+      <c r="CO8" s="11"/>
+      <c r="CP8" s="11"/>
+      <c r="CQ8" s="11"/>
+      <c r="CR8" s="11"/>
+      <c r="CS8" s="11"/>
+      <c r="CT8" s="11"/>
+      <c r="CU8" s="11"/>
+      <c r="CV8" s="11"/>
+      <c r="CW8" s="11"/>
+      <c r="CX8" s="11"/>
+      <c r="CY8" s="11"/>
+      <c r="CZ8" s="11"/>
+      <c r="DA8" s="11"/>
+      <c r="DB8" s="11"/>
+    </row>
+    <row r="9" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="11">
+        <v>31</v>
+      </c>
+      <c r="C9" s="11">
+        <v>30</v>
+      </c>
+      <c r="D9" s="11">
+        <v>27</v>
+      </c>
+      <c r="E9" s="11">
+        <v>1</v>
+      </c>
+      <c r="F9" s="11">
         <v>8</v>
       </c>
-      <c r="H7" s="12">
+      <c r="G9" s="11">
         <v>8</v>
       </c>
-      <c r="I7" s="12">
-        <v>6</v>
-      </c>
-      <c r="J7" s="12">
+      <c r="H9" s="11">
+        <v>8</v>
+      </c>
+      <c r="I9" s="11">
+        <v>8</v>
+      </c>
+      <c r="J9" s="11">
+        <v>2</v>
+      </c>
+      <c r="K9" s="11">
+        <v>2</v>
+      </c>
+      <c r="L9" s="11">
+        <v>12</v>
+      </c>
+      <c r="M9" s="11">
+        <v>12</v>
+      </c>
+      <c r="N9" s="11">
+        <v>12</v>
+      </c>
+      <c r="O9" s="11">
         <v>0</v>
       </c>
-      <c r="K7" s="12">
+      <c r="P9" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>15</v>
+      </c>
+      <c r="R9" s="11">
+        <v>15</v>
+      </c>
+      <c r="S9" s="11">
+        <v>15</v>
+      </c>
+      <c r="T9" s="11">
+        <v>1</v>
+      </c>
+      <c r="U9" s="11">
+        <v>1</v>
+      </c>
+      <c r="V9" s="11">
+        <v>15</v>
+      </c>
+      <c r="W9" s="11">
+        <v>15</v>
+      </c>
+      <c r="X9" s="11">
+        <v>15</v>
+      </c>
+      <c r="Y9" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="11">
+        <v>2</v>
+      </c>
+      <c r="AB9" s="11">
+        <v>2</v>
+      </c>
+      <c r="AC9" s="11">
+        <v>2</v>
+      </c>
+      <c r="AD9" s="11">
         <v>0</v>
       </c>
-      <c r="L7" s="12">
-        <v>9</v>
-      </c>
-      <c r="M7" s="12">
-        <v>9</v>
-      </c>
-      <c r="N7" s="12">
-        <v>9</v>
-      </c>
-      <c r="O7" s="12">
+      <c r="AE9" s="11">
         <v>1</v>
       </c>
-      <c r="P7" s="12">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="12">
-        <v>13</v>
-      </c>
-      <c r="R7" s="12">
-        <v>13</v>
-      </c>
-      <c r="S7" s="12">
-        <v>12</v>
-      </c>
-      <c r="T7" s="12">
-        <v>3</v>
-      </c>
-      <c r="U7" s="12">
-        <v>4</v>
-      </c>
-      <c r="V7" s="12">
-        <v>17</v>
-      </c>
-      <c r="W7" s="12">
-        <v>17</v>
-      </c>
-      <c r="X7" s="12">
-        <v>16</v>
-      </c>
-      <c r="Y7" s="12">
-        <v>2</v>
-      </c>
-      <c r="Z7" s="12">
-        <v>4</v>
-      </c>
-      <c r="AA7" s="12"/>
-      <c r="AB7" s="12"/>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="12"/>
-      <c r="AE7" s="12"/>
-      <c r="AF7" s="12"/>
-      <c r="AG7" s="12"/>
-      <c r="AH7" s="12"/>
-      <c r="AI7" s="12"/>
-      <c r="AJ7" s="12"/>
-      <c r="AK7" s="12"/>
-      <c r="AL7" s="12"/>
-      <c r="AM7" s="12"/>
-      <c r="AN7" s="12"/>
-      <c r="AO7" s="12"/>
-      <c r="AP7" s="12"/>
-      <c r="AQ7" s="12"/>
-      <c r="AR7" s="12"/>
-      <c r="AS7" s="12"/>
-      <c r="AT7" s="12"/>
-      <c r="AU7" s="12"/>
-      <c r="AV7" s="12"/>
-      <c r="AW7" s="12"/>
-      <c r="AX7" s="12"/>
-      <c r="AY7" s="12"/>
-      <c r="AZ7" s="12"/>
-      <c r="BA7" s="12"/>
-      <c r="BB7" s="12"/>
-      <c r="BC7" s="12"/>
-      <c r="BD7" s="12"/>
-      <c r="BE7" s="12"/>
-      <c r="BF7" s="12"/>
-      <c r="BG7" s="12"/>
-      <c r="BH7" s="12"/>
-      <c r="BI7" s="12"/>
-      <c r="BJ7" s="12"/>
-      <c r="BK7" s="12"/>
-      <c r="BL7" s="12"/>
-      <c r="BM7" s="12"/>
-      <c r="BN7" s="12"/>
-      <c r="BO7" s="12"/>
-      <c r="BP7" s="12"/>
-      <c r="BQ7" s="12"/>
-      <c r="BR7" s="12"/>
-      <c r="BS7" s="12"/>
-      <c r="BT7" s="12"/>
-      <c r="BU7" s="12"/>
-      <c r="BV7" s="12"/>
-      <c r="BW7" s="12"/>
-      <c r="BX7" s="12"/>
-      <c r="BY7" s="12"/>
-      <c r="BZ7" s="12"/>
-      <c r="CA7" s="12"/>
-      <c r="CB7" s="12"/>
-      <c r="CC7" s="12"/>
-      <c r="CD7" s="12"/>
-      <c r="CE7" s="12"/>
-      <c r="CF7" s="12"/>
-      <c r="CG7" s="12"/>
-      <c r="CH7" s="12"/>
-      <c r="CI7" s="12"/>
-      <c r="CJ7" s="12"/>
-      <c r="CK7" s="12"/>
-      <c r="CL7" s="12"/>
-      <c r="CM7" s="12"/>
-      <c r="CN7" s="12"/>
-      <c r="CO7" s="12"/>
-      <c r="CP7" s="12"/>
-      <c r="CQ7" s="12"/>
-      <c r="CR7" s="12"/>
-      <c r="CS7" s="12"/>
-      <c r="CT7" s="12"/>
-      <c r="CU7" s="12"/>
-      <c r="CV7" s="12"/>
-      <c r="CW7" s="12"/>
-      <c r="CX7" s="12"/>
-      <c r="CY7" s="12"/>
-      <c r="CZ7" s="12"/>
-      <c r="DA7" s="12"/>
-      <c r="DB7" s="12"/>
-    </row>
-    <row r="8" spans="1:106" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="12">
-        <v>27</v>
-      </c>
-      <c r="C8" s="12">
-        <v>26</v>
-      </c>
-      <c r="D8" s="12">
-        <v>22</v>
-      </c>
-      <c r="E8" s="12">
-        <v>2</v>
-      </c>
-      <c r="F8" s="12">
-        <v>10</v>
-      </c>
-      <c r="G8" s="12">
-        <v>6</v>
-      </c>
-      <c r="H8" s="12">
-        <v>6</v>
-      </c>
-      <c r="I8" s="12">
-        <v>6</v>
-      </c>
-      <c r="J8" s="12">
-        <v>0</v>
-      </c>
-      <c r="K8" s="12">
-        <v>2</v>
-      </c>
-      <c r="L8" s="12">
-        <v>10</v>
-      </c>
-      <c r="M8" s="12">
-        <v>10</v>
-      </c>
-      <c r="N8" s="12">
-        <v>9</v>
-      </c>
-      <c r="O8" s="12">
-        <v>1</v>
-      </c>
-      <c r="P8" s="12">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="12">
-        <v>12</v>
-      </c>
-      <c r="R8" s="12">
-        <v>11</v>
-      </c>
-      <c r="S8" s="12">
-        <v>11</v>
-      </c>
-      <c r="T8" s="12">
-        <v>2</v>
-      </c>
-      <c r="U8" s="12">
-        <v>2</v>
-      </c>
-      <c r="V8" s="12">
-        <v>12</v>
-      </c>
-      <c r="W8" s="12">
-        <v>11</v>
-      </c>
-      <c r="X8" s="12">
-        <v>11</v>
-      </c>
-      <c r="Y8" s="12">
-        <v>2</v>
-      </c>
-      <c r="Z8" s="12">
-        <v>2</v>
-      </c>
-      <c r="AA8" s="12"/>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
-      <c r="AE8" s="12"/>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="12"/>
-      <c r="AJ8" s="12"/>
-      <c r="AK8" s="12"/>
-      <c r="AL8" s="12"/>
-      <c r="AM8" s="12"/>
-      <c r="AN8" s="12"/>
-      <c r="AO8" s="12"/>
-      <c r="AP8" s="12"/>
-      <c r="AQ8" s="12"/>
-      <c r="AR8" s="12"/>
-      <c r="AS8" s="12"/>
-      <c r="AT8" s="12"/>
-      <c r="AU8" s="12"/>
-      <c r="AV8" s="12"/>
-      <c r="AW8" s="12"/>
-      <c r="AX8" s="12"/>
-      <c r="AY8" s="12"/>
-      <c r="AZ8" s="12"/>
-      <c r="BA8" s="12"/>
-      <c r="BB8" s="12"/>
-      <c r="BC8" s="12"/>
-      <c r="BD8" s="12"/>
-      <c r="BE8" s="12"/>
-      <c r="BF8" s="12"/>
-      <c r="BG8" s="12"/>
-      <c r="BH8" s="12"/>
-      <c r="BI8" s="12"/>
-      <c r="BJ8" s="12"/>
-      <c r="BK8" s="12"/>
-      <c r="BL8" s="12"/>
-      <c r="BM8" s="12"/>
-      <c r="BN8" s="12"/>
-      <c r="BO8" s="12"/>
-      <c r="BP8" s="12"/>
-      <c r="BQ8" s="12"/>
-      <c r="BR8" s="12"/>
-      <c r="BS8" s="12"/>
-      <c r="BT8" s="12"/>
-      <c r="BU8" s="12"/>
-      <c r="BV8" s="12"/>
-      <c r="BW8" s="12"/>
-      <c r="BX8" s="12"/>
-      <c r="BY8" s="12"/>
-      <c r="BZ8" s="12"/>
-      <c r="CA8" s="12"/>
-      <c r="CB8" s="12"/>
-      <c r="CC8" s="12"/>
-      <c r="CD8" s="12"/>
-      <c r="CE8" s="12"/>
-      <c r="CF8" s="12"/>
-      <c r="CG8" s="12"/>
-      <c r="CH8" s="12"/>
-      <c r="CI8" s="12"/>
-      <c r="CJ8" s="12"/>
-      <c r="CK8" s="12"/>
-      <c r="CL8" s="12"/>
-      <c r="CM8" s="12"/>
-      <c r="CN8" s="12"/>
-      <c r="CO8" s="12"/>
-      <c r="CP8" s="12"/>
-      <c r="CQ8" s="12"/>
-      <c r="CR8" s="12"/>
-      <c r="CS8" s="12"/>
-      <c r="CT8" s="12"/>
-      <c r="CU8" s="12"/>
-      <c r="CV8" s="12"/>
-      <c r="CW8" s="12"/>
-      <c r="CX8" s="12"/>
-      <c r="CY8" s="12"/>
-      <c r="CZ8" s="12"/>
-      <c r="DA8" s="12"/>
-      <c r="DB8" s="12"/>
-    </row>
-    <row r="9" spans="1:106" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="12">
-        <v>31</v>
-      </c>
-      <c r="C9" s="12">
-        <v>30</v>
-      </c>
-      <c r="D9" s="12">
-        <v>27</v>
-      </c>
-      <c r="E9" s="12">
-        <v>1</v>
-      </c>
-      <c r="F9" s="12">
-        <v>8</v>
-      </c>
-      <c r="G9" s="12">
-        <v>8</v>
-      </c>
-      <c r="H9" s="12">
-        <v>8</v>
-      </c>
-      <c r="I9" s="12">
-        <v>8</v>
-      </c>
-      <c r="J9" s="12">
-        <v>2</v>
-      </c>
-      <c r="K9" s="12">
-        <v>2</v>
-      </c>
-      <c r="L9" s="12">
-        <v>12</v>
-      </c>
-      <c r="M9" s="12">
-        <v>12</v>
-      </c>
-      <c r="N9" s="12">
-        <v>12</v>
-      </c>
-      <c r="O9" s="12">
-        <v>0</v>
-      </c>
-      <c r="P9" s="12">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="12">
-        <v>15</v>
-      </c>
-      <c r="R9" s="12">
-        <v>15</v>
-      </c>
-      <c r="S9" s="12">
-        <v>15</v>
-      </c>
-      <c r="T9" s="12">
-        <v>1</v>
-      </c>
-      <c r="U9" s="12">
-        <v>1</v>
-      </c>
-      <c r="V9" s="12">
-        <v>15</v>
-      </c>
-      <c r="W9" s="12">
-        <v>15</v>
-      </c>
-      <c r="X9" s="12">
-        <v>15</v>
-      </c>
-      <c r="Y9" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="12"/>
-      <c r="AB9" s="12"/>
-      <c r="AC9" s="12"/>
-      <c r="AD9" s="12"/>
-      <c r="AE9" s="12"/>
-      <c r="AF9" s="12"/>
-      <c r="AG9" s="12"/>
-      <c r="AH9" s="12"/>
-      <c r="AI9" s="12"/>
-      <c r="AJ9" s="12"/>
-      <c r="AK9" s="12"/>
-      <c r="AL9" s="12"/>
-      <c r="AM9" s="12"/>
-      <c r="AN9" s="12"/>
-      <c r="AO9" s="12"/>
-      <c r="AP9" s="12"/>
-      <c r="AQ9" s="12"/>
-      <c r="AR9" s="12"/>
-      <c r="AS9" s="12"/>
-      <c r="AT9" s="12"/>
-      <c r="AU9" s="12"/>
-      <c r="AV9" s="12"/>
-      <c r="AW9" s="12"/>
-      <c r="AX9" s="12"/>
-      <c r="AY9" s="12"/>
-      <c r="AZ9" s="12"/>
-      <c r="BA9" s="12"/>
-      <c r="BB9" s="12"/>
-      <c r="BC9" s="12"/>
-      <c r="BD9" s="12"/>
-      <c r="BE9" s="12"/>
-      <c r="BF9" s="12"/>
-      <c r="BG9" s="12"/>
-      <c r="BH9" s="12"/>
-      <c r="BI9" s="12"/>
-      <c r="BJ9" s="12"/>
-      <c r="BK9" s="12"/>
-      <c r="BL9" s="12"/>
-      <c r="BM9" s="12"/>
-      <c r="BN9" s="12"/>
-      <c r="BO9" s="12"/>
-      <c r="BP9" s="12"/>
-      <c r="BQ9" s="12"/>
-      <c r="BR9" s="12"/>
-      <c r="BS9" s="12"/>
-      <c r="BT9" s="12"/>
-      <c r="BU9" s="12"/>
-      <c r="BV9" s="12"/>
-      <c r="BW9" s="12"/>
-      <c r="BX9" s="12"/>
-      <c r="BY9" s="12"/>
-      <c r="BZ9" s="12"/>
-      <c r="CA9" s="12"/>
-      <c r="CB9" s="12"/>
-      <c r="CC9" s="12"/>
-      <c r="CD9" s="12"/>
-      <c r="CE9" s="12"/>
-      <c r="CF9" s="12"/>
-      <c r="CG9" s="12"/>
-      <c r="CH9" s="12"/>
-      <c r="CI9" s="12"/>
-      <c r="CJ9" s="12"/>
-      <c r="CK9" s="12"/>
-      <c r="CL9" s="12"/>
-      <c r="CM9" s="12"/>
-      <c r="CN9" s="12"/>
-      <c r="CO9" s="12"/>
-      <c r="CP9" s="12"/>
-      <c r="CQ9" s="12"/>
-      <c r="CR9" s="12"/>
-      <c r="CS9" s="12"/>
-      <c r="CT9" s="12"/>
-      <c r="CU9" s="12"/>
-      <c r="CV9" s="12"/>
-      <c r="CW9" s="12"/>
-      <c r="CX9" s="12"/>
-      <c r="CY9" s="12"/>
-      <c r="CZ9" s="12"/>
-      <c r="DA9" s="12"/>
-      <c r="DB9" s="12"/>
+      <c r="AF9" s="11"/>
+      <c r="AG9" s="11"/>
+      <c r="AH9" s="11"/>
+      <c r="AI9" s="11"/>
+      <c r="AJ9" s="11"/>
+      <c r="AK9" s="11"/>
+      <c r="AL9" s="11"/>
+      <c r="AM9" s="11"/>
+      <c r="AN9" s="11"/>
+      <c r="AO9" s="11"/>
+      <c r="AP9" s="11"/>
+      <c r="AQ9" s="11"/>
+      <c r="AR9" s="11"/>
+      <c r="AS9" s="11"/>
+      <c r="AT9" s="11"/>
+      <c r="AU9" s="11"/>
+      <c r="AV9" s="11"/>
+      <c r="AW9" s="11"/>
+      <c r="AX9" s="11"/>
+      <c r="AY9" s="11"/>
+      <c r="AZ9" s="11"/>
+      <c r="BA9" s="11"/>
+      <c r="BB9" s="11"/>
+      <c r="BC9" s="11"/>
+      <c r="BD9" s="11"/>
+      <c r="BE9" s="11"/>
+      <c r="BF9" s="11"/>
+      <c r="BG9" s="11"/>
+      <c r="BH9" s="11"/>
+      <c r="BI9" s="11"/>
+      <c r="BJ9" s="11"/>
+      <c r="BK9" s="11"/>
+      <c r="BL9" s="11"/>
+      <c r="BM9" s="11"/>
+      <c r="BN9" s="11"/>
+      <c r="BO9" s="11"/>
+      <c r="BP9" s="11"/>
+      <c r="BQ9" s="11"/>
+      <c r="BR9" s="11"/>
+      <c r="BS9" s="11"/>
+      <c r="BT9" s="11"/>
+      <c r="BU9" s="11"/>
+      <c r="BV9" s="11"/>
+      <c r="BW9" s="11"/>
+      <c r="BX9" s="11"/>
+      <c r="BY9" s="11"/>
+      <c r="BZ9" s="11"/>
+      <c r="CA9" s="11"/>
+      <c r="CB9" s="11"/>
+      <c r="CC9" s="11"/>
+      <c r="CD9" s="11"/>
+      <c r="CE9" s="11"/>
+      <c r="CF9" s="11"/>
+      <c r="CG9" s="11"/>
+      <c r="CH9" s="11"/>
+      <c r="CI9" s="11"/>
+      <c r="CJ9" s="11"/>
+      <c r="CK9" s="11"/>
+      <c r="CL9" s="11"/>
+      <c r="CM9" s="11"/>
+      <c r="CN9" s="11"/>
+      <c r="CO9" s="11"/>
+      <c r="CP9" s="11"/>
+      <c r="CQ9" s="11"/>
+      <c r="CR9" s="11"/>
+      <c r="CS9" s="11"/>
+      <c r="CT9" s="11"/>
+      <c r="CU9" s="11"/>
+      <c r="CV9" s="11"/>
+      <c r="CW9" s="11"/>
+      <c r="CX9" s="11"/>
+      <c r="CY9" s="11"/>
+      <c r="CZ9" s="11"/>
+      <c r="DA9" s="11"/>
+      <c r="DB9" s="11"/>
     </row>
     <row r="10" spans="1:106" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B10" s="6">
         <f>SUM(B3:B9)</f>
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C10" s="6">
         <f t="shared" ref="C10:Q10" si="0">SUM(C3:C9)</f>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="0"/>
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E10" s="6">
         <f t="shared" si="0"/>
@@ -11557,15 +14940,15 @@
       </c>
       <c r="F10" s="6">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" s="6">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H10" s="6">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="0"/>
@@ -11577,15 +14960,15 @@
       </c>
       <c r="K10" s="6">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L10" s="6">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M10" s="6">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
@@ -11593,71 +14976,71 @@
       </c>
       <c r="O10" s="6">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P10" s="6">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="R10" s="6">
         <f t="shared" ref="R10" si="1">SUM(R3:R9)</f>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S10" s="6">
         <f t="shared" ref="S10" si="2">SUM(S3:S9)</f>
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="T10" s="6">
         <f t="shared" ref="T10" si="3">SUM(T3:T9)</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U10" s="6">
         <f t="shared" ref="U10" si="4">SUM(U3:U9)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V10" s="6">
         <f t="shared" ref="V10" si="5">SUM(V3:V9)</f>
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="W10" s="6">
         <f t="shared" ref="W10" si="6">SUM(W3:W9)</f>
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="X10" s="6">
         <f t="shared" ref="X10" si="7">SUM(X3:X9)</f>
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="Y10" s="6">
         <f t="shared" ref="Y10" si="8">SUM(Y3:Y9)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z10" s="6">
         <f t="shared" ref="Z10" si="9">SUM(Z3:Z9)</f>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA10" s="6">
         <f t="shared" ref="AA10" si="10">SUM(AA3:AA9)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB10" s="6">
         <f t="shared" ref="AB10" si="11">SUM(AB3:AB9)</f>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AC10" s="6">
         <f t="shared" ref="AC10" si="12">SUM(AC3:AC9)</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AD10" s="6">
         <f t="shared" ref="AD10" si="13">SUM(AD3:AD9)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AE10" s="6">
         <f t="shared" ref="AE10:AF10" si="14">SUM(AE3:AE9)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AF10" s="6">
         <f t="shared" si="14"/>
@@ -12003,72 +15386,72 @@
   <sheetData>
     <row r="3" spans="2:23" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="L3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="M3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="N3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" t="s">
+      <c r="O3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
+      <c r="P3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" t="s">
+      <c r="Q3" t="s">
         <v>20</v>
       </c>
-      <c r="K3" t="s">
+      <c r="R3" t="s">
         <v>21</v>
       </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="S3" t="s">
         <v>23</v>
       </c>
-      <c r="N3" t="s">
+      <c r="T3" t="s">
         <v>24</v>
       </c>
-      <c r="O3" t="s">
+      <c r="U3" t="s">
         <v>25</v>
       </c>
-      <c r="P3" t="s">
+      <c r="V3" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="W3" t="s">
         <v>27</v>
-      </c>
-      <c r="R3" t="s">
-        <v>28</v>
-      </c>
-      <c r="S3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T3" t="s">
-        <v>31</v>
-      </c>
-      <c r="U3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V3" t="s">
-        <v>33</v>
-      </c>
-      <c r="W3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>125</v>
@@ -12076,7 +15459,7 @@
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>111</v>
@@ -12084,7 +15467,7 @@
     </row>
     <row r="6" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>101</v>
@@ -12092,7 +15475,7 @@
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -12100,7 +15483,7 @@
     </row>
     <row r="8" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>21</v>
@@ -12115,159 +15498,243 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88AF971A-0C51-450E-BC56-9CBEC167DAAD}">
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AP12"/>
   <sheetFormatPr defaultColWidth="6" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="8.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="17.125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.75" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="8.875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.75" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="8.875" style="4" customWidth="1"/>
+    <col min="14" max="14" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.75" style="4" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="8.875" style="4" customWidth="1"/>
+    <col min="20" max="20" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8" style="4" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.75" style="4" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="26" max="30" width="8.875" style="4" customWidth="1"/>
-    <col min="31" max="16384" width="6" style="4"/>
+    <col min="26" max="26" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8" style="4" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8" style="4" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="17.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="8" style="4" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="6" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A1" s="15"/>
-      <c r="B1" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA1" s="19"/>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
+    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A1" s="14"/>
+      <c r="B1" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" s="21"/>
+      <c r="V1" s="21"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="21"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG1" s="21"/>
+      <c r="AH1" s="21"/>
+      <c r="AI1" s="21"/>
+      <c r="AJ1" s="21"/>
+      <c r="AK1" s="14"/>
+      <c r="AL1" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM1" s="21"/>
+      <c r="AN1" s="21"/>
+      <c r="AO1" s="21"/>
+      <c r="AP1" s="21"/>
     </row>
-    <row r="2" spans="1:30" s="5" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="P2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q2" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="R2" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="U2" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="V2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="W2" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="X2" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y2" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z2" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA2" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB2" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC2" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD2" s="20" t="s">
-        <v>9</v>
+    <row r="2" spans="1:42" s="5" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="T2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="U2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="W2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="X2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP2" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
-        <v>35</v>
+    <row r="3" spans="1:42" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="B3" s="3">
         <v>10</v>
@@ -12284,17 +15751,17 @@
       <c r="F3" s="3">
         <v>0</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>35</v>
+      <c r="G3" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="H3" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I3" s="3">
         <v>5</v>
       </c>
       <c r="J3" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K3" s="3">
         <v>1</v>
@@ -12302,64 +15769,100 @@
       <c r="L3" s="3">
         <v>1</v>
       </c>
-      <c r="M3" s="14" t="s">
-        <v>35</v>
+      <c r="M3" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="N3" s="3">
+        <v>6</v>
+      </c>
+      <c r="O3" s="3">
+        <v>5</v>
+      </c>
+      <c r="P3" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1</v>
+      </c>
+      <c r="R3" s="3">
+        <v>1</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="T3" s="3">
+        <v>0</v>
+      </c>
+      <c r="U3" s="3">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3">
+        <v>0</v>
+      </c>
+      <c r="W3" s="3">
+        <v>0</v>
+      </c>
+      <c r="X3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z3" s="3">
         <v>47</v>
       </c>
-      <c r="O3" s="3">
+      <c r="AA3" s="3">
         <v>43</v>
       </c>
-      <c r="P3" s="3">
+      <c r="AB3" s="3">
         <v>39</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="AC3" s="3">
         <v>3</v>
       </c>
-      <c r="R3" s="3">
+      <c r="AD3" s="3">
         <v>2</v>
       </c>
-      <c r="S3" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="T3" s="3">
+      <c r="AE3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF3" s="3">
         <v>27</v>
       </c>
-      <c r="U3" s="3">
+      <c r="AG3" s="3">
         <v>26</v>
       </c>
-      <c r="V3" s="3">
+      <c r="AH3" s="3">
         <v>22</v>
       </c>
-      <c r="W3" s="3">
+      <c r="AI3" s="3">
         <v>2</v>
       </c>
-      <c r="X3" s="3">
+      <c r="AJ3" s="3">
         <v>10</v>
       </c>
-      <c r="Y3" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="3">
+      <c r="AK3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL3" s="3">
         <v>31</v>
       </c>
-      <c r="AA3" s="3">
+      <c r="AM3" s="3">
         <v>30</v>
       </c>
-      <c r="AB3" s="3">
+      <c r="AN3" s="3">
         <v>27</v>
       </c>
-      <c r="AC3" s="3">
+      <c r="AO3" s="3">
         <v>1</v>
       </c>
-      <c r="AD3" s="3">
+      <c r="AP3" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -12377,34 +15880,34 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H4" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I4" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="N4" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O4" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P4" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="3">
         <v>0</v>
@@ -12413,25 +15916,25 @@
         <v>0</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="T4" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U4" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V4" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W4" s="3">
         <v>0</v>
       </c>
       <c r="X4" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Z4" s="3">
         <v>8</v>
@@ -12440,18 +15943,54 @@
         <v>8</v>
       </c>
       <c r="AB4" s="3">
+        <v>6</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>6</v>
+      </c>
+      <c r="AG4" s="3">
+        <v>6</v>
+      </c>
+      <c r="AH4" s="3">
+        <v>6</v>
+      </c>
+      <c r="AI4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3">
+        <v>2</v>
+      </c>
+      <c r="AK4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL4" s="3">
         <v>8</v>
       </c>
-      <c r="AC4" s="3">
+      <c r="AM4" s="3">
+        <v>8</v>
+      </c>
+      <c r="AN4" s="3">
+        <v>8</v>
+      </c>
+      <c r="AO4" s="3">
         <v>2</v>
       </c>
-      <c r="AD4" s="3">
+      <c r="AP4" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -12469,81 +16008,117 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H5" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I5" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J5" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K5" s="3">
         <v>2</v>
       </c>
       <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5" s="3">
+        <v>20</v>
+      </c>
+      <c r="O5" s="3">
+        <v>20</v>
+      </c>
+      <c r="P5" s="3">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>2</v>
+      </c>
+      <c r="R5" s="3">
         <v>10</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N5" s="3">
+      <c r="S5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="T5" s="3">
+        <v>0</v>
+      </c>
+      <c r="U5" s="3">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3">
+        <v>0</v>
+      </c>
+      <c r="W5" s="3">
+        <v>0</v>
+      </c>
+      <c r="X5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z5" s="3">
         <v>9</v>
       </c>
-      <c r="O5" s="3">
+      <c r="AA5" s="3">
         <v>9</v>
       </c>
-      <c r="P5" s="3">
+      <c r="AB5" s="3">
         <v>9</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="AC5" s="3">
         <v>1</v>
       </c>
-      <c r="R5" s="3">
+      <c r="AD5" s="3">
         <v>2</v>
       </c>
-      <c r="S5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="T5" s="3">
+      <c r="AE5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF5" s="3">
         <v>10</v>
       </c>
-      <c r="U5" s="3">
+      <c r="AG5" s="3">
         <v>10</v>
       </c>
-      <c r="V5" s="3">
+      <c r="AH5" s="3">
         <v>9</v>
       </c>
-      <c r="W5" s="3">
+      <c r="AI5" s="3">
         <v>1</v>
       </c>
-      <c r="X5" s="3">
+      <c r="AJ5" s="3">
         <v>1</v>
       </c>
-      <c r="Y5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z5" s="3">
+      <c r="AK5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL5" s="3">
         <v>12</v>
       </c>
-      <c r="AA5" s="3">
+      <c r="AM5" s="3">
         <v>12</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AN5" s="3">
         <v>12</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AO5" s="3">
         <v>0</v>
       </c>
-      <c r="AD5" s="3">
+      <c r="AP5" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
@@ -12561,81 +16136,117 @@
         <v>3</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H6" s="3">
+        <v>15</v>
+      </c>
+      <c r="I6" s="3">
+        <v>14</v>
+      </c>
+      <c r="J6" s="3">
+        <v>10</v>
+      </c>
+      <c r="K6" s="3">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3">
+        <v>2</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="3">
         <v>34</v>
       </c>
-      <c r="I6" s="3">
+      <c r="O6" s="3">
         <v>32</v>
       </c>
-      <c r="J6" s="3">
+      <c r="P6" s="3">
         <v>31</v>
       </c>
-      <c r="K6" s="3">
+      <c r="Q6" s="3">
         <v>6</v>
       </c>
-      <c r="L6" s="3">
+      <c r="R6" s="3">
         <v>11</v>
       </c>
-      <c r="M6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N6" s="3">
+      <c r="S6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T6" s="3">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z6" s="3">
         <v>13</v>
       </c>
-      <c r="O6" s="3">
+      <c r="AA6" s="3">
         <v>13</v>
       </c>
-      <c r="P6" s="3">
+      <c r="AB6" s="3">
         <v>12</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="AC6" s="3">
         <v>3</v>
       </c>
-      <c r="R6" s="3">
+      <c r="AD6" s="3">
         <v>4</v>
       </c>
-      <c r="S6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="T6" s="3">
+      <c r="AE6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF6" s="3">
         <v>12</v>
       </c>
-      <c r="U6" s="3">
+      <c r="AG6" s="3">
         <v>11</v>
       </c>
-      <c r="V6" s="3">
+      <c r="AH6" s="3">
         <v>11</v>
       </c>
-      <c r="W6" s="3">
+      <c r="AI6" s="3">
         <v>2</v>
       </c>
-      <c r="X6" s="3">
+      <c r="AJ6" s="3">
         <v>2</v>
       </c>
-      <c r="Y6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z6" s="3">
+      <c r="AK6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AL6" s="3">
         <v>15</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AM6" s="3">
         <v>15</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AN6" s="3">
         <v>15</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AO6" s="3">
         <v>1</v>
       </c>
-      <c r="AD6" s="3">
+      <c r="AP6" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -12653,111 +16264,243 @@
         <v>3</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H7" s="3">
+        <v>10</v>
+      </c>
+      <c r="I7" s="3">
+        <v>9</v>
+      </c>
+      <c r="J7" s="3">
+        <v>8</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N7" s="3">
         <v>55</v>
       </c>
-      <c r="I7" s="3">
+      <c r="O7" s="3">
         <v>52</v>
       </c>
-      <c r="J7" s="3">
+      <c r="P7" s="3">
         <v>51</v>
       </c>
-      <c r="K7" s="3">
+      <c r="Q7" s="3">
         <v>7</v>
       </c>
-      <c r="L7" s="3">
+      <c r="R7" s="3">
         <v>16</v>
       </c>
-      <c r="M7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" s="3">
+      <c r="S7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T7" s="3">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z7" s="3">
         <v>17</v>
       </c>
-      <c r="O7" s="3">
+      <c r="AA7" s="3">
         <v>17</v>
       </c>
-      <c r="P7" s="3">
+      <c r="AB7" s="3">
         <v>16</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="AC7" s="3">
         <v>2</v>
       </c>
-      <c r="R7" s="3">
+      <c r="AD7" s="3">
         <v>4</v>
       </c>
-      <c r="S7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="T7" s="3">
+      <c r="AE7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF7" s="3">
         <v>12</v>
       </c>
-      <c r="U7" s="3">
+      <c r="AG7" s="3">
         <v>11</v>
       </c>
-      <c r="V7" s="3">
+      <c r="AH7" s="3">
         <v>11</v>
       </c>
-      <c r="W7" s="3">
+      <c r="AI7" s="3">
         <v>2</v>
       </c>
-      <c r="X7" s="3">
+      <c r="AJ7" s="3">
         <v>2</v>
       </c>
-      <c r="Y7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z7" s="3">
+      <c r="AK7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL7" s="3">
         <v>15</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AM7" s="3">
         <v>15</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AN7" s="3">
         <v>15</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AO7" s="3">
         <v>1</v>
       </c>
-      <c r="AD7" s="3">
+      <c r="AP7" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
+    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="3">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3">
+        <v>5</v>
+      </c>
+      <c r="D8" s="3">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="3">
+        <v>11</v>
+      </c>
+      <c r="I8" s="3">
+        <v>10</v>
+      </c>
+      <c r="J8" s="3">
+        <v>11</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8" s="3">
+        <v>28</v>
+      </c>
+      <c r="O8" s="3">
+        <v>26</v>
+      </c>
+      <c r="P8" s="3">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3">
+        <v>9</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>9</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>8</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>4</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AL8" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM8" s="3">
+        <v>2</v>
+      </c>
+      <c r="AN8" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -12788,8 +16531,20 @@
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
+      <c r="AH9" s="3"/>
+      <c r="AI9" s="3"/>
+      <c r="AJ9" s="3"/>
+      <c r="AK9" s="3"/>
+      <c r="AL9" s="3"/>
+      <c r="AM9" s="3"/>
+      <c r="AN9" s="3"/>
+      <c r="AO9" s="3"/>
+      <c r="AP9" s="3"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -12820,8 +16575,20 @@
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
+      <c r="AH10" s="3"/>
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="3"/>
+      <c r="AK10" s="3"/>
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="3"/>
+      <c r="AN10" s="3"/>
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="3"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -12852,8 +16619,20 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -12884,9 +16663,23 @@
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+      <c r="AH12" s="3"/>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="3"/>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="3"/>
+      <c r="AM12" s="3"/>
+      <c r="AN12" s="3"/>
+      <c r="AO12" s="3"/>
+      <c r="AP12" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="AF1:AJ1"/>
+    <mergeCell ref="AL1:AP1"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="N1:R1"/>

--- a/documents/지표/주별활동지수.xlsx
+++ b/documents/지표/주별활동지수.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf1f1df607fbac1a/Desktop/Github/2026-QI/documents/지표/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf1f1df607fbac1a/Desktop/Github/2026-QI/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{1F49EEAB-D64F-4024-878C-E43B7327B9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4BAC590-02B2-4D8E-BFFD-AECB49CEE05D}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{C34A7588-1100-49C1-938C-BE10454C6A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{075B84F0-8A35-4724-B426-0BFA5FD7299E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{0FC1208A-2CB8-4E1E-B9D0-F7D163D68827}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="49">
   <si>
     <t>1주차</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -208,6 +208,10 @@
   <si>
     <t>5주차(6/18~6/25)</t>
   </si>
+  <si>
+    <t>7주차(7/2~7/8)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -336,7 +340,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -346,28 +350,19 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -376,7 +371,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -391,6 +386,9 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -398,9 +396,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1473,9 +1468,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$8</c:f>
+              <c:f>Sheet1!$A$3:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1493,16 +1488,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$B$8</c:f>
+              <c:f>Sheet1!$B$3:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -1520,6 +1518,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1613,9 +1614,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$8</c:f>
+              <c:f>Sheet1!$A$3:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1633,16 +1634,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$3:$C$8</c:f>
+              <c:f>Sheet1!$C$3:$C$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -1659,6 +1663,9 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1753,9 +1760,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$8</c:f>
+              <c:f>Sheet1!$A$3:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1773,16 +1780,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$3:$D$8</c:f>
+              <c:f>Sheet1!$D$3:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1799,6 +1809,9 @@
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1893,9 +1906,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$8</c:f>
+              <c:f>Sheet1!$A$3:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1913,16 +1926,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$3:$E$8</c:f>
+              <c:f>Sheet1!$E$3:$E$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1939,6 +1955,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2033,9 +2052,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$8</c:f>
+              <c:f>Sheet1!$A$3:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2053,16 +2072,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$3:$F$8</c:f>
+              <c:f>Sheet1!$F$3:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2079,6 +2101,9 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2452,9 +2477,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$8</c:f>
+              <c:f>Sheet1!$G$3:$G$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2472,16 +2497,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$3:$H$8</c:f>
+              <c:f>Sheet1!$H$3:$H$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
@@ -2499,6 +2527,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2592,9 +2623,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$8</c:f>
+              <c:f>Sheet1!$G$3:$G$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2612,16 +2643,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$I$3:$I$8</c:f>
+              <c:f>Sheet1!$I$3:$I$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -2639,6 +2673,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2732,9 +2769,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$8</c:f>
+              <c:f>Sheet1!$G$3:$G$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2752,16 +2789,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$3:$J$8</c:f>
+              <c:f>Sheet1!$J$3:$J$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -2779,6 +2819,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2872,9 +2915,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$8</c:f>
+              <c:f>Sheet1!$G$3:$G$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2892,16 +2935,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$K$3:$K$8</c:f>
+              <c:f>Sheet1!$K$3:$K$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -2918,6 +2964,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3012,9 +3061,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$8</c:f>
+              <c:f>Sheet1!$G$3:$G$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3032,16 +3081,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$3:$L$8</c:f>
+              <c:f>Sheet1!$L$3:$L$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3059,6 +3111,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3432,9 +3487,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$8</c:f>
+              <c:f>Sheet1!$M$3:$M$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3452,16 +3507,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$N$3:$N$8</c:f>
+              <c:f>Sheet1!$N$3:$N$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>6</c:v>
                 </c:pt>
@@ -3478,6 +3536,9 @@
                   <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>28</c:v>
                 </c:pt>
               </c:numCache>
@@ -3573,9 +3634,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$8</c:f>
+              <c:f>Sheet1!$M$3:$M$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3593,16 +3654,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$O$3:$O$8</c:f>
+              <c:f>Sheet1!$O$3:$O$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -3619,6 +3683,9 @@
                   <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
@@ -3714,9 +3781,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$8</c:f>
+              <c:f>Sheet1!$M$3:$M$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3734,16 +3801,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$P$3:$P$8</c:f>
+              <c:f>Sheet1!$P$3:$P$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -3760,6 +3830,9 @@
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
@@ -3855,9 +3928,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$8</c:f>
+              <c:f>Sheet1!$M$3:$M$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3875,16 +3948,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Q$3:$Q$8</c:f>
+              <c:f>Sheet1!$Q$3:$Q$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3902,6 +3978,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3996,9 +4075,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$8</c:f>
+              <c:f>Sheet1!$M$3:$M$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4016,16 +4095,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$R$3:$R$8</c:f>
+              <c:f>Sheet1!$R$3:$R$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4043,6 +4125,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4417,9 +4502,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$8</c:f>
+              <c:f>Sheet1!$S$3:$S$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4437,16 +4522,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$T$3:$T$8</c:f>
+              <c:f>Sheet1!$T$3:$T$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4463,6 +4551,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4558,9 +4649,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$8</c:f>
+              <c:f>Sheet1!$S$3:$S$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4578,16 +4669,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$U$3:$U$8</c:f>
+              <c:f>Sheet1!$U$3:$U$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4604,6 +4698,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4699,9 +4796,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$8</c:f>
+              <c:f>Sheet1!$S$3:$S$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4719,16 +4816,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$V$3:$V$8</c:f>
+              <c:f>Sheet1!$V$3:$V$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4745,6 +4845,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4840,9 +4943,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$8</c:f>
+              <c:f>Sheet1!$S$3:$S$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4860,16 +4963,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$W$3:$W$8</c:f>
+              <c:f>Sheet1!$W$3:$W$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4886,6 +4992,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4981,9 +5090,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$8</c:f>
+              <c:f>Sheet1!$S$3:$S$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5001,16 +5110,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$X$3:$X$8</c:f>
+              <c:f>Sheet1!$X$3:$X$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5027,6 +5139,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5405,9 +5520,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$8</c:f>
+              <c:f>Sheet1!$Y$3:$Y$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5425,16 +5540,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Z$3:$Z$8</c:f>
+              <c:f>Sheet1!$Z$3:$Z$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>47</c:v>
                 </c:pt>
@@ -5452,6 +5570,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5546,9 +5667,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$8</c:f>
+              <c:f>Sheet1!$Y$3:$Y$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5566,16 +5687,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AA$3:$AA$8</c:f>
+              <c:f>Sheet1!$AA$3:$AA$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>43</c:v>
                 </c:pt>
@@ -5593,6 +5717,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5687,9 +5814,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$8</c:f>
+              <c:f>Sheet1!$Y$3:$Y$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5707,16 +5834,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AB$3:$AB$8</c:f>
+              <c:f>Sheet1!$AB$3:$AB$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>39</c:v>
                 </c:pt>
@@ -5734,6 +5864,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5828,9 +5961,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$8</c:f>
+              <c:f>Sheet1!$Y$3:$Y$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5848,16 +5981,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AC$3:$AC$8</c:f>
+              <c:f>Sheet1!$AC$3:$AC$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -5875,6 +6011,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5969,9 +6108,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$8</c:f>
+              <c:f>Sheet1!$Y$3:$Y$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5989,16 +6128,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AD$3:$AD$8</c:f>
+              <c:f>Sheet1!$AD$3:$AD$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -6016,6 +6158,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6393,9 +6538,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$8</c:f>
+              <c:f>Sheet1!$AE$3:$AE$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6413,16 +6558,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AF$3:$AF$8</c:f>
+              <c:f>Sheet1!$AF$3:$AF$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>27</c:v>
                 </c:pt>
@@ -6439,6 +6587,9 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -6534,9 +6685,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$8</c:f>
+              <c:f>Sheet1!$AE$3:$AE$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6554,16 +6705,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AG$3:$AG$8</c:f>
+              <c:f>Sheet1!$AG$3:$AG$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>26</c:v>
                 </c:pt>
@@ -6580,6 +6734,9 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -6675,9 +6832,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$8</c:f>
+              <c:f>Sheet1!$AE$3:$AE$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6695,16 +6852,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AH$3:$AH$8</c:f>
+              <c:f>Sheet1!$AH$3:$AH$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>22</c:v>
                 </c:pt>
@@ -6721,6 +6881,9 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -6816,9 +6979,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$8</c:f>
+              <c:f>Sheet1!$AE$3:$AE$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6836,16 +6999,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AI$3:$AI$8</c:f>
+              <c:f>Sheet1!$AI$3:$AI$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -6862,6 +7028,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -6957,9 +7126,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$8</c:f>
+              <c:f>Sheet1!$AE$3:$AE$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6977,16 +7146,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AJ$3:$AJ$8</c:f>
+              <c:f>Sheet1!$AJ$3:$AJ$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -7003,6 +7175,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -7382,9 +7557,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$8</c:f>
+              <c:f>Sheet1!$AK$3:$AK$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7402,16 +7577,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AL$3:$AL$8</c:f>
+              <c:f>Sheet1!$AL$3:$AL$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>31</c:v>
                 </c:pt>
@@ -7429,6 +7607,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7523,9 +7704,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$8</c:f>
+              <c:f>Sheet1!$AK$3:$AK$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7543,16 +7724,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AM$3:$AM$8</c:f>
+              <c:f>Sheet1!$AM$3:$AM$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>30</c:v>
                 </c:pt>
@@ -7570,6 +7754,9 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7664,9 +7851,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$8</c:f>
+              <c:f>Sheet1!$AK$3:$AK$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7684,16 +7871,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AN$3:$AN$8</c:f>
+              <c:f>Sheet1!$AN$3:$AN$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>27</c:v>
                 </c:pt>
@@ -7710,6 +7900,9 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -7805,9 +7998,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$8</c:f>
+              <c:f>Sheet1!$AK$3:$AK$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7825,16 +8018,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AO$3:$AO$8</c:f>
+              <c:f>Sheet1!$AO$3:$AO$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -7851,6 +8047,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -7946,9 +8145,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$8</c:f>
+              <c:f>Sheet1!$AK$3:$AK$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7966,16 +8165,19 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6주차(6/25~7/1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7주차(7/2~7/8)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AP$3:$AP$8</c:f>
+              <c:f>Sheet1!$AP$3:$AP$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -7992,6 +8194,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -13149,2211 +13354,2202 @@
   <dimension ref="A1:DB10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="107" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="107" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:106" x14ac:dyDescent="0.3">
-      <c r="A1" s="6"/>
-      <c r="B1" s="17" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17" t="s">
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17" t="s">
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17" t="s">
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17" t="s">
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17" t="s">
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="17" t="s">
+      <c r="AG1" s="14"/>
+      <c r="AH1" s="14"/>
+      <c r="AI1" s="14"/>
+      <c r="AJ1" s="14"/>
+      <c r="AK1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17" t="s">
+      <c r="AL1" s="14"/>
+      <c r="AM1" s="14"/>
+      <c r="AN1" s="14"/>
+      <c r="AO1" s="14"/>
+      <c r="AP1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="17"/>
-      <c r="AU1" s="17" t="s">
+      <c r="AQ1" s="14"/>
+      <c r="AR1" s="14"/>
+      <c r="AS1" s="14"/>
+      <c r="AT1" s="14"/>
+      <c r="AU1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="AV1" s="17"/>
-      <c r="AW1" s="17"/>
-      <c r="AX1" s="17"/>
-      <c r="AY1" s="17"/>
-      <c r="AZ1" s="17" t="s">
+      <c r="AV1" s="14"/>
+      <c r="AW1" s="14"/>
+      <c r="AX1" s="14"/>
+      <c r="AY1" s="14"/>
+      <c r="AZ1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="BA1" s="17"/>
-      <c r="BB1" s="17"/>
-      <c r="BC1" s="17"/>
-      <c r="BD1" s="17"/>
-      <c r="BE1" s="17" t="s">
+      <c r="BA1" s="14"/>
+      <c r="BB1" s="14"/>
+      <c r="BC1" s="14"/>
+      <c r="BD1" s="14"/>
+      <c r="BE1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="BF1" s="17"/>
-      <c r="BG1" s="17"/>
-      <c r="BH1" s="17"/>
-      <c r="BI1" s="17"/>
-      <c r="BJ1" s="17" t="s">
+      <c r="BF1" s="14"/>
+      <c r="BG1" s="14"/>
+      <c r="BH1" s="14"/>
+      <c r="BI1" s="14"/>
+      <c r="BJ1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="BK1" s="17"/>
-      <c r="BL1" s="17"/>
-      <c r="BM1" s="17"/>
-      <c r="BN1" s="17"/>
-      <c r="BO1" s="17" t="s">
+      <c r="BK1" s="14"/>
+      <c r="BL1" s="14"/>
+      <c r="BM1" s="14"/>
+      <c r="BN1" s="14"/>
+      <c r="BO1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="BP1" s="17"/>
-      <c r="BQ1" s="17"/>
-      <c r="BR1" s="17"/>
-      <c r="BS1" s="17"/>
-      <c r="BT1" s="17" t="s">
+      <c r="BP1" s="14"/>
+      <c r="BQ1" s="14"/>
+      <c r="BR1" s="14"/>
+      <c r="BS1" s="14"/>
+      <c r="BT1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="BU1" s="17"/>
-      <c r="BV1" s="17"/>
-      <c r="BW1" s="17"/>
-      <c r="BX1" s="17"/>
-      <c r="BY1" s="17" t="s">
+      <c r="BU1" s="14"/>
+      <c r="BV1" s="14"/>
+      <c r="BW1" s="14"/>
+      <c r="BX1" s="14"/>
+      <c r="BY1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="BZ1" s="17"/>
-      <c r="CA1" s="17"/>
-      <c r="CB1" s="17"/>
-      <c r="CC1" s="17"/>
-      <c r="CD1" s="17" t="s">
+      <c r="BZ1" s="14"/>
+      <c r="CA1" s="14"/>
+      <c r="CB1" s="14"/>
+      <c r="CC1" s="14"/>
+      <c r="CD1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="CE1" s="17"/>
-      <c r="CF1" s="17"/>
-      <c r="CG1" s="17"/>
-      <c r="CH1" s="17"/>
-      <c r="CI1" s="17" t="s">
+      <c r="CE1" s="14"/>
+      <c r="CF1" s="14"/>
+      <c r="CG1" s="14"/>
+      <c r="CH1" s="14"/>
+      <c r="CI1" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="CJ1" s="17"/>
-      <c r="CK1" s="17"/>
-      <c r="CL1" s="17"/>
-      <c r="CM1" s="17"/>
-      <c r="CN1" s="17" t="s">
+      <c r="CJ1" s="14"/>
+      <c r="CK1" s="14"/>
+      <c r="CL1" s="14"/>
+      <c r="CM1" s="14"/>
+      <c r="CN1" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="CO1" s="17"/>
-      <c r="CP1" s="17"/>
-      <c r="CQ1" s="17"/>
-      <c r="CR1" s="17"/>
-      <c r="CS1" s="17" t="s">
+      <c r="CO1" s="14"/>
+      <c r="CP1" s="14"/>
+      <c r="CQ1" s="14"/>
+      <c r="CR1" s="14"/>
+      <c r="CS1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="CT1" s="17"/>
-      <c r="CU1" s="17"/>
-      <c r="CV1" s="17"/>
-      <c r="CW1" s="17"/>
-      <c r="CX1" s="17" t="s">
+      <c r="CT1" s="14"/>
+      <c r="CU1" s="14"/>
+      <c r="CV1" s="14"/>
+      <c r="CW1" s="14"/>
+      <c r="CX1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="CY1" s="17"/>
-      <c r="CZ1" s="17"/>
-      <c r="DA1" s="17"/>
-      <c r="DB1" s="17"/>
+      <c r="CY1" s="14"/>
+      <c r="CZ1" s="14"/>
+      <c r="DA1" s="14"/>
+      <c r="DB1" s="14"/>
     </row>
-    <row r="2" spans="1:106" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:106" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="T2" s="8" t="s">
+      <c r="T2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="U2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="9" t="s">
+      <c r="V2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="W2" s="8" t="s">
+      <c r="W2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="8" t="s">
+      <c r="X2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="Y2" s="8" t="s">
+      <c r="Y2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Z2" s="8" t="s">
+      <c r="Z2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AA2" s="9" t="s">
+      <c r="AA2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AB2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="8" t="s">
+      <c r="AC2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="8" t="s">
+      <c r="AD2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="8" t="s">
+      <c r="AE2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AF2" s="9" t="s">
+      <c r="AF2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AG2" s="8" t="s">
+      <c r="AG2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AH2" s="8" t="s">
+      <c r="AH2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="AI2" s="8" t="s">
+      <c r="AI2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AJ2" s="8" t="s">
+      <c r="AJ2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="9" t="s">
+      <c r="AK2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AL2" s="8" t="s">
+      <c r="AL2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AM2" s="8" t="s">
+      <c r="AM2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="AN2" s="8" t="s">
+      <c r="AN2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AO2" s="8" t="s">
+      <c r="AO2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AP2" s="9" t="s">
+      <c r="AP2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AQ2" s="8" t="s">
+      <c r="AQ2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AR2" s="8" t="s">
+      <c r="AR2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="AS2" s="8" t="s">
+      <c r="AS2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AT2" s="8" t="s">
+      <c r="AT2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AU2" s="9" t="s">
+      <c r="AU2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AV2" s="8" t="s">
+      <c r="AV2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AW2" s="8" t="s">
+      <c r="AW2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="AX2" s="8" t="s">
+      <c r="AX2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AY2" s="8" t="s">
+      <c r="AY2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="9" t="s">
+      <c r="AZ2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BA2" s="8" t="s">
+      <c r="BA2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="BB2" s="8" t="s">
+      <c r="BB2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="BC2" s="8" t="s">
+      <c r="BC2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="BD2" s="8" t="s">
+      <c r="BD2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="BE2" s="9" t="s">
+      <c r="BE2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BF2" s="8" t="s">
+      <c r="BF2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="BG2" s="8" t="s">
+      <c r="BG2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="BH2" s="8" t="s">
+      <c r="BH2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="BI2" s="8" t="s">
+      <c r="BI2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="BJ2" s="9" t="s">
+      <c r="BJ2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BK2" s="8" t="s">
+      <c r="BK2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="BL2" s="8" t="s">
+      <c r="BL2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="BM2" s="8" t="s">
+      <c r="BM2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="BN2" s="8" t="s">
+      <c r="BN2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="BO2" s="9" t="s">
+      <c r="BO2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BP2" s="8" t="s">
+      <c r="BP2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="BQ2" s="8" t="s">
+      <c r="BQ2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="BR2" s="8" t="s">
+      <c r="BR2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="BS2" s="8" t="s">
+      <c r="BS2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="BT2" s="9" t="s">
+      <c r="BT2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BU2" s="8" t="s">
+      <c r="BU2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="BV2" s="8" t="s">
+      <c r="BV2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="BW2" s="8" t="s">
+      <c r="BW2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="BX2" s="8" t="s">
+      <c r="BX2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="BY2" s="9" t="s">
+      <c r="BY2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BZ2" s="8" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="CA2" s="8" t="s">
+      <c r="CA2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="CB2" s="8" t="s">
+      <c r="CB2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="CC2" s="8" t="s">
+      <c r="CC2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="CD2" s="9" t="s">
+      <c r="CD2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="CE2" s="8" t="s">
+      <c r="CE2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="CF2" s="8" t="s">
+      <c r="CF2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="CG2" s="8" t="s">
+      <c r="CG2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="CH2" s="8" t="s">
+      <c r="CH2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="CI2" s="9" t="s">
+      <c r="CI2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="CJ2" s="8" t="s">
+      <c r="CJ2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="CK2" s="8" t="s">
+      <c r="CK2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="CL2" s="8" t="s">
+      <c r="CL2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="CM2" s="8" t="s">
+      <c r="CM2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="CN2" s="9" t="s">
+      <c r="CN2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="CO2" s="8" t="s">
+      <c r="CO2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="CP2" s="8" t="s">
+      <c r="CP2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="CQ2" s="8" t="s">
+      <c r="CQ2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="CR2" s="8" t="s">
+      <c r="CR2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="CS2" s="9" t="s">
+      <c r="CS2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="CT2" s="8" t="s">
+      <c r="CT2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="CU2" s="8" t="s">
+      <c r="CU2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="CV2" s="8" t="s">
+      <c r="CV2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="CW2" s="8" t="s">
+      <c r="CW2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="CX2" s="9" t="s">
+      <c r="CX2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="CY2" s="8" t="s">
+      <c r="CY2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="CZ2" s="8" t="s">
+      <c r="CZ2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="DA2" s="8" t="s">
+      <c r="DA2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="DB2" s="8" t="s">
+      <c r="DB2" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="8">
         <v>10</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>4</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="8">
         <v>8</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="8">
         <v>1</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="8">
         <v>0</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="8">
         <v>4</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="8">
         <v>4</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="8">
         <v>4</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="8">
         <v>1</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="8">
         <v>1</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="8">
         <v>4</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="8">
         <v>4</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="8">
         <v>4</v>
       </c>
-      <c r="O3" s="11">
+      <c r="O3" s="8">
         <v>1</v>
       </c>
-      <c r="P3" s="11">
+      <c r="P3" s="8">
         <v>1</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="Q3" s="8">
         <v>13</v>
       </c>
-      <c r="R3" s="11">
+      <c r="R3" s="8">
         <v>13</v>
       </c>
-      <c r="S3" s="11">
+      <c r="S3" s="8">
         <v>13</v>
       </c>
-      <c r="T3" s="11">
+      <c r="T3" s="8">
         <v>3</v>
       </c>
-      <c r="U3" s="11">
+      <c r="U3" s="8">
         <v>3</v>
       </c>
-      <c r="V3" s="11">
+      <c r="V3" s="8">
         <v>14</v>
       </c>
-      <c r="W3" s="11">
+      <c r="W3" s="8">
         <v>14</v>
       </c>
-      <c r="X3" s="11">
+      <c r="X3" s="8">
         <v>13</v>
       </c>
-      <c r="Y3" s="11">
+      <c r="Y3" s="8">
         <v>2</v>
       </c>
-      <c r="Z3" s="11">
+      <c r="Z3" s="8">
         <v>3</v>
       </c>
-      <c r="AA3" s="11">
+      <c r="AA3" s="8">
         <v>6</v>
       </c>
-      <c r="AB3" s="11">
+      <c r="AB3" s="8">
         <v>5</v>
       </c>
-      <c r="AC3" s="11">
+      <c r="AC3" s="8">
         <v>5</v>
       </c>
-      <c r="AD3" s="11">
+      <c r="AD3" s="8">
         <v>1</v>
       </c>
-      <c r="AE3" s="11">
+      <c r="AE3" s="8">
         <v>1</v>
       </c>
-      <c r="AF3" s="11"/>
-      <c r="AG3" s="11"/>
-      <c r="AH3" s="11"/>
-      <c r="AI3" s="11"/>
-      <c r="AJ3" s="11"/>
-      <c r="AK3" s="11"/>
-      <c r="AL3" s="11"/>
-      <c r="AM3" s="11"/>
-      <c r="AN3" s="11"/>
-      <c r="AO3" s="11"/>
-      <c r="AP3" s="11"/>
-      <c r="AQ3" s="11"/>
-      <c r="AR3" s="11"/>
-      <c r="AS3" s="11"/>
-      <c r="AT3" s="11"/>
-      <c r="AU3" s="11"/>
-      <c r="AV3" s="11"/>
-      <c r="AW3" s="11"/>
-      <c r="AX3" s="11"/>
-      <c r="AY3" s="11"/>
-      <c r="AZ3" s="11"/>
-      <c r="BA3" s="11"/>
-      <c r="BB3" s="11"/>
-      <c r="BC3" s="11"/>
-      <c r="BD3" s="11"/>
-      <c r="BE3" s="11"/>
-      <c r="BF3" s="11"/>
-      <c r="BG3" s="11"/>
-      <c r="BH3" s="11"/>
-      <c r="BI3" s="11"/>
-      <c r="BJ3" s="11"/>
-      <c r="BK3" s="11"/>
-      <c r="BL3" s="11"/>
-      <c r="BM3" s="11"/>
-      <c r="BN3" s="11"/>
-      <c r="BO3" s="11"/>
-      <c r="BP3" s="11"/>
-      <c r="BQ3" s="11"/>
-      <c r="BR3" s="11"/>
-      <c r="BS3" s="11"/>
-      <c r="BT3" s="11"/>
-      <c r="BU3" s="11"/>
-      <c r="BV3" s="11"/>
-      <c r="BW3" s="11"/>
-      <c r="BX3" s="11"/>
-      <c r="BY3" s="11"/>
-      <c r="BZ3" s="11"/>
-      <c r="CA3" s="11"/>
-      <c r="CB3" s="11"/>
-      <c r="CC3" s="11"/>
-      <c r="CD3" s="11"/>
-      <c r="CE3" s="11"/>
-      <c r="CF3" s="11"/>
-      <c r="CG3" s="11"/>
-      <c r="CH3" s="11"/>
-      <c r="CI3" s="11"/>
-      <c r="CJ3" s="11"/>
-      <c r="CK3" s="11"/>
-      <c r="CL3" s="11"/>
-      <c r="CM3" s="11"/>
-      <c r="CN3" s="11"/>
-      <c r="CO3" s="11"/>
-      <c r="CP3" s="11"/>
-      <c r="CQ3" s="11"/>
-      <c r="CR3" s="11"/>
-      <c r="CS3" s="11"/>
-      <c r="CT3" s="11"/>
-      <c r="CU3" s="11"/>
-      <c r="CV3" s="11"/>
-      <c r="CW3" s="11"/>
-      <c r="CX3" s="11"/>
-      <c r="CY3" s="11"/>
-      <c r="CZ3" s="11"/>
-      <c r="DA3" s="11"/>
-      <c r="DB3" s="11"/>
+      <c r="AF3" s="8"/>
+      <c r="AG3" s="8"/>
+      <c r="AH3" s="8"/>
+      <c r="AI3" s="8"/>
+      <c r="AJ3" s="8"/>
+      <c r="AK3" s="8"/>
+      <c r="AL3" s="8"/>
+      <c r="AM3" s="8"/>
+      <c r="AN3" s="8"/>
+      <c r="AO3" s="8"/>
+      <c r="AP3" s="8"/>
+      <c r="AQ3" s="8"/>
+      <c r="AR3" s="8"/>
+      <c r="AS3" s="8"/>
+      <c r="AT3" s="8"/>
+      <c r="AU3" s="8"/>
+      <c r="AV3" s="8"/>
+      <c r="AW3" s="8"/>
+      <c r="AX3" s="8"/>
+      <c r="AY3" s="8"/>
+      <c r="AZ3" s="8"/>
+      <c r="BA3" s="8"/>
+      <c r="BB3" s="8"/>
+      <c r="BC3" s="8"/>
+      <c r="BD3" s="8"/>
+      <c r="BE3" s="8"/>
+      <c r="BF3" s="8"/>
+      <c r="BG3" s="8"/>
+      <c r="BH3" s="8"/>
+      <c r="BI3" s="8"/>
+      <c r="BJ3" s="8"/>
+      <c r="BK3" s="8"/>
+      <c r="BL3" s="8"/>
+      <c r="BM3" s="8"/>
+      <c r="BN3" s="8"/>
+      <c r="BO3" s="8"/>
+      <c r="BP3" s="8"/>
+      <c r="BQ3" s="8"/>
+      <c r="BR3" s="8"/>
+      <c r="BS3" s="8"/>
+      <c r="BT3" s="8"/>
+      <c r="BU3" s="8"/>
+      <c r="BV3" s="8"/>
+      <c r="BW3" s="8"/>
+      <c r="BX3" s="8"/>
+      <c r="BY3" s="8"/>
+      <c r="BZ3" s="8"/>
+      <c r="CA3" s="8"/>
+      <c r="CB3" s="8"/>
+      <c r="CC3" s="8"/>
+      <c r="CD3" s="8"/>
+      <c r="CE3" s="8"/>
+      <c r="CF3" s="8"/>
+      <c r="CG3" s="8"/>
+      <c r="CH3" s="8"/>
+      <c r="CI3" s="8"/>
+      <c r="CJ3" s="8"/>
+      <c r="CK3" s="8"/>
+      <c r="CL3" s="8"/>
+      <c r="CM3" s="8"/>
+      <c r="CN3" s="8"/>
+      <c r="CO3" s="8"/>
+      <c r="CP3" s="8"/>
+      <c r="CQ3" s="8"/>
+      <c r="CR3" s="8"/>
+      <c r="CS3" s="8"/>
+      <c r="CT3" s="8"/>
+      <c r="CU3" s="8"/>
+      <c r="CV3" s="8"/>
+      <c r="CW3" s="8"/>
+      <c r="CX3" s="8"/>
+      <c r="CY3" s="8"/>
+      <c r="CZ3" s="8"/>
+      <c r="DA3" s="8"/>
+      <c r="DB3" s="8"/>
     </row>
     <row r="4" spans="1:106" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>12</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>5</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>10</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>1</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>1</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>6</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>5</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>4</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>1</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>0</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>6</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>5</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>4</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="3">
         <v>2</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="3">
         <v>0</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="3">
         <v>15</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="3">
         <v>14</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="3">
         <v>10</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="3">
         <v>1</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="3">
         <v>2</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="3">
         <v>10</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="3">
         <v>9</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="3">
         <v>8</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="3">
         <v>1</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="3">
         <v>1</v>
       </c>
-      <c r="AA4" s="6">
+      <c r="AA4" s="3">
         <v>11</v>
       </c>
-      <c r="AB4" s="6">
+      <c r="AB4" s="3">
         <v>10</v>
       </c>
-      <c r="AC4" s="6">
+      <c r="AC4" s="3">
         <v>11</v>
       </c>
-      <c r="AD4" s="6">
+      <c r="AD4" s="3">
         <v>1</v>
       </c>
-      <c r="AE4" s="6">
+      <c r="AE4" s="3">
         <v>1</v>
       </c>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="6"/>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="6"/>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="6"/>
-      <c r="AL4" s="6"/>
-      <c r="AM4" s="6"/>
-      <c r="AN4" s="6"/>
-      <c r="AO4" s="6"/>
-      <c r="AP4" s="6"/>
-      <c r="AQ4" s="6"/>
-      <c r="AR4" s="6"/>
-      <c r="AS4" s="6"/>
-      <c r="AT4" s="6"/>
-      <c r="AU4" s="6"/>
-      <c r="AV4" s="6"/>
-      <c r="AW4" s="6"/>
-      <c r="AX4" s="6"/>
-      <c r="AY4" s="6"/>
-      <c r="AZ4" s="6"/>
-      <c r="BA4" s="6"/>
-      <c r="BB4" s="6"/>
-      <c r="BC4" s="6"/>
-      <c r="BD4" s="6"/>
-      <c r="BE4" s="6"/>
-      <c r="BF4" s="6"/>
-      <c r="BG4" s="6"/>
-      <c r="BH4" s="6"/>
-      <c r="BI4" s="6"/>
-      <c r="BJ4" s="6"/>
-      <c r="BK4" s="6"/>
-      <c r="BL4" s="6"/>
-      <c r="BM4" s="6"/>
-      <c r="BN4" s="6"/>
-      <c r="BO4" s="6"/>
-      <c r="BP4" s="6"/>
-      <c r="BQ4" s="6"/>
-      <c r="BR4" s="6"/>
-      <c r="BS4" s="6"/>
-      <c r="BT4" s="6"/>
-      <c r="BU4" s="6"/>
-      <c r="BV4" s="6"/>
-      <c r="BW4" s="6"/>
-      <c r="BX4" s="6"/>
-      <c r="BY4" s="6"/>
-      <c r="BZ4" s="6"/>
-      <c r="CA4" s="6"/>
-      <c r="CB4" s="6"/>
-      <c r="CC4" s="6"/>
-      <c r="CD4" s="6"/>
-      <c r="CE4" s="6"/>
-      <c r="CF4" s="6"/>
-      <c r="CG4" s="6"/>
-      <c r="CH4" s="6"/>
-      <c r="CI4" s="6"/>
-      <c r="CJ4" s="6"/>
-      <c r="CK4" s="6"/>
-      <c r="CL4" s="6"/>
-      <c r="CM4" s="6"/>
-      <c r="CN4" s="6"/>
-      <c r="CO4" s="6"/>
-      <c r="CP4" s="6"/>
-      <c r="CQ4" s="6"/>
-      <c r="CR4" s="6"/>
-      <c r="CS4" s="6"/>
-      <c r="CT4" s="6"/>
-      <c r="CU4" s="6"/>
-      <c r="CV4" s="6"/>
-      <c r="CW4" s="6"/>
-      <c r="CX4" s="6"/>
-      <c r="CY4" s="6"/>
-      <c r="CZ4" s="6"/>
-      <c r="DA4" s="6"/>
-      <c r="DB4" s="6"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3"/>
+      <c r="AL4" s="3"/>
+      <c r="AM4" s="3"/>
+      <c r="AN4" s="3"/>
+      <c r="AO4" s="3"/>
+      <c r="AP4" s="3"/>
+      <c r="AQ4" s="3"/>
+      <c r="AR4" s="3"/>
+      <c r="AS4" s="3"/>
+      <c r="AT4" s="3"/>
+      <c r="AU4" s="3"/>
+      <c r="AV4" s="3"/>
+      <c r="AW4" s="3"/>
+      <c r="AX4" s="3"/>
+      <c r="AY4" s="3"/>
+      <c r="AZ4" s="3"/>
+      <c r="BA4" s="3"/>
+      <c r="BB4" s="3"/>
+      <c r="BC4" s="3"/>
+      <c r="BD4" s="3"/>
+      <c r="BE4" s="3"/>
+      <c r="BF4" s="3"/>
+      <c r="BG4" s="3"/>
+      <c r="BH4" s="3"/>
+      <c r="BI4" s="3"/>
+      <c r="BJ4" s="3"/>
+      <c r="BK4" s="3"/>
+      <c r="BL4" s="3"/>
+      <c r="BM4" s="3"/>
+      <c r="BN4" s="3"/>
+      <c r="BO4" s="3"/>
+      <c r="BP4" s="3"/>
+      <c r="BQ4" s="3"/>
+      <c r="BR4" s="3"/>
+      <c r="BS4" s="3"/>
+      <c r="BT4" s="3"/>
+      <c r="BU4" s="3"/>
+      <c r="BV4" s="3"/>
+      <c r="BW4" s="3"/>
+      <c r="BX4" s="3"/>
+      <c r="BY4" s="3"/>
+      <c r="BZ4" s="3"/>
+      <c r="CA4" s="3"/>
+      <c r="CB4" s="3"/>
+      <c r="CC4" s="3"/>
+      <c r="CD4" s="3"/>
+      <c r="CE4" s="3"/>
+      <c r="CF4" s="3"/>
+      <c r="CG4" s="3"/>
+      <c r="CH4" s="3"/>
+      <c r="CI4" s="3"/>
+      <c r="CJ4" s="3"/>
+      <c r="CK4" s="3"/>
+      <c r="CL4" s="3"/>
+      <c r="CM4" s="3"/>
+      <c r="CN4" s="3"/>
+      <c r="CO4" s="3"/>
+      <c r="CP4" s="3"/>
+      <c r="CQ4" s="3"/>
+      <c r="CR4" s="3"/>
+      <c r="CS4" s="3"/>
+      <c r="CT4" s="3"/>
+      <c r="CU4" s="3"/>
+      <c r="CV4" s="3"/>
+      <c r="CW4" s="3"/>
+      <c r="CX4" s="3"/>
+      <c r="CY4" s="3"/>
+      <c r="CZ4" s="3"/>
+      <c r="DA4" s="3"/>
+      <c r="DB4" s="3"/>
     </row>
-    <row r="5" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="8">
         <v>6</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="8">
         <v>5</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="8">
         <v>3</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="8">
         <v>1</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="8">
         <v>1</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="8">
         <v>2</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="8">
         <v>2</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="8">
         <v>2</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="8">
         <v>0</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="8">
         <v>0</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="8">
         <v>20</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="8">
         <v>20</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="8">
         <v>15</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="8">
         <v>2</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="8">
         <v>10</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="8">
         <v>34</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="8">
         <v>32</v>
       </c>
-      <c r="S5" s="11">
+      <c r="S5" s="8">
         <v>31</v>
       </c>
-      <c r="T5" s="11">
+      <c r="T5" s="8">
         <v>6</v>
       </c>
-      <c r="U5" s="11">
+      <c r="U5" s="8">
         <v>11</v>
       </c>
-      <c r="V5" s="11">
+      <c r="V5" s="8">
         <v>55</v>
       </c>
-      <c r="W5" s="11">
+      <c r="W5" s="8">
         <v>52</v>
       </c>
-      <c r="X5" s="11">
+      <c r="X5" s="8">
         <v>51</v>
       </c>
-      <c r="Y5" s="11">
+      <c r="Y5" s="8">
         <v>7</v>
       </c>
-      <c r="Z5" s="11">
+      <c r="Z5" s="8">
         <v>16</v>
       </c>
-      <c r="AA5" s="11">
+      <c r="AA5" s="8">
         <v>28</v>
       </c>
-      <c r="AB5" s="11">
+      <c r="AB5" s="8">
         <v>26</v>
       </c>
-      <c r="AC5" s="11">
+      <c r="AC5" s="8">
         <v>25</v>
       </c>
-      <c r="AD5" s="11">
+      <c r="AD5" s="8">
         <v>4</v>
       </c>
-      <c r="AE5" s="11">
+      <c r="AE5" s="8">
         <v>9</v>
       </c>
-      <c r="AF5" s="11"/>
-      <c r="AG5" s="11"/>
-      <c r="AH5" s="11"/>
-      <c r="AI5" s="11"/>
-      <c r="AJ5" s="11"/>
-      <c r="AK5" s="11"/>
-      <c r="AL5" s="11"/>
-      <c r="AM5" s="11"/>
-      <c r="AN5" s="11"/>
-      <c r="AO5" s="11"/>
-      <c r="AP5" s="11"/>
-      <c r="AQ5" s="11"/>
-      <c r="AR5" s="11"/>
-      <c r="AS5" s="11"/>
-      <c r="AT5" s="11"/>
-      <c r="AU5" s="11"/>
-      <c r="AV5" s="11"/>
-      <c r="AW5" s="11"/>
-      <c r="AX5" s="11"/>
-      <c r="AY5" s="11"/>
-      <c r="AZ5" s="11"/>
-      <c r="BA5" s="11"/>
-      <c r="BB5" s="11"/>
-      <c r="BC5" s="11"/>
-      <c r="BD5" s="11"/>
-      <c r="BE5" s="11"/>
-      <c r="BF5" s="11"/>
-      <c r="BG5" s="11"/>
-      <c r="BH5" s="11"/>
-      <c r="BI5" s="11"/>
-      <c r="BJ5" s="11"/>
-      <c r="BK5" s="11"/>
-      <c r="BL5" s="11"/>
-      <c r="BM5" s="11"/>
-      <c r="BN5" s="11"/>
-      <c r="BO5" s="11"/>
-      <c r="BP5" s="11"/>
-      <c r="BQ5" s="11"/>
-      <c r="BR5" s="11"/>
-      <c r="BS5" s="11"/>
-      <c r="BT5" s="11"/>
-      <c r="BU5" s="11"/>
-      <c r="BV5" s="11"/>
-      <c r="BW5" s="11"/>
-      <c r="BX5" s="11"/>
-      <c r="BY5" s="11"/>
-      <c r="BZ5" s="11"/>
-      <c r="CA5" s="11"/>
-      <c r="CB5" s="11"/>
-      <c r="CC5" s="11"/>
-      <c r="CD5" s="11"/>
-      <c r="CE5" s="11"/>
-      <c r="CF5" s="11"/>
-      <c r="CG5" s="11"/>
-      <c r="CH5" s="11"/>
-      <c r="CI5" s="11"/>
-      <c r="CJ5" s="11"/>
-      <c r="CK5" s="11"/>
-      <c r="CL5" s="11"/>
-      <c r="CM5" s="11"/>
-      <c r="CN5" s="11"/>
-      <c r="CO5" s="11"/>
-      <c r="CP5" s="11"/>
-      <c r="CQ5" s="11"/>
-      <c r="CR5" s="11"/>
-      <c r="CS5" s="11"/>
-      <c r="CT5" s="11"/>
-      <c r="CU5" s="11"/>
-      <c r="CV5" s="11"/>
-      <c r="CW5" s="11"/>
-      <c r="CX5" s="11"/>
-      <c r="CY5" s="11"/>
-      <c r="CZ5" s="11"/>
-      <c r="DA5" s="11"/>
-      <c r="DB5" s="11"/>
+      <c r="AF5" s="8"/>
+      <c r="AG5" s="8"/>
+      <c r="AH5" s="8"/>
+      <c r="AI5" s="8"/>
+      <c r="AJ5" s="8"/>
+      <c r="AK5" s="8"/>
+      <c r="AL5" s="8"/>
+      <c r="AM5" s="8"/>
+      <c r="AN5" s="8"/>
+      <c r="AO5" s="8"/>
+      <c r="AP5" s="8"/>
+      <c r="AQ5" s="8"/>
+      <c r="AR5" s="8"/>
+      <c r="AS5" s="8"/>
+      <c r="AT5" s="8"/>
+      <c r="AU5" s="8"/>
+      <c r="AV5" s="8"/>
+      <c r="AW5" s="8"/>
+      <c r="AX5" s="8"/>
+      <c r="AY5" s="8"/>
+      <c r="AZ5" s="8"/>
+      <c r="BA5" s="8"/>
+      <c r="BB5" s="8"/>
+      <c r="BC5" s="8"/>
+      <c r="BD5" s="8"/>
+      <c r="BE5" s="8"/>
+      <c r="BF5" s="8"/>
+      <c r="BG5" s="8"/>
+      <c r="BH5" s="8"/>
+      <c r="BI5" s="8"/>
+      <c r="BJ5" s="8"/>
+      <c r="BK5" s="8"/>
+      <c r="BL5" s="8"/>
+      <c r="BM5" s="8"/>
+      <c r="BN5" s="8"/>
+      <c r="BO5" s="8"/>
+      <c r="BP5" s="8"/>
+      <c r="BQ5" s="8"/>
+      <c r="BR5" s="8"/>
+      <c r="BS5" s="8"/>
+      <c r="BT5" s="8"/>
+      <c r="BU5" s="8"/>
+      <c r="BV5" s="8"/>
+      <c r="BW5" s="8"/>
+      <c r="BX5" s="8"/>
+      <c r="BY5" s="8"/>
+      <c r="BZ5" s="8"/>
+      <c r="CA5" s="8"/>
+      <c r="CB5" s="8"/>
+      <c r="CC5" s="8"/>
+      <c r="CD5" s="8"/>
+      <c r="CE5" s="8"/>
+      <c r="CF5" s="8"/>
+      <c r="CG5" s="8"/>
+      <c r="CH5" s="8"/>
+      <c r="CI5" s="8"/>
+      <c r="CJ5" s="8"/>
+      <c r="CK5" s="8"/>
+      <c r="CL5" s="8"/>
+      <c r="CM5" s="8"/>
+      <c r="CN5" s="8"/>
+      <c r="CO5" s="8"/>
+      <c r="CP5" s="8"/>
+      <c r="CQ5" s="8"/>
+      <c r="CR5" s="8"/>
+      <c r="CS5" s="8"/>
+      <c r="CT5" s="8"/>
+      <c r="CU5" s="8"/>
+      <c r="CV5" s="8"/>
+      <c r="CW5" s="8"/>
+      <c r="CX5" s="8"/>
+      <c r="CY5" s="8"/>
+      <c r="CZ5" s="8"/>
+      <c r="DA5" s="8"/>
+      <c r="DB5" s="8"/>
     </row>
     <row r="6" spans="1:106" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="3">
         <v>0</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="3">
         <v>0</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>0</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="3">
         <v>0</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="3">
         <v>0</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="3">
         <v>0</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="3">
         <v>0</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="3">
         <v>0</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="3">
         <v>0</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="3">
         <v>0</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="3">
         <v>0</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>0</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="3">
         <v>0</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="3">
         <v>0</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="3">
         <v>0</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="3">
         <v>0</v>
       </c>
-      <c r="R6" s="6">
+      <c r="R6" s="3">
         <v>0</v>
       </c>
-      <c r="S6" s="6">
+      <c r="S6" s="3">
         <v>0</v>
       </c>
-      <c r="T6" s="6">
+      <c r="T6" s="3">
         <v>0</v>
       </c>
-      <c r="U6" s="6">
+      <c r="U6" s="3">
         <v>0</v>
       </c>
-      <c r="V6" s="6">
+      <c r="V6" s="3">
         <v>0</v>
       </c>
-      <c r="W6" s="6">
+      <c r="W6" s="3">
         <v>0</v>
       </c>
-      <c r="X6" s="6">
+      <c r="X6" s="3">
         <v>0</v>
       </c>
-      <c r="Y6" s="6">
+      <c r="Y6" s="3">
         <v>0</v>
       </c>
-      <c r="Z6" s="6">
+      <c r="Z6" s="3">
         <v>0</v>
       </c>
-      <c r="AA6" s="6">
+      <c r="AA6" s="3">
         <v>0</v>
       </c>
-      <c r="AB6" s="6">
+      <c r="AB6" s="3">
         <v>0</v>
       </c>
-      <c r="AC6" s="6">
+      <c r="AC6" s="3">
         <v>0</v>
       </c>
-      <c r="AD6" s="6">
+      <c r="AD6" s="3">
         <v>0</v>
       </c>
-      <c r="AE6" s="6">
+      <c r="AE6" s="3">
         <v>0</v>
       </c>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="6"/>
-      <c r="AO6" s="6"/>
-      <c r="AP6" s="6"/>
-      <c r="AQ6" s="6"/>
-      <c r="AR6" s="6"/>
-      <c r="AS6" s="6"/>
-      <c r="AT6" s="6"/>
-      <c r="AU6" s="6"/>
-      <c r="AV6" s="6"/>
-      <c r="AW6" s="6"/>
-      <c r="AX6" s="6"/>
-      <c r="AY6" s="6"/>
-      <c r="AZ6" s="6"/>
-      <c r="BA6" s="6"/>
-      <c r="BB6" s="6"/>
-      <c r="BC6" s="6"/>
-      <c r="BD6" s="6"/>
-      <c r="BE6" s="6"/>
-      <c r="BF6" s="6"/>
-      <c r="BG6" s="6"/>
-      <c r="BH6" s="6"/>
-      <c r="BI6" s="6"/>
-      <c r="BJ6" s="6"/>
-      <c r="BK6" s="6"/>
-      <c r="BL6" s="6"/>
-      <c r="BM6" s="6"/>
-      <c r="BN6" s="6"/>
-      <c r="BO6" s="6"/>
-      <c r="BP6" s="6"/>
-      <c r="BQ6" s="6"/>
-      <c r="BR6" s="6"/>
-      <c r="BS6" s="6"/>
-      <c r="BT6" s="6"/>
-      <c r="BU6" s="6"/>
-      <c r="BV6" s="6"/>
-      <c r="BW6" s="6"/>
-      <c r="BX6" s="6"/>
-      <c r="BY6" s="6"/>
-      <c r="BZ6" s="6"/>
-      <c r="CA6" s="6"/>
-      <c r="CB6" s="6"/>
-      <c r="CC6" s="6"/>
-      <c r="CD6" s="6"/>
-      <c r="CE6" s="6"/>
-      <c r="CF6" s="6"/>
-      <c r="CG6" s="6"/>
-      <c r="CH6" s="6"/>
-      <c r="CI6" s="6"/>
-      <c r="CJ6" s="6"/>
-      <c r="CK6" s="6"/>
-      <c r="CL6" s="6"/>
-      <c r="CM6" s="6"/>
-      <c r="CN6" s="6"/>
-      <c r="CO6" s="6"/>
-      <c r="CP6" s="6"/>
-      <c r="CQ6" s="6"/>
-      <c r="CR6" s="6"/>
-      <c r="CS6" s="6"/>
-      <c r="CT6" s="6"/>
-      <c r="CU6" s="6"/>
-      <c r="CV6" s="6"/>
-      <c r="CW6" s="6"/>
-      <c r="CX6" s="6"/>
-      <c r="CY6" s="6"/>
-      <c r="CZ6" s="6"/>
-      <c r="DA6" s="6"/>
-      <c r="DB6" s="6"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
+      <c r="AP6" s="3"/>
+      <c r="AQ6" s="3"/>
+      <c r="AR6" s="3"/>
+      <c r="AS6" s="3"/>
+      <c r="AT6" s="3"/>
+      <c r="AU6" s="3"/>
+      <c r="AV6" s="3"/>
+      <c r="AW6" s="3"/>
+      <c r="AX6" s="3"/>
+      <c r="AY6" s="3"/>
+      <c r="AZ6" s="3"/>
+      <c r="BA6" s="3"/>
+      <c r="BB6" s="3"/>
+      <c r="BC6" s="3"/>
+      <c r="BD6" s="3"/>
+      <c r="BE6" s="3"/>
+      <c r="BF6" s="3"/>
+      <c r="BG6" s="3"/>
+      <c r="BH6" s="3"/>
+      <c r="BI6" s="3"/>
+      <c r="BJ6" s="3"/>
+      <c r="BK6" s="3"/>
+      <c r="BL6" s="3"/>
+      <c r="BM6" s="3"/>
+      <c r="BN6" s="3"/>
+      <c r="BO6" s="3"/>
+      <c r="BP6" s="3"/>
+      <c r="BQ6" s="3"/>
+      <c r="BR6" s="3"/>
+      <c r="BS6" s="3"/>
+      <c r="BT6" s="3"/>
+      <c r="BU6" s="3"/>
+      <c r="BV6" s="3"/>
+      <c r="BW6" s="3"/>
+      <c r="BX6" s="3"/>
+      <c r="BY6" s="3"/>
+      <c r="BZ6" s="3"/>
+      <c r="CA6" s="3"/>
+      <c r="CB6" s="3"/>
+      <c r="CC6" s="3"/>
+      <c r="CD6" s="3"/>
+      <c r="CE6" s="3"/>
+      <c r="CF6" s="3"/>
+      <c r="CG6" s="3"/>
+      <c r="CH6" s="3"/>
+      <c r="CI6" s="3"/>
+      <c r="CJ6" s="3"/>
+      <c r="CK6" s="3"/>
+      <c r="CL6" s="3"/>
+      <c r="CM6" s="3"/>
+      <c r="CN6" s="3"/>
+      <c r="CO6" s="3"/>
+      <c r="CP6" s="3"/>
+      <c r="CQ6" s="3"/>
+      <c r="CR6" s="3"/>
+      <c r="CS6" s="3"/>
+      <c r="CT6" s="3"/>
+      <c r="CU6" s="3"/>
+      <c r="CV6" s="3"/>
+      <c r="CW6" s="3"/>
+      <c r="CX6" s="3"/>
+      <c r="CY6" s="3"/>
+      <c r="CZ6" s="3"/>
+      <c r="DA6" s="3"/>
+      <c r="DB6" s="3"/>
     </row>
-    <row r="7" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="8">
         <v>47</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="8">
         <v>43</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="8">
         <v>39</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="8">
         <v>3</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="8">
         <v>2</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="8">
         <v>8</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="8">
         <v>8</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="8">
         <v>6</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="8">
         <v>0</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="8">
         <v>0</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="8">
         <v>9</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="8">
         <v>9</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="8">
         <v>9</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="8">
         <v>1</v>
       </c>
-      <c r="P7" s="11">
+      <c r="P7" s="8">
         <v>2</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="Q7" s="8">
         <v>13</v>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="8">
         <v>13</v>
       </c>
-      <c r="S7" s="11">
+      <c r="S7" s="8">
         <v>12</v>
       </c>
-      <c r="T7" s="11">
+      <c r="T7" s="8">
         <v>3</v>
       </c>
-      <c r="U7" s="11">
+      <c r="U7" s="8">
         <v>4</v>
       </c>
-      <c r="V7" s="11">
+      <c r="V7" s="8">
         <v>17</v>
       </c>
-      <c r="W7" s="11">
+      <c r="W7" s="8">
         <v>17</v>
       </c>
-      <c r="X7" s="11">
+      <c r="X7" s="8">
         <v>16</v>
       </c>
-      <c r="Y7" s="11">
+      <c r="Y7" s="8">
         <v>2</v>
       </c>
-      <c r="Z7" s="11">
+      <c r="Z7" s="8">
         <v>4</v>
       </c>
-      <c r="AA7" s="11">
+      <c r="AA7" s="8">
         <v>9</v>
       </c>
-      <c r="AB7" s="11">
+      <c r="AB7" s="8">
         <v>9</v>
       </c>
-      <c r="AC7" s="11">
+      <c r="AC7" s="8">
         <v>8</v>
       </c>
-      <c r="AD7" s="11">
+      <c r="AD7" s="8">
         <v>1</v>
       </c>
-      <c r="AE7" s="11">
+      <c r="AE7" s="8">
         <v>1</v>
       </c>
-      <c r="AF7" s="11"/>
-      <c r="AG7" s="11"/>
-      <c r="AH7" s="11"/>
-      <c r="AI7" s="11"/>
-      <c r="AJ7" s="11"/>
-      <c r="AK7" s="11"/>
-      <c r="AL7" s="11"/>
-      <c r="AM7" s="11"/>
-      <c r="AN7" s="11"/>
-      <c r="AO7" s="11"/>
-      <c r="AP7" s="11"/>
-      <c r="AQ7" s="11"/>
-      <c r="AR7" s="11"/>
-      <c r="AS7" s="11"/>
-      <c r="AT7" s="11"/>
-      <c r="AU7" s="11"/>
-      <c r="AV7" s="11"/>
-      <c r="AW7" s="11"/>
-      <c r="AX7" s="11"/>
-      <c r="AY7" s="11"/>
-      <c r="AZ7" s="11"/>
-      <c r="BA7" s="11"/>
-      <c r="BB7" s="11"/>
-      <c r="BC7" s="11"/>
-      <c r="BD7" s="11"/>
-      <c r="BE7" s="11"/>
-      <c r="BF7" s="11"/>
-      <c r="BG7" s="11"/>
-      <c r="BH7" s="11"/>
-      <c r="BI7" s="11"/>
-      <c r="BJ7" s="11"/>
-      <c r="BK7" s="11"/>
-      <c r="BL7" s="11"/>
-      <c r="BM7" s="11"/>
-      <c r="BN7" s="11"/>
-      <c r="BO7" s="11"/>
-      <c r="BP7" s="11"/>
-      <c r="BQ7" s="11"/>
-      <c r="BR7" s="11"/>
-      <c r="BS7" s="11"/>
-      <c r="BT7" s="11"/>
-      <c r="BU7" s="11"/>
-      <c r="BV7" s="11"/>
-      <c r="BW7" s="11"/>
-      <c r="BX7" s="11"/>
-      <c r="BY7" s="11"/>
-      <c r="BZ7" s="11"/>
-      <c r="CA7" s="11"/>
-      <c r="CB7" s="11"/>
-      <c r="CC7" s="11"/>
-      <c r="CD7" s="11"/>
-      <c r="CE7" s="11"/>
-      <c r="CF7" s="11"/>
-      <c r="CG7" s="11"/>
-      <c r="CH7" s="11"/>
-      <c r="CI7" s="11"/>
-      <c r="CJ7" s="11"/>
-      <c r="CK7" s="11"/>
-      <c r="CL7" s="11"/>
-      <c r="CM7" s="11"/>
-      <c r="CN7" s="11"/>
-      <c r="CO7" s="11"/>
-      <c r="CP7" s="11"/>
-      <c r="CQ7" s="11"/>
-      <c r="CR7" s="11"/>
-      <c r="CS7" s="11"/>
-      <c r="CT7" s="11"/>
-      <c r="CU7" s="11"/>
-      <c r="CV7" s="11"/>
-      <c r="CW7" s="11"/>
-      <c r="CX7" s="11"/>
-      <c r="CY7" s="11"/>
-      <c r="CZ7" s="11"/>
-      <c r="DA7" s="11"/>
-      <c r="DB7" s="11"/>
+      <c r="AF7" s="8"/>
+      <c r="AG7" s="8"/>
+      <c r="AH7" s="8"/>
+      <c r="AI7" s="8"/>
+      <c r="AJ7" s="8"/>
+      <c r="AK7" s="8"/>
+      <c r="AL7" s="8"/>
+      <c r="AM7" s="8"/>
+      <c r="AN7" s="8"/>
+      <c r="AO7" s="8"/>
+      <c r="AP7" s="8"/>
+      <c r="AQ7" s="8"/>
+      <c r="AR7" s="8"/>
+      <c r="AS7" s="8"/>
+      <c r="AT7" s="8"/>
+      <c r="AU7" s="8"/>
+      <c r="AV7" s="8"/>
+      <c r="AW7" s="8"/>
+      <c r="AX7" s="8"/>
+      <c r="AY7" s="8"/>
+      <c r="AZ7" s="8"/>
+      <c r="BA7" s="8"/>
+      <c r="BB7" s="8"/>
+      <c r="BC7" s="8"/>
+      <c r="BD7" s="8"/>
+      <c r="BE7" s="8"/>
+      <c r="BF7" s="8"/>
+      <c r="BG7" s="8"/>
+      <c r="BH7" s="8"/>
+      <c r="BI7" s="8"/>
+      <c r="BJ7" s="8"/>
+      <c r="BK7" s="8"/>
+      <c r="BL7" s="8"/>
+      <c r="BM7" s="8"/>
+      <c r="BN7" s="8"/>
+      <c r="BO7" s="8"/>
+      <c r="BP7" s="8"/>
+      <c r="BQ7" s="8"/>
+      <c r="BR7" s="8"/>
+      <c r="BS7" s="8"/>
+      <c r="BT7" s="8"/>
+      <c r="BU7" s="8"/>
+      <c r="BV7" s="8"/>
+      <c r="BW7" s="8"/>
+      <c r="BX7" s="8"/>
+      <c r="BY7" s="8"/>
+      <c r="BZ7" s="8"/>
+      <c r="CA7" s="8"/>
+      <c r="CB7" s="8"/>
+      <c r="CC7" s="8"/>
+      <c r="CD7" s="8"/>
+      <c r="CE7" s="8"/>
+      <c r="CF7" s="8"/>
+      <c r="CG7" s="8"/>
+      <c r="CH7" s="8"/>
+      <c r="CI7" s="8"/>
+      <c r="CJ7" s="8"/>
+      <c r="CK7" s="8"/>
+      <c r="CL7" s="8"/>
+      <c r="CM7" s="8"/>
+      <c r="CN7" s="8"/>
+      <c r="CO7" s="8"/>
+      <c r="CP7" s="8"/>
+      <c r="CQ7" s="8"/>
+      <c r="CR7" s="8"/>
+      <c r="CS7" s="8"/>
+      <c r="CT7" s="8"/>
+      <c r="CU7" s="8"/>
+      <c r="CV7" s="8"/>
+      <c r="CW7" s="8"/>
+      <c r="CX7" s="8"/>
+      <c r="CY7" s="8"/>
+      <c r="CZ7" s="8"/>
+      <c r="DA7" s="8"/>
+      <c r="DB7" s="8"/>
     </row>
-    <row r="8" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="8">
         <v>27</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="8">
         <v>26</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="8">
         <v>22</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="8">
         <v>2</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="8">
         <v>10</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="8">
         <v>6</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="8">
         <v>6</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="8">
         <v>6</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="8">
         <v>0</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="8">
         <v>2</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="8">
         <v>10</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="8">
         <v>10</v>
       </c>
-      <c r="N8" s="11">
+      <c r="N8" s="8">
         <v>9</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="8">
         <v>1</v>
       </c>
-      <c r="P8" s="11">
+      <c r="P8" s="8">
         <v>1</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="Q8" s="8">
         <v>12</v>
       </c>
-      <c r="R8" s="11">
+      <c r="R8" s="8">
         <v>11</v>
       </c>
-      <c r="S8" s="11">
+      <c r="S8" s="8">
         <v>11</v>
       </c>
-      <c r="T8" s="11">
+      <c r="T8" s="8">
         <v>2</v>
       </c>
-      <c r="U8" s="11">
+      <c r="U8" s="8">
         <v>2</v>
       </c>
-      <c r="V8" s="11">
+      <c r="V8" s="8">
         <v>12</v>
       </c>
-      <c r="W8" s="11">
+      <c r="W8" s="8">
         <v>11</v>
       </c>
-      <c r="X8" s="11">
+      <c r="X8" s="8">
         <v>11</v>
       </c>
-      <c r="Y8" s="11">
+      <c r="Y8" s="8">
         <v>2</v>
       </c>
-      <c r="Z8" s="11">
+      <c r="Z8" s="8">
         <v>2</v>
       </c>
-      <c r="AA8" s="11">
+      <c r="AA8" s="8">
         <v>4</v>
       </c>
-      <c r="AB8" s="11">
+      <c r="AB8" s="8">
         <v>4</v>
       </c>
-      <c r="AC8" s="11">
+      <c r="AC8" s="8">
         <v>4</v>
       </c>
-      <c r="AD8" s="11">
+      <c r="AD8" s="8">
         <v>1</v>
       </c>
-      <c r="AE8" s="11">
+      <c r="AE8" s="8">
         <v>1</v>
       </c>
-      <c r="AF8" s="11"/>
-      <c r="AG8" s="11"/>
-      <c r="AH8" s="11"/>
-      <c r="AI8" s="11"/>
-      <c r="AJ8" s="11"/>
-      <c r="AK8" s="11"/>
-      <c r="AL8" s="11"/>
-      <c r="AM8" s="11"/>
-      <c r="AN8" s="11"/>
-      <c r="AO8" s="11"/>
-      <c r="AP8" s="11"/>
-      <c r="AQ8" s="11"/>
-      <c r="AR8" s="11"/>
-      <c r="AS8" s="11"/>
-      <c r="AT8" s="11"/>
-      <c r="AU8" s="11"/>
-      <c r="AV8" s="11"/>
-      <c r="AW8" s="11"/>
-      <c r="AX8" s="11"/>
-      <c r="AY8" s="11"/>
-      <c r="AZ8" s="11"/>
-      <c r="BA8" s="11"/>
-      <c r="BB8" s="11"/>
-      <c r="BC8" s="11"/>
-      <c r="BD8" s="11"/>
-      <c r="BE8" s="11"/>
-      <c r="BF8" s="11"/>
-      <c r="BG8" s="11"/>
-      <c r="BH8" s="11"/>
-      <c r="BI8" s="11"/>
-      <c r="BJ8" s="11"/>
-      <c r="BK8" s="11"/>
-      <c r="BL8" s="11"/>
-      <c r="BM8" s="11"/>
-      <c r="BN8" s="11"/>
-      <c r="BO8" s="11"/>
-      <c r="BP8" s="11"/>
-      <c r="BQ8" s="11"/>
-      <c r="BR8" s="11"/>
-      <c r="BS8" s="11"/>
-      <c r="BT8" s="11"/>
-      <c r="BU8" s="11"/>
-      <c r="BV8" s="11"/>
-      <c r="BW8" s="11"/>
-      <c r="BX8" s="11"/>
-      <c r="BY8" s="11"/>
-      <c r="BZ8" s="11"/>
-      <c r="CA8" s="11"/>
-      <c r="CB8" s="11"/>
-      <c r="CC8" s="11"/>
-      <c r="CD8" s="11"/>
-      <c r="CE8" s="11"/>
-      <c r="CF8" s="11"/>
-      <c r="CG8" s="11"/>
-      <c r="CH8" s="11"/>
-      <c r="CI8" s="11"/>
-      <c r="CJ8" s="11"/>
-      <c r="CK8" s="11"/>
-      <c r="CL8" s="11"/>
-      <c r="CM8" s="11"/>
-      <c r="CN8" s="11"/>
-      <c r="CO8" s="11"/>
-      <c r="CP8" s="11"/>
-      <c r="CQ8" s="11"/>
-      <c r="CR8" s="11"/>
-      <c r="CS8" s="11"/>
-      <c r="CT8" s="11"/>
-      <c r="CU8" s="11"/>
-      <c r="CV8" s="11"/>
-      <c r="CW8" s="11"/>
-      <c r="CX8" s="11"/>
-      <c r="CY8" s="11"/>
-      <c r="CZ8" s="11"/>
-      <c r="DA8" s="11"/>
-      <c r="DB8" s="11"/>
+      <c r="AF8" s="8"/>
+      <c r="AG8" s="8"/>
+      <c r="AH8" s="8"/>
+      <c r="AI8" s="8"/>
+      <c r="AJ8" s="8"/>
+      <c r="AK8" s="8"/>
+      <c r="AL8" s="8"/>
+      <c r="AM8" s="8"/>
+      <c r="AN8" s="8"/>
+      <c r="AO8" s="8"/>
+      <c r="AP8" s="8"/>
+      <c r="AQ8" s="8"/>
+      <c r="AR8" s="8"/>
+      <c r="AS8" s="8"/>
+      <c r="AT8" s="8"/>
+      <c r="AU8" s="8"/>
+      <c r="AV8" s="8"/>
+      <c r="AW8" s="8"/>
+      <c r="AX8" s="8"/>
+      <c r="AY8" s="8"/>
+      <c r="AZ8" s="8"/>
+      <c r="BA8" s="8"/>
+      <c r="BB8" s="8"/>
+      <c r="BC8" s="8"/>
+      <c r="BD8" s="8"/>
+      <c r="BE8" s="8"/>
+      <c r="BF8" s="8"/>
+      <c r="BG8" s="8"/>
+      <c r="BH8" s="8"/>
+      <c r="BI8" s="8"/>
+      <c r="BJ8" s="8"/>
+      <c r="BK8" s="8"/>
+      <c r="BL8" s="8"/>
+      <c r="BM8" s="8"/>
+      <c r="BN8" s="8"/>
+      <c r="BO8" s="8"/>
+      <c r="BP8" s="8"/>
+      <c r="BQ8" s="8"/>
+      <c r="BR8" s="8"/>
+      <c r="BS8" s="8"/>
+      <c r="BT8" s="8"/>
+      <c r="BU8" s="8"/>
+      <c r="BV8" s="8"/>
+      <c r="BW8" s="8"/>
+      <c r="BX8" s="8"/>
+      <c r="BY8" s="8"/>
+      <c r="BZ8" s="8"/>
+      <c r="CA8" s="8"/>
+      <c r="CB8" s="8"/>
+      <c r="CC8" s="8"/>
+      <c r="CD8" s="8"/>
+      <c r="CE8" s="8"/>
+      <c r="CF8" s="8"/>
+      <c r="CG8" s="8"/>
+      <c r="CH8" s="8"/>
+      <c r="CI8" s="8"/>
+      <c r="CJ8" s="8"/>
+      <c r="CK8" s="8"/>
+      <c r="CL8" s="8"/>
+      <c r="CM8" s="8"/>
+      <c r="CN8" s="8"/>
+      <c r="CO8" s="8"/>
+      <c r="CP8" s="8"/>
+      <c r="CQ8" s="8"/>
+      <c r="CR8" s="8"/>
+      <c r="CS8" s="8"/>
+      <c r="CT8" s="8"/>
+      <c r="CU8" s="8"/>
+      <c r="CV8" s="8"/>
+      <c r="CW8" s="8"/>
+      <c r="CX8" s="8"/>
+      <c r="CY8" s="8"/>
+      <c r="CZ8" s="8"/>
+      <c r="DA8" s="8"/>
+      <c r="DB8" s="8"/>
     </row>
-    <row r="9" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="8">
         <v>31</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <v>30</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="8">
         <v>27</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="8">
         <v>1</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <v>8</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="8">
         <v>8</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="8">
         <v>8</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="8">
         <v>8</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="8">
         <v>2</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="8">
         <v>2</v>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="8">
         <v>12</v>
       </c>
-      <c r="M9" s="11">
+      <c r="M9" s="8">
         <v>12</v>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="8">
         <v>12</v>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="8">
         <v>0</v>
       </c>
-      <c r="P9" s="11">
+      <c r="P9" s="8">
         <v>1</v>
       </c>
-      <c r="Q9" s="11">
+      <c r="Q9" s="8">
         <v>15</v>
       </c>
-      <c r="R9" s="11">
+      <c r="R9" s="8">
         <v>15</v>
       </c>
-      <c r="S9" s="11">
+      <c r="S9" s="8">
         <v>15</v>
       </c>
-      <c r="T9" s="11">
+      <c r="T9" s="8">
         <v>1</v>
       </c>
-      <c r="U9" s="11">
+      <c r="U9" s="8">
         <v>1</v>
       </c>
-      <c r="V9" s="11">
+      <c r="V9" s="8">
         <v>15</v>
       </c>
-      <c r="W9" s="11">
+      <c r="W9" s="8">
         <v>15</v>
       </c>
-      <c r="X9" s="11">
+      <c r="X9" s="8">
         <v>15</v>
       </c>
-      <c r="Y9" s="11">
+      <c r="Y9" s="8">
         <v>1</v>
       </c>
-      <c r="Z9" s="11">
+      <c r="Z9" s="8">
         <v>1</v>
       </c>
-      <c r="AA9" s="11">
+      <c r="AA9" s="8">
         <v>2</v>
       </c>
-      <c r="AB9" s="11">
+      <c r="AB9" s="8">
         <v>2</v>
       </c>
-      <c r="AC9" s="11">
+      <c r="AC9" s="8">
         <v>2</v>
       </c>
-      <c r="AD9" s="11">
+      <c r="AD9" s="8">
         <v>0</v>
       </c>
-      <c r="AE9" s="11">
+      <c r="AE9" s="8">
         <v>1</v>
       </c>
-      <c r="AF9" s="11"/>
-      <c r="AG9" s="11"/>
-      <c r="AH9" s="11"/>
-      <c r="AI9" s="11"/>
-      <c r="AJ9" s="11"/>
-      <c r="AK9" s="11"/>
-      <c r="AL9" s="11"/>
-      <c r="AM9" s="11"/>
-      <c r="AN9" s="11"/>
-      <c r="AO9" s="11"/>
-      <c r="AP9" s="11"/>
-      <c r="AQ9" s="11"/>
-      <c r="AR9" s="11"/>
-      <c r="AS9" s="11"/>
-      <c r="AT9" s="11"/>
-      <c r="AU9" s="11"/>
-      <c r="AV9" s="11"/>
-      <c r="AW9" s="11"/>
-      <c r="AX9" s="11"/>
-      <c r="AY9" s="11"/>
-      <c r="AZ9" s="11"/>
-      <c r="BA9" s="11"/>
-      <c r="BB9" s="11"/>
-      <c r="BC9" s="11"/>
-      <c r="BD9" s="11"/>
-      <c r="BE9" s="11"/>
-      <c r="BF9" s="11"/>
-      <c r="BG9" s="11"/>
-      <c r="BH9" s="11"/>
-      <c r="BI9" s="11"/>
-      <c r="BJ9" s="11"/>
-      <c r="BK9" s="11"/>
-      <c r="BL9" s="11"/>
-      <c r="BM9" s="11"/>
-      <c r="BN9" s="11"/>
-      <c r="BO9" s="11"/>
-      <c r="BP9" s="11"/>
-      <c r="BQ9" s="11"/>
-      <c r="BR9" s="11"/>
-      <c r="BS9" s="11"/>
-      <c r="BT9" s="11"/>
-      <c r="BU9" s="11"/>
-      <c r="BV9" s="11"/>
-      <c r="BW9" s="11"/>
-      <c r="BX9" s="11"/>
-      <c r="BY9" s="11"/>
-      <c r="BZ9" s="11"/>
-      <c r="CA9" s="11"/>
-      <c r="CB9" s="11"/>
-      <c r="CC9" s="11"/>
-      <c r="CD9" s="11"/>
-      <c r="CE9" s="11"/>
-      <c r="CF9" s="11"/>
-      <c r="CG9" s="11"/>
-      <c r="CH9" s="11"/>
-      <c r="CI9" s="11"/>
-      <c r="CJ9" s="11"/>
-      <c r="CK9" s="11"/>
-      <c r="CL9" s="11"/>
-      <c r="CM9" s="11"/>
-      <c r="CN9" s="11"/>
-      <c r="CO9" s="11"/>
-      <c r="CP9" s="11"/>
-      <c r="CQ9" s="11"/>
-      <c r="CR9" s="11"/>
-      <c r="CS9" s="11"/>
-      <c r="CT9" s="11"/>
-      <c r="CU9" s="11"/>
-      <c r="CV9" s="11"/>
-      <c r="CW9" s="11"/>
-      <c r="CX9" s="11"/>
-      <c r="CY9" s="11"/>
-      <c r="CZ9" s="11"/>
-      <c r="DA9" s="11"/>
-      <c r="DB9" s="11"/>
+      <c r="AF9" s="8"/>
+      <c r="AG9" s="8"/>
+      <c r="AH9" s="8"/>
+      <c r="AI9" s="8"/>
+      <c r="AJ9" s="8"/>
+      <c r="AK9" s="8"/>
+      <c r="AL9" s="8"/>
+      <c r="AM9" s="8"/>
+      <c r="AN9" s="8"/>
+      <c r="AO9" s="8"/>
+      <c r="AP9" s="8"/>
+      <c r="AQ9" s="8"/>
+      <c r="AR9" s="8"/>
+      <c r="AS9" s="8"/>
+      <c r="AT9" s="8"/>
+      <c r="AU9" s="8"/>
+      <c r="AV9" s="8"/>
+      <c r="AW9" s="8"/>
+      <c r="AX9" s="8"/>
+      <c r="AY9" s="8"/>
+      <c r="AZ9" s="8"/>
+      <c r="BA9" s="8"/>
+      <c r="BB9" s="8"/>
+      <c r="BC9" s="8"/>
+      <c r="BD9" s="8"/>
+      <c r="BE9" s="8"/>
+      <c r="BF9" s="8"/>
+      <c r="BG9" s="8"/>
+      <c r="BH9" s="8"/>
+      <c r="BI9" s="8"/>
+      <c r="BJ9" s="8"/>
+      <c r="BK9" s="8"/>
+      <c r="BL9" s="8"/>
+      <c r="BM9" s="8"/>
+      <c r="BN9" s="8"/>
+      <c r="BO9" s="8"/>
+      <c r="BP9" s="8"/>
+      <c r="BQ9" s="8"/>
+      <c r="BR9" s="8"/>
+      <c r="BS9" s="8"/>
+      <c r="BT9" s="8"/>
+      <c r="BU9" s="8"/>
+      <c r="BV9" s="8"/>
+      <c r="BW9" s="8"/>
+      <c r="BX9" s="8"/>
+      <c r="BY9" s="8"/>
+      <c r="BZ9" s="8"/>
+      <c r="CA9" s="8"/>
+      <c r="CB9" s="8"/>
+      <c r="CC9" s="8"/>
+      <c r="CD9" s="8"/>
+      <c r="CE9" s="8"/>
+      <c r="CF9" s="8"/>
+      <c r="CG9" s="8"/>
+      <c r="CH9" s="8"/>
+      <c r="CI9" s="8"/>
+      <c r="CJ9" s="8"/>
+      <c r="CK9" s="8"/>
+      <c r="CL9" s="8"/>
+      <c r="CM9" s="8"/>
+      <c r="CN9" s="8"/>
+      <c r="CO9" s="8"/>
+      <c r="CP9" s="8"/>
+      <c r="CQ9" s="8"/>
+      <c r="CR9" s="8"/>
+      <c r="CS9" s="8"/>
+      <c r="CT9" s="8"/>
+      <c r="CU9" s="8"/>
+      <c r="CV9" s="8"/>
+      <c r="CW9" s="8"/>
+      <c r="CX9" s="8"/>
+      <c r="CY9" s="8"/>
+      <c r="CZ9" s="8"/>
+      <c r="DA9" s="8"/>
+      <c r="DB9" s="8"/>
     </row>
     <row r="10" spans="1:106" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="3">
         <f>SUM(B3:B9)</f>
         <v>133</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="3">
         <f t="shared" ref="C10:Q10" si="0">SUM(C3:C9)</f>
         <v>113</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="3">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="3">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="3">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="3">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="3">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="3">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="R10" s="6">
+      <c r="R10" s="3">
         <f t="shared" ref="R10" si="1">SUM(R3:R9)</f>
         <v>98</v>
       </c>
-      <c r="S10" s="6">
+      <c r="S10" s="3">
         <f t="shared" ref="S10" si="2">SUM(S3:S9)</f>
         <v>92</v>
       </c>
-      <c r="T10" s="6">
+      <c r="T10" s="3">
         <f t="shared" ref="T10" si="3">SUM(T3:T9)</f>
         <v>16</v>
       </c>
-      <c r="U10" s="6">
+      <c r="U10" s="3">
         <f t="shared" ref="U10" si="4">SUM(U3:U9)</f>
         <v>23</v>
       </c>
-      <c r="V10" s="6">
+      <c r="V10" s="3">
         <f t="shared" ref="V10" si="5">SUM(V3:V9)</f>
         <v>123</v>
       </c>
-      <c r="W10" s="6">
+      <c r="W10" s="3">
         <f t="shared" ref="W10" si="6">SUM(W3:W9)</f>
         <v>118</v>
       </c>
-      <c r="X10" s="6">
+      <c r="X10" s="3">
         <f t="shared" ref="X10" si="7">SUM(X3:X9)</f>
         <v>114</v>
       </c>
-      <c r="Y10" s="6">
+      <c r="Y10" s="3">
         <f t="shared" ref="Y10" si="8">SUM(Y3:Y9)</f>
         <v>15</v>
       </c>
-      <c r="Z10" s="6">
+      <c r="Z10" s="3">
         <f t="shared" ref="Z10" si="9">SUM(Z3:Z9)</f>
         <v>27</v>
       </c>
-      <c r="AA10" s="6">
+      <c r="AA10" s="3">
         <f t="shared" ref="AA10" si="10">SUM(AA3:AA9)</f>
         <v>60</v>
       </c>
-      <c r="AB10" s="6">
+      <c r="AB10" s="3">
         <f t="shared" ref="AB10" si="11">SUM(AB3:AB9)</f>
         <v>56</v>
       </c>
-      <c r="AC10" s="6">
+      <c r="AC10" s="3">
         <f t="shared" ref="AC10" si="12">SUM(AC3:AC9)</f>
         <v>55</v>
       </c>
-      <c r="AD10" s="6">
+      <c r="AD10" s="3">
         <f t="shared" ref="AD10" si="13">SUM(AD3:AD9)</f>
         <v>8</v>
       </c>
-      <c r="AE10" s="6">
+      <c r="AE10" s="3">
         <f t="shared" ref="AE10:AF10" si="14">SUM(AE3:AE9)</f>
         <v>14</v>
       </c>
-      <c r="AF10" s="6">
+      <c r="AF10" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AG10" s="6">
+      <c r="AG10" s="3">
         <f t="shared" ref="AG10" si="15">SUM(AG3:AG9)</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="6">
+      <c r="AH10" s="3">
         <f t="shared" ref="AH10" si="16">SUM(AH3:AH9)</f>
         <v>0</v>
       </c>
-      <c r="AI10" s="6">
+      <c r="AI10" s="3">
         <f t="shared" ref="AI10" si="17">SUM(AI3:AI9)</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="6">
+      <c r="AJ10" s="3">
         <f t="shared" ref="AJ10" si="18">SUM(AJ3:AJ9)</f>
         <v>0</v>
       </c>
-      <c r="AK10" s="6">
+      <c r="AK10" s="3">
         <f t="shared" ref="AK10" si="19">SUM(AK3:AK9)</f>
         <v>0</v>
       </c>
-      <c r="AL10" s="6">
+      <c r="AL10" s="3">
         <f t="shared" ref="AL10" si="20">SUM(AL3:AL9)</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="6">
+      <c r="AM10" s="3">
         <f t="shared" ref="AM10" si="21">SUM(AM3:AM9)</f>
         <v>0</v>
       </c>
-      <c r="AN10" s="6">
+      <c r="AN10" s="3">
         <f t="shared" ref="AN10" si="22">SUM(AN3:AN9)</f>
         <v>0</v>
       </c>
-      <c r="AO10" s="6">
+      <c r="AO10" s="3">
         <f t="shared" ref="AO10" si="23">SUM(AO3:AO9)</f>
         <v>0</v>
       </c>
-      <c r="AP10" s="6">
+      <c r="AP10" s="3">
         <f t="shared" ref="AP10" si="24">SUM(AP3:AP9)</f>
         <v>0</v>
       </c>
-      <c r="AQ10" s="6">
+      <c r="AQ10" s="3">
         <f t="shared" ref="AQ10" si="25">SUM(AQ3:AQ9)</f>
         <v>0</v>
       </c>
-      <c r="AR10" s="6">
+      <c r="AR10" s="3">
         <f t="shared" ref="AR10" si="26">SUM(AR3:AR9)</f>
         <v>0</v>
       </c>
-      <c r="AS10" s="6">
+      <c r="AS10" s="3">
         <f t="shared" ref="AS10" si="27">SUM(AS3:AS9)</f>
         <v>0</v>
       </c>
-      <c r="AT10" s="6">
+      <c r="AT10" s="3">
         <f t="shared" ref="AT10:AU10" si="28">SUM(AT3:AT9)</f>
         <v>0</v>
       </c>
-      <c r="AU10" s="6">
+      <c r="AU10" s="3">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AV10" s="6">
+      <c r="AV10" s="3">
         <f t="shared" ref="AV10" si="29">SUM(AV3:AV9)</f>
         <v>0</v>
       </c>
-      <c r="AW10" s="6">
+      <c r="AW10" s="3">
         <f t="shared" ref="AW10" si="30">SUM(AW3:AW9)</f>
         <v>0</v>
       </c>
-      <c r="AX10" s="6">
+      <c r="AX10" s="3">
         <f t="shared" ref="AX10" si="31">SUM(AX3:AX9)</f>
         <v>0</v>
       </c>
-      <c r="AY10" s="6">
+      <c r="AY10" s="3">
         <f t="shared" ref="AY10" si="32">SUM(AY3:AY9)</f>
         <v>0</v>
       </c>
-      <c r="AZ10" s="6">
+      <c r="AZ10" s="3">
         <f t="shared" ref="AZ10" si="33">SUM(AZ3:AZ9)</f>
         <v>0</v>
       </c>
-      <c r="BA10" s="6">
+      <c r="BA10" s="3">
         <f t="shared" ref="BA10" si="34">SUM(BA3:BA9)</f>
         <v>0</v>
       </c>
-      <c r="BB10" s="6">
+      <c r="BB10" s="3">
         <f t="shared" ref="BB10" si="35">SUM(BB3:BB9)</f>
         <v>0</v>
       </c>
-      <c r="BC10" s="6">
+      <c r="BC10" s="3">
         <f t="shared" ref="BC10" si="36">SUM(BC3:BC9)</f>
         <v>0</v>
       </c>
-      <c r="BD10" s="6">
+      <c r="BD10" s="3">
         <f t="shared" ref="BD10" si="37">SUM(BD3:BD9)</f>
         <v>0</v>
       </c>
-      <c r="BE10" s="6">
+      <c r="BE10" s="3">
         <f t="shared" ref="BE10" si="38">SUM(BE3:BE9)</f>
         <v>0</v>
       </c>
-      <c r="BF10" s="6">
+      <c r="BF10" s="3">
         <f t="shared" ref="BF10" si="39">SUM(BF3:BF9)</f>
         <v>0</v>
       </c>
-      <c r="BG10" s="6">
+      <c r="BG10" s="3">
         <f t="shared" ref="BG10" si="40">SUM(BG3:BG9)</f>
         <v>0</v>
       </c>
-      <c r="BH10" s="6">
+      <c r="BH10" s="3">
         <f t="shared" ref="BH10" si="41">SUM(BH3:BH9)</f>
         <v>0</v>
       </c>
-      <c r="BI10" s="6">
+      <c r="BI10" s="3">
         <f t="shared" ref="BI10:BJ10" si="42">SUM(BI3:BI9)</f>
         <v>0</v>
       </c>
-      <c r="BJ10" s="6">
+      <c r="BJ10" s="3">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="BK10" s="6">
+      <c r="BK10" s="3">
         <f t="shared" ref="BK10" si="43">SUM(BK3:BK9)</f>
         <v>0</v>
       </c>
-      <c r="BL10" s="6">
+      <c r="BL10" s="3">
         <f t="shared" ref="BL10" si="44">SUM(BL3:BL9)</f>
         <v>0</v>
       </c>
-      <c r="BM10" s="6">
+      <c r="BM10" s="3">
         <f t="shared" ref="BM10" si="45">SUM(BM3:BM9)</f>
         <v>0</v>
       </c>
-      <c r="BN10" s="6">
+      <c r="BN10" s="3">
         <f t="shared" ref="BN10" si="46">SUM(BN3:BN9)</f>
         <v>0</v>
       </c>
-      <c r="BO10" s="6">
+      <c r="BO10" s="3">
         <f t="shared" ref="BO10" si="47">SUM(BO3:BO9)</f>
         <v>0</v>
       </c>
-      <c r="BP10" s="6">
+      <c r="BP10" s="3">
         <f t="shared" ref="BP10" si="48">SUM(BP3:BP9)</f>
         <v>0</v>
       </c>
-      <c r="BQ10" s="6">
+      <c r="BQ10" s="3">
         <f t="shared" ref="BQ10" si="49">SUM(BQ3:BQ9)</f>
         <v>0</v>
       </c>
-      <c r="BR10" s="6">
+      <c r="BR10" s="3">
         <f t="shared" ref="BR10" si="50">SUM(BR3:BR9)</f>
         <v>0</v>
       </c>
-      <c r="BS10" s="6">
+      <c r="BS10" s="3">
         <f t="shared" ref="BS10" si="51">SUM(BS3:BS9)</f>
         <v>0</v>
       </c>
-      <c r="BT10" s="6">
+      <c r="BT10" s="3">
         <f t="shared" ref="BT10" si="52">SUM(BT3:BT9)</f>
         <v>0</v>
       </c>
-      <c r="BU10" s="6">
+      <c r="BU10" s="3">
         <f t="shared" ref="BU10" si="53">SUM(BU3:BU9)</f>
         <v>0</v>
       </c>
-      <c r="BV10" s="6">
+      <c r="BV10" s="3">
         <f t="shared" ref="BV10" si="54">SUM(BV3:BV9)</f>
         <v>0</v>
       </c>
-      <c r="BW10" s="6">
+      <c r="BW10" s="3">
         <f t="shared" ref="BW10" si="55">SUM(BW3:BW9)</f>
         <v>0</v>
       </c>
-      <c r="BX10" s="6">
+      <c r="BX10" s="3">
         <f t="shared" ref="BX10" si="56">SUM(BX3:BX9)</f>
         <v>0</v>
       </c>
-      <c r="BY10" s="6">
+      <c r="BY10" s="3">
         <f t="shared" ref="BY10" si="57">SUM(BY3:BY9)</f>
         <v>0</v>
       </c>
-      <c r="BZ10" s="6">
+      <c r="BZ10" s="3">
         <f t="shared" ref="BZ10" si="58">SUM(BZ3:BZ9)</f>
         <v>0</v>
       </c>
-      <c r="CA10" s="6">
+      <c r="CA10" s="3">
         <f t="shared" ref="CA10" si="59">SUM(CA3:CA9)</f>
         <v>0</v>
       </c>
-      <c r="CB10" s="6">
+      <c r="CB10" s="3">
         <f t="shared" ref="CB10" si="60">SUM(CB3:CB9)</f>
         <v>0</v>
       </c>
-      <c r="CC10" s="6">
+      <c r="CC10" s="3">
         <f t="shared" ref="CC10" si="61">SUM(CC3:CC9)</f>
         <v>0</v>
       </c>
-      <c r="CD10" s="6">
+      <c r="CD10" s="3">
         <f t="shared" ref="CD10" si="62">SUM(CD3:CD9)</f>
         <v>0</v>
       </c>
-      <c r="CE10" s="6">
+      <c r="CE10" s="3">
         <f t="shared" ref="CE10" si="63">SUM(CE3:CE9)</f>
         <v>0</v>
       </c>
-      <c r="CF10" s="6">
+      <c r="CF10" s="3">
         <f t="shared" ref="CF10" si="64">SUM(CF3:CF9)</f>
         <v>0</v>
       </c>
-      <c r="CG10" s="6">
+      <c r="CG10" s="3">
         <f t="shared" ref="CG10" si="65">SUM(CG3:CG9)</f>
         <v>0</v>
       </c>
-      <c r="CH10" s="6">
+      <c r="CH10" s="3">
         <f t="shared" ref="CH10" si="66">SUM(CH3:CH9)</f>
         <v>0</v>
       </c>
-      <c r="CI10" s="6">
+      <c r="CI10" s="3">
         <f t="shared" ref="CI10" si="67">SUM(CI3:CI9)</f>
         <v>0</v>
       </c>
-      <c r="CJ10" s="6">
+      <c r="CJ10" s="3">
         <f t="shared" ref="CJ10" si="68">SUM(CJ3:CJ9)</f>
         <v>0</v>
       </c>
-      <c r="CK10" s="6">
+      <c r="CK10" s="3">
         <f t="shared" ref="CK10" si="69">SUM(CK3:CK9)</f>
         <v>0</v>
       </c>
-      <c r="CL10" s="6">
+      <c r="CL10" s="3">
         <f t="shared" ref="CL10" si="70">SUM(CL3:CL9)</f>
         <v>0</v>
       </c>
-      <c r="CM10" s="6">
+      <c r="CM10" s="3">
         <f t="shared" ref="CM10" si="71">SUM(CM3:CM9)</f>
         <v>0</v>
       </c>
-      <c r="CN10" s="6">
+      <c r="CN10" s="3">
         <f t="shared" ref="CN10" si="72">SUM(CN3:CN9)</f>
         <v>0</v>
       </c>
-      <c r="CO10" s="6">
+      <c r="CO10" s="3">
         <f t="shared" ref="CO10" si="73">SUM(CO3:CO9)</f>
         <v>0</v>
       </c>
-      <c r="CP10" s="6">
+      <c r="CP10" s="3">
         <f t="shared" ref="CP10" si="74">SUM(CP3:CP9)</f>
         <v>0</v>
       </c>
-      <c r="CQ10" s="6">
+      <c r="CQ10" s="3">
         <f t="shared" ref="CQ10" si="75">SUM(CQ3:CQ9)</f>
         <v>0</v>
       </c>
-      <c r="CR10" s="6">
+      <c r="CR10" s="3">
         <f t="shared" ref="CR10" si="76">SUM(CR3:CR9)</f>
         <v>0</v>
       </c>
-      <c r="CS10" s="6">
+      <c r="CS10" s="3">
         <f t="shared" ref="CS10" si="77">SUM(CS3:CS9)</f>
         <v>0</v>
       </c>
-      <c r="CT10" s="6">
+      <c r="CT10" s="3">
         <f t="shared" ref="CT10" si="78">SUM(CT3:CT9)</f>
         <v>0</v>
       </c>
-      <c r="CU10" s="6">
+      <c r="CU10" s="3">
         <f t="shared" ref="CU10" si="79">SUM(CU3:CU9)</f>
         <v>0</v>
       </c>
-      <c r="CV10" s="6">
+      <c r="CV10" s="3">
         <f t="shared" ref="CV10" si="80">SUM(CV3:CV9)</f>
         <v>0</v>
       </c>
-      <c r="CW10" s="6">
+      <c r="CW10" s="3">
         <f t="shared" ref="CW10" si="81">SUM(CW3:CW9)</f>
         <v>0</v>
       </c>
-      <c r="CX10" s="6">
+      <c r="CX10" s="3">
         <f t="shared" ref="CX10" si="82">SUM(CX3:CX9)</f>
         <v>0</v>
       </c>
-      <c r="CY10" s="6">
+      <c r="CY10" s="3">
         <f t="shared" ref="CY10" si="83">SUM(CY3:CY9)</f>
         <v>0</v>
       </c>
-      <c r="CZ10" s="6">
+      <c r="CZ10" s="3">
         <f t="shared" ref="CZ10" si="84">SUM(CZ3:CZ9)</f>
         <v>0</v>
       </c>
-      <c r="DA10" s="6">
+      <c r="DA10" s="3">
         <f t="shared" ref="DA10" si="85">SUM(DA3:DA9)</f>
         <v>0</v>
       </c>
-      <c r="DB10" s="6">
+      <c r="DB10" s="3">
         <f t="shared" ref="DB10" si="86">SUM(DB3:DB9)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="CN1:CR1"/>
-    <mergeCell ref="CS1:CW1"/>
-    <mergeCell ref="CX1:DB1"/>
-    <mergeCell ref="BJ1:BN1"/>
-    <mergeCell ref="BO1:BS1"/>
-    <mergeCell ref="BT1:BX1"/>
-    <mergeCell ref="BY1:CC1"/>
-    <mergeCell ref="CD1:CH1"/>
-    <mergeCell ref="CI1:CM1"/>
     <mergeCell ref="BE1:BI1"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:K1"/>
@@ -15366,6 +15562,15 @@
     <mergeCell ref="AP1:AT1"/>
     <mergeCell ref="AU1:AY1"/>
     <mergeCell ref="AZ1:BD1"/>
+    <mergeCell ref="CN1:CR1"/>
+    <mergeCell ref="CS1:CW1"/>
+    <mergeCell ref="CX1:DB1"/>
+    <mergeCell ref="BJ1:BN1"/>
+    <mergeCell ref="BO1:BS1"/>
+    <mergeCell ref="BT1:BX1"/>
+    <mergeCell ref="BY1:CC1"/>
+    <mergeCell ref="CD1:CH1"/>
+    <mergeCell ref="CI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15547,193 +15752,193 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A1" s="14"/>
-      <c r="B1" s="18" t="s">
+      <c r="A1" s="11"/>
+      <c r="B1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="21" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="21" t="s">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="21" t="s">
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="21"/>
-      <c r="X1" s="21"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="21" t="s">
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="21"/>
-      <c r="AB1" s="21"/>
-      <c r="AC1" s="21"/>
-      <c r="AD1" s="21"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="21" t="s">
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="AG1" s="21"/>
-      <c r="AH1" s="21"/>
-      <c r="AI1" s="21"/>
-      <c r="AJ1" s="21"/>
-      <c r="AK1" s="14"/>
-      <c r="AL1" s="21" t="s">
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="11"/>
+      <c r="AL1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="AM1" s="21"/>
-      <c r="AN1" s="21"/>
-      <c r="AO1" s="21"/>
-      <c r="AP1" s="21"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15"/>
     </row>
     <row r="2" spans="1:42" s="5" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="O2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="Q2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="R2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="S2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="T2" s="16" t="s">
+      <c r="T2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="U2" s="15" t="s">
+      <c r="U2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="15" t="s">
+      <c r="V2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="W2" s="15" t="s">
+      <c r="W2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="X2" s="15" t="s">
+      <c r="X2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="Y2" s="15" t="s">
+      <c r="Y2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="Z2" s="16" t="s">
+      <c r="Z2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AA2" s="15" t="s">
+      <c r="AA2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AB2" s="15" t="s">
+      <c r="AB2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="AC2" s="15" t="s">
+      <c r="AC2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="AD2" s="15" t="s">
+      <c r="AD2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="AE2" s="15" t="s">
+      <c r="AE2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AF2" s="16" t="s">
+      <c r="AF2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AG2" s="15" t="s">
+      <c r="AG2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AH2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="AI2" s="15" t="s">
+      <c r="AI2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="AJ2" s="15" t="s">
+      <c r="AJ2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="15" t="s">
+      <c r="AK2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AL2" s="16" t="s">
+      <c r="AL2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AM2" s="15" t="s">
+      <c r="AM2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AN2" s="15" t="s">
+      <c r="AN2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="AO2" s="15" t="s">
+      <c r="AO2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="AP2" s="15" t="s">
+      <c r="AP2" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:42" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B3" s="3">
@@ -15751,7 +15956,7 @@
       <c r="F3" s="3">
         <v>0</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="H3" s="3">
@@ -15769,7 +15974,7 @@
       <c r="L3" s="3">
         <v>1</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="N3" s="3">
@@ -15787,7 +15992,7 @@
       <c r="R3" s="3">
         <v>1</v>
       </c>
-      <c r="S3" s="13" t="s">
+      <c r="S3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="T3" s="3">
@@ -15805,7 +16010,7 @@
       <c r="X3" s="3">
         <v>0</v>
       </c>
-      <c r="Y3" s="13" t="s">
+      <c r="Y3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="Z3" s="3">
@@ -15823,7 +16028,7 @@
       <c r="AD3" s="3">
         <v>2</v>
       </c>
-      <c r="AE3" s="13" t="s">
+      <c r="AE3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="AF3" s="3">
@@ -15841,7 +16046,7 @@
       <c r="AJ3" s="3">
         <v>10</v>
       </c>
-      <c r="AK3" s="13" t="s">
+      <c r="AK3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="AL3" s="3">
@@ -16501,48 +16706,132 @@
       </c>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="3"/>
-      <c r="AH9" s="3"/>
-      <c r="AI9" s="3"/>
-      <c r="AJ9" s="3"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="3"/>
-      <c r="AN9" s="3"/>
-      <c r="AO9" s="3"/>
-      <c r="AP9" s="3"/>
+      <c r="A9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="3">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="3">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3">
+        <v>7</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1</v>
+      </c>
+      <c r="L9" s="3">
+        <v>2</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9" s="3">
+        <v>28</v>
+      </c>
+      <c r="O9" s="3">
+        <v>26</v>
+      </c>
+      <c r="P9" s="3">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
+        <v>11</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>15</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>15</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>14</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>2</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>4</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL9" s="3">
+        <v>22</v>
+      </c>
+      <c r="AM9" s="3">
+        <v>22</v>
+      </c>
+      <c r="AN9" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>

--- a/documents/지표/주별활동지수.xlsx
+++ b/documents/지표/주별활동지수.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf1f1df607fbac1a/Desktop/Github/2026-QI/documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf1f1df607fbac1a/Desktop/Github/2026-QI/documents/지표/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{C34A7588-1100-49C1-938C-BE10454C6A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{075B84F0-8A35-4724-B426-0BFA5FD7299E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4713887E-CD6E-4815-B4CA-C61188946519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{0FC1208A-2CB8-4E1E-B9D0-F7D163D68827}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="50">
   <si>
     <t>1주차</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -212,6 +212,10 @@
     <t>7주차(7/2~7/8)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>8주차(7/9~7/15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -340,7 +344,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -350,19 +354,28 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -371,7 +384,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1468,9 +1481,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$9</c:f>
+              <c:f>Sheet1!$A$3:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1491,16 +1504,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$B$9</c:f>
+              <c:f>Sheet1!$B$3:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -1520,7 +1536,10 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5</c:v>
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1614,9 +1633,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$9</c:f>
+              <c:f>Sheet1!$A$3:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1637,16 +1656,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$3:$C$9</c:f>
+              <c:f>Sheet1!$C$3:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -1666,7 +1688,10 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5</c:v>
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1760,9 +1785,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$9</c:f>
+              <c:f>Sheet1!$A$3:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1783,16 +1808,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$3:$D$9</c:f>
+              <c:f>Sheet1!$D$3:$D$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1812,7 +1840,10 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5</c:v>
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1906,9 +1937,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$9</c:f>
+              <c:f>Sheet1!$A$3:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1929,16 +1960,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$3:$E$9</c:f>
+              <c:f>Sheet1!$E$3:$E$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1958,6 +1992,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2052,9 +2089,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$9</c:f>
+              <c:f>Sheet1!$A$3:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2075,16 +2112,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$3:$F$9</c:f>
+              <c:f>Sheet1!$F$3:$F$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2104,6 +2144,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2477,9 +2520,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$9</c:f>
+              <c:f>Sheet1!$G$3:$G$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2500,16 +2543,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$3:$H$9</c:f>
+              <c:f>Sheet1!$H$3:$H$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
@@ -2529,7 +2575,10 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8</c:v>
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2623,9 +2672,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$9</c:f>
+              <c:f>Sheet1!$G$3:$G$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2646,16 +2695,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$I$3:$I$9</c:f>
+              <c:f>Sheet1!$I$3:$I$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -2675,7 +2727,10 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8</c:v>
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2769,9 +2824,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$9</c:f>
+              <c:f>Sheet1!$G$3:$G$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2792,16 +2847,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$3:$J$9</c:f>
+              <c:f>Sheet1!$J$3:$J$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -2821,7 +2879,10 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2915,9 +2976,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$9</c:f>
+              <c:f>Sheet1!$G$3:$G$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2938,16 +2999,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$K$3:$K$9</c:f>
+              <c:f>Sheet1!$K$3:$K$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -2968,6 +3032,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3061,9 +3128,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$9</c:f>
+              <c:f>Sheet1!$G$3:$G$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3084,16 +3151,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$3:$L$9</c:f>
+              <c:f>Sheet1!$L$3:$L$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3114,6 +3184,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3487,9 +3560,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$9</c:f>
+              <c:f>Sheet1!$M$3:$M$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3510,16 +3583,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$N$3:$N$9</c:f>
+              <c:f>Sheet1!$N$3:$N$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>6</c:v>
                 </c:pt>
@@ -3540,6 +3616,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>31</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3634,9 +3713,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$9</c:f>
+              <c:f>Sheet1!$M$3:$M$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3657,16 +3736,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$O$3:$O$9</c:f>
+              <c:f>Sheet1!$O$3:$O$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -3687,6 +3769,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3781,9 +3866,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$9</c:f>
+              <c:f>Sheet1!$M$3:$M$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3804,16 +3889,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$P$3:$P$9</c:f>
+              <c:f>Sheet1!$P$3:$P$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -3834,6 +3922,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>29</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3928,9 +4019,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$9</c:f>
+              <c:f>Sheet1!$M$3:$M$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3951,16 +4042,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Q$3:$Q$9</c:f>
+              <c:f>Sheet1!$Q$3:$Q$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3980,6 +4074,9 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -4075,9 +4172,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$9</c:f>
+              <c:f>Sheet1!$M$3:$M$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4098,16 +4195,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$R$3:$R$9</c:f>
+              <c:f>Sheet1!$R$3:$R$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4128,6 +4228,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4502,9 +4605,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$9</c:f>
+              <c:f>Sheet1!$S$3:$S$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4525,16 +4628,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$T$3:$T$9</c:f>
+              <c:f>Sheet1!$T$3:$T$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4554,6 +4660,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4649,9 +4758,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$9</c:f>
+              <c:f>Sheet1!$S$3:$S$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4672,16 +4781,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$U$3:$U$9</c:f>
+              <c:f>Sheet1!$U$3:$U$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4701,6 +4813,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4796,9 +4911,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$9</c:f>
+              <c:f>Sheet1!$S$3:$S$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4819,16 +4934,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$V$3:$V$9</c:f>
+              <c:f>Sheet1!$V$3:$V$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4848,6 +4966,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4943,9 +5064,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$9</c:f>
+              <c:f>Sheet1!$S$3:$S$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4966,16 +5087,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$W$3:$W$9</c:f>
+              <c:f>Sheet1!$W$3:$W$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4995,6 +5119,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5090,9 +5217,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$9</c:f>
+              <c:f>Sheet1!$S$3:$S$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5113,16 +5240,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$X$3:$X$9</c:f>
+              <c:f>Sheet1!$X$3:$X$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5142,6 +5272,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5520,9 +5653,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$9</c:f>
+              <c:f>Sheet1!$Y$3:$Y$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5543,16 +5676,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Z$3:$Z$9</c:f>
+              <c:f>Sheet1!$Z$3:$Z$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>47</c:v>
                 </c:pt>
@@ -5573,6 +5709,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5667,9 +5806,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$9</c:f>
+              <c:f>Sheet1!$Y$3:$Y$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5690,16 +5829,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AA$3:$AA$9</c:f>
+              <c:f>Sheet1!$AA$3:$AA$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>43</c:v>
                 </c:pt>
@@ -5720,6 +5862,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5814,9 +5959,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$9</c:f>
+              <c:f>Sheet1!$Y$3:$Y$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5837,16 +5982,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AB$3:$AB$9</c:f>
+              <c:f>Sheet1!$AB$3:$AB$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>39</c:v>
                 </c:pt>
@@ -5867,6 +6015,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5961,9 +6112,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$9</c:f>
+              <c:f>Sheet1!$Y$3:$Y$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5984,16 +6135,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AC$3:$AC$9</c:f>
+              <c:f>Sheet1!$AC$3:$AC$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -6014,6 +6168,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6108,9 +6265,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$9</c:f>
+              <c:f>Sheet1!$Y$3:$Y$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6131,16 +6288,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AD$3:$AD$9</c:f>
+              <c:f>Sheet1!$AD$3:$AD$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -6160,6 +6320,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
@@ -6538,9 +6701,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$9</c:f>
+              <c:f>Sheet1!$AE$3:$AE$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6561,16 +6724,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AF$3:$AF$9</c:f>
+              <c:f>Sheet1!$AF$3:$AF$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>27</c:v>
                 </c:pt>
@@ -6590,7 +6756,10 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4</c:v>
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6685,9 +6854,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$9</c:f>
+              <c:f>Sheet1!$AE$3:$AE$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6708,16 +6877,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AG$3:$AG$9</c:f>
+              <c:f>Sheet1!$AG$3:$AG$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>26</c:v>
                 </c:pt>
@@ -6737,7 +6909,10 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4</c:v>
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6832,9 +7007,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$9</c:f>
+              <c:f>Sheet1!$AE$3:$AE$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6855,16 +7030,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AH$3:$AH$9</c:f>
+              <c:f>Sheet1!$AH$3:$AH$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>22</c:v>
                 </c:pt>
@@ -6884,7 +7062,10 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4</c:v>
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6979,9 +7160,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$9</c:f>
+              <c:f>Sheet1!$AE$3:$AE$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7002,16 +7183,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AI$3:$AI$9</c:f>
+              <c:f>Sheet1!$AI$3:$AI$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -7032,6 +7216,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7126,9 +7313,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$9</c:f>
+              <c:f>Sheet1!$AE$3:$AE$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7149,16 +7336,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AJ$3:$AJ$9</c:f>
+              <c:f>Sheet1!$AJ$3:$AJ$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -7179,6 +7369,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7557,9 +7750,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$9</c:f>
+              <c:f>Sheet1!$AK$3:$AK$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7580,16 +7773,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AL$3:$AL$9</c:f>
+              <c:f>Sheet1!$AL$3:$AL$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>31</c:v>
                 </c:pt>
@@ -7610,6 +7806,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7704,9 +7903,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$9</c:f>
+              <c:f>Sheet1!$AK$3:$AK$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7727,16 +7926,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AM$3:$AM$9</c:f>
+              <c:f>Sheet1!$AM$3:$AM$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>30</c:v>
                 </c:pt>
@@ -7757,6 +7959,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7851,9 +8056,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$9</c:f>
+              <c:f>Sheet1!$AK$3:$AK$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7874,16 +8079,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AN$3:$AN$9</c:f>
+              <c:f>Sheet1!$AN$3:$AN$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>27</c:v>
                 </c:pt>
@@ -7903,6 +8111,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -7998,9 +8209,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$9</c:f>
+              <c:f>Sheet1!$AK$3:$AK$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8021,16 +8232,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AO$3:$AO$9</c:f>
+              <c:f>Sheet1!$AO$3:$AO$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -8051,6 +8265,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8145,9 +8362,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$9</c:f>
+              <c:f>Sheet1!$AK$3:$AK$10</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8168,16 +8385,19 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7주차(7/2~7/8)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8주차(7/9~7/15)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AP$3:$AP$9</c:f>
+              <c:f>Sheet1!$AP$3:$AP$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -8198,6 +8418,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13354,2202 +13577,2211 @@
   <dimension ref="A1:DB10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="5.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="18.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="107" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="13" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="5.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="13.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="107" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:106" x14ac:dyDescent="0.3">
-      <c r="A1" s="3"/>
-      <c r="B1" s="14" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14" t="s">
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14" t="s">
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14" t="s">
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14" t="s">
+      <c r="W1" s="17"/>
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17"/>
+      <c r="AA1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14" t="s">
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="17"/>
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="17"/>
+      <c r="AF1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="14"/>
-      <c r="AH1" s="14"/>
-      <c r="AI1" s="14"/>
-      <c r="AJ1" s="14"/>
-      <c r="AK1" s="14" t="s">
+      <c r="AG1" s="17"/>
+      <c r="AH1" s="17"/>
+      <c r="AI1" s="17"/>
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="AL1" s="14"/>
-      <c r="AM1" s="14"/>
-      <c r="AN1" s="14"/>
-      <c r="AO1" s="14"/>
-      <c r="AP1" s="14" t="s">
+      <c r="AL1" s="17"/>
+      <c r="AM1" s="17"/>
+      <c r="AN1" s="17"/>
+      <c r="AO1" s="17"/>
+      <c r="AP1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="AQ1" s="14"/>
-      <c r="AR1" s="14"/>
-      <c r="AS1" s="14"/>
-      <c r="AT1" s="14"/>
-      <c r="AU1" s="14" t="s">
+      <c r="AQ1" s="17"/>
+      <c r="AR1" s="17"/>
+      <c r="AS1" s="17"/>
+      <c r="AT1" s="17"/>
+      <c r="AU1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="AV1" s="14"/>
-      <c r="AW1" s="14"/>
-      <c r="AX1" s="14"/>
-      <c r="AY1" s="14"/>
-      <c r="AZ1" s="14" t="s">
+      <c r="AV1" s="17"/>
+      <c r="AW1" s="17"/>
+      <c r="AX1" s="17"/>
+      <c r="AY1" s="17"/>
+      <c r="AZ1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="BA1" s="14"/>
-      <c r="BB1" s="14"/>
-      <c r="BC1" s="14"/>
-      <c r="BD1" s="14"/>
-      <c r="BE1" s="14" t="s">
+      <c r="BA1" s="17"/>
+      <c r="BB1" s="17"/>
+      <c r="BC1" s="17"/>
+      <c r="BD1" s="17"/>
+      <c r="BE1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="BF1" s="14"/>
-      <c r="BG1" s="14"/>
-      <c r="BH1" s="14"/>
-      <c r="BI1" s="14"/>
-      <c r="BJ1" s="14" t="s">
+      <c r="BF1" s="17"/>
+      <c r="BG1" s="17"/>
+      <c r="BH1" s="17"/>
+      <c r="BI1" s="17"/>
+      <c r="BJ1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="BK1" s="14"/>
-      <c r="BL1" s="14"/>
-      <c r="BM1" s="14"/>
-      <c r="BN1" s="14"/>
-      <c r="BO1" s="14" t="s">
+      <c r="BK1" s="17"/>
+      <c r="BL1" s="17"/>
+      <c r="BM1" s="17"/>
+      <c r="BN1" s="17"/>
+      <c r="BO1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="BP1" s="14"/>
-      <c r="BQ1" s="14"/>
-      <c r="BR1" s="14"/>
-      <c r="BS1" s="14"/>
-      <c r="BT1" s="14" t="s">
+      <c r="BP1" s="17"/>
+      <c r="BQ1" s="17"/>
+      <c r="BR1" s="17"/>
+      <c r="BS1" s="17"/>
+      <c r="BT1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="BU1" s="14"/>
-      <c r="BV1" s="14"/>
-      <c r="BW1" s="14"/>
-      <c r="BX1" s="14"/>
-      <c r="BY1" s="14" t="s">
+      <c r="BU1" s="17"/>
+      <c r="BV1" s="17"/>
+      <c r="BW1" s="17"/>
+      <c r="BX1" s="17"/>
+      <c r="BY1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="BZ1" s="14"/>
-      <c r="CA1" s="14"/>
-      <c r="CB1" s="14"/>
-      <c r="CC1" s="14"/>
-      <c r="CD1" s="14" t="s">
+      <c r="BZ1" s="17"/>
+      <c r="CA1" s="17"/>
+      <c r="CB1" s="17"/>
+      <c r="CC1" s="17"/>
+      <c r="CD1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="CE1" s="14"/>
-      <c r="CF1" s="14"/>
-      <c r="CG1" s="14"/>
-      <c r="CH1" s="14"/>
-      <c r="CI1" s="14" t="s">
+      <c r="CE1" s="17"/>
+      <c r="CF1" s="17"/>
+      <c r="CG1" s="17"/>
+      <c r="CH1" s="17"/>
+      <c r="CI1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="CJ1" s="14"/>
-      <c r="CK1" s="14"/>
-      <c r="CL1" s="14"/>
-      <c r="CM1" s="14"/>
-      <c r="CN1" s="14" t="s">
+      <c r="CJ1" s="17"/>
+      <c r="CK1" s="17"/>
+      <c r="CL1" s="17"/>
+      <c r="CM1" s="17"/>
+      <c r="CN1" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="CO1" s="14"/>
-      <c r="CP1" s="14"/>
-      <c r="CQ1" s="14"/>
-      <c r="CR1" s="14"/>
-      <c r="CS1" s="14" t="s">
+      <c r="CO1" s="17"/>
+      <c r="CP1" s="17"/>
+      <c r="CQ1" s="17"/>
+      <c r="CR1" s="17"/>
+      <c r="CS1" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="CT1" s="14"/>
-      <c r="CU1" s="14"/>
-      <c r="CV1" s="14"/>
-      <c r="CW1" s="14"/>
-      <c r="CX1" s="14" t="s">
+      <c r="CT1" s="17"/>
+      <c r="CU1" s="17"/>
+      <c r="CV1" s="17"/>
+      <c r="CW1" s="17"/>
+      <c r="CX1" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="CY1" s="14"/>
-      <c r="CZ1" s="14"/>
-      <c r="DA1" s="14"/>
-      <c r="DB1" s="14"/>
+      <c r="CY1" s="17"/>
+      <c r="CZ1" s="17"/>
+      <c r="DA1" s="17"/>
+      <c r="DB1" s="17"/>
     </row>
-    <row r="2" spans="1:106" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:106" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="7" t="s">
+      <c r="V2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="X2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Y2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="Z2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AA2" s="7" t="s">
+      <c r="AA2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="AB2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="AC2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="6" t="s">
+      <c r="AD2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="6" t="s">
+      <c r="AE2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AF2" s="7" t="s">
+      <c r="AF2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AG2" s="6" t="s">
+      <c r="AG2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="AH2" s="6" t="s">
+      <c r="AH2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="AI2" s="6" t="s">
+      <c r="AI2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AJ2" s="6" t="s">
+      <c r="AJ2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="7" t="s">
+      <c r="AK2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AL2" s="6" t="s">
+      <c r="AL2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="AM2" s="6" t="s">
+      <c r="AM2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="AN2" s="6" t="s">
+      <c r="AN2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AO2" s="6" t="s">
+      <c r="AO2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AP2" s="7" t="s">
+      <c r="AP2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AQ2" s="6" t="s">
+      <c r="AQ2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="AR2" s="6" t="s">
+      <c r="AR2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="AS2" s="6" t="s">
+      <c r="AS2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AT2" s="6" t="s">
+      <c r="AT2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AU2" s="7" t="s">
+      <c r="AU2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="AV2" s="6" t="s">
+      <c r="AV2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="AW2" s="6" t="s">
+      <c r="AW2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="AX2" s="6" t="s">
+      <c r="AX2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AY2" s="6" t="s">
+      <c r="AY2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="7" t="s">
+      <c r="AZ2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="BA2" s="6" t="s">
+      <c r="BA2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="BB2" s="6" t="s">
+      <c r="BB2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="BC2" s="6" t="s">
+      <c r="BC2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="BD2" s="6" t="s">
+      <c r="BD2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="BE2" s="7" t="s">
+      <c r="BE2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="BF2" s="6" t="s">
+      <c r="BF2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="BG2" s="6" t="s">
+      <c r="BG2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="BH2" s="6" t="s">
+      <c r="BH2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="BI2" s="6" t="s">
+      <c r="BI2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="BJ2" s="7" t="s">
+      <c r="BJ2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="BK2" s="6" t="s">
+      <c r="BK2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="BL2" s="6" t="s">
+      <c r="BL2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="BM2" s="6" t="s">
+      <c r="BM2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="BN2" s="6" t="s">
+      <c r="BN2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="BO2" s="7" t="s">
+      <c r="BO2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="BP2" s="6" t="s">
+      <c r="BP2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="BQ2" s="6" t="s">
+      <c r="BQ2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="BR2" s="6" t="s">
+      <c r="BR2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="BS2" s="6" t="s">
+      <c r="BS2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="BT2" s="7" t="s">
+      <c r="BT2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="BU2" s="6" t="s">
+      <c r="BU2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="BV2" s="6" t="s">
+      <c r="BV2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="BW2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="BX2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="BY2" s="7" t="s">
+      <c r="BY2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="BZ2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CA2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="CB2" s="6" t="s">
+      <c r="CB2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="CC2" s="6" t="s">
+      <c r="CC2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="CD2" s="7" t="s">
+      <c r="CD2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="CE2" s="6" t="s">
+      <c r="CE2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="CF2" s="6" t="s">
+      <c r="CF2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="CG2" s="6" t="s">
+      <c r="CG2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="CH2" s="6" t="s">
+      <c r="CH2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="CI2" s="7" t="s">
+      <c r="CI2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="CJ2" s="6" t="s">
+      <c r="CJ2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="CK2" s="6" t="s">
+      <c r="CK2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="CL2" s="6" t="s">
+      <c r="CL2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="CM2" s="6" t="s">
+      <c r="CM2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="CN2" s="7" t="s">
+      <c r="CN2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="CO2" s="6" t="s">
+      <c r="CO2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="CP2" s="6" t="s">
+      <c r="CP2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="CQ2" s="6" t="s">
+      <c r="CQ2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="CR2" s="6" t="s">
+      <c r="CR2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="CS2" s="7" t="s">
+      <c r="CS2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="CT2" s="6" t="s">
+      <c r="CT2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="CU2" s="6" t="s">
+      <c r="CU2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="CV2" s="6" t="s">
+      <c r="CV2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="CW2" s="6" t="s">
+      <c r="CW2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="CX2" s="7" t="s">
+      <c r="CX2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="CY2" s="6" t="s">
+      <c r="CY2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="CZ2" s="6" t="s">
+      <c r="CZ2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="DA2" s="6" t="s">
+      <c r="DA2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="DB2" s="6" t="s">
+      <c r="DB2" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="11">
         <v>10</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>4</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="11">
         <v>8</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>1</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="11">
         <v>0</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="11">
         <v>4</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="11">
         <v>4</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="11">
         <v>4</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="11">
         <v>1</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="11">
         <v>1</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="11">
         <v>4</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="11">
         <v>4</v>
       </c>
-      <c r="N3" s="8">
+      <c r="N3" s="11">
         <v>4</v>
       </c>
-      <c r="O3" s="8">
+      <c r="O3" s="11">
         <v>1</v>
       </c>
-      <c r="P3" s="8">
+      <c r="P3" s="11">
         <v>1</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="Q3" s="11">
         <v>13</v>
       </c>
-      <c r="R3" s="8">
+      <c r="R3" s="11">
         <v>13</v>
       </c>
-      <c r="S3" s="8">
+      <c r="S3" s="11">
         <v>13</v>
       </c>
-      <c r="T3" s="8">
+      <c r="T3" s="11">
         <v>3</v>
       </c>
-      <c r="U3" s="8">
+      <c r="U3" s="11">
         <v>3</v>
       </c>
-      <c r="V3" s="8">
+      <c r="V3" s="11">
         <v>14</v>
       </c>
-      <c r="W3" s="8">
+      <c r="W3" s="11">
         <v>14</v>
       </c>
-      <c r="X3" s="8">
+      <c r="X3" s="11">
         <v>13</v>
       </c>
-      <c r="Y3" s="8">
+      <c r="Y3" s="11">
         <v>2</v>
       </c>
-      <c r="Z3" s="8">
+      <c r="Z3" s="11">
         <v>3</v>
       </c>
-      <c r="AA3" s="8">
+      <c r="AA3" s="11">
         <v>6</v>
       </c>
-      <c r="AB3" s="8">
+      <c r="AB3" s="11">
         <v>5</v>
       </c>
-      <c r="AC3" s="8">
+      <c r="AC3" s="11">
         <v>5</v>
       </c>
-      <c r="AD3" s="8">
+      <c r="AD3" s="11">
         <v>1</v>
       </c>
-      <c r="AE3" s="8">
+      <c r="AE3" s="11">
         <v>1</v>
       </c>
-      <c r="AF3" s="8"/>
-      <c r="AG3" s="8"/>
-      <c r="AH3" s="8"/>
-      <c r="AI3" s="8"/>
-      <c r="AJ3" s="8"/>
-      <c r="AK3" s="8"/>
-      <c r="AL3" s="8"/>
-      <c r="AM3" s="8"/>
-      <c r="AN3" s="8"/>
-      <c r="AO3" s="8"/>
-      <c r="AP3" s="8"/>
-      <c r="AQ3" s="8"/>
-      <c r="AR3" s="8"/>
-      <c r="AS3" s="8"/>
-      <c r="AT3" s="8"/>
-      <c r="AU3" s="8"/>
-      <c r="AV3" s="8"/>
-      <c r="AW3" s="8"/>
-      <c r="AX3" s="8"/>
-      <c r="AY3" s="8"/>
-      <c r="AZ3" s="8"/>
-      <c r="BA3" s="8"/>
-      <c r="BB3" s="8"/>
-      <c r="BC3" s="8"/>
-      <c r="BD3" s="8"/>
-      <c r="BE3" s="8"/>
-      <c r="BF3" s="8"/>
-      <c r="BG3" s="8"/>
-      <c r="BH3" s="8"/>
-      <c r="BI3" s="8"/>
-      <c r="BJ3" s="8"/>
-      <c r="BK3" s="8"/>
-      <c r="BL3" s="8"/>
-      <c r="BM3" s="8"/>
-      <c r="BN3" s="8"/>
-      <c r="BO3" s="8"/>
-      <c r="BP3" s="8"/>
-      <c r="BQ3" s="8"/>
-      <c r="BR3" s="8"/>
-      <c r="BS3" s="8"/>
-      <c r="BT3" s="8"/>
-      <c r="BU3" s="8"/>
-      <c r="BV3" s="8"/>
-      <c r="BW3" s="8"/>
-      <c r="BX3" s="8"/>
-      <c r="BY3" s="8"/>
-      <c r="BZ3" s="8"/>
-      <c r="CA3" s="8"/>
-      <c r="CB3" s="8"/>
-      <c r="CC3" s="8"/>
-      <c r="CD3" s="8"/>
-      <c r="CE3" s="8"/>
-      <c r="CF3" s="8"/>
-      <c r="CG3" s="8"/>
-      <c r="CH3" s="8"/>
-      <c r="CI3" s="8"/>
-      <c r="CJ3" s="8"/>
-      <c r="CK3" s="8"/>
-      <c r="CL3" s="8"/>
-      <c r="CM3" s="8"/>
-      <c r="CN3" s="8"/>
-      <c r="CO3" s="8"/>
-      <c r="CP3" s="8"/>
-      <c r="CQ3" s="8"/>
-      <c r="CR3" s="8"/>
-      <c r="CS3" s="8"/>
-      <c r="CT3" s="8"/>
-      <c r="CU3" s="8"/>
-      <c r="CV3" s="8"/>
-      <c r="CW3" s="8"/>
-      <c r="CX3" s="8"/>
-      <c r="CY3" s="8"/>
-      <c r="CZ3" s="8"/>
-      <c r="DA3" s="8"/>
-      <c r="DB3" s="8"/>
+      <c r="AF3" s="11"/>
+      <c r="AG3" s="11"/>
+      <c r="AH3" s="11"/>
+      <c r="AI3" s="11"/>
+      <c r="AJ3" s="11"/>
+      <c r="AK3" s="11"/>
+      <c r="AL3" s="11"/>
+      <c r="AM3" s="11"/>
+      <c r="AN3" s="11"/>
+      <c r="AO3" s="11"/>
+      <c r="AP3" s="11"/>
+      <c r="AQ3" s="11"/>
+      <c r="AR3" s="11"/>
+      <c r="AS3" s="11"/>
+      <c r="AT3" s="11"/>
+      <c r="AU3" s="11"/>
+      <c r="AV3" s="11"/>
+      <c r="AW3" s="11"/>
+      <c r="AX3" s="11"/>
+      <c r="AY3" s="11"/>
+      <c r="AZ3" s="11"/>
+      <c r="BA3" s="11"/>
+      <c r="BB3" s="11"/>
+      <c r="BC3" s="11"/>
+      <c r="BD3" s="11"/>
+      <c r="BE3" s="11"/>
+      <c r="BF3" s="11"/>
+      <c r="BG3" s="11"/>
+      <c r="BH3" s="11"/>
+      <c r="BI3" s="11"/>
+      <c r="BJ3" s="11"/>
+      <c r="BK3" s="11"/>
+      <c r="BL3" s="11"/>
+      <c r="BM3" s="11"/>
+      <c r="BN3" s="11"/>
+      <c r="BO3" s="11"/>
+      <c r="BP3" s="11"/>
+      <c r="BQ3" s="11"/>
+      <c r="BR3" s="11"/>
+      <c r="BS3" s="11"/>
+      <c r="BT3" s="11"/>
+      <c r="BU3" s="11"/>
+      <c r="BV3" s="11"/>
+      <c r="BW3" s="11"/>
+      <c r="BX3" s="11"/>
+      <c r="BY3" s="11"/>
+      <c r="BZ3" s="11"/>
+      <c r="CA3" s="11"/>
+      <c r="CB3" s="11"/>
+      <c r="CC3" s="11"/>
+      <c r="CD3" s="11"/>
+      <c r="CE3" s="11"/>
+      <c r="CF3" s="11"/>
+      <c r="CG3" s="11"/>
+      <c r="CH3" s="11"/>
+      <c r="CI3" s="11"/>
+      <c r="CJ3" s="11"/>
+      <c r="CK3" s="11"/>
+      <c r="CL3" s="11"/>
+      <c r="CM3" s="11"/>
+      <c r="CN3" s="11"/>
+      <c r="CO3" s="11"/>
+      <c r="CP3" s="11"/>
+      <c r="CQ3" s="11"/>
+      <c r="CR3" s="11"/>
+      <c r="CS3" s="11"/>
+      <c r="CT3" s="11"/>
+      <c r="CU3" s="11"/>
+      <c r="CV3" s="11"/>
+      <c r="CW3" s="11"/>
+      <c r="CX3" s="11"/>
+      <c r="CY3" s="11"/>
+      <c r="CZ3" s="11"/>
+      <c r="DA3" s="11"/>
+      <c r="DB3" s="11"/>
     </row>
     <row r="4" spans="1:106" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="6">
         <v>12</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>5</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="6">
         <v>10</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="6">
         <v>1</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="6">
         <v>6</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="6">
         <v>5</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="6">
         <v>4</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="6">
         <v>1</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="6">
         <v>0</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="6">
         <v>6</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="6">
         <v>5</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="6">
         <v>4</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="6">
         <v>2</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="6">
         <v>0</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="6">
         <v>15</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="6">
         <v>14</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="6">
         <v>10</v>
       </c>
-      <c r="T4" s="3">
+      <c r="T4" s="6">
         <v>1</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U4" s="6">
         <v>2</v>
       </c>
-      <c r="V4" s="3">
+      <c r="V4" s="6">
         <v>10</v>
       </c>
-      <c r="W4" s="3">
+      <c r="W4" s="6">
         <v>9</v>
       </c>
-      <c r="X4" s="3">
+      <c r="X4" s="6">
         <v>8</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="Y4" s="6">
         <v>1</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="Z4" s="6">
         <v>1</v>
       </c>
-      <c r="AA4" s="3">
+      <c r="AA4" s="6">
         <v>11</v>
       </c>
-      <c r="AB4" s="3">
+      <c r="AB4" s="6">
         <v>10</v>
       </c>
-      <c r="AC4" s="3">
+      <c r="AC4" s="6">
         <v>11</v>
       </c>
-      <c r="AD4" s="3">
+      <c r="AD4" s="6">
         <v>1</v>
       </c>
-      <c r="AE4" s="3">
+      <c r="AE4" s="6">
         <v>1</v>
       </c>
-      <c r="AF4" s="3"/>
-      <c r="AG4" s="3"/>
-      <c r="AH4" s="3"/>
-      <c r="AI4" s="3"/>
-      <c r="AJ4" s="3"/>
-      <c r="AK4" s="3"/>
-      <c r="AL4" s="3"/>
-      <c r="AM4" s="3"/>
-      <c r="AN4" s="3"/>
-      <c r="AO4" s="3"/>
-      <c r="AP4" s="3"/>
-      <c r="AQ4" s="3"/>
-      <c r="AR4" s="3"/>
-      <c r="AS4" s="3"/>
-      <c r="AT4" s="3"/>
-      <c r="AU4" s="3"/>
-      <c r="AV4" s="3"/>
-      <c r="AW4" s="3"/>
-      <c r="AX4" s="3"/>
-      <c r="AY4" s="3"/>
-      <c r="AZ4" s="3"/>
-      <c r="BA4" s="3"/>
-      <c r="BB4" s="3"/>
-      <c r="BC4" s="3"/>
-      <c r="BD4" s="3"/>
-      <c r="BE4" s="3"/>
-      <c r="BF4" s="3"/>
-      <c r="BG4" s="3"/>
-      <c r="BH4" s="3"/>
-      <c r="BI4" s="3"/>
-      <c r="BJ4" s="3"/>
-      <c r="BK4" s="3"/>
-      <c r="BL4" s="3"/>
-      <c r="BM4" s="3"/>
-      <c r="BN4" s="3"/>
-      <c r="BO4" s="3"/>
-      <c r="BP4" s="3"/>
-      <c r="BQ4" s="3"/>
-      <c r="BR4" s="3"/>
-      <c r="BS4" s="3"/>
-      <c r="BT4" s="3"/>
-      <c r="BU4" s="3"/>
-      <c r="BV4" s="3"/>
-      <c r="BW4" s="3"/>
-      <c r="BX4" s="3"/>
-      <c r="BY4" s="3"/>
-      <c r="BZ4" s="3"/>
-      <c r="CA4" s="3"/>
-      <c r="CB4" s="3"/>
-      <c r="CC4" s="3"/>
-      <c r="CD4" s="3"/>
-      <c r="CE4" s="3"/>
-      <c r="CF4" s="3"/>
-      <c r="CG4" s="3"/>
-      <c r="CH4" s="3"/>
-      <c r="CI4" s="3"/>
-      <c r="CJ4" s="3"/>
-      <c r="CK4" s="3"/>
-      <c r="CL4" s="3"/>
-      <c r="CM4" s="3"/>
-      <c r="CN4" s="3"/>
-      <c r="CO4" s="3"/>
-      <c r="CP4" s="3"/>
-      <c r="CQ4" s="3"/>
-      <c r="CR4" s="3"/>
-      <c r="CS4" s="3"/>
-      <c r="CT4" s="3"/>
-      <c r="CU4" s="3"/>
-      <c r="CV4" s="3"/>
-      <c r="CW4" s="3"/>
-      <c r="CX4" s="3"/>
-      <c r="CY4" s="3"/>
-      <c r="CZ4" s="3"/>
-      <c r="DA4" s="3"/>
-      <c r="DB4" s="3"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6"/>
+      <c r="AI4" s="6"/>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="6"/>
+      <c r="AL4" s="6"/>
+      <c r="AM4" s="6"/>
+      <c r="AN4" s="6"/>
+      <c r="AO4" s="6"/>
+      <c r="AP4" s="6"/>
+      <c r="AQ4" s="6"/>
+      <c r="AR4" s="6"/>
+      <c r="AS4" s="6"/>
+      <c r="AT4" s="6"/>
+      <c r="AU4" s="6"/>
+      <c r="AV4" s="6"/>
+      <c r="AW4" s="6"/>
+      <c r="AX4" s="6"/>
+      <c r="AY4" s="6"/>
+      <c r="AZ4" s="6"/>
+      <c r="BA4" s="6"/>
+      <c r="BB4" s="6"/>
+      <c r="BC4" s="6"/>
+      <c r="BD4" s="6"/>
+      <c r="BE4" s="6"/>
+      <c r="BF4" s="6"/>
+      <c r="BG4" s="6"/>
+      <c r="BH4" s="6"/>
+      <c r="BI4" s="6"/>
+      <c r="BJ4" s="6"/>
+      <c r="BK4" s="6"/>
+      <c r="BL4" s="6"/>
+      <c r="BM4" s="6"/>
+      <c r="BN4" s="6"/>
+      <c r="BO4" s="6"/>
+      <c r="BP4" s="6"/>
+      <c r="BQ4" s="6"/>
+      <c r="BR4" s="6"/>
+      <c r="BS4" s="6"/>
+      <c r="BT4" s="6"/>
+      <c r="BU4" s="6"/>
+      <c r="BV4" s="6"/>
+      <c r="BW4" s="6"/>
+      <c r="BX4" s="6"/>
+      <c r="BY4" s="6"/>
+      <c r="BZ4" s="6"/>
+      <c r="CA4" s="6"/>
+      <c r="CB4" s="6"/>
+      <c r="CC4" s="6"/>
+      <c r="CD4" s="6"/>
+      <c r="CE4" s="6"/>
+      <c r="CF4" s="6"/>
+      <c r="CG4" s="6"/>
+      <c r="CH4" s="6"/>
+      <c r="CI4" s="6"/>
+      <c r="CJ4" s="6"/>
+      <c r="CK4" s="6"/>
+      <c r="CL4" s="6"/>
+      <c r="CM4" s="6"/>
+      <c r="CN4" s="6"/>
+      <c r="CO4" s="6"/>
+      <c r="CP4" s="6"/>
+      <c r="CQ4" s="6"/>
+      <c r="CR4" s="6"/>
+      <c r="CS4" s="6"/>
+      <c r="CT4" s="6"/>
+      <c r="CU4" s="6"/>
+      <c r="CV4" s="6"/>
+      <c r="CW4" s="6"/>
+      <c r="CX4" s="6"/>
+      <c r="CY4" s="6"/>
+      <c r="CZ4" s="6"/>
+      <c r="DA4" s="6"/>
+      <c r="DB4" s="6"/>
     </row>
-    <row r="5" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="11">
         <v>6</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="11">
         <v>5</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="11">
         <v>3</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="11">
         <v>1</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="11">
         <v>1</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="11">
         <v>2</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="11">
         <v>2</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="11">
         <v>2</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="11">
         <v>0</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="11">
         <v>0</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="11">
         <v>20</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="11">
         <v>20</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="11">
         <v>15</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="11">
         <v>2</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5" s="11">
         <v>10</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q5" s="11">
         <v>34</v>
       </c>
-      <c r="R5" s="8">
+      <c r="R5" s="11">
         <v>32</v>
       </c>
-      <c r="S5" s="8">
+      <c r="S5" s="11">
         <v>31</v>
       </c>
-      <c r="T5" s="8">
+      <c r="T5" s="11">
         <v>6</v>
       </c>
-      <c r="U5" s="8">
+      <c r="U5" s="11">
         <v>11</v>
       </c>
-      <c r="V5" s="8">
+      <c r="V5" s="11">
         <v>55</v>
       </c>
-      <c r="W5" s="8">
+      <c r="W5" s="11">
         <v>52</v>
       </c>
-      <c r="X5" s="8">
+      <c r="X5" s="11">
         <v>51</v>
       </c>
-      <c r="Y5" s="8">
+      <c r="Y5" s="11">
         <v>7</v>
       </c>
-      <c r="Z5" s="8">
+      <c r="Z5" s="11">
         <v>16</v>
       </c>
-      <c r="AA5" s="8">
+      <c r="AA5" s="11">
         <v>28</v>
       </c>
-      <c r="AB5" s="8">
+      <c r="AB5" s="11">
         <v>26</v>
       </c>
-      <c r="AC5" s="8">
+      <c r="AC5" s="11">
         <v>25</v>
       </c>
-      <c r="AD5" s="8">
+      <c r="AD5" s="11">
         <v>4</v>
       </c>
-      <c r="AE5" s="8">
+      <c r="AE5" s="11">
         <v>9</v>
       </c>
-      <c r="AF5" s="8"/>
-      <c r="AG5" s="8"/>
-      <c r="AH5" s="8"/>
-      <c r="AI5" s="8"/>
-      <c r="AJ5" s="8"/>
-      <c r="AK5" s="8"/>
-      <c r="AL5" s="8"/>
-      <c r="AM5" s="8"/>
-      <c r="AN5" s="8"/>
-      <c r="AO5" s="8"/>
-      <c r="AP5" s="8"/>
-      <c r="AQ5" s="8"/>
-      <c r="AR5" s="8"/>
-      <c r="AS5" s="8"/>
-      <c r="AT5" s="8"/>
-      <c r="AU5" s="8"/>
-      <c r="AV5" s="8"/>
-      <c r="AW5" s="8"/>
-      <c r="AX5" s="8"/>
-      <c r="AY5" s="8"/>
-      <c r="AZ5" s="8"/>
-      <c r="BA5" s="8"/>
-      <c r="BB5" s="8"/>
-      <c r="BC5" s="8"/>
-      <c r="BD5" s="8"/>
-      <c r="BE5" s="8"/>
-      <c r="BF5" s="8"/>
-      <c r="BG5" s="8"/>
-      <c r="BH5" s="8"/>
-      <c r="BI5" s="8"/>
-      <c r="BJ5" s="8"/>
-      <c r="BK5" s="8"/>
-      <c r="BL5" s="8"/>
-      <c r="BM5" s="8"/>
-      <c r="BN5" s="8"/>
-      <c r="BO5" s="8"/>
-      <c r="BP5" s="8"/>
-      <c r="BQ5" s="8"/>
-      <c r="BR5" s="8"/>
-      <c r="BS5" s="8"/>
-      <c r="BT5" s="8"/>
-      <c r="BU5" s="8"/>
-      <c r="BV5" s="8"/>
-      <c r="BW5" s="8"/>
-      <c r="BX5" s="8"/>
-      <c r="BY5" s="8"/>
-      <c r="BZ5" s="8"/>
-      <c r="CA5" s="8"/>
-      <c r="CB5" s="8"/>
-      <c r="CC5" s="8"/>
-      <c r="CD5" s="8"/>
-      <c r="CE5" s="8"/>
-      <c r="CF5" s="8"/>
-      <c r="CG5" s="8"/>
-      <c r="CH5" s="8"/>
-      <c r="CI5" s="8"/>
-      <c r="CJ5" s="8"/>
-      <c r="CK5" s="8"/>
-      <c r="CL5" s="8"/>
-      <c r="CM5" s="8"/>
-      <c r="CN5" s="8"/>
-      <c r="CO5" s="8"/>
-      <c r="CP5" s="8"/>
-      <c r="CQ5" s="8"/>
-      <c r="CR5" s="8"/>
-      <c r="CS5" s="8"/>
-      <c r="CT5" s="8"/>
-      <c r="CU5" s="8"/>
-      <c r="CV5" s="8"/>
-      <c r="CW5" s="8"/>
-      <c r="CX5" s="8"/>
-      <c r="CY5" s="8"/>
-      <c r="CZ5" s="8"/>
-      <c r="DA5" s="8"/>
-      <c r="DB5" s="8"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+      <c r="BC5" s="11"/>
+      <c r="BD5" s="11"/>
+      <c r="BE5" s="11"/>
+      <c r="BF5" s="11"/>
+      <c r="BG5" s="11"/>
+      <c r="BH5" s="11"/>
+      <c r="BI5" s="11"/>
+      <c r="BJ5" s="11"/>
+      <c r="BK5" s="11"/>
+      <c r="BL5" s="11"/>
+      <c r="BM5" s="11"/>
+      <c r="BN5" s="11"/>
+      <c r="BO5" s="11"/>
+      <c r="BP5" s="11"/>
+      <c r="BQ5" s="11"/>
+      <c r="BR5" s="11"/>
+      <c r="BS5" s="11"/>
+      <c r="BT5" s="11"/>
+      <c r="BU5" s="11"/>
+      <c r="BV5" s="11"/>
+      <c r="BW5" s="11"/>
+      <c r="BX5" s="11"/>
+      <c r="BY5" s="11"/>
+      <c r="BZ5" s="11"/>
+      <c r="CA5" s="11"/>
+      <c r="CB5" s="11"/>
+      <c r="CC5" s="11"/>
+      <c r="CD5" s="11"/>
+      <c r="CE5" s="11"/>
+      <c r="CF5" s="11"/>
+      <c r="CG5" s="11"/>
+      <c r="CH5" s="11"/>
+      <c r="CI5" s="11"/>
+      <c r="CJ5" s="11"/>
+      <c r="CK5" s="11"/>
+      <c r="CL5" s="11"/>
+      <c r="CM5" s="11"/>
+      <c r="CN5" s="11"/>
+      <c r="CO5" s="11"/>
+      <c r="CP5" s="11"/>
+      <c r="CQ5" s="11"/>
+      <c r="CR5" s="11"/>
+      <c r="CS5" s="11"/>
+      <c r="CT5" s="11"/>
+      <c r="CU5" s="11"/>
+      <c r="CV5" s="11"/>
+      <c r="CW5" s="11"/>
+      <c r="CX5" s="11"/>
+      <c r="CY5" s="11"/>
+      <c r="CZ5" s="11"/>
+      <c r="DA5" s="11"/>
+      <c r="DB5" s="11"/>
     </row>
     <row r="6" spans="1:106" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="6">
         <v>0</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>0</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="6">
         <v>0</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="6">
         <v>0</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="6">
         <v>0</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="6">
         <v>0</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="6">
         <v>0</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="6">
         <v>0</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="6">
         <v>0</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="6">
         <v>0</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="6">
         <v>0</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="6">
         <v>0</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="6">
         <v>0</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="6">
         <v>0</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="6">
         <v>0</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="6">
         <v>0</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="6">
         <v>0</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="6">
         <v>0</v>
       </c>
-      <c r="T6" s="3">
+      <c r="T6" s="6">
         <v>0</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U6" s="6">
         <v>0</v>
       </c>
-      <c r="V6" s="3">
+      <c r="V6" s="6">
         <v>0</v>
       </c>
-      <c r="W6" s="3">
+      <c r="W6" s="6">
         <v>0</v>
       </c>
-      <c r="X6" s="3">
+      <c r="X6" s="6">
         <v>0</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="Y6" s="6">
         <v>0</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="Z6" s="6">
         <v>0</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AA6" s="6">
         <v>0</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AB6" s="6">
         <v>0</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AC6" s="6">
         <v>0</v>
       </c>
-      <c r="AD6" s="3">
+      <c r="AD6" s="6">
         <v>0</v>
       </c>
-      <c r="AE6" s="3">
+      <c r="AE6" s="6">
         <v>0</v>
       </c>
-      <c r="AF6" s="3"/>
-      <c r="AG6" s="3"/>
-      <c r="AH6" s="3"/>
-      <c r="AI6" s="3"/>
-      <c r="AJ6" s="3"/>
-      <c r="AK6" s="3"/>
-      <c r="AL6" s="3"/>
-      <c r="AM6" s="3"/>
-      <c r="AN6" s="3"/>
-      <c r="AO6" s="3"/>
-      <c r="AP6" s="3"/>
-      <c r="AQ6" s="3"/>
-      <c r="AR6" s="3"/>
-      <c r="AS6" s="3"/>
-      <c r="AT6" s="3"/>
-      <c r="AU6" s="3"/>
-      <c r="AV6" s="3"/>
-      <c r="AW6" s="3"/>
-      <c r="AX6" s="3"/>
-      <c r="AY6" s="3"/>
-      <c r="AZ6" s="3"/>
-      <c r="BA6" s="3"/>
-      <c r="BB6" s="3"/>
-      <c r="BC6" s="3"/>
-      <c r="BD6" s="3"/>
-      <c r="BE6" s="3"/>
-      <c r="BF6" s="3"/>
-      <c r="BG6" s="3"/>
-      <c r="BH6" s="3"/>
-      <c r="BI6" s="3"/>
-      <c r="BJ6" s="3"/>
-      <c r="BK6" s="3"/>
-      <c r="BL6" s="3"/>
-      <c r="BM6" s="3"/>
-      <c r="BN6" s="3"/>
-      <c r="BO6" s="3"/>
-      <c r="BP6" s="3"/>
-      <c r="BQ6" s="3"/>
-      <c r="BR6" s="3"/>
-      <c r="BS6" s="3"/>
-      <c r="BT6" s="3"/>
-      <c r="BU6" s="3"/>
-      <c r="BV6" s="3"/>
-      <c r="BW6" s="3"/>
-      <c r="BX6" s="3"/>
-      <c r="BY6" s="3"/>
-      <c r="BZ6" s="3"/>
-      <c r="CA6" s="3"/>
-      <c r="CB6" s="3"/>
-      <c r="CC6" s="3"/>
-      <c r="CD6" s="3"/>
-      <c r="CE6" s="3"/>
-      <c r="CF6" s="3"/>
-      <c r="CG6" s="3"/>
-      <c r="CH6" s="3"/>
-      <c r="CI6" s="3"/>
-      <c r="CJ6" s="3"/>
-      <c r="CK6" s="3"/>
-      <c r="CL6" s="3"/>
-      <c r="CM6" s="3"/>
-      <c r="CN6" s="3"/>
-      <c r="CO6" s="3"/>
-      <c r="CP6" s="3"/>
-      <c r="CQ6" s="3"/>
-      <c r="CR6" s="3"/>
-      <c r="CS6" s="3"/>
-      <c r="CT6" s="3"/>
-      <c r="CU6" s="3"/>
-      <c r="CV6" s="3"/>
-      <c r="CW6" s="3"/>
-      <c r="CX6" s="3"/>
-      <c r="CY6" s="3"/>
-      <c r="CZ6" s="3"/>
-      <c r="DA6" s="3"/>
-      <c r="DB6" s="3"/>
+      <c r="AF6" s="6"/>
+      <c r="AG6" s="6"/>
+      <c r="AH6" s="6"/>
+      <c r="AI6" s="6"/>
+      <c r="AJ6" s="6"/>
+      <c r="AK6" s="6"/>
+      <c r="AL6" s="6"/>
+      <c r="AM6" s="6"/>
+      <c r="AN6" s="6"/>
+      <c r="AO6" s="6"/>
+      <c r="AP6" s="6"/>
+      <c r="AQ6" s="6"/>
+      <c r="AR6" s="6"/>
+      <c r="AS6" s="6"/>
+      <c r="AT6" s="6"/>
+      <c r="AU6" s="6"/>
+      <c r="AV6" s="6"/>
+      <c r="AW6" s="6"/>
+      <c r="AX6" s="6"/>
+      <c r="AY6" s="6"/>
+      <c r="AZ6" s="6"/>
+      <c r="BA6" s="6"/>
+      <c r="BB6" s="6"/>
+      <c r="BC6" s="6"/>
+      <c r="BD6" s="6"/>
+      <c r="BE6" s="6"/>
+      <c r="BF6" s="6"/>
+      <c r="BG6" s="6"/>
+      <c r="BH6" s="6"/>
+      <c r="BI6" s="6"/>
+      <c r="BJ6" s="6"/>
+      <c r="BK6" s="6"/>
+      <c r="BL6" s="6"/>
+      <c r="BM6" s="6"/>
+      <c r="BN6" s="6"/>
+      <c r="BO6" s="6"/>
+      <c r="BP6" s="6"/>
+      <c r="BQ6" s="6"/>
+      <c r="BR6" s="6"/>
+      <c r="BS6" s="6"/>
+      <c r="BT6" s="6"/>
+      <c r="BU6" s="6"/>
+      <c r="BV6" s="6"/>
+      <c r="BW6" s="6"/>
+      <c r="BX6" s="6"/>
+      <c r="BY6" s="6"/>
+      <c r="BZ6" s="6"/>
+      <c r="CA6" s="6"/>
+      <c r="CB6" s="6"/>
+      <c r="CC6" s="6"/>
+      <c r="CD6" s="6"/>
+      <c r="CE6" s="6"/>
+      <c r="CF6" s="6"/>
+      <c r="CG6" s="6"/>
+      <c r="CH6" s="6"/>
+      <c r="CI6" s="6"/>
+      <c r="CJ6" s="6"/>
+      <c r="CK6" s="6"/>
+      <c r="CL6" s="6"/>
+      <c r="CM6" s="6"/>
+      <c r="CN6" s="6"/>
+      <c r="CO6" s="6"/>
+      <c r="CP6" s="6"/>
+      <c r="CQ6" s="6"/>
+      <c r="CR6" s="6"/>
+      <c r="CS6" s="6"/>
+      <c r="CT6" s="6"/>
+      <c r="CU6" s="6"/>
+      <c r="CV6" s="6"/>
+      <c r="CW6" s="6"/>
+      <c r="CX6" s="6"/>
+      <c r="CY6" s="6"/>
+      <c r="CZ6" s="6"/>
+      <c r="DA6" s="6"/>
+      <c r="DB6" s="6"/>
     </row>
-    <row r="7" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="11">
         <v>47</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <v>43</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="11">
         <v>39</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <v>3</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="11">
         <v>2</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="11">
         <v>8</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="11">
         <v>8</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="11">
         <v>6</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="11">
         <v>0</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="11">
         <v>0</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="11">
         <v>9</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="11">
         <v>9</v>
       </c>
-      <c r="N7" s="8">
+      <c r="N7" s="11">
         <v>9</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O7" s="11">
         <v>1</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P7" s="11">
         <v>2</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q7" s="11">
         <v>13</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="11">
         <v>13</v>
       </c>
-      <c r="S7" s="8">
+      <c r="S7" s="11">
         <v>12</v>
       </c>
-      <c r="T7" s="8">
+      <c r="T7" s="11">
         <v>3</v>
       </c>
-      <c r="U7" s="8">
+      <c r="U7" s="11">
         <v>4</v>
       </c>
-      <c r="V7" s="8">
+      <c r="V7" s="11">
         <v>17</v>
       </c>
-      <c r="W7" s="8">
+      <c r="W7" s="11">
         <v>17</v>
       </c>
-      <c r="X7" s="8">
+      <c r="X7" s="11">
         <v>16</v>
       </c>
-      <c r="Y7" s="8">
+      <c r="Y7" s="11">
         <v>2</v>
       </c>
-      <c r="Z7" s="8">
+      <c r="Z7" s="11">
         <v>4</v>
       </c>
-      <c r="AA7" s="8">
+      <c r="AA7" s="11">
         <v>9</v>
       </c>
-      <c r="AB7" s="8">
+      <c r="AB7" s="11">
         <v>9</v>
       </c>
-      <c r="AC7" s="8">
+      <c r="AC7" s="11">
         <v>8</v>
       </c>
-      <c r="AD7" s="8">
+      <c r="AD7" s="11">
         <v>1</v>
       </c>
-      <c r="AE7" s="8">
+      <c r="AE7" s="11">
         <v>1</v>
       </c>
-      <c r="AF7" s="8"/>
-      <c r="AG7" s="8"/>
-      <c r="AH7" s="8"/>
-      <c r="AI7" s="8"/>
-      <c r="AJ7" s="8"/>
-      <c r="AK7" s="8"/>
-      <c r="AL7" s="8"/>
-      <c r="AM7" s="8"/>
-      <c r="AN7" s="8"/>
-      <c r="AO7" s="8"/>
-      <c r="AP7" s="8"/>
-      <c r="AQ7" s="8"/>
-      <c r="AR7" s="8"/>
-      <c r="AS7" s="8"/>
-      <c r="AT7" s="8"/>
-      <c r="AU7" s="8"/>
-      <c r="AV7" s="8"/>
-      <c r="AW7" s="8"/>
-      <c r="AX7" s="8"/>
-      <c r="AY7" s="8"/>
-      <c r="AZ7" s="8"/>
-      <c r="BA7" s="8"/>
-      <c r="BB7" s="8"/>
-      <c r="BC7" s="8"/>
-      <c r="BD7" s="8"/>
-      <c r="BE7" s="8"/>
-      <c r="BF7" s="8"/>
-      <c r="BG7" s="8"/>
-      <c r="BH7" s="8"/>
-      <c r="BI7" s="8"/>
-      <c r="BJ7" s="8"/>
-      <c r="BK7" s="8"/>
-      <c r="BL7" s="8"/>
-      <c r="BM7" s="8"/>
-      <c r="BN7" s="8"/>
-      <c r="BO7" s="8"/>
-      <c r="BP7" s="8"/>
-      <c r="BQ7" s="8"/>
-      <c r="BR7" s="8"/>
-      <c r="BS7" s="8"/>
-      <c r="BT7" s="8"/>
-      <c r="BU7" s="8"/>
-      <c r="BV7" s="8"/>
-      <c r="BW7" s="8"/>
-      <c r="BX7" s="8"/>
-      <c r="BY7" s="8"/>
-      <c r="BZ7" s="8"/>
-      <c r="CA7" s="8"/>
-      <c r="CB7" s="8"/>
-      <c r="CC7" s="8"/>
-      <c r="CD7" s="8"/>
-      <c r="CE7" s="8"/>
-      <c r="CF7" s="8"/>
-      <c r="CG7" s="8"/>
-      <c r="CH7" s="8"/>
-      <c r="CI7" s="8"/>
-      <c r="CJ7" s="8"/>
-      <c r="CK7" s="8"/>
-      <c r="CL7" s="8"/>
-      <c r="CM7" s="8"/>
-      <c r="CN7" s="8"/>
-      <c r="CO7" s="8"/>
-      <c r="CP7" s="8"/>
-      <c r="CQ7" s="8"/>
-      <c r="CR7" s="8"/>
-      <c r="CS7" s="8"/>
-      <c r="CT7" s="8"/>
-      <c r="CU7" s="8"/>
-      <c r="CV7" s="8"/>
-      <c r="CW7" s="8"/>
-      <c r="CX7" s="8"/>
-      <c r="CY7" s="8"/>
-      <c r="CZ7" s="8"/>
-      <c r="DA7" s="8"/>
-      <c r="DB7" s="8"/>
+      <c r="AF7" s="11"/>
+      <c r="AG7" s="11"/>
+      <c r="AH7" s="11"/>
+      <c r="AI7" s="11"/>
+      <c r="AJ7" s="11"/>
+      <c r="AK7" s="11"/>
+      <c r="AL7" s="11"/>
+      <c r="AM7" s="11"/>
+      <c r="AN7" s="11"/>
+      <c r="AO7" s="11"/>
+      <c r="AP7" s="11"/>
+      <c r="AQ7" s="11"/>
+      <c r="AR7" s="11"/>
+      <c r="AS7" s="11"/>
+      <c r="AT7" s="11"/>
+      <c r="AU7" s="11"/>
+      <c r="AV7" s="11"/>
+      <c r="AW7" s="11"/>
+      <c r="AX7" s="11"/>
+      <c r="AY7" s="11"/>
+      <c r="AZ7" s="11"/>
+      <c r="BA7" s="11"/>
+      <c r="BB7" s="11"/>
+      <c r="BC7" s="11"/>
+      <c r="BD7" s="11"/>
+      <c r="BE7" s="11"/>
+      <c r="BF7" s="11"/>
+      <c r="BG7" s="11"/>
+      <c r="BH7" s="11"/>
+      <c r="BI7" s="11"/>
+      <c r="BJ7" s="11"/>
+      <c r="BK7" s="11"/>
+      <c r="BL7" s="11"/>
+      <c r="BM7" s="11"/>
+      <c r="BN7" s="11"/>
+      <c r="BO7" s="11"/>
+      <c r="BP7" s="11"/>
+      <c r="BQ7" s="11"/>
+      <c r="BR7" s="11"/>
+      <c r="BS7" s="11"/>
+      <c r="BT7" s="11"/>
+      <c r="BU7" s="11"/>
+      <c r="BV7" s="11"/>
+      <c r="BW7" s="11"/>
+      <c r="BX7" s="11"/>
+      <c r="BY7" s="11"/>
+      <c r="BZ7" s="11"/>
+      <c r="CA7" s="11"/>
+      <c r="CB7" s="11"/>
+      <c r="CC7" s="11"/>
+      <c r="CD7" s="11"/>
+      <c r="CE7" s="11"/>
+      <c r="CF7" s="11"/>
+      <c r="CG7" s="11"/>
+      <c r="CH7" s="11"/>
+      <c r="CI7" s="11"/>
+      <c r="CJ7" s="11"/>
+      <c r="CK7" s="11"/>
+      <c r="CL7" s="11"/>
+      <c r="CM7" s="11"/>
+      <c r="CN7" s="11"/>
+      <c r="CO7" s="11"/>
+      <c r="CP7" s="11"/>
+      <c r="CQ7" s="11"/>
+      <c r="CR7" s="11"/>
+      <c r="CS7" s="11"/>
+      <c r="CT7" s="11"/>
+      <c r="CU7" s="11"/>
+      <c r="CV7" s="11"/>
+      <c r="CW7" s="11"/>
+      <c r="CX7" s="11"/>
+      <c r="CY7" s="11"/>
+      <c r="CZ7" s="11"/>
+      <c r="DA7" s="11"/>
+      <c r="DB7" s="11"/>
     </row>
-    <row r="8" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="11">
         <v>27</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="11">
         <v>26</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="11">
         <v>22</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="11">
         <v>2</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="11">
         <v>10</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="11">
         <v>6</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="11">
         <v>6</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="11">
         <v>6</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="11">
         <v>0</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="11">
         <v>2</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="11">
         <v>10</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="11">
         <v>10</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="11">
         <v>9</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="11">
         <v>1</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="11">
         <v>1</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="Q8" s="11">
         <v>12</v>
       </c>
-      <c r="R8" s="8">
+      <c r="R8" s="11">
         <v>11</v>
       </c>
-      <c r="S8" s="8">
+      <c r="S8" s="11">
         <v>11</v>
       </c>
-      <c r="T8" s="8">
+      <c r="T8" s="11">
         <v>2</v>
       </c>
-      <c r="U8" s="8">
+      <c r="U8" s="11">
         <v>2</v>
       </c>
-      <c r="V8" s="8">
+      <c r="V8" s="11">
         <v>12</v>
       </c>
-      <c r="W8" s="8">
+      <c r="W8" s="11">
         <v>11</v>
       </c>
-      <c r="X8" s="8">
+      <c r="X8" s="11">
         <v>11</v>
       </c>
-      <c r="Y8" s="8">
+      <c r="Y8" s="11">
         <v>2</v>
       </c>
-      <c r="Z8" s="8">
+      <c r="Z8" s="11">
         <v>2</v>
       </c>
-      <c r="AA8" s="8">
+      <c r="AA8" s="11">
         <v>4</v>
       </c>
-      <c r="AB8" s="8">
+      <c r="AB8" s="11">
         <v>4</v>
       </c>
-      <c r="AC8" s="8">
+      <c r="AC8" s="11">
         <v>4</v>
       </c>
-      <c r="AD8" s="8">
+      <c r="AD8" s="11">
         <v>1</v>
       </c>
-      <c r="AE8" s="8">
+      <c r="AE8" s="11">
         <v>1</v>
       </c>
-      <c r="AF8" s="8"/>
-      <c r="AG8" s="8"/>
-      <c r="AH8" s="8"/>
-      <c r="AI8" s="8"/>
-      <c r="AJ8" s="8"/>
-      <c r="AK8" s="8"/>
-      <c r="AL8" s="8"/>
-      <c r="AM8" s="8"/>
-      <c r="AN8" s="8"/>
-      <c r="AO8" s="8"/>
-      <c r="AP8" s="8"/>
-      <c r="AQ8" s="8"/>
-      <c r="AR8" s="8"/>
-      <c r="AS8" s="8"/>
-      <c r="AT8" s="8"/>
-      <c r="AU8" s="8"/>
-      <c r="AV8" s="8"/>
-      <c r="AW8" s="8"/>
-      <c r="AX8" s="8"/>
-      <c r="AY8" s="8"/>
-      <c r="AZ8" s="8"/>
-      <c r="BA8" s="8"/>
-      <c r="BB8" s="8"/>
-      <c r="BC8" s="8"/>
-      <c r="BD8" s="8"/>
-      <c r="BE8" s="8"/>
-      <c r="BF8" s="8"/>
-      <c r="BG8" s="8"/>
-      <c r="BH8" s="8"/>
-      <c r="BI8" s="8"/>
-      <c r="BJ8" s="8"/>
-      <c r="BK8" s="8"/>
-      <c r="BL8" s="8"/>
-      <c r="BM8" s="8"/>
-      <c r="BN8" s="8"/>
-      <c r="BO8" s="8"/>
-      <c r="BP8" s="8"/>
-      <c r="BQ8" s="8"/>
-      <c r="BR8" s="8"/>
-      <c r="BS8" s="8"/>
-      <c r="BT8" s="8"/>
-      <c r="BU8" s="8"/>
-      <c r="BV8" s="8"/>
-      <c r="BW8" s="8"/>
-      <c r="BX8" s="8"/>
-      <c r="BY8" s="8"/>
-      <c r="BZ8" s="8"/>
-      <c r="CA8" s="8"/>
-      <c r="CB8" s="8"/>
-      <c r="CC8" s="8"/>
-      <c r="CD8" s="8"/>
-      <c r="CE8" s="8"/>
-      <c r="CF8" s="8"/>
-      <c r="CG8" s="8"/>
-      <c r="CH8" s="8"/>
-      <c r="CI8" s="8"/>
-      <c r="CJ8" s="8"/>
-      <c r="CK8" s="8"/>
-      <c r="CL8" s="8"/>
-      <c r="CM8" s="8"/>
-      <c r="CN8" s="8"/>
-      <c r="CO8" s="8"/>
-      <c r="CP8" s="8"/>
-      <c r="CQ8" s="8"/>
-      <c r="CR8" s="8"/>
-      <c r="CS8" s="8"/>
-      <c r="CT8" s="8"/>
-      <c r="CU8" s="8"/>
-      <c r="CV8" s="8"/>
-      <c r="CW8" s="8"/>
-      <c r="CX8" s="8"/>
-      <c r="CY8" s="8"/>
-      <c r="CZ8" s="8"/>
-      <c r="DA8" s="8"/>
-      <c r="DB8" s="8"/>
+      <c r="AF8" s="11"/>
+      <c r="AG8" s="11"/>
+      <c r="AH8" s="11"/>
+      <c r="AI8" s="11"/>
+      <c r="AJ8" s="11"/>
+      <c r="AK8" s="11"/>
+      <c r="AL8" s="11"/>
+      <c r="AM8" s="11"/>
+      <c r="AN8" s="11"/>
+      <c r="AO8" s="11"/>
+      <c r="AP8" s="11"/>
+      <c r="AQ8" s="11"/>
+      <c r="AR8" s="11"/>
+      <c r="AS8" s="11"/>
+      <c r="AT8" s="11"/>
+      <c r="AU8" s="11"/>
+      <c r="AV8" s="11"/>
+      <c r="AW8" s="11"/>
+      <c r="AX8" s="11"/>
+      <c r="AY8" s="11"/>
+      <c r="AZ8" s="11"/>
+      <c r="BA8" s="11"/>
+      <c r="BB8" s="11"/>
+      <c r="BC8" s="11"/>
+      <c r="BD8" s="11"/>
+      <c r="BE8" s="11"/>
+      <c r="BF8" s="11"/>
+      <c r="BG8" s="11"/>
+      <c r="BH8" s="11"/>
+      <c r="BI8" s="11"/>
+      <c r="BJ8" s="11"/>
+      <c r="BK8" s="11"/>
+      <c r="BL8" s="11"/>
+      <c r="BM8" s="11"/>
+      <c r="BN8" s="11"/>
+      <c r="BO8" s="11"/>
+      <c r="BP8" s="11"/>
+      <c r="BQ8" s="11"/>
+      <c r="BR8" s="11"/>
+      <c r="BS8" s="11"/>
+      <c r="BT8" s="11"/>
+      <c r="BU8" s="11"/>
+      <c r="BV8" s="11"/>
+      <c r="BW8" s="11"/>
+      <c r="BX8" s="11"/>
+      <c r="BY8" s="11"/>
+      <c r="BZ8" s="11"/>
+      <c r="CA8" s="11"/>
+      <c r="CB8" s="11"/>
+      <c r="CC8" s="11"/>
+      <c r="CD8" s="11"/>
+      <c r="CE8" s="11"/>
+      <c r="CF8" s="11"/>
+      <c r="CG8" s="11"/>
+      <c r="CH8" s="11"/>
+      <c r="CI8" s="11"/>
+      <c r="CJ8" s="11"/>
+      <c r="CK8" s="11"/>
+      <c r="CL8" s="11"/>
+      <c r="CM8" s="11"/>
+      <c r="CN8" s="11"/>
+      <c r="CO8" s="11"/>
+      <c r="CP8" s="11"/>
+      <c r="CQ8" s="11"/>
+      <c r="CR8" s="11"/>
+      <c r="CS8" s="11"/>
+      <c r="CT8" s="11"/>
+      <c r="CU8" s="11"/>
+      <c r="CV8" s="11"/>
+      <c r="CW8" s="11"/>
+      <c r="CX8" s="11"/>
+      <c r="CY8" s="11"/>
+      <c r="CZ8" s="11"/>
+      <c r="DA8" s="11"/>
+      <c r="DB8" s="11"/>
     </row>
-    <row r="9" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="11">
         <v>31</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="11">
         <v>30</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="11">
         <v>27</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="11">
         <v>1</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="11">
         <v>8</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="11">
         <v>8</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="11">
         <v>8</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="11">
         <v>8</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="11">
         <v>2</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="11">
         <v>2</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="11">
         <v>12</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="11">
         <v>12</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="11">
         <v>12</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="11">
         <v>0</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="11">
         <v>1</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="11">
         <v>15</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="11">
         <v>15</v>
       </c>
-      <c r="S9" s="8">
+      <c r="S9" s="11">
         <v>15</v>
       </c>
-      <c r="T9" s="8">
+      <c r="T9" s="11">
         <v>1</v>
       </c>
-      <c r="U9" s="8">
+      <c r="U9" s="11">
         <v>1</v>
       </c>
-      <c r="V9" s="8">
+      <c r="V9" s="11">
         <v>15</v>
       </c>
-      <c r="W9" s="8">
+      <c r="W9" s="11">
         <v>15</v>
       </c>
-      <c r="X9" s="8">
+      <c r="X9" s="11">
         <v>15</v>
       </c>
-      <c r="Y9" s="8">
+      <c r="Y9" s="11">
         <v>1</v>
       </c>
-      <c r="Z9" s="8">
+      <c r="Z9" s="11">
         <v>1</v>
       </c>
-      <c r="AA9" s="8">
+      <c r="AA9" s="11">
         <v>2</v>
       </c>
-      <c r="AB9" s="8">
+      <c r="AB9" s="11">
         <v>2</v>
       </c>
-      <c r="AC9" s="8">
+      <c r="AC9" s="11">
         <v>2</v>
       </c>
-      <c r="AD9" s="8">
+      <c r="AD9" s="11">
         <v>0</v>
       </c>
-      <c r="AE9" s="8">
+      <c r="AE9" s="11">
         <v>1</v>
       </c>
-      <c r="AF9" s="8"/>
-      <c r="AG9" s="8"/>
-      <c r="AH9" s="8"/>
-      <c r="AI9" s="8"/>
-      <c r="AJ9" s="8"/>
-      <c r="AK9" s="8"/>
-      <c r="AL9" s="8"/>
-      <c r="AM9" s="8"/>
-      <c r="AN9" s="8"/>
-      <c r="AO9" s="8"/>
-      <c r="AP9" s="8"/>
-      <c r="AQ9" s="8"/>
-      <c r="AR9" s="8"/>
-      <c r="AS9" s="8"/>
-      <c r="AT9" s="8"/>
-      <c r="AU9" s="8"/>
-      <c r="AV9" s="8"/>
-      <c r="AW9" s="8"/>
-      <c r="AX9" s="8"/>
-      <c r="AY9" s="8"/>
-      <c r="AZ9" s="8"/>
-      <c r="BA9" s="8"/>
-      <c r="BB9" s="8"/>
-      <c r="BC9" s="8"/>
-      <c r="BD9" s="8"/>
-      <c r="BE9" s="8"/>
-      <c r="BF9" s="8"/>
-      <c r="BG9" s="8"/>
-      <c r="BH9" s="8"/>
-      <c r="BI9" s="8"/>
-      <c r="BJ9" s="8"/>
-      <c r="BK9" s="8"/>
-      <c r="BL9" s="8"/>
-      <c r="BM9" s="8"/>
-      <c r="BN9" s="8"/>
-      <c r="BO9" s="8"/>
-      <c r="BP9" s="8"/>
-      <c r="BQ9" s="8"/>
-      <c r="BR9" s="8"/>
-      <c r="BS9" s="8"/>
-      <c r="BT9" s="8"/>
-      <c r="BU9" s="8"/>
-      <c r="BV9" s="8"/>
-      <c r="BW9" s="8"/>
-      <c r="BX9" s="8"/>
-      <c r="BY9" s="8"/>
-      <c r="BZ9" s="8"/>
-      <c r="CA9" s="8"/>
-      <c r="CB9" s="8"/>
-      <c r="CC9" s="8"/>
-      <c r="CD9" s="8"/>
-      <c r="CE9" s="8"/>
-      <c r="CF9" s="8"/>
-      <c r="CG9" s="8"/>
-      <c r="CH9" s="8"/>
-      <c r="CI9" s="8"/>
-      <c r="CJ9" s="8"/>
-      <c r="CK9" s="8"/>
-      <c r="CL9" s="8"/>
-      <c r="CM9" s="8"/>
-      <c r="CN9" s="8"/>
-      <c r="CO9" s="8"/>
-      <c r="CP9" s="8"/>
-      <c r="CQ9" s="8"/>
-      <c r="CR9" s="8"/>
-      <c r="CS9" s="8"/>
-      <c r="CT9" s="8"/>
-      <c r="CU9" s="8"/>
-      <c r="CV9" s="8"/>
-      <c r="CW9" s="8"/>
-      <c r="CX9" s="8"/>
-      <c r="CY9" s="8"/>
-      <c r="CZ9" s="8"/>
-      <c r="DA9" s="8"/>
-      <c r="DB9" s="8"/>
+      <c r="AF9" s="11"/>
+      <c r="AG9" s="11"/>
+      <c r="AH9" s="11"/>
+      <c r="AI9" s="11"/>
+      <c r="AJ9" s="11"/>
+      <c r="AK9" s="11"/>
+      <c r="AL9" s="11"/>
+      <c r="AM9" s="11"/>
+      <c r="AN9" s="11"/>
+      <c r="AO9" s="11"/>
+      <c r="AP9" s="11"/>
+      <c r="AQ9" s="11"/>
+      <c r="AR9" s="11"/>
+      <c r="AS9" s="11"/>
+      <c r="AT9" s="11"/>
+      <c r="AU9" s="11"/>
+      <c r="AV9" s="11"/>
+      <c r="AW9" s="11"/>
+      <c r="AX9" s="11"/>
+      <c r="AY9" s="11"/>
+      <c r="AZ9" s="11"/>
+      <c r="BA9" s="11"/>
+      <c r="BB9" s="11"/>
+      <c r="BC9" s="11"/>
+      <c r="BD9" s="11"/>
+      <c r="BE9" s="11"/>
+      <c r="BF9" s="11"/>
+      <c r="BG9" s="11"/>
+      <c r="BH9" s="11"/>
+      <c r="BI9" s="11"/>
+      <c r="BJ9" s="11"/>
+      <c r="BK9" s="11"/>
+      <c r="BL9" s="11"/>
+      <c r="BM9" s="11"/>
+      <c r="BN9" s="11"/>
+      <c r="BO9" s="11"/>
+      <c r="BP9" s="11"/>
+      <c r="BQ9" s="11"/>
+      <c r="BR9" s="11"/>
+      <c r="BS9" s="11"/>
+      <c r="BT9" s="11"/>
+      <c r="BU9" s="11"/>
+      <c r="BV9" s="11"/>
+      <c r="BW9" s="11"/>
+      <c r="BX9" s="11"/>
+      <c r="BY9" s="11"/>
+      <c r="BZ9" s="11"/>
+      <c r="CA9" s="11"/>
+      <c r="CB9" s="11"/>
+      <c r="CC9" s="11"/>
+      <c r="CD9" s="11"/>
+      <c r="CE9" s="11"/>
+      <c r="CF9" s="11"/>
+      <c r="CG9" s="11"/>
+      <c r="CH9" s="11"/>
+      <c r="CI9" s="11"/>
+      <c r="CJ9" s="11"/>
+      <c r="CK9" s="11"/>
+      <c r="CL9" s="11"/>
+      <c r="CM9" s="11"/>
+      <c r="CN9" s="11"/>
+      <c r="CO9" s="11"/>
+      <c r="CP9" s="11"/>
+      <c r="CQ9" s="11"/>
+      <c r="CR9" s="11"/>
+      <c r="CS9" s="11"/>
+      <c r="CT9" s="11"/>
+      <c r="CU9" s="11"/>
+      <c r="CV9" s="11"/>
+      <c r="CW9" s="11"/>
+      <c r="CX9" s="11"/>
+      <c r="CY9" s="11"/>
+      <c r="CZ9" s="11"/>
+      <c r="DA9" s="11"/>
+      <c r="DB9" s="11"/>
     </row>
     <row r="10" spans="1:106" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="6">
         <f>SUM(B3:B9)</f>
         <v>133</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="6">
         <f t="shared" ref="C10:Q10" si="0">SUM(C3:C9)</f>
         <v>113</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="6">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="6">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="6">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="6">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="6">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="6">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="6">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="6">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="6">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="6">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="6">
         <f t="shared" ref="R10" si="1">SUM(R3:R9)</f>
         <v>98</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="6">
         <f t="shared" ref="S10" si="2">SUM(S3:S9)</f>
         <v>92</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="6">
         <f t="shared" ref="T10" si="3">SUM(T3:T9)</f>
         <v>16</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="6">
         <f t="shared" ref="U10" si="4">SUM(U3:U9)</f>
         <v>23</v>
       </c>
-      <c r="V10" s="3">
+      <c r="V10" s="6">
         <f t="shared" ref="V10" si="5">SUM(V3:V9)</f>
         <v>123</v>
       </c>
-      <c r="W10" s="3">
+      <c r="W10" s="6">
         <f t="shared" ref="W10" si="6">SUM(W3:W9)</f>
         <v>118</v>
       </c>
-      <c r="X10" s="3">
+      <c r="X10" s="6">
         <f t="shared" ref="X10" si="7">SUM(X3:X9)</f>
         <v>114</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="6">
         <f t="shared" ref="Y10" si="8">SUM(Y3:Y9)</f>
         <v>15</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="6">
         <f t="shared" ref="Z10" si="9">SUM(Z3:Z9)</f>
         <v>27</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="6">
         <f t="shared" ref="AA10" si="10">SUM(AA3:AA9)</f>
         <v>60</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="6">
         <f t="shared" ref="AB10" si="11">SUM(AB3:AB9)</f>
         <v>56</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="6">
         <f t="shared" ref="AC10" si="12">SUM(AC3:AC9)</f>
         <v>55</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AD10" s="6">
         <f t="shared" ref="AD10" si="13">SUM(AD3:AD9)</f>
         <v>8</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AE10" s="6">
         <f t="shared" ref="AE10:AF10" si="14">SUM(AE3:AE9)</f>
         <v>14</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AF10" s="6">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AG10" s="6">
         <f t="shared" ref="AG10" si="15">SUM(AG3:AG9)</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AH10" s="6">
         <f t="shared" ref="AH10" si="16">SUM(AH3:AH9)</f>
         <v>0</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AI10" s="6">
         <f t="shared" ref="AI10" si="17">SUM(AI3:AI9)</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AJ10" s="6">
         <f t="shared" ref="AJ10" si="18">SUM(AJ3:AJ9)</f>
         <v>0</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AK10" s="6">
         <f t="shared" ref="AK10" si="19">SUM(AK3:AK9)</f>
         <v>0</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AL10" s="6">
         <f t="shared" ref="AL10" si="20">SUM(AL3:AL9)</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AM10" s="6">
         <f t="shared" ref="AM10" si="21">SUM(AM3:AM9)</f>
         <v>0</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AN10" s="6">
         <f t="shared" ref="AN10" si="22">SUM(AN3:AN9)</f>
         <v>0</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AO10" s="6">
         <f t="shared" ref="AO10" si="23">SUM(AO3:AO9)</f>
         <v>0</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AP10" s="6">
         <f t="shared" ref="AP10" si="24">SUM(AP3:AP9)</f>
         <v>0</v>
       </c>
-      <c r="AQ10" s="3">
+      <c r="AQ10" s="6">
         <f t="shared" ref="AQ10" si="25">SUM(AQ3:AQ9)</f>
         <v>0</v>
       </c>
-      <c r="AR10" s="3">
+      <c r="AR10" s="6">
         <f t="shared" ref="AR10" si="26">SUM(AR3:AR9)</f>
         <v>0</v>
       </c>
-      <c r="AS10" s="3">
+      <c r="AS10" s="6">
         <f t="shared" ref="AS10" si="27">SUM(AS3:AS9)</f>
         <v>0</v>
       </c>
-      <c r="AT10" s="3">
+      <c r="AT10" s="6">
         <f t="shared" ref="AT10:AU10" si="28">SUM(AT3:AT9)</f>
         <v>0</v>
       </c>
-      <c r="AU10" s="3">
+      <c r="AU10" s="6">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AV10" s="3">
+      <c r="AV10" s="6">
         <f t="shared" ref="AV10" si="29">SUM(AV3:AV9)</f>
         <v>0</v>
       </c>
-      <c r="AW10" s="3">
+      <c r="AW10" s="6">
         <f t="shared" ref="AW10" si="30">SUM(AW3:AW9)</f>
         <v>0</v>
       </c>
-      <c r="AX10" s="3">
+      <c r="AX10" s="6">
         <f t="shared" ref="AX10" si="31">SUM(AX3:AX9)</f>
         <v>0</v>
       </c>
-      <c r="AY10" s="3">
+      <c r="AY10" s="6">
         <f t="shared" ref="AY10" si="32">SUM(AY3:AY9)</f>
         <v>0</v>
       </c>
-      <c r="AZ10" s="3">
+      <c r="AZ10" s="6">
         <f t="shared" ref="AZ10" si="33">SUM(AZ3:AZ9)</f>
         <v>0</v>
       </c>
-      <c r="BA10" s="3">
+      <c r="BA10" s="6">
         <f t="shared" ref="BA10" si="34">SUM(BA3:BA9)</f>
         <v>0</v>
       </c>
-      <c r="BB10" s="3">
+      <c r="BB10" s="6">
         <f t="shared" ref="BB10" si="35">SUM(BB3:BB9)</f>
         <v>0</v>
       </c>
-      <c r="BC10" s="3">
+      <c r="BC10" s="6">
         <f t="shared" ref="BC10" si="36">SUM(BC3:BC9)</f>
         <v>0</v>
       </c>
-      <c r="BD10" s="3">
+      <c r="BD10" s="6">
         <f t="shared" ref="BD10" si="37">SUM(BD3:BD9)</f>
         <v>0</v>
       </c>
-      <c r="BE10" s="3">
+      <c r="BE10" s="6">
         <f t="shared" ref="BE10" si="38">SUM(BE3:BE9)</f>
         <v>0</v>
       </c>
-      <c r="BF10" s="3">
+      <c r="BF10" s="6">
         <f t="shared" ref="BF10" si="39">SUM(BF3:BF9)</f>
         <v>0</v>
       </c>
-      <c r="BG10" s="3">
+      <c r="BG10" s="6">
         <f t="shared" ref="BG10" si="40">SUM(BG3:BG9)</f>
         <v>0</v>
       </c>
-      <c r="BH10" s="3">
+      <c r="BH10" s="6">
         <f t="shared" ref="BH10" si="41">SUM(BH3:BH9)</f>
         <v>0</v>
       </c>
-      <c r="BI10" s="3">
+      <c r="BI10" s="6">
         <f t="shared" ref="BI10:BJ10" si="42">SUM(BI3:BI9)</f>
         <v>0</v>
       </c>
-      <c r="BJ10" s="3">
+      <c r="BJ10" s="6">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="BK10" s="3">
+      <c r="BK10" s="6">
         <f t="shared" ref="BK10" si="43">SUM(BK3:BK9)</f>
         <v>0</v>
       </c>
-      <c r="BL10" s="3">
+      <c r="BL10" s="6">
         <f t="shared" ref="BL10" si="44">SUM(BL3:BL9)</f>
         <v>0</v>
       </c>
-      <c r="BM10" s="3">
+      <c r="BM10" s="6">
         <f t="shared" ref="BM10" si="45">SUM(BM3:BM9)</f>
         <v>0</v>
       </c>
-      <c r="BN10" s="3">
+      <c r="BN10" s="6">
         <f t="shared" ref="BN10" si="46">SUM(BN3:BN9)</f>
         <v>0</v>
       </c>
-      <c r="BO10" s="3">
+      <c r="BO10" s="6">
         <f t="shared" ref="BO10" si="47">SUM(BO3:BO9)</f>
         <v>0</v>
       </c>
-      <c r="BP10" s="3">
+      <c r="BP10" s="6">
         <f t="shared" ref="BP10" si="48">SUM(BP3:BP9)</f>
         <v>0</v>
       </c>
-      <c r="BQ10" s="3">
+      <c r="BQ10" s="6">
         <f t="shared" ref="BQ10" si="49">SUM(BQ3:BQ9)</f>
         <v>0</v>
       </c>
-      <c r="BR10" s="3">
+      <c r="BR10" s="6">
         <f t="shared" ref="BR10" si="50">SUM(BR3:BR9)</f>
         <v>0</v>
       </c>
-      <c r="BS10" s="3">
+      <c r="BS10" s="6">
         <f t="shared" ref="BS10" si="51">SUM(BS3:BS9)</f>
         <v>0</v>
       </c>
-      <c r="BT10" s="3">
+      <c r="BT10" s="6">
         <f t="shared" ref="BT10" si="52">SUM(BT3:BT9)</f>
         <v>0</v>
       </c>
-      <c r="BU10" s="3">
+      <c r="BU10" s="6">
         <f t="shared" ref="BU10" si="53">SUM(BU3:BU9)</f>
         <v>0</v>
       </c>
-      <c r="BV10" s="3">
+      <c r="BV10" s="6">
         <f t="shared" ref="BV10" si="54">SUM(BV3:BV9)</f>
         <v>0</v>
       </c>
-      <c r="BW10" s="3">
+      <c r="BW10" s="6">
         <f t="shared" ref="BW10" si="55">SUM(BW3:BW9)</f>
         <v>0</v>
       </c>
-      <c r="BX10" s="3">
+      <c r="BX10" s="6">
         <f t="shared" ref="BX10" si="56">SUM(BX3:BX9)</f>
         <v>0</v>
       </c>
-      <c r="BY10" s="3">
+      <c r="BY10" s="6">
         <f t="shared" ref="BY10" si="57">SUM(BY3:BY9)</f>
         <v>0</v>
       </c>
-      <c r="BZ10" s="3">
+      <c r="BZ10" s="6">
         <f t="shared" ref="BZ10" si="58">SUM(BZ3:BZ9)</f>
         <v>0</v>
       </c>
-      <c r="CA10" s="3">
+      <c r="CA10" s="6">
         <f t="shared" ref="CA10" si="59">SUM(CA3:CA9)</f>
         <v>0</v>
       </c>
-      <c r="CB10" s="3">
+      <c r="CB10" s="6">
         <f t="shared" ref="CB10" si="60">SUM(CB3:CB9)</f>
         <v>0</v>
       </c>
-      <c r="CC10" s="3">
+      <c r="CC10" s="6">
         <f t="shared" ref="CC10" si="61">SUM(CC3:CC9)</f>
         <v>0</v>
       </c>
-      <c r="CD10" s="3">
+      <c r="CD10" s="6">
         <f t="shared" ref="CD10" si="62">SUM(CD3:CD9)</f>
         <v>0</v>
       </c>
-      <c r="CE10" s="3">
+      <c r="CE10" s="6">
         <f t="shared" ref="CE10" si="63">SUM(CE3:CE9)</f>
         <v>0</v>
       </c>
-      <c r="CF10" s="3">
+      <c r="CF10" s="6">
         <f t="shared" ref="CF10" si="64">SUM(CF3:CF9)</f>
         <v>0</v>
       </c>
-      <c r="CG10" s="3">
+      <c r="CG10" s="6">
         <f t="shared" ref="CG10" si="65">SUM(CG3:CG9)</f>
         <v>0</v>
       </c>
-      <c r="CH10" s="3">
+      <c r="CH10" s="6">
         <f t="shared" ref="CH10" si="66">SUM(CH3:CH9)</f>
         <v>0</v>
       </c>
-      <c r="CI10" s="3">
+      <c r="CI10" s="6">
         <f t="shared" ref="CI10" si="67">SUM(CI3:CI9)</f>
         <v>0</v>
       </c>
-      <c r="CJ10" s="3">
+      <c r="CJ10" s="6">
         <f t="shared" ref="CJ10" si="68">SUM(CJ3:CJ9)</f>
         <v>0</v>
       </c>
-      <c r="CK10" s="3">
+      <c r="CK10" s="6">
         <f t="shared" ref="CK10" si="69">SUM(CK3:CK9)</f>
         <v>0</v>
       </c>
-      <c r="CL10" s="3">
+      <c r="CL10" s="6">
         <f t="shared" ref="CL10" si="70">SUM(CL3:CL9)</f>
         <v>0</v>
       </c>
-      <c r="CM10" s="3">
+      <c r="CM10" s="6">
         <f t="shared" ref="CM10" si="71">SUM(CM3:CM9)</f>
         <v>0</v>
       </c>
-      <c r="CN10" s="3">
+      <c r="CN10" s="6">
         <f t="shared" ref="CN10" si="72">SUM(CN3:CN9)</f>
         <v>0</v>
       </c>
-      <c r="CO10" s="3">
+      <c r="CO10" s="6">
         <f t="shared" ref="CO10" si="73">SUM(CO3:CO9)</f>
         <v>0</v>
       </c>
-      <c r="CP10" s="3">
+      <c r="CP10" s="6">
         <f t="shared" ref="CP10" si="74">SUM(CP3:CP9)</f>
         <v>0</v>
       </c>
-      <c r="CQ10" s="3">
+      <c r="CQ10" s="6">
         <f t="shared" ref="CQ10" si="75">SUM(CQ3:CQ9)</f>
         <v>0</v>
       </c>
-      <c r="CR10" s="3">
+      <c r="CR10" s="6">
         <f t="shared" ref="CR10" si="76">SUM(CR3:CR9)</f>
         <v>0</v>
       </c>
-      <c r="CS10" s="3">
+      <c r="CS10" s="6">
         <f t="shared" ref="CS10" si="77">SUM(CS3:CS9)</f>
         <v>0</v>
       </c>
-      <c r="CT10" s="3">
+      <c r="CT10" s="6">
         <f t="shared" ref="CT10" si="78">SUM(CT3:CT9)</f>
         <v>0</v>
       </c>
-      <c r="CU10" s="3">
+      <c r="CU10" s="6">
         <f t="shared" ref="CU10" si="79">SUM(CU3:CU9)</f>
         <v>0</v>
       </c>
-      <c r="CV10" s="3">
+      <c r="CV10" s="6">
         <f t="shared" ref="CV10" si="80">SUM(CV3:CV9)</f>
         <v>0</v>
       </c>
-      <c r="CW10" s="3">
+      <c r="CW10" s="6">
         <f t="shared" ref="CW10" si="81">SUM(CW3:CW9)</f>
         <v>0</v>
       </c>
-      <c r="CX10" s="3">
+      <c r="CX10" s="6">
         <f t="shared" ref="CX10" si="82">SUM(CX3:CX9)</f>
         <v>0</v>
       </c>
-      <c r="CY10" s="3">
+      <c r="CY10" s="6">
         <f t="shared" ref="CY10" si="83">SUM(CY3:CY9)</f>
         <v>0</v>
       </c>
-      <c r="CZ10" s="3">
+      <c r="CZ10" s="6">
         <f t="shared" ref="CZ10" si="84">SUM(CZ3:CZ9)</f>
         <v>0</v>
       </c>
-      <c r="DA10" s="3">
+      <c r="DA10" s="6">
         <f t="shared" ref="DA10" si="85">SUM(DA3:DA9)</f>
         <v>0</v>
       </c>
-      <c r="DB10" s="3">
+      <c r="DB10" s="6">
         <f t="shared" ref="DB10" si="86">SUM(DB3:DB9)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="CN1:CR1"/>
+    <mergeCell ref="CS1:CW1"/>
+    <mergeCell ref="CX1:DB1"/>
+    <mergeCell ref="BJ1:BN1"/>
+    <mergeCell ref="BO1:BS1"/>
+    <mergeCell ref="BT1:BX1"/>
+    <mergeCell ref="BY1:CC1"/>
+    <mergeCell ref="CD1:CH1"/>
+    <mergeCell ref="CI1:CM1"/>
     <mergeCell ref="BE1:BI1"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:K1"/>
@@ -15562,15 +15794,6 @@
     <mergeCell ref="AP1:AT1"/>
     <mergeCell ref="AU1:AY1"/>
     <mergeCell ref="AZ1:BD1"/>
-    <mergeCell ref="CN1:CR1"/>
-    <mergeCell ref="CS1:CW1"/>
-    <mergeCell ref="CX1:DB1"/>
-    <mergeCell ref="BJ1:BN1"/>
-    <mergeCell ref="BO1:BS1"/>
-    <mergeCell ref="BT1:BX1"/>
-    <mergeCell ref="BY1:CC1"/>
-    <mergeCell ref="CD1:CH1"/>
-    <mergeCell ref="CI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15752,193 +15975,193 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A1" s="11"/>
-      <c r="B1" s="16" t="s">
+      <c r="A1" s="14"/>
+      <c r="B1" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="15" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="15" t="s">
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="15" t="s">
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="15" t="s">
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="15" t="s">
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="18"/>
+      <c r="AC1" s="18"/>
+      <c r="AD1" s="18"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15"/>
-      <c r="AI1" s="15"/>
-      <c r="AJ1" s="15"/>
-      <c r="AK1" s="11"/>
-      <c r="AL1" s="15" t="s">
+      <c r="AG1" s="18"/>
+      <c r="AH1" s="18"/>
+      <c r="AI1" s="18"/>
+      <c r="AJ1" s="18"/>
+      <c r="AK1" s="14"/>
+      <c r="AL1" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="AM1" s="15"/>
-      <c r="AN1" s="15"/>
-      <c r="AO1" s="15"/>
-      <c r="AP1" s="15"/>
+      <c r="AM1" s="18"/>
+      <c r="AN1" s="18"/>
+      <c r="AO1" s="18"/>
+      <c r="AP1" s="18"/>
     </row>
     <row r="2" spans="1:42" s="5" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="P2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="T2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="U2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="V2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="W2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Y2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="Z2" s="13" t="s">
+      <c r="Z2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="AA2" s="12" t="s">
+      <c r="AA2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="AB2" s="12" t="s">
+      <c r="AB2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="AC2" s="12" t="s">
+      <c r="AC2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AD2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="AE2" s="12" t="s">
+      <c r="AE2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="AF2" s="13" t="s">
+      <c r="AF2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="AG2" s="12" t="s">
+      <c r="AG2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="AH2" s="12" t="s">
+      <c r="AH2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="AI2" s="12" t="s">
+      <c r="AI2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AJ2" s="12" t="s">
+      <c r="AJ2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="12" t="s">
+      <c r="AK2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="AL2" s="13" t="s">
+      <c r="AL2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="AM2" s="12" t="s">
+      <c r="AM2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="AN2" s="12" t="s">
+      <c r="AN2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="AO2" s="12" t="s">
+      <c r="AO2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AP2" s="12" t="s">
+      <c r="AP2" s="15" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="13" t="s">
         <v>28</v>
       </c>
       <c r="B3" s="3">
@@ -15956,7 +16179,7 @@
       <c r="F3" s="3">
         <v>0</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="13" t="s">
         <v>43</v>
       </c>
       <c r="H3" s="3">
@@ -15974,7 +16197,7 @@
       <c r="L3" s="3">
         <v>1</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="13" t="s">
         <v>43</v>
       </c>
       <c r="N3" s="3">
@@ -15992,7 +16215,7 @@
       <c r="R3" s="3">
         <v>1</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="S3" s="13" t="s">
         <v>43</v>
       </c>
       <c r="T3" s="3">
@@ -16010,7 +16233,7 @@
       <c r="X3" s="3">
         <v>0</v>
       </c>
-      <c r="Y3" s="10" t="s">
+      <c r="Y3" s="13" t="s">
         <v>43</v>
       </c>
       <c r="Z3" s="3">
@@ -16028,7 +16251,7 @@
       <c r="AD3" s="3">
         <v>2</v>
       </c>
-      <c r="AE3" s="10" t="s">
+      <c r="AE3" s="13" t="s">
         <v>43</v>
       </c>
       <c r="AF3" s="3">
@@ -16046,7 +16269,7 @@
       <c r="AJ3" s="3">
         <v>10</v>
       </c>
-      <c r="AK3" s="10" t="s">
+      <c r="AK3" s="13" t="s">
         <v>43</v>
       </c>
       <c r="AL3" s="3">
@@ -16710,13 +16933,13 @@
         <v>48</v>
       </c>
       <c r="B9" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E9" s="3">
         <v>1</v>
@@ -16728,13 +16951,13 @@
         <v>48</v>
       </c>
       <c r="H9" s="3">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I9" s="3">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J9" s="3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K9" s="3">
         <v>1</v>
@@ -16800,13 +17023,13 @@
         <v>48</v>
       </c>
       <c r="AF9" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AG9" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AH9" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AI9" s="3">
         <v>1</v>
@@ -16834,48 +17057,132 @@
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3"/>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="3"/>
-      <c r="AF10" s="3"/>
-      <c r="AG10" s="3"/>
-      <c r="AH10" s="3"/>
-      <c r="AI10" s="3"/>
-      <c r="AJ10" s="3"/>
-      <c r="AK10" s="3"/>
-      <c r="AL10" s="3"/>
-      <c r="AM10" s="3"/>
-      <c r="AN10" s="3"/>
-      <c r="AO10" s="3"/>
-      <c r="AP10" s="3"/>
+      <c r="A10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="3">
+        <v>16</v>
+      </c>
+      <c r="C10" s="3">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3">
+        <v>15</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="3">
+        <v>14</v>
+      </c>
+      <c r="I10" s="3">
+        <v>14</v>
+      </c>
+      <c r="J10" s="3">
+        <v>13</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2</v>
+      </c>
+      <c r="L10" s="3">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" s="3">
+        <v>31</v>
+      </c>
+      <c r="O10" s="3">
+        <v>28</v>
+      </c>
+      <c r="P10" s="3">
+        <v>29</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
+        <v>12</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>16</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>16</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>15</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>3</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>14</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>14</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>14</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>2</v>
+      </c>
+      <c r="AJ10" s="3">
+        <v>2</v>
+      </c>
+      <c r="AK10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL10" s="3">
+        <v>12</v>
+      </c>
+      <c r="AM10" s="3">
+        <v>12</v>
+      </c>
+      <c r="AN10" s="3">
+        <v>2</v>
+      </c>
+      <c r="AO10" s="3">
+        <v>1</v>
+      </c>
+      <c r="AP10" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>

--- a/documents/지표/주별활동지수.xlsx
+++ b/documents/지표/주별활동지수.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf1f1df607fbac1a/Desktop/Github/2026-QI/documents/지표/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4713887E-CD6E-4815-B4CA-C61188946519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1417F7F4-6396-4D55-8B4F-F564B8A920D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{0FC1208A-2CB8-4E1E-B9D0-F7D163D68827}"/>
   </bookViews>
@@ -22,15 +22,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -39,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="52">
   <si>
     <t>1주차</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -216,6 +207,13 @@
     <t>8주차(7/9~7/15)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>9주차(7/16~7/22)</t>
+  </si>
+  <si>
+    <t>9주차(7/16~7/22)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -344,7 +342,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -354,28 +352,19 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -384,7 +373,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -395,6 +384,9 @@
     </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1481,9 +1473,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$10</c:f>
+              <c:f>Sheet1!$A$3:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1507,16 +1499,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$B$10</c:f>
+              <c:f>Sheet1!$B$3:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -1540,6 +1535,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1633,9 +1631,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$10</c:f>
+              <c:f>Sheet1!$A$3:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1659,16 +1657,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$3:$C$10</c:f>
+              <c:f>Sheet1!$C$3:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -1692,6 +1693,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1785,9 +1789,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$10</c:f>
+              <c:f>Sheet1!$A$3:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1811,16 +1815,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$3:$D$10</c:f>
+              <c:f>Sheet1!$D$3:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1844,6 +1851,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1937,9 +1947,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$10</c:f>
+              <c:f>Sheet1!$A$3:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1963,16 +1973,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$3:$E$10</c:f>
+              <c:f>Sheet1!$E$3:$E$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1995,6 +2008,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2089,9 +2105,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$10</c:f>
+              <c:f>Sheet1!$A$3:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2115,16 +2131,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$3:$F$10</c:f>
+              <c:f>Sheet1!$F$3:$F$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2147,6 +2166,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2520,9 +2542,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$10</c:f>
+              <c:f>Sheet1!$G$3:$G$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2546,16 +2568,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$3:$H$10</c:f>
+              <c:f>Sheet1!$H$3:$H$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
@@ -2579,6 +2604,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2672,9 +2700,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$10</c:f>
+              <c:f>Sheet1!$G$3:$G$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2698,16 +2726,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$I$3:$I$10</c:f>
+              <c:f>Sheet1!$I$3:$I$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -2731,6 +2762,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2824,9 +2858,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$10</c:f>
+              <c:f>Sheet1!$G$3:$G$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2850,16 +2884,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$3:$J$10</c:f>
+              <c:f>Sheet1!$J$3:$J$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -2883,6 +2920,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2976,9 +3016,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$10</c:f>
+              <c:f>Sheet1!$G$3:$G$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3002,16 +3042,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$K$3:$K$10</c:f>
+              <c:f>Sheet1!$K$3:$K$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3035,6 +3078,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3128,9 +3174,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$10</c:f>
+              <c:f>Sheet1!$G$3:$G$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3154,16 +3200,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$3:$L$10</c:f>
+              <c:f>Sheet1!$L$3:$L$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3187,6 +3236,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3560,9 +3612,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$10</c:f>
+              <c:f>Sheet1!$M$3:$M$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3586,16 +3638,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$N$3:$N$10</c:f>
+              <c:f>Sheet1!$N$3:$N$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>6</c:v>
                 </c:pt>
@@ -3619,6 +3674,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3713,9 +3771,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$10</c:f>
+              <c:f>Sheet1!$M$3:$M$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3739,16 +3797,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$O$3:$O$10</c:f>
+              <c:f>Sheet1!$O$3:$O$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -3772,6 +3833,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3866,9 +3930,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$10</c:f>
+              <c:f>Sheet1!$M$3:$M$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3892,16 +3956,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$P$3:$P$10</c:f>
+              <c:f>Sheet1!$P$3:$P$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -3925,6 +3992,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4019,9 +4089,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$10</c:f>
+              <c:f>Sheet1!$M$3:$M$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4045,16 +4115,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Q$3:$Q$10</c:f>
+              <c:f>Sheet1!$Q$3:$Q$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4078,6 +4151,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4172,9 +4248,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$10</c:f>
+              <c:f>Sheet1!$M$3:$M$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4198,16 +4274,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$R$3:$R$10</c:f>
+              <c:f>Sheet1!$R$3:$R$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4231,6 +4310,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4605,9 +4687,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$10</c:f>
+              <c:f>Sheet1!$S$3:$S$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4631,16 +4713,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$T$3:$T$10</c:f>
+              <c:f>Sheet1!$T$3:$T$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4663,6 +4748,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4758,9 +4846,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$10</c:f>
+              <c:f>Sheet1!$S$3:$S$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4784,16 +4872,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$U$3:$U$10</c:f>
+              <c:f>Sheet1!$U$3:$U$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4816,6 +4907,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4911,9 +5005,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$10</c:f>
+              <c:f>Sheet1!$S$3:$S$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4937,16 +5031,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$V$3:$V$10</c:f>
+              <c:f>Sheet1!$V$3:$V$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4969,6 +5066,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5064,9 +5164,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$10</c:f>
+              <c:f>Sheet1!$S$3:$S$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5090,16 +5190,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$W$3:$W$10</c:f>
+              <c:f>Sheet1!$W$3:$W$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5122,6 +5225,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5217,9 +5323,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$10</c:f>
+              <c:f>Sheet1!$S$3:$S$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5243,16 +5349,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$X$3:$X$10</c:f>
+              <c:f>Sheet1!$X$3:$X$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5275,6 +5384,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5653,9 +5765,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$10</c:f>
+              <c:f>Sheet1!$Y$3:$Y$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5679,16 +5791,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Z$3:$Z$10</c:f>
+              <c:f>Sheet1!$Z$3:$Z$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>47</c:v>
                 </c:pt>
@@ -5712,6 +5827,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5806,9 +5924,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$10</c:f>
+              <c:f>Sheet1!$Y$3:$Y$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5832,16 +5950,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AA$3:$AA$10</c:f>
+              <c:f>Sheet1!$AA$3:$AA$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>43</c:v>
                 </c:pt>
@@ -5865,6 +5986,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5959,9 +6083,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$10</c:f>
+              <c:f>Sheet1!$Y$3:$Y$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5985,16 +6109,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AB$3:$AB$10</c:f>
+              <c:f>Sheet1!$AB$3:$AB$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>39</c:v>
                 </c:pt>
@@ -6018,6 +6145,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6112,9 +6242,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$10</c:f>
+              <c:f>Sheet1!$Y$3:$Y$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6138,16 +6268,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AC$3:$AC$10</c:f>
+              <c:f>Sheet1!$AC$3:$AC$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -6171,6 +6304,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6265,9 +6401,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$10</c:f>
+              <c:f>Sheet1!$Y$3:$Y$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6291,16 +6427,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AD$3:$AD$10</c:f>
+              <c:f>Sheet1!$AD$3:$AD$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -6324,6 +6463,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6701,9 +6843,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$10</c:f>
+              <c:f>Sheet1!$AE$3:$AE$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6727,16 +6869,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AF$3:$AF$10</c:f>
+              <c:f>Sheet1!$AF$3:$AF$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>27</c:v>
                 </c:pt>
@@ -6759,6 +6904,9 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
@@ -6854,9 +7002,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$10</c:f>
+              <c:f>Sheet1!$AE$3:$AE$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6880,16 +7028,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AG$3:$AG$10</c:f>
+              <c:f>Sheet1!$AG$3:$AG$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>26</c:v>
                 </c:pt>
@@ -6913,6 +7064,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7007,9 +7161,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$10</c:f>
+              <c:f>Sheet1!$AE$3:$AE$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7033,16 +7187,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AH$3:$AH$10</c:f>
+              <c:f>Sheet1!$AH$3:$AH$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>22</c:v>
                 </c:pt>
@@ -7066,6 +7223,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7160,9 +7320,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$10</c:f>
+              <c:f>Sheet1!$AE$3:$AE$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7186,16 +7346,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AI$3:$AI$10</c:f>
+              <c:f>Sheet1!$AI$3:$AI$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -7219,6 +7382,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7313,9 +7479,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$10</c:f>
+              <c:f>Sheet1!$AE$3:$AE$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7339,16 +7505,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AJ$3:$AJ$10</c:f>
+              <c:f>Sheet1!$AJ$3:$AJ$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -7372,6 +7541,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7750,9 +7922,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$10</c:f>
+              <c:f>Sheet1!$AK$3:$AK$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7776,16 +7948,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AL$3:$AL$10</c:f>
+              <c:f>Sheet1!$AL$3:$AL$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>31</c:v>
                 </c:pt>
@@ -7809,6 +7984,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7903,9 +8081,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$10</c:f>
+              <c:f>Sheet1!$AK$3:$AK$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7929,16 +8107,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AM$3:$AM$10</c:f>
+              <c:f>Sheet1!$AM$3:$AM$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>30</c:v>
                 </c:pt>
@@ -7962,6 +8143,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8056,9 +8240,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$10</c:f>
+              <c:f>Sheet1!$AK$3:$AK$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8082,16 +8266,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AN$3:$AN$10</c:f>
+              <c:f>Sheet1!$AN$3:$AN$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>27</c:v>
                 </c:pt>
@@ -8115,6 +8302,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8209,9 +8399,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$10</c:f>
+              <c:f>Sheet1!$AK$3:$AK$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8235,16 +8425,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AO$3:$AO$10</c:f>
+              <c:f>Sheet1!$AO$3:$AO$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -8267,6 +8460,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -8362,9 +8558,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$10</c:f>
+              <c:f>Sheet1!$AK$3:$AK$11</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8388,16 +8584,19 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8주차(7/9~7/15)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9주차(7/16~7/22)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AP$3:$AP$10</c:f>
+              <c:f>Sheet1!$AP$3:$AP$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -8420,6 +8619,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -13061,13 +13263,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>233362</xdr:colOff>
+      <xdr:colOff>266979</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>119062</xdr:colOff>
+      <xdr:colOff>152679</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>123265</xdr:rowOff>
     </xdr:to>
@@ -13102,8 +13304,8 @@
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>166687</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>470647</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>134471</xdr:rowOff>
     </xdr:to>
@@ -13577,2211 +13779,2202 @@
   <dimension ref="A1:DB10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="5.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="18.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="13.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="107" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="5.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="18.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="107" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:106" x14ac:dyDescent="0.3">
-      <c r="A1" s="6"/>
-      <c r="B1" s="17" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17" t="s">
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17" t="s">
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17" t="s">
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17" t="s">
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17" t="s">
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="17" t="s">
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17" t="s">
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="17"/>
-      <c r="AU1" s="17" t="s">
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15"/>
+      <c r="AS1" s="15"/>
+      <c r="AT1" s="15"/>
+      <c r="AU1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="AV1" s="17"/>
-      <c r="AW1" s="17"/>
-      <c r="AX1" s="17"/>
-      <c r="AY1" s="17"/>
-      <c r="AZ1" s="17" t="s">
+      <c r="AV1" s="15"/>
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15"/>
+      <c r="AY1" s="15"/>
+      <c r="AZ1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="BA1" s="17"/>
-      <c r="BB1" s="17"/>
-      <c r="BC1" s="17"/>
-      <c r="BD1" s="17"/>
-      <c r="BE1" s="17" t="s">
+      <c r="BA1" s="15"/>
+      <c r="BB1" s="15"/>
+      <c r="BC1" s="15"/>
+      <c r="BD1" s="15"/>
+      <c r="BE1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="BF1" s="17"/>
-      <c r="BG1" s="17"/>
-      <c r="BH1" s="17"/>
-      <c r="BI1" s="17"/>
-      <c r="BJ1" s="17" t="s">
+      <c r="BF1" s="15"/>
+      <c r="BG1" s="15"/>
+      <c r="BH1" s="15"/>
+      <c r="BI1" s="15"/>
+      <c r="BJ1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="BK1" s="17"/>
-      <c r="BL1" s="17"/>
-      <c r="BM1" s="17"/>
-      <c r="BN1" s="17"/>
-      <c r="BO1" s="17" t="s">
+      <c r="BK1" s="15"/>
+      <c r="BL1" s="15"/>
+      <c r="BM1" s="15"/>
+      <c r="BN1" s="15"/>
+      <c r="BO1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="BP1" s="17"/>
-      <c r="BQ1" s="17"/>
-      <c r="BR1" s="17"/>
-      <c r="BS1" s="17"/>
-      <c r="BT1" s="17" t="s">
+      <c r="BP1" s="15"/>
+      <c r="BQ1" s="15"/>
+      <c r="BR1" s="15"/>
+      <c r="BS1" s="15"/>
+      <c r="BT1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="BU1" s="17"/>
-      <c r="BV1" s="17"/>
-      <c r="BW1" s="17"/>
-      <c r="BX1" s="17"/>
-      <c r="BY1" s="17" t="s">
+      <c r="BU1" s="15"/>
+      <c r="BV1" s="15"/>
+      <c r="BW1" s="15"/>
+      <c r="BX1" s="15"/>
+      <c r="BY1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="BZ1" s="17"/>
-      <c r="CA1" s="17"/>
-      <c r="CB1" s="17"/>
-      <c r="CC1" s="17"/>
-      <c r="CD1" s="17" t="s">
+      <c r="BZ1" s="15"/>
+      <c r="CA1" s="15"/>
+      <c r="CB1" s="15"/>
+      <c r="CC1" s="15"/>
+      <c r="CD1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="CE1" s="17"/>
-      <c r="CF1" s="17"/>
-      <c r="CG1" s="17"/>
-      <c r="CH1" s="17"/>
-      <c r="CI1" s="17" t="s">
+      <c r="CE1" s="15"/>
+      <c r="CF1" s="15"/>
+      <c r="CG1" s="15"/>
+      <c r="CH1" s="15"/>
+      <c r="CI1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="CJ1" s="17"/>
-      <c r="CK1" s="17"/>
-      <c r="CL1" s="17"/>
-      <c r="CM1" s="17"/>
-      <c r="CN1" s="17" t="s">
+      <c r="CJ1" s="15"/>
+      <c r="CK1" s="15"/>
+      <c r="CL1" s="15"/>
+      <c r="CM1" s="15"/>
+      <c r="CN1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="CO1" s="17"/>
-      <c r="CP1" s="17"/>
-      <c r="CQ1" s="17"/>
-      <c r="CR1" s="17"/>
-      <c r="CS1" s="17" t="s">
+      <c r="CO1" s="15"/>
+      <c r="CP1" s="15"/>
+      <c r="CQ1" s="15"/>
+      <c r="CR1" s="15"/>
+      <c r="CS1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="CT1" s="17"/>
-      <c r="CU1" s="17"/>
-      <c r="CV1" s="17"/>
-      <c r="CW1" s="17"/>
-      <c r="CX1" s="17" t="s">
+      <c r="CT1" s="15"/>
+      <c r="CU1" s="15"/>
+      <c r="CV1" s="15"/>
+      <c r="CW1" s="15"/>
+      <c r="CX1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="CY1" s="17"/>
-      <c r="CZ1" s="17"/>
-      <c r="DA1" s="17"/>
-      <c r="DB1" s="17"/>
+      <c r="CY1" s="15"/>
+      <c r="CZ1" s="15"/>
+      <c r="DA1" s="15"/>
+      <c r="DB1" s="15"/>
     </row>
-    <row r="2" spans="1:106" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:106" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="T2" s="8" t="s">
+      <c r="T2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="U2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="9" t="s">
+      <c r="V2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="W2" s="8" t="s">
+      <c r="W2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="8" t="s">
+      <c r="X2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="Y2" s="8" t="s">
+      <c r="Y2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Z2" s="8" t="s">
+      <c r="Z2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AA2" s="9" t="s">
+      <c r="AA2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AB2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="8" t="s">
+      <c r="AC2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="8" t="s">
+      <c r="AD2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="8" t="s">
+      <c r="AE2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AF2" s="9" t="s">
+      <c r="AF2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AG2" s="8" t="s">
+      <c r="AG2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AH2" s="8" t="s">
+      <c r="AH2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="AI2" s="8" t="s">
+      <c r="AI2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AJ2" s="8" t="s">
+      <c r="AJ2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="9" t="s">
+      <c r="AK2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AL2" s="8" t="s">
+      <c r="AL2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AM2" s="8" t="s">
+      <c r="AM2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="AN2" s="8" t="s">
+      <c r="AN2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AO2" s="8" t="s">
+      <c r="AO2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AP2" s="9" t="s">
+      <c r="AP2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AQ2" s="8" t="s">
+      <c r="AQ2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AR2" s="8" t="s">
+      <c r="AR2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="AS2" s="8" t="s">
+      <c r="AS2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AT2" s="8" t="s">
+      <c r="AT2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AU2" s="9" t="s">
+      <c r="AU2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AV2" s="8" t="s">
+      <c r="AV2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AW2" s="8" t="s">
+      <c r="AW2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="AX2" s="8" t="s">
+      <c r="AX2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AY2" s="8" t="s">
+      <c r="AY2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AZ2" s="9" t="s">
+      <c r="AZ2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BA2" s="8" t="s">
+      <c r="BA2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="BB2" s="8" t="s">
+      <c r="BB2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="BC2" s="8" t="s">
+      <c r="BC2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="BD2" s="8" t="s">
+      <c r="BD2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="BE2" s="9" t="s">
+      <c r="BE2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BF2" s="8" t="s">
+      <c r="BF2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="BG2" s="8" t="s">
+      <c r="BG2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="BH2" s="8" t="s">
+      <c r="BH2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="BI2" s="8" t="s">
+      <c r="BI2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="BJ2" s="9" t="s">
+      <c r="BJ2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BK2" s="8" t="s">
+      <c r="BK2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="BL2" s="8" t="s">
+      <c r="BL2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="BM2" s="8" t="s">
+      <c r="BM2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="BN2" s="8" t="s">
+      <c r="BN2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="BO2" s="9" t="s">
+      <c r="BO2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BP2" s="8" t="s">
+      <c r="BP2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="BQ2" s="8" t="s">
+      <c r="BQ2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="BR2" s="8" t="s">
+      <c r="BR2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="BS2" s="8" t="s">
+      <c r="BS2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="BT2" s="9" t="s">
+      <c r="BT2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BU2" s="8" t="s">
+      <c r="BU2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="BV2" s="8" t="s">
+      <c r="BV2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="BW2" s="8" t="s">
+      <c r="BW2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="BX2" s="8" t="s">
+      <c r="BX2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="BY2" s="9" t="s">
+      <c r="BY2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BZ2" s="8" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="CA2" s="8" t="s">
+      <c r="CA2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="CB2" s="8" t="s">
+      <c r="CB2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="CC2" s="8" t="s">
+      <c r="CC2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="CD2" s="9" t="s">
+      <c r="CD2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="CE2" s="8" t="s">
+      <c r="CE2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="CF2" s="8" t="s">
+      <c r="CF2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="CG2" s="8" t="s">
+      <c r="CG2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="CH2" s="8" t="s">
+      <c r="CH2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="CI2" s="9" t="s">
+      <c r="CI2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="CJ2" s="8" t="s">
+      <c r="CJ2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="CK2" s="8" t="s">
+      <c r="CK2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="CL2" s="8" t="s">
+      <c r="CL2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="CM2" s="8" t="s">
+      <c r="CM2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="CN2" s="9" t="s">
+      <c r="CN2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="CO2" s="8" t="s">
+      <c r="CO2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="CP2" s="8" t="s">
+      <c r="CP2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="CQ2" s="8" t="s">
+      <c r="CQ2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="CR2" s="8" t="s">
+      <c r="CR2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="CS2" s="9" t="s">
+      <c r="CS2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="CT2" s="8" t="s">
+      <c r="CT2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="CU2" s="8" t="s">
+      <c r="CU2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="CV2" s="8" t="s">
+      <c r="CV2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="CW2" s="8" t="s">
+      <c r="CW2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="CX2" s="9" t="s">
+      <c r="CX2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="CY2" s="8" t="s">
+      <c r="CY2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="CZ2" s="8" t="s">
+      <c r="CZ2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="DA2" s="8" t="s">
+      <c r="DA2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="DB2" s="8" t="s">
+      <c r="DB2" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="8">
         <v>10</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>4</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="8">
         <v>8</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="8">
         <v>1</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="8">
         <v>0</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="8">
         <v>4</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="8">
         <v>4</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="8">
         <v>4</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="8">
         <v>1</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="8">
         <v>1</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="8">
         <v>4</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="8">
         <v>4</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="8">
         <v>4</v>
       </c>
-      <c r="O3" s="11">
+      <c r="O3" s="8">
         <v>1</v>
       </c>
-      <c r="P3" s="11">
+      <c r="P3" s="8">
         <v>1</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="Q3" s="8">
         <v>13</v>
       </c>
-      <c r="R3" s="11">
+      <c r="R3" s="8">
         <v>13</v>
       </c>
-      <c r="S3" s="11">
+      <c r="S3" s="8">
         <v>13</v>
       </c>
-      <c r="T3" s="11">
+      <c r="T3" s="8">
         <v>3</v>
       </c>
-      <c r="U3" s="11">
+      <c r="U3" s="8">
         <v>3</v>
       </c>
-      <c r="V3" s="11">
+      <c r="V3" s="8">
         <v>14</v>
       </c>
-      <c r="W3" s="11">
+      <c r="W3" s="8">
         <v>14</v>
       </c>
-      <c r="X3" s="11">
+      <c r="X3" s="8">
         <v>13</v>
       </c>
-      <c r="Y3" s="11">
+      <c r="Y3" s="8">
         <v>2</v>
       </c>
-      <c r="Z3" s="11">
+      <c r="Z3" s="8">
         <v>3</v>
       </c>
-      <c r="AA3" s="11">
+      <c r="AA3" s="8">
         <v>6</v>
       </c>
-      <c r="AB3" s="11">
+      <c r="AB3" s="8">
         <v>5</v>
       </c>
-      <c r="AC3" s="11">
+      <c r="AC3" s="8">
         <v>5</v>
       </c>
-      <c r="AD3" s="11">
+      <c r="AD3" s="8">
         <v>1</v>
       </c>
-      <c r="AE3" s="11">
+      <c r="AE3" s="8">
         <v>1</v>
       </c>
-      <c r="AF3" s="11"/>
-      <c r="AG3" s="11"/>
-      <c r="AH3" s="11"/>
-      <c r="AI3" s="11"/>
-      <c r="AJ3" s="11"/>
-      <c r="AK3" s="11"/>
-      <c r="AL3" s="11"/>
-      <c r="AM3" s="11"/>
-      <c r="AN3" s="11"/>
-      <c r="AO3" s="11"/>
-      <c r="AP3" s="11"/>
-      <c r="AQ3" s="11"/>
-      <c r="AR3" s="11"/>
-      <c r="AS3" s="11"/>
-      <c r="AT3" s="11"/>
-      <c r="AU3" s="11"/>
-      <c r="AV3" s="11"/>
-      <c r="AW3" s="11"/>
-      <c r="AX3" s="11"/>
-      <c r="AY3" s="11"/>
-      <c r="AZ3" s="11"/>
-      <c r="BA3" s="11"/>
-      <c r="BB3" s="11"/>
-      <c r="BC3" s="11"/>
-      <c r="BD3" s="11"/>
-      <c r="BE3" s="11"/>
-      <c r="BF3" s="11"/>
-      <c r="BG3" s="11"/>
-      <c r="BH3" s="11"/>
-      <c r="BI3" s="11"/>
-      <c r="BJ3" s="11"/>
-      <c r="BK3" s="11"/>
-      <c r="BL3" s="11"/>
-      <c r="BM3" s="11"/>
-      <c r="BN3" s="11"/>
-      <c r="BO3" s="11"/>
-      <c r="BP3" s="11"/>
-      <c r="BQ3" s="11"/>
-      <c r="BR3" s="11"/>
-      <c r="BS3" s="11"/>
-      <c r="BT3" s="11"/>
-      <c r="BU3" s="11"/>
-      <c r="BV3" s="11"/>
-      <c r="BW3" s="11"/>
-      <c r="BX3" s="11"/>
-      <c r="BY3" s="11"/>
-      <c r="BZ3" s="11"/>
-      <c r="CA3" s="11"/>
-      <c r="CB3" s="11"/>
-      <c r="CC3" s="11"/>
-      <c r="CD3" s="11"/>
-      <c r="CE3" s="11"/>
-      <c r="CF3" s="11"/>
-      <c r="CG3" s="11"/>
-      <c r="CH3" s="11"/>
-      <c r="CI3" s="11"/>
-      <c r="CJ3" s="11"/>
-      <c r="CK3" s="11"/>
-      <c r="CL3" s="11"/>
-      <c r="CM3" s="11"/>
-      <c r="CN3" s="11"/>
-      <c r="CO3" s="11"/>
-      <c r="CP3" s="11"/>
-      <c r="CQ3" s="11"/>
-      <c r="CR3" s="11"/>
-      <c r="CS3" s="11"/>
-      <c r="CT3" s="11"/>
-      <c r="CU3" s="11"/>
-      <c r="CV3" s="11"/>
-      <c r="CW3" s="11"/>
-      <c r="CX3" s="11"/>
-      <c r="CY3" s="11"/>
-      <c r="CZ3" s="11"/>
-      <c r="DA3" s="11"/>
-      <c r="DB3" s="11"/>
+      <c r="AF3" s="8"/>
+      <c r="AG3" s="8"/>
+      <c r="AH3" s="8"/>
+      <c r="AI3" s="8"/>
+      <c r="AJ3" s="8"/>
+      <c r="AK3" s="8"/>
+      <c r="AL3" s="8"/>
+      <c r="AM3" s="8"/>
+      <c r="AN3" s="8"/>
+      <c r="AO3" s="8"/>
+      <c r="AP3" s="8"/>
+      <c r="AQ3" s="8"/>
+      <c r="AR3" s="8"/>
+      <c r="AS3" s="8"/>
+      <c r="AT3" s="8"/>
+      <c r="AU3" s="8"/>
+      <c r="AV3" s="8"/>
+      <c r="AW3" s="8"/>
+      <c r="AX3" s="8"/>
+      <c r="AY3" s="8"/>
+      <c r="AZ3" s="8"/>
+      <c r="BA3" s="8"/>
+      <c r="BB3" s="8"/>
+      <c r="BC3" s="8"/>
+      <c r="BD3" s="8"/>
+      <c r="BE3" s="8"/>
+      <c r="BF3" s="8"/>
+      <c r="BG3" s="8"/>
+      <c r="BH3" s="8"/>
+      <c r="BI3" s="8"/>
+      <c r="BJ3" s="8"/>
+      <c r="BK3" s="8"/>
+      <c r="BL3" s="8"/>
+      <c r="BM3" s="8"/>
+      <c r="BN3" s="8"/>
+      <c r="BO3" s="8"/>
+      <c r="BP3" s="8"/>
+      <c r="BQ3" s="8"/>
+      <c r="BR3" s="8"/>
+      <c r="BS3" s="8"/>
+      <c r="BT3" s="8"/>
+      <c r="BU3" s="8"/>
+      <c r="BV3" s="8"/>
+      <c r="BW3" s="8"/>
+      <c r="BX3" s="8"/>
+      <c r="BY3" s="8"/>
+      <c r="BZ3" s="8"/>
+      <c r="CA3" s="8"/>
+      <c r="CB3" s="8"/>
+      <c r="CC3" s="8"/>
+      <c r="CD3" s="8"/>
+      <c r="CE3" s="8"/>
+      <c r="CF3" s="8"/>
+      <c r="CG3" s="8"/>
+      <c r="CH3" s="8"/>
+      <c r="CI3" s="8"/>
+      <c r="CJ3" s="8"/>
+      <c r="CK3" s="8"/>
+      <c r="CL3" s="8"/>
+      <c r="CM3" s="8"/>
+      <c r="CN3" s="8"/>
+      <c r="CO3" s="8"/>
+      <c r="CP3" s="8"/>
+      <c r="CQ3" s="8"/>
+      <c r="CR3" s="8"/>
+      <c r="CS3" s="8"/>
+      <c r="CT3" s="8"/>
+      <c r="CU3" s="8"/>
+      <c r="CV3" s="8"/>
+      <c r="CW3" s="8"/>
+      <c r="CX3" s="8"/>
+      <c r="CY3" s="8"/>
+      <c r="CZ3" s="8"/>
+      <c r="DA3" s="8"/>
+      <c r="DB3" s="8"/>
     </row>
     <row r="4" spans="1:106" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>12</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>5</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>10</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>1</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>1</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>6</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>5</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="3">
         <v>4</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="3">
         <v>1</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="3">
         <v>0</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="3">
         <v>6</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>5</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="3">
         <v>4</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="3">
         <v>2</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="3">
         <v>0</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="3">
         <v>15</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="3">
         <v>14</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="3">
         <v>10</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="3">
         <v>1</v>
       </c>
-      <c r="U4" s="6">
+      <c r="U4" s="3">
         <v>2</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="3">
         <v>10</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="3">
         <v>9</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="3">
         <v>8</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="3">
         <v>1</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="3">
         <v>1</v>
       </c>
-      <c r="AA4" s="6">
+      <c r="AA4" s="3">
         <v>11</v>
       </c>
-      <c r="AB4" s="6">
+      <c r="AB4" s="3">
         <v>10</v>
       </c>
-      <c r="AC4" s="6">
+      <c r="AC4" s="3">
         <v>11</v>
       </c>
-      <c r="AD4" s="6">
+      <c r="AD4" s="3">
         <v>1</v>
       </c>
-      <c r="AE4" s="6">
+      <c r="AE4" s="3">
         <v>1</v>
       </c>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="6"/>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="6"/>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="6"/>
-      <c r="AL4" s="6"/>
-      <c r="AM4" s="6"/>
-      <c r="AN4" s="6"/>
-      <c r="AO4" s="6"/>
-      <c r="AP4" s="6"/>
-      <c r="AQ4" s="6"/>
-      <c r="AR4" s="6"/>
-      <c r="AS4" s="6"/>
-      <c r="AT4" s="6"/>
-      <c r="AU4" s="6"/>
-      <c r="AV4" s="6"/>
-      <c r="AW4" s="6"/>
-      <c r="AX4" s="6"/>
-      <c r="AY4" s="6"/>
-      <c r="AZ4" s="6"/>
-      <c r="BA4" s="6"/>
-      <c r="BB4" s="6"/>
-      <c r="BC4" s="6"/>
-      <c r="BD4" s="6"/>
-      <c r="BE4" s="6"/>
-      <c r="BF4" s="6"/>
-      <c r="BG4" s="6"/>
-      <c r="BH4" s="6"/>
-      <c r="BI4" s="6"/>
-      <c r="BJ4" s="6"/>
-      <c r="BK4" s="6"/>
-      <c r="BL4" s="6"/>
-      <c r="BM4" s="6"/>
-      <c r="BN4" s="6"/>
-      <c r="BO4" s="6"/>
-      <c r="BP4" s="6"/>
-      <c r="BQ4" s="6"/>
-      <c r="BR4" s="6"/>
-      <c r="BS4" s="6"/>
-      <c r="BT4" s="6"/>
-      <c r="BU4" s="6"/>
-      <c r="BV4" s="6"/>
-      <c r="BW4" s="6"/>
-      <c r="BX4" s="6"/>
-      <c r="BY4" s="6"/>
-      <c r="BZ4" s="6"/>
-      <c r="CA4" s="6"/>
-      <c r="CB4" s="6"/>
-      <c r="CC4" s="6"/>
-      <c r="CD4" s="6"/>
-      <c r="CE4" s="6"/>
-      <c r="CF4" s="6"/>
-      <c r="CG4" s="6"/>
-      <c r="CH4" s="6"/>
-      <c r="CI4" s="6"/>
-      <c r="CJ4" s="6"/>
-      <c r="CK4" s="6"/>
-      <c r="CL4" s="6"/>
-      <c r="CM4" s="6"/>
-      <c r="CN4" s="6"/>
-      <c r="CO4" s="6"/>
-      <c r="CP4" s="6"/>
-      <c r="CQ4" s="6"/>
-      <c r="CR4" s="6"/>
-      <c r="CS4" s="6"/>
-      <c r="CT4" s="6"/>
-      <c r="CU4" s="6"/>
-      <c r="CV4" s="6"/>
-      <c r="CW4" s="6"/>
-      <c r="CX4" s="6"/>
-      <c r="CY4" s="6"/>
-      <c r="CZ4" s="6"/>
-      <c r="DA4" s="6"/>
-      <c r="DB4" s="6"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3"/>
+      <c r="AL4" s="3"/>
+      <c r="AM4" s="3"/>
+      <c r="AN4" s="3"/>
+      <c r="AO4" s="3"/>
+      <c r="AP4" s="3"/>
+      <c r="AQ4" s="3"/>
+      <c r="AR4" s="3"/>
+      <c r="AS4" s="3"/>
+      <c r="AT4" s="3"/>
+      <c r="AU4" s="3"/>
+      <c r="AV4" s="3"/>
+      <c r="AW4" s="3"/>
+      <c r="AX4" s="3"/>
+      <c r="AY4" s="3"/>
+      <c r="AZ4" s="3"/>
+      <c r="BA4" s="3"/>
+      <c r="BB4" s="3"/>
+      <c r="BC4" s="3"/>
+      <c r="BD4" s="3"/>
+      <c r="BE4" s="3"/>
+      <c r="BF4" s="3"/>
+      <c r="BG4" s="3"/>
+      <c r="BH4" s="3"/>
+      <c r="BI4" s="3"/>
+      <c r="BJ4" s="3"/>
+      <c r="BK4" s="3"/>
+      <c r="BL4" s="3"/>
+      <c r="BM4" s="3"/>
+      <c r="BN4" s="3"/>
+      <c r="BO4" s="3"/>
+      <c r="BP4" s="3"/>
+      <c r="BQ4" s="3"/>
+      <c r="BR4" s="3"/>
+      <c r="BS4" s="3"/>
+      <c r="BT4" s="3"/>
+      <c r="BU4" s="3"/>
+      <c r="BV4" s="3"/>
+      <c r="BW4" s="3"/>
+      <c r="BX4" s="3"/>
+      <c r="BY4" s="3"/>
+      <c r="BZ4" s="3"/>
+      <c r="CA4" s="3"/>
+      <c r="CB4" s="3"/>
+      <c r="CC4" s="3"/>
+      <c r="CD4" s="3"/>
+      <c r="CE4" s="3"/>
+      <c r="CF4" s="3"/>
+      <c r="CG4" s="3"/>
+      <c r="CH4" s="3"/>
+      <c r="CI4" s="3"/>
+      <c r="CJ4" s="3"/>
+      <c r="CK4" s="3"/>
+      <c r="CL4" s="3"/>
+      <c r="CM4" s="3"/>
+      <c r="CN4" s="3"/>
+      <c r="CO4" s="3"/>
+      <c r="CP4" s="3"/>
+      <c r="CQ4" s="3"/>
+      <c r="CR4" s="3"/>
+      <c r="CS4" s="3"/>
+      <c r="CT4" s="3"/>
+      <c r="CU4" s="3"/>
+      <c r="CV4" s="3"/>
+      <c r="CW4" s="3"/>
+      <c r="CX4" s="3"/>
+      <c r="CY4" s="3"/>
+      <c r="CZ4" s="3"/>
+      <c r="DA4" s="3"/>
+      <c r="DB4" s="3"/>
     </row>
-    <row r="5" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="8">
         <v>6</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="8">
         <v>5</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="8">
         <v>3</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="8">
         <v>1</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="8">
         <v>1</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="8">
         <v>2</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="8">
         <v>2</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="8">
         <v>2</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="8">
         <v>0</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="8">
         <v>0</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="8">
         <v>20</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="8">
         <v>20</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="8">
         <v>15</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="8">
         <v>2</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="8">
         <v>10</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="8">
         <v>34</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="8">
         <v>32</v>
       </c>
-      <c r="S5" s="11">
+      <c r="S5" s="8">
         <v>31</v>
       </c>
-      <c r="T5" s="11">
+      <c r="T5" s="8">
         <v>6</v>
       </c>
-      <c r="U5" s="11">
+      <c r="U5" s="8">
         <v>11</v>
       </c>
-      <c r="V5" s="11">
+      <c r="V5" s="8">
         <v>55</v>
       </c>
-      <c r="W5" s="11">
+      <c r="W5" s="8">
         <v>52</v>
       </c>
-      <c r="X5" s="11">
+      <c r="X5" s="8">
         <v>51</v>
       </c>
-      <c r="Y5" s="11">
+      <c r="Y5" s="8">
         <v>7</v>
       </c>
-      <c r="Z5" s="11">
+      <c r="Z5" s="8">
         <v>16</v>
       </c>
-      <c r="AA5" s="11">
+      <c r="AA5" s="8">
         <v>28</v>
       </c>
-      <c r="AB5" s="11">
+      <c r="AB5" s="8">
         <v>26</v>
       </c>
-      <c r="AC5" s="11">
+      <c r="AC5" s="8">
         <v>25</v>
       </c>
-      <c r="AD5" s="11">
+      <c r="AD5" s="8">
         <v>4</v>
       </c>
-      <c r="AE5" s="11">
+      <c r="AE5" s="8">
         <v>9</v>
       </c>
-      <c r="AF5" s="11"/>
-      <c r="AG5" s="11"/>
-      <c r="AH5" s="11"/>
-      <c r="AI5" s="11"/>
-      <c r="AJ5" s="11"/>
-      <c r="AK5" s="11"/>
-      <c r="AL5" s="11"/>
-      <c r="AM5" s="11"/>
-      <c r="AN5" s="11"/>
-      <c r="AO5" s="11"/>
-      <c r="AP5" s="11"/>
-      <c r="AQ5" s="11"/>
-      <c r="AR5" s="11"/>
-      <c r="AS5" s="11"/>
-      <c r="AT5" s="11"/>
-      <c r="AU5" s="11"/>
-      <c r="AV5" s="11"/>
-      <c r="AW5" s="11"/>
-      <c r="AX5" s="11"/>
-      <c r="AY5" s="11"/>
-      <c r="AZ5" s="11"/>
-      <c r="BA5" s="11"/>
-      <c r="BB5" s="11"/>
-      <c r="BC5" s="11"/>
-      <c r="BD5" s="11"/>
-      <c r="BE5" s="11"/>
-      <c r="BF5" s="11"/>
-      <c r="BG5" s="11"/>
-      <c r="BH5" s="11"/>
-      <c r="BI5" s="11"/>
-      <c r="BJ5" s="11"/>
-      <c r="BK5" s="11"/>
-      <c r="BL5" s="11"/>
-      <c r="BM5" s="11"/>
-      <c r="BN5" s="11"/>
-      <c r="BO5" s="11"/>
-      <c r="BP5" s="11"/>
-      <c r="BQ5" s="11"/>
-      <c r="BR5" s="11"/>
-      <c r="BS5" s="11"/>
-      <c r="BT5" s="11"/>
-      <c r="BU5" s="11"/>
-      <c r="BV5" s="11"/>
-      <c r="BW5" s="11"/>
-      <c r="BX5" s="11"/>
-      <c r="BY5" s="11"/>
-      <c r="BZ5" s="11"/>
-      <c r="CA5" s="11"/>
-      <c r="CB5" s="11"/>
-      <c r="CC5" s="11"/>
-      <c r="CD5" s="11"/>
-      <c r="CE5" s="11"/>
-      <c r="CF5" s="11"/>
-      <c r="CG5" s="11"/>
-      <c r="CH5" s="11"/>
-      <c r="CI5" s="11"/>
-      <c r="CJ5" s="11"/>
-      <c r="CK5" s="11"/>
-      <c r="CL5" s="11"/>
-      <c r="CM5" s="11"/>
-      <c r="CN5" s="11"/>
-      <c r="CO5" s="11"/>
-      <c r="CP5" s="11"/>
-      <c r="CQ5" s="11"/>
-      <c r="CR5" s="11"/>
-      <c r="CS5" s="11"/>
-      <c r="CT5" s="11"/>
-      <c r="CU5" s="11"/>
-      <c r="CV5" s="11"/>
-      <c r="CW5" s="11"/>
-      <c r="CX5" s="11"/>
-      <c r="CY5" s="11"/>
-      <c r="CZ5" s="11"/>
-      <c r="DA5" s="11"/>
-      <c r="DB5" s="11"/>
+      <c r="AF5" s="8"/>
+      <c r="AG5" s="8"/>
+      <c r="AH5" s="8"/>
+      <c r="AI5" s="8"/>
+      <c r="AJ5" s="8"/>
+      <c r="AK5" s="8"/>
+      <c r="AL5" s="8"/>
+      <c r="AM5" s="8"/>
+      <c r="AN5" s="8"/>
+      <c r="AO5" s="8"/>
+      <c r="AP5" s="8"/>
+      <c r="AQ5" s="8"/>
+      <c r="AR5" s="8"/>
+      <c r="AS5" s="8"/>
+      <c r="AT5" s="8"/>
+      <c r="AU5" s="8"/>
+      <c r="AV5" s="8"/>
+      <c r="AW5" s="8"/>
+      <c r="AX5" s="8"/>
+      <c r="AY5" s="8"/>
+      <c r="AZ5" s="8"/>
+      <c r="BA5" s="8"/>
+      <c r="BB5" s="8"/>
+      <c r="BC5" s="8"/>
+      <c r="BD5" s="8"/>
+      <c r="BE5" s="8"/>
+      <c r="BF5" s="8"/>
+      <c r="BG5" s="8"/>
+      <c r="BH5" s="8"/>
+      <c r="BI5" s="8"/>
+      <c r="BJ5" s="8"/>
+      <c r="BK5" s="8"/>
+      <c r="BL5" s="8"/>
+      <c r="BM5" s="8"/>
+      <c r="BN5" s="8"/>
+      <c r="BO5" s="8"/>
+      <c r="BP5" s="8"/>
+      <c r="BQ5" s="8"/>
+      <c r="BR5" s="8"/>
+      <c r="BS5" s="8"/>
+      <c r="BT5" s="8"/>
+      <c r="BU5" s="8"/>
+      <c r="BV5" s="8"/>
+      <c r="BW5" s="8"/>
+      <c r="BX5" s="8"/>
+      <c r="BY5" s="8"/>
+      <c r="BZ5" s="8"/>
+      <c r="CA5" s="8"/>
+      <c r="CB5" s="8"/>
+      <c r="CC5" s="8"/>
+      <c r="CD5" s="8"/>
+      <c r="CE5" s="8"/>
+      <c r="CF5" s="8"/>
+      <c r="CG5" s="8"/>
+      <c r="CH5" s="8"/>
+      <c r="CI5" s="8"/>
+      <c r="CJ5" s="8"/>
+      <c r="CK5" s="8"/>
+      <c r="CL5" s="8"/>
+      <c r="CM5" s="8"/>
+      <c r="CN5" s="8"/>
+      <c r="CO5" s="8"/>
+      <c r="CP5" s="8"/>
+      <c r="CQ5" s="8"/>
+      <c r="CR5" s="8"/>
+      <c r="CS5" s="8"/>
+      <c r="CT5" s="8"/>
+      <c r="CU5" s="8"/>
+      <c r="CV5" s="8"/>
+      <c r="CW5" s="8"/>
+      <c r="CX5" s="8"/>
+      <c r="CY5" s="8"/>
+      <c r="CZ5" s="8"/>
+      <c r="DA5" s="8"/>
+      <c r="DB5" s="8"/>
     </row>
     <row r="6" spans="1:106" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="3">
         <v>0</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="3">
         <v>0</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>0</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="3">
         <v>0</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="3">
         <v>0</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="3">
         <v>0</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="3">
         <v>0</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="3">
         <v>0</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="3">
         <v>0</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="3">
         <v>0</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="3">
         <v>0</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>0</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="3">
         <v>0</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="3">
         <v>0</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="3">
         <v>0</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="3">
         <v>0</v>
       </c>
-      <c r="R6" s="6">
+      <c r="R6" s="3">
         <v>0</v>
       </c>
-      <c r="S6" s="6">
+      <c r="S6" s="3">
         <v>0</v>
       </c>
-      <c r="T6" s="6">
+      <c r="T6" s="3">
         <v>0</v>
       </c>
-      <c r="U6" s="6">
+      <c r="U6" s="3">
         <v>0</v>
       </c>
-      <c r="V6" s="6">
+      <c r="V6" s="3">
         <v>0</v>
       </c>
-      <c r="W6" s="6">
+      <c r="W6" s="3">
         <v>0</v>
       </c>
-      <c r="X6" s="6">
+      <c r="X6" s="3">
         <v>0</v>
       </c>
-      <c r="Y6" s="6">
+      <c r="Y6" s="3">
         <v>0</v>
       </c>
-      <c r="Z6" s="6">
+      <c r="Z6" s="3">
         <v>0</v>
       </c>
-      <c r="AA6" s="6">
+      <c r="AA6" s="3">
         <v>0</v>
       </c>
-      <c r="AB6" s="6">
+      <c r="AB6" s="3">
         <v>0</v>
       </c>
-      <c r="AC6" s="6">
+      <c r="AC6" s="3">
         <v>0</v>
       </c>
-      <c r="AD6" s="6">
+      <c r="AD6" s="3">
         <v>0</v>
       </c>
-      <c r="AE6" s="6">
+      <c r="AE6" s="3">
         <v>0</v>
       </c>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="6"/>
-      <c r="AO6" s="6"/>
-      <c r="AP6" s="6"/>
-      <c r="AQ6" s="6"/>
-      <c r="AR6" s="6"/>
-      <c r="AS6" s="6"/>
-      <c r="AT6" s="6"/>
-      <c r="AU6" s="6"/>
-      <c r="AV6" s="6"/>
-      <c r="AW6" s="6"/>
-      <c r="AX6" s="6"/>
-      <c r="AY6" s="6"/>
-      <c r="AZ6" s="6"/>
-      <c r="BA6" s="6"/>
-      <c r="BB6" s="6"/>
-      <c r="BC6" s="6"/>
-      <c r="BD6" s="6"/>
-      <c r="BE6" s="6"/>
-      <c r="BF6" s="6"/>
-      <c r="BG6" s="6"/>
-      <c r="BH6" s="6"/>
-      <c r="BI6" s="6"/>
-      <c r="BJ6" s="6"/>
-      <c r="BK6" s="6"/>
-      <c r="BL6" s="6"/>
-      <c r="BM6" s="6"/>
-      <c r="BN6" s="6"/>
-      <c r="BO6" s="6"/>
-      <c r="BP6" s="6"/>
-      <c r="BQ6" s="6"/>
-      <c r="BR6" s="6"/>
-      <c r="BS6" s="6"/>
-      <c r="BT6" s="6"/>
-      <c r="BU6" s="6"/>
-      <c r="BV6" s="6"/>
-      <c r="BW6" s="6"/>
-      <c r="BX6" s="6"/>
-      <c r="BY6" s="6"/>
-      <c r="BZ6" s="6"/>
-      <c r="CA6" s="6"/>
-      <c r="CB6" s="6"/>
-      <c r="CC6" s="6"/>
-      <c r="CD6" s="6"/>
-      <c r="CE6" s="6"/>
-      <c r="CF6" s="6"/>
-      <c r="CG6" s="6"/>
-      <c r="CH6" s="6"/>
-      <c r="CI6" s="6"/>
-      <c r="CJ6" s="6"/>
-      <c r="CK6" s="6"/>
-      <c r="CL6" s="6"/>
-      <c r="CM6" s="6"/>
-      <c r="CN6" s="6"/>
-      <c r="CO6" s="6"/>
-      <c r="CP6" s="6"/>
-      <c r="CQ6" s="6"/>
-      <c r="CR6" s="6"/>
-      <c r="CS6" s="6"/>
-      <c r="CT6" s="6"/>
-      <c r="CU6" s="6"/>
-      <c r="CV6" s="6"/>
-      <c r="CW6" s="6"/>
-      <c r="CX6" s="6"/>
-      <c r="CY6" s="6"/>
-      <c r="CZ6" s="6"/>
-      <c r="DA6" s="6"/>
-      <c r="DB6" s="6"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
+      <c r="AP6" s="3"/>
+      <c r="AQ6" s="3"/>
+      <c r="AR6" s="3"/>
+      <c r="AS6" s="3"/>
+      <c r="AT6" s="3"/>
+      <c r="AU6" s="3"/>
+      <c r="AV6" s="3"/>
+      <c r="AW6" s="3"/>
+      <c r="AX6" s="3"/>
+      <c r="AY6" s="3"/>
+      <c r="AZ6" s="3"/>
+      <c r="BA6" s="3"/>
+      <c r="BB6" s="3"/>
+      <c r="BC6" s="3"/>
+      <c r="BD6" s="3"/>
+      <c r="BE6" s="3"/>
+      <c r="BF6" s="3"/>
+      <c r="BG6" s="3"/>
+      <c r="BH6" s="3"/>
+      <c r="BI6" s="3"/>
+      <c r="BJ6" s="3"/>
+      <c r="BK6" s="3"/>
+      <c r="BL6" s="3"/>
+      <c r="BM6" s="3"/>
+      <c r="BN6" s="3"/>
+      <c r="BO6" s="3"/>
+      <c r="BP6" s="3"/>
+      <c r="BQ6" s="3"/>
+      <c r="BR6" s="3"/>
+      <c r="BS6" s="3"/>
+      <c r="BT6" s="3"/>
+      <c r="BU6" s="3"/>
+      <c r="BV6" s="3"/>
+      <c r="BW6" s="3"/>
+      <c r="BX6" s="3"/>
+      <c r="BY6" s="3"/>
+      <c r="BZ6" s="3"/>
+      <c r="CA6" s="3"/>
+      <c r="CB6" s="3"/>
+      <c r="CC6" s="3"/>
+      <c r="CD6" s="3"/>
+      <c r="CE6" s="3"/>
+      <c r="CF6" s="3"/>
+      <c r="CG6" s="3"/>
+      <c r="CH6" s="3"/>
+      <c r="CI6" s="3"/>
+      <c r="CJ6" s="3"/>
+      <c r="CK6" s="3"/>
+      <c r="CL6" s="3"/>
+      <c r="CM6" s="3"/>
+      <c r="CN6" s="3"/>
+      <c r="CO6" s="3"/>
+      <c r="CP6" s="3"/>
+      <c r="CQ6" s="3"/>
+      <c r="CR6" s="3"/>
+      <c r="CS6" s="3"/>
+      <c r="CT6" s="3"/>
+      <c r="CU6" s="3"/>
+      <c r="CV6" s="3"/>
+      <c r="CW6" s="3"/>
+      <c r="CX6" s="3"/>
+      <c r="CY6" s="3"/>
+      <c r="CZ6" s="3"/>
+      <c r="DA6" s="3"/>
+      <c r="DB6" s="3"/>
     </row>
-    <row r="7" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="8">
         <v>47</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="8">
         <v>43</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="8">
         <v>39</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="8">
         <v>3</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="8">
         <v>2</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="8">
         <v>8</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="8">
         <v>8</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="8">
         <v>6</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="8">
         <v>0</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="8">
         <v>0</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="8">
         <v>9</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="8">
         <v>9</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="8">
         <v>9</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="8">
         <v>1</v>
       </c>
-      <c r="P7" s="11">
+      <c r="P7" s="8">
         <v>2</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="Q7" s="8">
         <v>13</v>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="8">
         <v>13</v>
       </c>
-      <c r="S7" s="11">
+      <c r="S7" s="8">
         <v>12</v>
       </c>
-      <c r="T7" s="11">
+      <c r="T7" s="8">
         <v>3</v>
       </c>
-      <c r="U7" s="11">
+      <c r="U7" s="8">
         <v>4</v>
       </c>
-      <c r="V7" s="11">
+      <c r="V7" s="8">
         <v>17</v>
       </c>
-      <c r="W7" s="11">
+      <c r="W7" s="8">
         <v>17</v>
       </c>
-      <c r="X7" s="11">
+      <c r="X7" s="8">
         <v>16</v>
       </c>
-      <c r="Y7" s="11">
+      <c r="Y7" s="8">
         <v>2</v>
       </c>
-      <c r="Z7" s="11">
+      <c r="Z7" s="8">
         <v>4</v>
       </c>
-      <c r="AA7" s="11">
+      <c r="AA7" s="8">
         <v>9</v>
       </c>
-      <c r="AB7" s="11">
+      <c r="AB7" s="8">
         <v>9</v>
       </c>
-      <c r="AC7" s="11">
+      <c r="AC7" s="8">
         <v>8</v>
       </c>
-      <c r="AD7" s="11">
+      <c r="AD7" s="8">
         <v>1</v>
       </c>
-      <c r="AE7" s="11">
+      <c r="AE7" s="8">
         <v>1</v>
       </c>
-      <c r="AF7" s="11"/>
-      <c r="AG7" s="11"/>
-      <c r="AH7" s="11"/>
-      <c r="AI7" s="11"/>
-      <c r="AJ7" s="11"/>
-      <c r="AK7" s="11"/>
-      <c r="AL7" s="11"/>
-      <c r="AM7" s="11"/>
-      <c r="AN7" s="11"/>
-      <c r="AO7" s="11"/>
-      <c r="AP7" s="11"/>
-      <c r="AQ7" s="11"/>
-      <c r="AR7" s="11"/>
-      <c r="AS7" s="11"/>
-      <c r="AT7" s="11"/>
-      <c r="AU7" s="11"/>
-      <c r="AV7" s="11"/>
-      <c r="AW7" s="11"/>
-      <c r="AX7" s="11"/>
-      <c r="AY7" s="11"/>
-      <c r="AZ7" s="11"/>
-      <c r="BA7" s="11"/>
-      <c r="BB7" s="11"/>
-      <c r="BC7" s="11"/>
-      <c r="BD7" s="11"/>
-      <c r="BE7" s="11"/>
-      <c r="BF7" s="11"/>
-      <c r="BG7" s="11"/>
-      <c r="BH7" s="11"/>
-      <c r="BI7" s="11"/>
-      <c r="BJ7" s="11"/>
-      <c r="BK7" s="11"/>
-      <c r="BL7" s="11"/>
-      <c r="BM7" s="11"/>
-      <c r="BN7" s="11"/>
-      <c r="BO7" s="11"/>
-      <c r="BP7" s="11"/>
-      <c r="BQ7" s="11"/>
-      <c r="BR7" s="11"/>
-      <c r="BS7" s="11"/>
-      <c r="BT7" s="11"/>
-      <c r="BU7" s="11"/>
-      <c r="BV7" s="11"/>
-      <c r="BW7" s="11"/>
-      <c r="BX7" s="11"/>
-      <c r="BY7" s="11"/>
-      <c r="BZ7" s="11"/>
-      <c r="CA7" s="11"/>
-      <c r="CB7" s="11"/>
-      <c r="CC7" s="11"/>
-      <c r="CD7" s="11"/>
-      <c r="CE7" s="11"/>
-      <c r="CF7" s="11"/>
-      <c r="CG7" s="11"/>
-      <c r="CH7" s="11"/>
-      <c r="CI7" s="11"/>
-      <c r="CJ7" s="11"/>
-      <c r="CK7" s="11"/>
-      <c r="CL7" s="11"/>
-      <c r="CM7" s="11"/>
-      <c r="CN7" s="11"/>
-      <c r="CO7" s="11"/>
-      <c r="CP7" s="11"/>
-      <c r="CQ7" s="11"/>
-      <c r="CR7" s="11"/>
-      <c r="CS7" s="11"/>
-      <c r="CT7" s="11"/>
-      <c r="CU7" s="11"/>
-      <c r="CV7" s="11"/>
-      <c r="CW7" s="11"/>
-      <c r="CX7" s="11"/>
-      <c r="CY7" s="11"/>
-      <c r="CZ7" s="11"/>
-      <c r="DA7" s="11"/>
-      <c r="DB7" s="11"/>
+      <c r="AF7" s="8"/>
+      <c r="AG7" s="8"/>
+      <c r="AH7" s="8"/>
+      <c r="AI7" s="8"/>
+      <c r="AJ7" s="8"/>
+      <c r="AK7" s="8"/>
+      <c r="AL7" s="8"/>
+      <c r="AM7" s="8"/>
+      <c r="AN7" s="8"/>
+      <c r="AO7" s="8"/>
+      <c r="AP7" s="8"/>
+      <c r="AQ7" s="8"/>
+      <c r="AR7" s="8"/>
+      <c r="AS7" s="8"/>
+      <c r="AT7" s="8"/>
+      <c r="AU7" s="8"/>
+      <c r="AV7" s="8"/>
+      <c r="AW7" s="8"/>
+      <c r="AX7" s="8"/>
+      <c r="AY7" s="8"/>
+      <c r="AZ7" s="8"/>
+      <c r="BA7" s="8"/>
+      <c r="BB7" s="8"/>
+      <c r="BC7" s="8"/>
+      <c r="BD7" s="8"/>
+      <c r="BE7" s="8"/>
+      <c r="BF7" s="8"/>
+      <c r="BG7" s="8"/>
+      <c r="BH7" s="8"/>
+      <c r="BI7" s="8"/>
+      <c r="BJ7" s="8"/>
+      <c r="BK7" s="8"/>
+      <c r="BL7" s="8"/>
+      <c r="BM7" s="8"/>
+      <c r="BN7" s="8"/>
+      <c r="BO7" s="8"/>
+      <c r="BP7" s="8"/>
+      <c r="BQ7" s="8"/>
+      <c r="BR7" s="8"/>
+      <c r="BS7" s="8"/>
+      <c r="BT7" s="8"/>
+      <c r="BU7" s="8"/>
+      <c r="BV7" s="8"/>
+      <c r="BW7" s="8"/>
+      <c r="BX7" s="8"/>
+      <c r="BY7" s="8"/>
+      <c r="BZ7" s="8"/>
+      <c r="CA7" s="8"/>
+      <c r="CB7" s="8"/>
+      <c r="CC7" s="8"/>
+      <c r="CD7" s="8"/>
+      <c r="CE7" s="8"/>
+      <c r="CF7" s="8"/>
+      <c r="CG7" s="8"/>
+      <c r="CH7" s="8"/>
+      <c r="CI7" s="8"/>
+      <c r="CJ7" s="8"/>
+      <c r="CK7" s="8"/>
+      <c r="CL7" s="8"/>
+      <c r="CM7" s="8"/>
+      <c r="CN7" s="8"/>
+      <c r="CO7" s="8"/>
+      <c r="CP7" s="8"/>
+      <c r="CQ7" s="8"/>
+      <c r="CR7" s="8"/>
+      <c r="CS7" s="8"/>
+      <c r="CT7" s="8"/>
+      <c r="CU7" s="8"/>
+      <c r="CV7" s="8"/>
+      <c r="CW7" s="8"/>
+      <c r="CX7" s="8"/>
+      <c r="CY7" s="8"/>
+      <c r="CZ7" s="8"/>
+      <c r="DA7" s="8"/>
+      <c r="DB7" s="8"/>
     </row>
-    <row r="8" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="8">
         <v>27</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="8">
         <v>26</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="8">
         <v>22</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="8">
         <v>2</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="8">
         <v>10</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="8">
         <v>6</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="8">
         <v>6</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="8">
         <v>6</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="8">
         <v>0</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="8">
         <v>2</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="8">
         <v>10</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="8">
         <v>10</v>
       </c>
-      <c r="N8" s="11">
+      <c r="N8" s="8">
         <v>9</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="8">
         <v>1</v>
       </c>
-      <c r="P8" s="11">
+      <c r="P8" s="8">
         <v>1</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="Q8" s="8">
         <v>12</v>
       </c>
-      <c r="R8" s="11">
+      <c r="R8" s="8">
         <v>11</v>
       </c>
-      <c r="S8" s="11">
+      <c r="S8" s="8">
         <v>11</v>
       </c>
-      <c r="T8" s="11">
+      <c r="T8" s="8">
         <v>2</v>
       </c>
-      <c r="U8" s="11">
+      <c r="U8" s="8">
         <v>2</v>
       </c>
-      <c r="V8" s="11">
+      <c r="V8" s="8">
         <v>12</v>
       </c>
-      <c r="W8" s="11">
+      <c r="W8" s="8">
         <v>11</v>
       </c>
-      <c r="X8" s="11">
+      <c r="X8" s="8">
         <v>11</v>
       </c>
-      <c r="Y8" s="11">
+      <c r="Y8" s="8">
         <v>2</v>
       </c>
-      <c r="Z8" s="11">
+      <c r="Z8" s="8">
         <v>2</v>
       </c>
-      <c r="AA8" s="11">
+      <c r="AA8" s="8">
         <v>4</v>
       </c>
-      <c r="AB8" s="11">
+      <c r="AB8" s="8">
         <v>4</v>
       </c>
-      <c r="AC8" s="11">
+      <c r="AC8" s="8">
         <v>4</v>
       </c>
-      <c r="AD8" s="11">
+      <c r="AD8" s="8">
         <v>1</v>
       </c>
-      <c r="AE8" s="11">
+      <c r="AE8" s="8">
         <v>1</v>
       </c>
-      <c r="AF8" s="11"/>
-      <c r="AG8" s="11"/>
-      <c r="AH8" s="11"/>
-      <c r="AI8" s="11"/>
-      <c r="AJ8" s="11"/>
-      <c r="AK8" s="11"/>
-      <c r="AL8" s="11"/>
-      <c r="AM8" s="11"/>
-      <c r="AN8" s="11"/>
-      <c r="AO8" s="11"/>
-      <c r="AP8" s="11"/>
-      <c r="AQ8" s="11"/>
-      <c r="AR8" s="11"/>
-      <c r="AS8" s="11"/>
-      <c r="AT8" s="11"/>
-      <c r="AU8" s="11"/>
-      <c r="AV8" s="11"/>
-      <c r="AW8" s="11"/>
-      <c r="AX8" s="11"/>
-      <c r="AY8" s="11"/>
-      <c r="AZ8" s="11"/>
-      <c r="BA8" s="11"/>
-      <c r="BB8" s="11"/>
-      <c r="BC8" s="11"/>
-      <c r="BD8" s="11"/>
-      <c r="BE8" s="11"/>
-      <c r="BF8" s="11"/>
-      <c r="BG8" s="11"/>
-      <c r="BH8" s="11"/>
-      <c r="BI8" s="11"/>
-      <c r="BJ8" s="11"/>
-      <c r="BK8" s="11"/>
-      <c r="BL8" s="11"/>
-      <c r="BM8" s="11"/>
-      <c r="BN8" s="11"/>
-      <c r="BO8" s="11"/>
-      <c r="BP8" s="11"/>
-      <c r="BQ8" s="11"/>
-      <c r="BR8" s="11"/>
-      <c r="BS8" s="11"/>
-      <c r="BT8" s="11"/>
-      <c r="BU8" s="11"/>
-      <c r="BV8" s="11"/>
-      <c r="BW8" s="11"/>
-      <c r="BX8" s="11"/>
-      <c r="BY8" s="11"/>
-      <c r="BZ8" s="11"/>
-      <c r="CA8" s="11"/>
-      <c r="CB8" s="11"/>
-      <c r="CC8" s="11"/>
-      <c r="CD8" s="11"/>
-      <c r="CE8" s="11"/>
-      <c r="CF8" s="11"/>
-      <c r="CG8" s="11"/>
-      <c r="CH8" s="11"/>
-      <c r="CI8" s="11"/>
-      <c r="CJ8" s="11"/>
-      <c r="CK8" s="11"/>
-      <c r="CL8" s="11"/>
-      <c r="CM8" s="11"/>
-      <c r="CN8" s="11"/>
-      <c r="CO8" s="11"/>
-      <c r="CP8" s="11"/>
-      <c r="CQ8" s="11"/>
-      <c r="CR8" s="11"/>
-      <c r="CS8" s="11"/>
-      <c r="CT8" s="11"/>
-      <c r="CU8" s="11"/>
-      <c r="CV8" s="11"/>
-      <c r="CW8" s="11"/>
-      <c r="CX8" s="11"/>
-      <c r="CY8" s="11"/>
-      <c r="CZ8" s="11"/>
-      <c r="DA8" s="11"/>
-      <c r="DB8" s="11"/>
+      <c r="AF8" s="8"/>
+      <c r="AG8" s="8"/>
+      <c r="AH8" s="8"/>
+      <c r="AI8" s="8"/>
+      <c r="AJ8" s="8"/>
+      <c r="AK8" s="8"/>
+      <c r="AL8" s="8"/>
+      <c r="AM8" s="8"/>
+      <c r="AN8" s="8"/>
+      <c r="AO8" s="8"/>
+      <c r="AP8" s="8"/>
+      <c r="AQ8" s="8"/>
+      <c r="AR8" s="8"/>
+      <c r="AS8" s="8"/>
+      <c r="AT8" s="8"/>
+      <c r="AU8" s="8"/>
+      <c r="AV8" s="8"/>
+      <c r="AW8" s="8"/>
+      <c r="AX8" s="8"/>
+      <c r="AY8" s="8"/>
+      <c r="AZ8" s="8"/>
+      <c r="BA8" s="8"/>
+      <c r="BB8" s="8"/>
+      <c r="BC8" s="8"/>
+      <c r="BD8" s="8"/>
+      <c r="BE8" s="8"/>
+      <c r="BF8" s="8"/>
+      <c r="BG8" s="8"/>
+      <c r="BH8" s="8"/>
+      <c r="BI8" s="8"/>
+      <c r="BJ8" s="8"/>
+      <c r="BK8" s="8"/>
+      <c r="BL8" s="8"/>
+      <c r="BM8" s="8"/>
+      <c r="BN8" s="8"/>
+      <c r="BO8" s="8"/>
+      <c r="BP8" s="8"/>
+      <c r="BQ8" s="8"/>
+      <c r="BR8" s="8"/>
+      <c r="BS8" s="8"/>
+      <c r="BT8" s="8"/>
+      <c r="BU8" s="8"/>
+      <c r="BV8" s="8"/>
+      <c r="BW8" s="8"/>
+      <c r="BX8" s="8"/>
+      <c r="BY8" s="8"/>
+      <c r="BZ8" s="8"/>
+      <c r="CA8" s="8"/>
+      <c r="CB8" s="8"/>
+      <c r="CC8" s="8"/>
+      <c r="CD8" s="8"/>
+      <c r="CE8" s="8"/>
+      <c r="CF8" s="8"/>
+      <c r="CG8" s="8"/>
+      <c r="CH8" s="8"/>
+      <c r="CI8" s="8"/>
+      <c r="CJ8" s="8"/>
+      <c r="CK8" s="8"/>
+      <c r="CL8" s="8"/>
+      <c r="CM8" s="8"/>
+      <c r="CN8" s="8"/>
+      <c r="CO8" s="8"/>
+      <c r="CP8" s="8"/>
+      <c r="CQ8" s="8"/>
+      <c r="CR8" s="8"/>
+      <c r="CS8" s="8"/>
+      <c r="CT8" s="8"/>
+      <c r="CU8" s="8"/>
+      <c r="CV8" s="8"/>
+      <c r="CW8" s="8"/>
+      <c r="CX8" s="8"/>
+      <c r="CY8" s="8"/>
+      <c r="CZ8" s="8"/>
+      <c r="DA8" s="8"/>
+      <c r="DB8" s="8"/>
     </row>
-    <row r="9" spans="1:106" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:106" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="8">
         <v>31</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <v>30</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="8">
         <v>27</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="8">
         <v>1</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <v>8</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="8">
         <v>8</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="8">
         <v>8</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="8">
         <v>8</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="8">
         <v>2</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="8">
         <v>2</v>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="8">
         <v>12</v>
       </c>
-      <c r="M9" s="11">
+      <c r="M9" s="8">
         <v>12</v>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="8">
         <v>12</v>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="8">
         <v>0</v>
       </c>
-      <c r="P9" s="11">
+      <c r="P9" s="8">
         <v>1</v>
       </c>
-      <c r="Q9" s="11">
+      <c r="Q9" s="8">
         <v>15</v>
       </c>
-      <c r="R9" s="11">
+      <c r="R9" s="8">
         <v>15</v>
       </c>
-      <c r="S9" s="11">
+      <c r="S9" s="8">
         <v>15</v>
       </c>
-      <c r="T9" s="11">
+      <c r="T9" s="8">
         <v>1</v>
       </c>
-      <c r="U9" s="11">
+      <c r="U9" s="8">
         <v>1</v>
       </c>
-      <c r="V9" s="11">
+      <c r="V9" s="8">
         <v>15</v>
       </c>
-      <c r="W9" s="11">
+      <c r="W9" s="8">
         <v>15</v>
       </c>
-      <c r="X9" s="11">
+      <c r="X9" s="8">
         <v>15</v>
       </c>
-      <c r="Y9" s="11">
+      <c r="Y9" s="8">
         <v>1</v>
       </c>
-      <c r="Z9" s="11">
+      <c r="Z9" s="8">
         <v>1</v>
       </c>
-      <c r="AA9" s="11">
+      <c r="AA9" s="8">
         <v>2</v>
       </c>
-      <c r="AB9" s="11">
+      <c r="AB9" s="8">
         <v>2</v>
       </c>
-      <c r="AC9" s="11">
+      <c r="AC9" s="8">
         <v>2</v>
       </c>
-      <c r="AD9" s="11">
+      <c r="AD9" s="8">
         <v>0</v>
       </c>
-      <c r="AE9" s="11">
+      <c r="AE9" s="8">
         <v>1</v>
       </c>
-      <c r="AF9" s="11"/>
-      <c r="AG9" s="11"/>
-      <c r="AH9" s="11"/>
-      <c r="AI9" s="11"/>
-      <c r="AJ9" s="11"/>
-      <c r="AK9" s="11"/>
-      <c r="AL9" s="11"/>
-      <c r="AM9" s="11"/>
-      <c r="AN9" s="11"/>
-      <c r="AO9" s="11"/>
-      <c r="AP9" s="11"/>
-      <c r="AQ9" s="11"/>
-      <c r="AR9" s="11"/>
-      <c r="AS9" s="11"/>
-      <c r="AT9" s="11"/>
-      <c r="AU9" s="11"/>
-      <c r="AV9" s="11"/>
-      <c r="AW9" s="11"/>
-      <c r="AX9" s="11"/>
-      <c r="AY9" s="11"/>
-      <c r="AZ9" s="11"/>
-      <c r="BA9" s="11"/>
-      <c r="BB9" s="11"/>
-      <c r="BC9" s="11"/>
-      <c r="BD9" s="11"/>
-      <c r="BE9" s="11"/>
-      <c r="BF9" s="11"/>
-      <c r="BG9" s="11"/>
-      <c r="BH9" s="11"/>
-      <c r="BI9" s="11"/>
-      <c r="BJ9" s="11"/>
-      <c r="BK9" s="11"/>
-      <c r="BL9" s="11"/>
-      <c r="BM9" s="11"/>
-      <c r="BN9" s="11"/>
-      <c r="BO9" s="11"/>
-      <c r="BP9" s="11"/>
-      <c r="BQ9" s="11"/>
-      <c r="BR9" s="11"/>
-      <c r="BS9" s="11"/>
-      <c r="BT9" s="11"/>
-      <c r="BU9" s="11"/>
-      <c r="BV9" s="11"/>
-      <c r="BW9" s="11"/>
-      <c r="BX9" s="11"/>
-      <c r="BY9" s="11"/>
-      <c r="BZ9" s="11"/>
-      <c r="CA9" s="11"/>
-      <c r="CB9" s="11"/>
-      <c r="CC9" s="11"/>
-      <c r="CD9" s="11"/>
-      <c r="CE9" s="11"/>
-      <c r="CF9" s="11"/>
-      <c r="CG9" s="11"/>
-      <c r="CH9" s="11"/>
-      <c r="CI9" s="11"/>
-      <c r="CJ9" s="11"/>
-      <c r="CK9" s="11"/>
-      <c r="CL9" s="11"/>
-      <c r="CM9" s="11"/>
-      <c r="CN9" s="11"/>
-      <c r="CO9" s="11"/>
-      <c r="CP9" s="11"/>
-      <c r="CQ9" s="11"/>
-      <c r="CR9" s="11"/>
-      <c r="CS9" s="11"/>
-      <c r="CT9" s="11"/>
-      <c r="CU9" s="11"/>
-      <c r="CV9" s="11"/>
-      <c r="CW9" s="11"/>
-      <c r="CX9" s="11"/>
-      <c r="CY9" s="11"/>
-      <c r="CZ9" s="11"/>
-      <c r="DA9" s="11"/>
-      <c r="DB9" s="11"/>
+      <c r="AF9" s="8"/>
+      <c r="AG9" s="8"/>
+      <c r="AH9" s="8"/>
+      <c r="AI9" s="8"/>
+      <c r="AJ9" s="8"/>
+      <c r="AK9" s="8"/>
+      <c r="AL9" s="8"/>
+      <c r="AM9" s="8"/>
+      <c r="AN9" s="8"/>
+      <c r="AO9" s="8"/>
+      <c r="AP9" s="8"/>
+      <c r="AQ9" s="8"/>
+      <c r="AR9" s="8"/>
+      <c r="AS9" s="8"/>
+      <c r="AT9" s="8"/>
+      <c r="AU9" s="8"/>
+      <c r="AV9" s="8"/>
+      <c r="AW9" s="8"/>
+      <c r="AX9" s="8"/>
+      <c r="AY9" s="8"/>
+      <c r="AZ9" s="8"/>
+      <c r="BA9" s="8"/>
+      <c r="BB9" s="8"/>
+      <c r="BC9" s="8"/>
+      <c r="BD9" s="8"/>
+      <c r="BE9" s="8"/>
+      <c r="BF9" s="8"/>
+      <c r="BG9" s="8"/>
+      <c r="BH9" s="8"/>
+      <c r="BI9" s="8"/>
+      <c r="BJ9" s="8"/>
+      <c r="BK9" s="8"/>
+      <c r="BL9" s="8"/>
+      <c r="BM9" s="8"/>
+      <c r="BN9" s="8"/>
+      <c r="BO9" s="8"/>
+      <c r="BP9" s="8"/>
+      <c r="BQ9" s="8"/>
+      <c r="BR9" s="8"/>
+      <c r="BS9" s="8"/>
+      <c r="BT9" s="8"/>
+      <c r="BU9" s="8"/>
+      <c r="BV9" s="8"/>
+      <c r="BW9" s="8"/>
+      <c r="BX9" s="8"/>
+      <c r="BY9" s="8"/>
+      <c r="BZ9" s="8"/>
+      <c r="CA9" s="8"/>
+      <c r="CB9" s="8"/>
+      <c r="CC9" s="8"/>
+      <c r="CD9" s="8"/>
+      <c r="CE9" s="8"/>
+      <c r="CF9" s="8"/>
+      <c r="CG9" s="8"/>
+      <c r="CH9" s="8"/>
+      <c r="CI9" s="8"/>
+      <c r="CJ9" s="8"/>
+      <c r="CK9" s="8"/>
+      <c r="CL9" s="8"/>
+      <c r="CM9" s="8"/>
+      <c r="CN9" s="8"/>
+      <c r="CO9" s="8"/>
+      <c r="CP9" s="8"/>
+      <c r="CQ9" s="8"/>
+      <c r="CR9" s="8"/>
+      <c r="CS9" s="8"/>
+      <c r="CT9" s="8"/>
+      <c r="CU9" s="8"/>
+      <c r="CV9" s="8"/>
+      <c r="CW9" s="8"/>
+      <c r="CX9" s="8"/>
+      <c r="CY9" s="8"/>
+      <c r="CZ9" s="8"/>
+      <c r="DA9" s="8"/>
+      <c r="DB9" s="8"/>
     </row>
     <row r="10" spans="1:106" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="3">
         <f>SUM(B3:B9)</f>
         <v>133</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="3">
         <f t="shared" ref="C10:Q10" si="0">SUM(C3:C9)</f>
         <v>113</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="3">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="3">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="3">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="3">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="3">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="3">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="R10" s="6">
+      <c r="R10" s="3">
         <f t="shared" ref="R10" si="1">SUM(R3:R9)</f>
         <v>98</v>
       </c>
-      <c r="S10" s="6">
+      <c r="S10" s="3">
         <f t="shared" ref="S10" si="2">SUM(S3:S9)</f>
         <v>92</v>
       </c>
-      <c r="T10" s="6">
+      <c r="T10" s="3">
         <f t="shared" ref="T10" si="3">SUM(T3:T9)</f>
         <v>16</v>
       </c>
-      <c r="U10" s="6">
+      <c r="U10" s="3">
         <f t="shared" ref="U10" si="4">SUM(U3:U9)</f>
         <v>23</v>
       </c>
-      <c r="V10" s="6">
+      <c r="V10" s="3">
         <f t="shared" ref="V10" si="5">SUM(V3:V9)</f>
         <v>123</v>
       </c>
-      <c r="W10" s="6">
+      <c r="W10" s="3">
         <f t="shared" ref="W10" si="6">SUM(W3:W9)</f>
         <v>118</v>
       </c>
-      <c r="X10" s="6">
+      <c r="X10" s="3">
         <f t="shared" ref="X10" si="7">SUM(X3:X9)</f>
         <v>114</v>
       </c>
-      <c r="Y10" s="6">
+      <c r="Y10" s="3">
         <f t="shared" ref="Y10" si="8">SUM(Y3:Y9)</f>
         <v>15</v>
       </c>
-      <c r="Z10" s="6">
+      <c r="Z10" s="3">
         <f t="shared" ref="Z10" si="9">SUM(Z3:Z9)</f>
         <v>27</v>
       </c>
-      <c r="AA10" s="6">
+      <c r="AA10" s="3">
         <f t="shared" ref="AA10" si="10">SUM(AA3:AA9)</f>
         <v>60</v>
       </c>
-      <c r="AB10" s="6">
+      <c r="AB10" s="3">
         <f t="shared" ref="AB10" si="11">SUM(AB3:AB9)</f>
         <v>56</v>
       </c>
-      <c r="AC10" s="6">
+      <c r="AC10" s="3">
         <f t="shared" ref="AC10" si="12">SUM(AC3:AC9)</f>
         <v>55</v>
       </c>
-      <c r="AD10" s="6">
+      <c r="AD10" s="3">
         <f t="shared" ref="AD10" si="13">SUM(AD3:AD9)</f>
         <v>8</v>
       </c>
-      <c r="AE10" s="6">
+      <c r="AE10" s="3">
         <f t="shared" ref="AE10:AF10" si="14">SUM(AE3:AE9)</f>
         <v>14</v>
       </c>
-      <c r="AF10" s="6">
+      <c r="AF10" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AG10" s="6">
+      <c r="AG10" s="3">
         <f t="shared" ref="AG10" si="15">SUM(AG3:AG9)</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="6">
+      <c r="AH10" s="3">
         <f t="shared" ref="AH10" si="16">SUM(AH3:AH9)</f>
         <v>0</v>
       </c>
-      <c r="AI10" s="6">
+      <c r="AI10" s="3">
         <f t="shared" ref="AI10" si="17">SUM(AI3:AI9)</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="6">
+      <c r="AJ10" s="3">
         <f t="shared" ref="AJ10" si="18">SUM(AJ3:AJ9)</f>
         <v>0</v>
       </c>
-      <c r="AK10" s="6">
+      <c r="AK10" s="3">
         <f t="shared" ref="AK10" si="19">SUM(AK3:AK9)</f>
         <v>0</v>
       </c>
-      <c r="AL10" s="6">
+      <c r="AL10" s="3">
         <f t="shared" ref="AL10" si="20">SUM(AL3:AL9)</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="6">
+      <c r="AM10" s="3">
         <f t="shared" ref="AM10" si="21">SUM(AM3:AM9)</f>
         <v>0</v>
       </c>
-      <c r="AN10" s="6">
+      <c r="AN10" s="3">
         <f t="shared" ref="AN10" si="22">SUM(AN3:AN9)</f>
         <v>0</v>
       </c>
-      <c r="AO10" s="6">
+      <c r="AO10" s="3">
         <f t="shared" ref="AO10" si="23">SUM(AO3:AO9)</f>
         <v>0</v>
       </c>
-      <c r="AP10" s="6">
+      <c r="AP10" s="3">
         <f t="shared" ref="AP10" si="24">SUM(AP3:AP9)</f>
         <v>0</v>
       </c>
-      <c r="AQ10" s="6">
+      <c r="AQ10" s="3">
         <f t="shared" ref="AQ10" si="25">SUM(AQ3:AQ9)</f>
         <v>0</v>
       </c>
-      <c r="AR10" s="6">
+      <c r="AR10" s="3">
         <f t="shared" ref="AR10" si="26">SUM(AR3:AR9)</f>
         <v>0</v>
       </c>
-      <c r="AS10" s="6">
+      <c r="AS10" s="3">
         <f t="shared" ref="AS10" si="27">SUM(AS3:AS9)</f>
         <v>0</v>
       </c>
-      <c r="AT10" s="6">
+      <c r="AT10" s="3">
         <f t="shared" ref="AT10:AU10" si="28">SUM(AT3:AT9)</f>
         <v>0</v>
       </c>
-      <c r="AU10" s="6">
+      <c r="AU10" s="3">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AV10" s="6">
+      <c r="AV10" s="3">
         <f t="shared" ref="AV10" si="29">SUM(AV3:AV9)</f>
         <v>0</v>
       </c>
-      <c r="AW10" s="6">
+      <c r="AW10" s="3">
         <f t="shared" ref="AW10" si="30">SUM(AW3:AW9)</f>
         <v>0</v>
       </c>
-      <c r="AX10" s="6">
+      <c r="AX10" s="3">
         <f t="shared" ref="AX10" si="31">SUM(AX3:AX9)</f>
         <v>0</v>
       </c>
-      <c r="AY10" s="6">
+      <c r="AY10" s="3">
         <f t="shared" ref="AY10" si="32">SUM(AY3:AY9)</f>
         <v>0</v>
       </c>
-      <c r="AZ10" s="6">
+      <c r="AZ10" s="3">
         <f t="shared" ref="AZ10" si="33">SUM(AZ3:AZ9)</f>
         <v>0</v>
       </c>
-      <c r="BA10" s="6">
+      <c r="BA10" s="3">
         <f t="shared" ref="BA10" si="34">SUM(BA3:BA9)</f>
         <v>0</v>
       </c>
-      <c r="BB10" s="6">
+      <c r="BB10" s="3">
         <f t="shared" ref="BB10" si="35">SUM(BB3:BB9)</f>
         <v>0</v>
       </c>
-      <c r="BC10" s="6">
+      <c r="BC10" s="3">
         <f t="shared" ref="BC10" si="36">SUM(BC3:BC9)</f>
         <v>0</v>
       </c>
-      <c r="BD10" s="6">
+      <c r="BD10" s="3">
         <f t="shared" ref="BD10" si="37">SUM(BD3:BD9)</f>
         <v>0</v>
       </c>
-      <c r="BE10" s="6">
+      <c r="BE10" s="3">
         <f t="shared" ref="BE10" si="38">SUM(BE3:BE9)</f>
         <v>0</v>
       </c>
-      <c r="BF10" s="6">
+      <c r="BF10" s="3">
         <f t="shared" ref="BF10" si="39">SUM(BF3:BF9)</f>
         <v>0</v>
       </c>
-      <c r="BG10" s="6">
+      <c r="BG10" s="3">
         <f t="shared" ref="BG10" si="40">SUM(BG3:BG9)</f>
         <v>0</v>
       </c>
-      <c r="BH10" s="6">
+      <c r="BH10" s="3">
         <f t="shared" ref="BH10" si="41">SUM(BH3:BH9)</f>
         <v>0</v>
       </c>
-      <c r="BI10" s="6">
+      <c r="BI10" s="3">
         <f t="shared" ref="BI10:BJ10" si="42">SUM(BI3:BI9)</f>
         <v>0</v>
       </c>
-      <c r="BJ10" s="6">
+      <c r="BJ10" s="3">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="BK10" s="6">
+      <c r="BK10" s="3">
         <f t="shared" ref="BK10" si="43">SUM(BK3:BK9)</f>
         <v>0</v>
       </c>
-      <c r="BL10" s="6">
+      <c r="BL10" s="3">
         <f t="shared" ref="BL10" si="44">SUM(BL3:BL9)</f>
         <v>0</v>
       </c>
-      <c r="BM10" s="6">
+      <c r="BM10" s="3">
         <f t="shared" ref="BM10" si="45">SUM(BM3:BM9)</f>
         <v>0</v>
       </c>
-      <c r="BN10" s="6">
+      <c r="BN10" s="3">
         <f t="shared" ref="BN10" si="46">SUM(BN3:BN9)</f>
         <v>0</v>
       </c>
-      <c r="BO10" s="6">
+      <c r="BO10" s="3">
         <f t="shared" ref="BO10" si="47">SUM(BO3:BO9)</f>
         <v>0</v>
       </c>
-      <c r="BP10" s="6">
+      <c r="BP10" s="3">
         <f t="shared" ref="BP10" si="48">SUM(BP3:BP9)</f>
         <v>0</v>
       </c>
-      <c r="BQ10" s="6">
+      <c r="BQ10" s="3">
         <f t="shared" ref="BQ10" si="49">SUM(BQ3:BQ9)</f>
         <v>0</v>
       </c>
-      <c r="BR10" s="6">
+      <c r="BR10" s="3">
         <f t="shared" ref="BR10" si="50">SUM(BR3:BR9)</f>
         <v>0</v>
       </c>
-      <c r="BS10" s="6">
+      <c r="BS10" s="3">
         <f t="shared" ref="BS10" si="51">SUM(BS3:BS9)</f>
         <v>0</v>
       </c>
-      <c r="BT10" s="6">
+      <c r="BT10" s="3">
         <f t="shared" ref="BT10" si="52">SUM(BT3:BT9)</f>
         <v>0</v>
       </c>
-      <c r="BU10" s="6">
+      <c r="BU10" s="3">
         <f t="shared" ref="BU10" si="53">SUM(BU3:BU9)</f>
         <v>0</v>
       </c>
-      <c r="BV10" s="6">
+      <c r="BV10" s="3">
         <f t="shared" ref="BV10" si="54">SUM(BV3:BV9)</f>
         <v>0</v>
       </c>
-      <c r="BW10" s="6">
+      <c r="BW10" s="3">
         <f t="shared" ref="BW10" si="55">SUM(BW3:BW9)</f>
         <v>0</v>
       </c>
-      <c r="BX10" s="6">
+      <c r="BX10" s="3">
         <f t="shared" ref="BX10" si="56">SUM(BX3:BX9)</f>
         <v>0</v>
       </c>
-      <c r="BY10" s="6">
+      <c r="BY10" s="3">
         <f t="shared" ref="BY10" si="57">SUM(BY3:BY9)</f>
         <v>0</v>
       </c>
-      <c r="BZ10" s="6">
+      <c r="BZ10" s="3">
         <f t="shared" ref="BZ10" si="58">SUM(BZ3:BZ9)</f>
         <v>0</v>
       </c>
-      <c r="CA10" s="6">
+      <c r="CA10" s="3">
         <f t="shared" ref="CA10" si="59">SUM(CA3:CA9)</f>
         <v>0</v>
       </c>
-      <c r="CB10" s="6">
+      <c r="CB10" s="3">
         <f t="shared" ref="CB10" si="60">SUM(CB3:CB9)</f>
         <v>0</v>
       </c>
-      <c r="CC10" s="6">
+      <c r="CC10" s="3">
         <f t="shared" ref="CC10" si="61">SUM(CC3:CC9)</f>
         <v>0</v>
       </c>
-      <c r="CD10" s="6">
+      <c r="CD10" s="3">
         <f t="shared" ref="CD10" si="62">SUM(CD3:CD9)</f>
         <v>0</v>
       </c>
-      <c r="CE10" s="6">
+      <c r="CE10" s="3">
         <f t="shared" ref="CE10" si="63">SUM(CE3:CE9)</f>
         <v>0</v>
       </c>
-      <c r="CF10" s="6">
+      <c r="CF10" s="3">
         <f t="shared" ref="CF10" si="64">SUM(CF3:CF9)</f>
         <v>0</v>
       </c>
-      <c r="CG10" s="6">
+      <c r="CG10" s="3">
         <f t="shared" ref="CG10" si="65">SUM(CG3:CG9)</f>
         <v>0</v>
       </c>
-      <c r="CH10" s="6">
+      <c r="CH10" s="3">
         <f t="shared" ref="CH10" si="66">SUM(CH3:CH9)</f>
         <v>0</v>
       </c>
-      <c r="CI10" s="6">
+      <c r="CI10" s="3">
         <f t="shared" ref="CI10" si="67">SUM(CI3:CI9)</f>
         <v>0</v>
       </c>
-      <c r="CJ10" s="6">
+      <c r="CJ10" s="3">
         <f t="shared" ref="CJ10" si="68">SUM(CJ3:CJ9)</f>
         <v>0</v>
       </c>
-      <c r="CK10" s="6">
+      <c r="CK10" s="3">
         <f t="shared" ref="CK10" si="69">SUM(CK3:CK9)</f>
         <v>0</v>
       </c>
-      <c r="CL10" s="6">
+      <c r="CL10" s="3">
         <f t="shared" ref="CL10" si="70">SUM(CL3:CL9)</f>
         <v>0</v>
       </c>
-      <c r="CM10" s="6">
+      <c r="CM10" s="3">
         <f t="shared" ref="CM10" si="71">SUM(CM3:CM9)</f>
         <v>0</v>
       </c>
-      <c r="CN10" s="6">
+      <c r="CN10" s="3">
         <f t="shared" ref="CN10" si="72">SUM(CN3:CN9)</f>
         <v>0</v>
       </c>
-      <c r="CO10" s="6">
+      <c r="CO10" s="3">
         <f t="shared" ref="CO10" si="73">SUM(CO3:CO9)</f>
         <v>0</v>
       </c>
-      <c r="CP10" s="6">
+      <c r="CP10" s="3">
         <f t="shared" ref="CP10" si="74">SUM(CP3:CP9)</f>
         <v>0</v>
       </c>
-      <c r="CQ10" s="6">
+      <c r="CQ10" s="3">
         <f t="shared" ref="CQ10" si="75">SUM(CQ3:CQ9)</f>
         <v>0</v>
       </c>
-      <c r="CR10" s="6">
+      <c r="CR10" s="3">
         <f t="shared" ref="CR10" si="76">SUM(CR3:CR9)</f>
         <v>0</v>
       </c>
-      <c r="CS10" s="6">
+      <c r="CS10" s="3">
         <f t="shared" ref="CS10" si="77">SUM(CS3:CS9)</f>
         <v>0</v>
       </c>
-      <c r="CT10" s="6">
+      <c r="CT10" s="3">
         <f t="shared" ref="CT10" si="78">SUM(CT3:CT9)</f>
         <v>0</v>
       </c>
-      <c r="CU10" s="6">
+      <c r="CU10" s="3">
         <f t="shared" ref="CU10" si="79">SUM(CU3:CU9)</f>
         <v>0</v>
       </c>
-      <c r="CV10" s="6">
+      <c r="CV10" s="3">
         <f t="shared" ref="CV10" si="80">SUM(CV3:CV9)</f>
         <v>0</v>
       </c>
-      <c r="CW10" s="6">
+      <c r="CW10" s="3">
         <f t="shared" ref="CW10" si="81">SUM(CW3:CW9)</f>
         <v>0</v>
       </c>
-      <c r="CX10" s="6">
+      <c r="CX10" s="3">
         <f t="shared" ref="CX10" si="82">SUM(CX3:CX9)</f>
         <v>0</v>
       </c>
-      <c r="CY10" s="6">
+      <c r="CY10" s="3">
         <f t="shared" ref="CY10" si="83">SUM(CY3:CY9)</f>
         <v>0</v>
       </c>
-      <c r="CZ10" s="6">
+      <c r="CZ10" s="3">
         <f t="shared" ref="CZ10" si="84">SUM(CZ3:CZ9)</f>
         <v>0</v>
       </c>
-      <c r="DA10" s="6">
+      <c r="DA10" s="3">
         <f t="shared" ref="DA10" si="85">SUM(DA3:DA9)</f>
         <v>0</v>
       </c>
-      <c r="DB10" s="6">
+      <c r="DB10" s="3">
         <f t="shared" ref="DB10" si="86">SUM(DB3:DB9)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="CN1:CR1"/>
-    <mergeCell ref="CS1:CW1"/>
-    <mergeCell ref="CX1:DB1"/>
-    <mergeCell ref="BJ1:BN1"/>
-    <mergeCell ref="BO1:BS1"/>
-    <mergeCell ref="BT1:BX1"/>
-    <mergeCell ref="BY1:CC1"/>
-    <mergeCell ref="CD1:CH1"/>
-    <mergeCell ref="CI1:CM1"/>
     <mergeCell ref="BE1:BI1"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:K1"/>
@@ -15794,6 +15987,15 @@
     <mergeCell ref="AP1:AT1"/>
     <mergeCell ref="AU1:AY1"/>
     <mergeCell ref="AZ1:BD1"/>
+    <mergeCell ref="CN1:CR1"/>
+    <mergeCell ref="CS1:CW1"/>
+    <mergeCell ref="CX1:DB1"/>
+    <mergeCell ref="BJ1:BN1"/>
+    <mergeCell ref="BO1:BS1"/>
+    <mergeCell ref="BT1:BX1"/>
+    <mergeCell ref="BY1:CC1"/>
+    <mergeCell ref="CD1:CH1"/>
+    <mergeCell ref="CI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15975,193 +16177,193 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A1" s="14"/>
-      <c r="B1" s="19" t="s">
+      <c r="A1" s="11"/>
+      <c r="B1" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="18" t="s">
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="18" t="s">
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="18" t="s">
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="18" t="s">
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="18"/>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="18" t="s">
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-      <c r="AI1" s="18"/>
-      <c r="AJ1" s="18"/>
-      <c r="AK1" s="14"/>
-      <c r="AL1" s="18" t="s">
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16"/>
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="16"/>
+      <c r="AK1" s="11"/>
+      <c r="AL1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="AM1" s="18"/>
-      <c r="AN1" s="18"/>
-      <c r="AO1" s="18"/>
-      <c r="AP1" s="18"/>
+      <c r="AM1" s="16"/>
+      <c r="AN1" s="16"/>
+      <c r="AO1" s="16"/>
+      <c r="AP1" s="16"/>
     </row>
     <row r="2" spans="1:42" s="5" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="O2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="Q2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="R2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="S2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="T2" s="16" t="s">
+      <c r="T2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="U2" s="15" t="s">
+      <c r="U2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="15" t="s">
+      <c r="V2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="W2" s="15" t="s">
+      <c r="W2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="X2" s="15" t="s">
+      <c r="X2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="Y2" s="15" t="s">
+      <c r="Y2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="Z2" s="16" t="s">
+      <c r="Z2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AA2" s="15" t="s">
+      <c r="AA2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AB2" s="15" t="s">
+      <c r="AB2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="AC2" s="15" t="s">
+      <c r="AC2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="AD2" s="15" t="s">
+      <c r="AD2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="AE2" s="15" t="s">
+      <c r="AE2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AF2" s="16" t="s">
+      <c r="AF2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AG2" s="15" t="s">
+      <c r="AG2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AH2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="AI2" s="15" t="s">
+      <c r="AI2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="AJ2" s="15" t="s">
+      <c r="AJ2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="AK2" s="15" t="s">
+      <c r="AK2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AL2" s="16" t="s">
+      <c r="AL2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AM2" s="15" t="s">
+      <c r="AM2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AN2" s="15" t="s">
+      <c r="AN2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="AO2" s="15" t="s">
+      <c r="AO2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="AP2" s="15" t="s">
+      <c r="AP2" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B3" s="3">
@@ -16179,7 +16381,7 @@
       <c r="F3" s="3">
         <v>0</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="H3" s="3">
@@ -16197,7 +16399,7 @@
       <c r="L3" s="3">
         <v>1</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="N3" s="3">
@@ -16215,7 +16417,7 @@
       <c r="R3" s="3">
         <v>1</v>
       </c>
-      <c r="S3" s="13" t="s">
+      <c r="S3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="T3" s="3">
@@ -16233,7 +16435,7 @@
       <c r="X3" s="3">
         <v>0</v>
       </c>
-      <c r="Y3" s="13" t="s">
+      <c r="Y3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="Z3" s="3">
@@ -16251,7 +16453,7 @@
       <c r="AD3" s="3">
         <v>2</v>
       </c>
-      <c r="AE3" s="13" t="s">
+      <c r="AE3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="AF3" s="3">
@@ -16269,7 +16471,7 @@
       <c r="AJ3" s="3">
         <v>10</v>
       </c>
-      <c r="AK3" s="13" t="s">
+      <c r="AK3" s="10" t="s">
         <v>43</v>
       </c>
       <c r="AL3" s="3">
@@ -17185,48 +17387,132 @@
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="3"/>
-      <c r="AH11" s="3"/>
-      <c r="AI11" s="3"/>
-      <c r="AJ11" s="3"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="3"/>
-      <c r="AP11" s="3"/>
+      <c r="A11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="3">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="3">
+        <v>5</v>
+      </c>
+      <c r="I11" s="3">
+        <v>5</v>
+      </c>
+      <c r="J11" s="3">
+        <v>4</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1</v>
+      </c>
+      <c r="L11" s="3">
+        <v>1</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="3">
+        <v>50</v>
+      </c>
+      <c r="O11" s="3">
+        <v>45</v>
+      </c>
+      <c r="P11" s="3">
+        <v>42</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>10</v>
+      </c>
+      <c r="R11" s="3">
+        <v>13</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T11" s="3">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3">
+        <v>0</v>
+      </c>
+      <c r="V11" s="3">
+        <v>0</v>
+      </c>
+      <c r="W11" s="3">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>18</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>18</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>17</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>4</v>
+      </c>
+      <c r="AE11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>14</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>10</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>4</v>
+      </c>
+      <c r="AI11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK11" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="AL11" s="3">
+        <v>15</v>
+      </c>
+      <c r="AM11" s="3">
+        <v>14</v>
+      </c>
+      <c r="AN11" s="3">
+        <v>5</v>
+      </c>
+      <c r="AO11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AP11" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>

--- a/documents/지표/주별활동지수.xlsx
+++ b/documents/지표/주별활동지수.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf1f1df607fbac1a/Desktop/Github/2026-QI/documents/지표/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1417F7F4-6396-4D55-8B4F-F564B8A920D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1DA1A0A-19A7-4975-A79D-A7FF1F99D0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{0FC1208A-2CB8-4E1E-B9D0-F7D163D68827}"/>
   </bookViews>
@@ -22,6 +22,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -30,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="53">
   <si>
     <t>1주차</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -214,6 +223,10 @@
     <t>9주차(7/16~7/22)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>10주차(7/23~7/29)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -342,7 +355,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -384,9 +397,6 @@
     </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1473,9 +1483,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$11</c:f>
+              <c:f>Sheet1!$A$3:$A$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1502,16 +1512,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$B$11</c:f>
+              <c:f>Sheet1!$B$3:$B$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -1538,6 +1551,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1631,9 +1647,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$11</c:f>
+              <c:f>Sheet1!$A$3:$A$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1660,16 +1676,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$3:$C$11</c:f>
+              <c:f>Sheet1!$C$3:$C$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -1696,6 +1715,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1789,9 +1811,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$11</c:f>
+              <c:f>Sheet1!$A$3:$A$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1818,16 +1840,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$3:$D$11</c:f>
+              <c:f>Sheet1!$D$3:$D$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1854,6 +1879,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1947,9 +1975,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$11</c:f>
+              <c:f>Sheet1!$A$3:$A$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1976,16 +2004,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$3:$E$11</c:f>
+              <c:f>Sheet1!$E$3:$E$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -2011,6 +2042,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2105,9 +2139,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$11</c:f>
+              <c:f>Sheet1!$A$3:$A$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2134,16 +2168,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$3:$F$11</c:f>
+              <c:f>Sheet1!$F$3:$F$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2170,6 +2207,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2542,9 +2582,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$11</c:f>
+              <c:f>Sheet1!$G$3:$G$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2571,16 +2611,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$3:$H$11</c:f>
+              <c:f>Sheet1!$H$3:$H$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
@@ -2607,6 +2650,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2700,9 +2746,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$11</c:f>
+              <c:f>Sheet1!$G$3:$G$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2729,16 +2775,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$I$3:$I$11</c:f>
+              <c:f>Sheet1!$I$3:$I$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -2765,6 +2814,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2858,9 +2910,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$11</c:f>
+              <c:f>Sheet1!$G$3:$G$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2887,16 +2939,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$3:$J$11</c:f>
+              <c:f>Sheet1!$J$3:$J$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -2923,6 +2978,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3016,9 +3074,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$11</c:f>
+              <c:f>Sheet1!$G$3:$G$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3045,16 +3103,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$K$3:$K$11</c:f>
+              <c:f>Sheet1!$K$3:$K$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3080,6 +3141,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3174,9 +3238,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$11</c:f>
+              <c:f>Sheet1!$G$3:$G$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3203,16 +3267,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$3:$L$11</c:f>
+              <c:f>Sheet1!$L$3:$L$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3238,6 +3305,9 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3612,9 +3682,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$11</c:f>
+              <c:f>Sheet1!$M$3:$M$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3641,16 +3711,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$N$3:$N$11</c:f>
+              <c:f>Sheet1!$N$3:$N$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>6</c:v>
                 </c:pt>
@@ -3677,6 +3750,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>29</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3771,9 +3847,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$11</c:f>
+              <c:f>Sheet1!$M$3:$M$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3800,16 +3876,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$O$3:$O$11</c:f>
+              <c:f>Sheet1!$O$3:$O$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -3836,6 +3915,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3930,9 +4012,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$11</c:f>
+              <c:f>Sheet1!$M$3:$M$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3959,16 +4041,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$P$3:$P$11</c:f>
+              <c:f>Sheet1!$P$3:$P$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -3995,6 +4080,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4089,9 +4177,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$11</c:f>
+              <c:f>Sheet1!$M$3:$M$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4118,16 +4206,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Q$3:$Q$11</c:f>
+              <c:f>Sheet1!$Q$3:$Q$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4154,6 +4245,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4248,9 +4342,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$11</c:f>
+              <c:f>Sheet1!$M$3:$M$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4277,16 +4371,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$R$3:$R$11</c:f>
+              <c:f>Sheet1!$R$3:$R$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4313,6 +4410,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4687,9 +4787,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$11</c:f>
+              <c:f>Sheet1!$S$3:$S$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4716,16 +4816,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$T$3:$T$11</c:f>
+              <c:f>Sheet1!$T$3:$T$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4751,6 +4854,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4846,9 +4952,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$11</c:f>
+              <c:f>Sheet1!$S$3:$S$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4875,16 +4981,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$U$3:$U$11</c:f>
+              <c:f>Sheet1!$U$3:$U$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4910,6 +5019,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5005,9 +5117,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$11</c:f>
+              <c:f>Sheet1!$S$3:$S$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5034,16 +5146,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$V$3:$V$11</c:f>
+              <c:f>Sheet1!$V$3:$V$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5069,6 +5184,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5164,9 +5282,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$11</c:f>
+              <c:f>Sheet1!$S$3:$S$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5193,16 +5311,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$W$3:$W$11</c:f>
+              <c:f>Sheet1!$W$3:$W$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5228,6 +5349,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5323,9 +5447,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$11</c:f>
+              <c:f>Sheet1!$S$3:$S$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5352,16 +5476,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$X$3:$X$11</c:f>
+              <c:f>Sheet1!$X$3:$X$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5387,6 +5514,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5765,9 +5895,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$11</c:f>
+              <c:f>Sheet1!$Y$3:$Y$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5794,16 +5924,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Z$3:$Z$11</c:f>
+              <c:f>Sheet1!$Z$3:$Z$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>47</c:v>
                 </c:pt>
@@ -5830,6 +5963,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5924,9 +6060,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$11</c:f>
+              <c:f>Sheet1!$Y$3:$Y$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5953,16 +6089,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AA$3:$AA$11</c:f>
+              <c:f>Sheet1!$AA$3:$AA$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>43</c:v>
                 </c:pt>
@@ -5989,6 +6128,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6083,9 +6225,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$11</c:f>
+              <c:f>Sheet1!$Y$3:$Y$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6112,16 +6254,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AB$3:$AB$11</c:f>
+              <c:f>Sheet1!$AB$3:$AB$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>39</c:v>
                 </c:pt>
@@ -6148,6 +6293,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6242,9 +6390,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$11</c:f>
+              <c:f>Sheet1!$Y$3:$Y$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6271,16 +6419,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AC$3:$AC$11</c:f>
+              <c:f>Sheet1!$AC$3:$AC$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -6307,6 +6458,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6401,9 +6555,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$11</c:f>
+              <c:f>Sheet1!$Y$3:$Y$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6430,16 +6584,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AD$3:$AD$11</c:f>
+              <c:f>Sheet1!$AD$3:$AD$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -6466,6 +6623,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6843,9 +7003,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$11</c:f>
+              <c:f>Sheet1!$AE$3:$AE$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6872,16 +7032,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AF$3:$AF$11</c:f>
+              <c:f>Sheet1!$AF$3:$AF$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>27</c:v>
                 </c:pt>
@@ -6908,6 +7071,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7002,9 +7168,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$11</c:f>
+              <c:f>Sheet1!$AE$3:$AE$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7031,16 +7197,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AG$3:$AG$11</c:f>
+              <c:f>Sheet1!$AG$3:$AG$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>26</c:v>
                 </c:pt>
@@ -7067,6 +7236,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7161,9 +7333,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$11</c:f>
+              <c:f>Sheet1!$AE$3:$AE$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7190,16 +7362,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AH$3:$AH$11</c:f>
+              <c:f>Sheet1!$AH$3:$AH$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>22</c:v>
                 </c:pt>
@@ -7226,6 +7401,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7320,9 +7498,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$11</c:f>
+              <c:f>Sheet1!$AE$3:$AE$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7349,16 +7527,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AI$3:$AI$11</c:f>
+              <c:f>Sheet1!$AI$3:$AI$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -7385,6 +7566,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7479,9 +7663,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$11</c:f>
+              <c:f>Sheet1!$AE$3:$AE$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7508,16 +7692,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AJ$3:$AJ$11</c:f>
+              <c:f>Sheet1!$AJ$3:$AJ$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -7544,6 +7731,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7922,9 +8112,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$11</c:f>
+              <c:f>Sheet1!$AK$3:$AK$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7951,16 +8141,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AL$3:$AL$11</c:f>
+              <c:f>Sheet1!$AL$3:$AL$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>31</c:v>
                 </c:pt>
@@ -7987,6 +8180,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8081,9 +8277,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$11</c:f>
+              <c:f>Sheet1!$AK$3:$AK$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8110,16 +8306,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AM$3:$AM$11</c:f>
+              <c:f>Sheet1!$AM$3:$AM$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>30</c:v>
                 </c:pt>
@@ -8146,6 +8345,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8240,9 +8442,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$11</c:f>
+              <c:f>Sheet1!$AK$3:$AK$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8269,16 +8471,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AN$3:$AN$11</c:f>
+              <c:f>Sheet1!$AN$3:$AN$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>27</c:v>
                 </c:pt>
@@ -8305,6 +8510,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8399,9 +8607,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$11</c:f>
+              <c:f>Sheet1!$AK$3:$AK$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8428,16 +8636,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AO$3:$AO$11</c:f>
+              <c:f>Sheet1!$AO$3:$AO$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -8463,6 +8674,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -8558,9 +8772,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$11</c:f>
+              <c:f>Sheet1!$AK$3:$AK$12</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8587,16 +8801,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9주차(7/16~7/22)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10주차(7/23~7/29)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AP$3:$AP$11</c:f>
+              <c:f>Sheet1!$AP$3:$AP$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -8622,6 +8839,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -13227,15 +13447,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>80962</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>193301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>112059</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>31097</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>78441</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13304,8 +13524,8 @@
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>470647</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>166687</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>134471</xdr:rowOff>
     </xdr:to>
@@ -13890,153 +14110,153 @@
   <sheetData>
     <row r="1" spans="1:106" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15" t="s">
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15" t="s">
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15" t="s">
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15" t="s">
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15"/>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15" t="s">
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15"/>
-      <c r="AI1" s="15"/>
-      <c r="AJ1" s="15"/>
-      <c r="AK1" s="15" t="s">
+      <c r="AG1" s="14"/>
+      <c r="AH1" s="14"/>
+      <c r="AI1" s="14"/>
+      <c r="AJ1" s="14"/>
+      <c r="AK1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AL1" s="15"/>
-      <c r="AM1" s="15"/>
-      <c r="AN1" s="15"/>
-      <c r="AO1" s="15"/>
-      <c r="AP1" s="15" t="s">
+      <c r="AL1" s="14"/>
+      <c r="AM1" s="14"/>
+      <c r="AN1" s="14"/>
+      <c r="AO1" s="14"/>
+      <c r="AP1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="AQ1" s="15"/>
-      <c r="AR1" s="15"/>
-      <c r="AS1" s="15"/>
-      <c r="AT1" s="15"/>
-      <c r="AU1" s="15" t="s">
+      <c r="AQ1" s="14"/>
+      <c r="AR1" s="14"/>
+      <c r="AS1" s="14"/>
+      <c r="AT1" s="14"/>
+      <c r="AU1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="AV1" s="15"/>
-      <c r="AW1" s="15"/>
-      <c r="AX1" s="15"/>
-      <c r="AY1" s="15"/>
-      <c r="AZ1" s="15" t="s">
+      <c r="AV1" s="14"/>
+      <c r="AW1" s="14"/>
+      <c r="AX1" s="14"/>
+      <c r="AY1" s="14"/>
+      <c r="AZ1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="BA1" s="15"/>
-      <c r="BB1" s="15"/>
-      <c r="BC1" s="15"/>
-      <c r="BD1" s="15"/>
-      <c r="BE1" s="15" t="s">
+      <c r="BA1" s="14"/>
+      <c r="BB1" s="14"/>
+      <c r="BC1" s="14"/>
+      <c r="BD1" s="14"/>
+      <c r="BE1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="BF1" s="15"/>
-      <c r="BG1" s="15"/>
-      <c r="BH1" s="15"/>
-      <c r="BI1" s="15"/>
-      <c r="BJ1" s="15" t="s">
+      <c r="BF1" s="14"/>
+      <c r="BG1" s="14"/>
+      <c r="BH1" s="14"/>
+      <c r="BI1" s="14"/>
+      <c r="BJ1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="BK1" s="15"/>
-      <c r="BL1" s="15"/>
-      <c r="BM1" s="15"/>
-      <c r="BN1" s="15"/>
-      <c r="BO1" s="15" t="s">
+      <c r="BK1" s="14"/>
+      <c r="BL1" s="14"/>
+      <c r="BM1" s="14"/>
+      <c r="BN1" s="14"/>
+      <c r="BO1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="BP1" s="15"/>
-      <c r="BQ1" s="15"/>
-      <c r="BR1" s="15"/>
-      <c r="BS1" s="15"/>
-      <c r="BT1" s="15" t="s">
+      <c r="BP1" s="14"/>
+      <c r="BQ1" s="14"/>
+      <c r="BR1" s="14"/>
+      <c r="BS1" s="14"/>
+      <c r="BT1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="BU1" s="15"/>
-      <c r="BV1" s="15"/>
-      <c r="BW1" s="15"/>
-      <c r="BX1" s="15"/>
-      <c r="BY1" s="15" t="s">
+      <c r="BU1" s="14"/>
+      <c r="BV1" s="14"/>
+      <c r="BW1" s="14"/>
+      <c r="BX1" s="14"/>
+      <c r="BY1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="BZ1" s="15"/>
-      <c r="CA1" s="15"/>
-      <c r="CB1" s="15"/>
-      <c r="CC1" s="15"/>
-      <c r="CD1" s="15" t="s">
+      <c r="BZ1" s="14"/>
+      <c r="CA1" s="14"/>
+      <c r="CB1" s="14"/>
+      <c r="CC1" s="14"/>
+      <c r="CD1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="CE1" s="15"/>
-      <c r="CF1" s="15"/>
-      <c r="CG1" s="15"/>
-      <c r="CH1" s="15"/>
-      <c r="CI1" s="15" t="s">
+      <c r="CE1" s="14"/>
+      <c r="CF1" s="14"/>
+      <c r="CG1" s="14"/>
+      <c r="CH1" s="14"/>
+      <c r="CI1" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="CJ1" s="15"/>
-      <c r="CK1" s="15"/>
-      <c r="CL1" s="15"/>
-      <c r="CM1" s="15"/>
-      <c r="CN1" s="15" t="s">
+      <c r="CJ1" s="14"/>
+      <c r="CK1" s="14"/>
+      <c r="CL1" s="14"/>
+      <c r="CM1" s="14"/>
+      <c r="CN1" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="CO1" s="15"/>
-      <c r="CP1" s="15"/>
-      <c r="CQ1" s="15"/>
-      <c r="CR1" s="15"/>
-      <c r="CS1" s="15" t="s">
+      <c r="CO1" s="14"/>
+      <c r="CP1" s="14"/>
+      <c r="CQ1" s="14"/>
+      <c r="CR1" s="14"/>
+      <c r="CS1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="CT1" s="15"/>
-      <c r="CU1" s="15"/>
-      <c r="CV1" s="15"/>
-      <c r="CW1" s="15"/>
-      <c r="CX1" s="15" t="s">
+      <c r="CT1" s="14"/>
+      <c r="CU1" s="14"/>
+      <c r="CV1" s="14"/>
+      <c r="CW1" s="14"/>
+      <c r="CX1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="CY1" s="15"/>
-      <c r="CZ1" s="15"/>
-      <c r="DA1" s="15"/>
-      <c r="DB1" s="15"/>
+      <c r="CY1" s="14"/>
+      <c r="CZ1" s="14"/>
+      <c r="DA1" s="14"/>
+      <c r="DB1" s="14"/>
     </row>
     <row r="2" spans="1:106" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -16178,61 +16398,61 @@
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A1" s="11"/>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="19"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
       <c r="G1" s="11"/>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
       <c r="M1" s="11"/>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
       <c r="S1" s="11"/>
-      <c r="T1" s="16" t="s">
+      <c r="T1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
       <c r="Y1" s="11"/>
-      <c r="Z1" s="16" t="s">
+      <c r="Z1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16"/>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
       <c r="AE1" s="11"/>
-      <c r="AF1" s="16" t="s">
+      <c r="AF1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16"/>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
       <c r="AK1" s="11"/>
-      <c r="AL1" s="16" t="s">
+      <c r="AL1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="AM1" s="16"/>
-      <c r="AN1" s="16"/>
-      <c r="AO1" s="16"/>
-      <c r="AP1" s="16"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15"/>
     </row>
     <row r="2" spans="1:42" s="5" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -17495,7 +17715,7 @@
       <c r="AJ11" s="3">
         <v>1</v>
       </c>
-      <c r="AK11" s="14" t="s">
+      <c r="AK11" s="3" t="s">
         <v>51</v>
       </c>
       <c r="AL11" s="3">
@@ -17515,48 +17735,132 @@
       </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
-      <c r="AF12" s="3"/>
-      <c r="AG12" s="3"/>
-      <c r="AH12" s="3"/>
-      <c r="AI12" s="3"/>
-      <c r="AJ12" s="3"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
-      <c r="AM12" s="3"/>
-      <c r="AN12" s="3"/>
-      <c r="AO12" s="3"/>
-      <c r="AP12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="3">
+        <v>14</v>
+      </c>
+      <c r="C12" s="3">
+        <v>14</v>
+      </c>
+      <c r="D12" s="3">
+        <v>14</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="3">
+        <v>13</v>
+      </c>
+      <c r="I12" s="3">
+        <v>13</v>
+      </c>
+      <c r="J12" s="3">
+        <v>13</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N12" s="3">
+        <v>29</v>
+      </c>
+      <c r="O12" s="3">
+        <v>27</v>
+      </c>
+      <c r="P12" s="3">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3">
+        <v>11</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>28</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>28</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>26</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>4</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>5</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>17</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>17</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>16</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>2</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>4</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AL12" s="3">
+        <v>8</v>
+      </c>
+      <c r="AM12" s="3">
+        <v>8</v>
+      </c>
+      <c r="AN12" s="3">
+        <v>8</v>
+      </c>
+      <c r="AO12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AP12" s="3">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/documents/지표/주별활동지수.xlsx
+++ b/documents/지표/주별활동지수.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf1f1df607fbac1a/Desktop/Github/2026-QI/documents/지표/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1DA1A0A-19A7-4975-A79D-A7FF1F99D0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DDA23EC-436E-4956-947D-B498594A0EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{0FC1208A-2CB8-4E1E-B9D0-F7D163D68827}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="55">
   <si>
     <t>1주차</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -227,6 +227,13 @@
     <t>10주차(7/23~7/29)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>11주차(7/30~8/5)</t>
+  </si>
+  <si>
+    <t>11주차(7/30~8/5)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -289,7 +296,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -349,13 +356,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -397,6 +415,9 @@
     </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1483,9 +1504,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$12</c:f>
+              <c:f>Sheet1!$A$3:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1515,16 +1536,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$B$12</c:f>
+              <c:f>Sheet1!$B$3:$B$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -1554,6 +1578,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1647,9 +1674,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$12</c:f>
+              <c:f>Sheet1!$A$3:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1679,16 +1706,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$3:$C$12</c:f>
+              <c:f>Sheet1!$C$3:$C$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
@@ -1718,6 +1748,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1811,9 +1844,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$12</c:f>
+              <c:f>Sheet1!$A$3:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -1843,16 +1876,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$3:$D$12</c:f>
+              <c:f>Sheet1!$D$3:$D$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1882,6 +1918,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1975,9 +2014,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$12</c:f>
+              <c:f>Sheet1!$A$3:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2007,16 +2046,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$3:$E$12</c:f>
+              <c:f>Sheet1!$E$3:$E$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -2045,6 +2087,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2139,9 +2184,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$12</c:f>
+              <c:f>Sheet1!$A$3:$A$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2171,16 +2216,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$3:$F$12</c:f>
+              <c:f>Sheet1!$F$3:$F$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2209,6 +2257,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -2582,9 +2633,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$12</c:f>
+              <c:f>Sheet1!$G$3:$G$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2614,16 +2665,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$3:$H$12</c:f>
+              <c:f>Sheet1!$H$3:$H$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
@@ -2653,6 +2707,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2746,9 +2803,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$12</c:f>
+              <c:f>Sheet1!$G$3:$G$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2778,16 +2835,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$I$3:$I$12</c:f>
+              <c:f>Sheet1!$I$3:$I$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -2817,6 +2877,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2910,9 +2973,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$12</c:f>
+              <c:f>Sheet1!$G$3:$G$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -2942,16 +3005,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$3:$J$12</c:f>
+              <c:f>Sheet1!$J$3:$J$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -2981,6 +3047,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3074,9 +3143,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$12</c:f>
+              <c:f>Sheet1!$G$3:$G$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3106,16 +3175,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$K$3:$K$12</c:f>
+              <c:f>Sheet1!$K$3:$K$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3144,6 +3216,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3238,9 +3313,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$G$3:$G$12</c:f>
+              <c:f>Sheet1!$G$3:$G$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3270,16 +3345,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$3:$L$12</c:f>
+              <c:f>Sheet1!$L$3:$L$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3309,6 +3387,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3682,9 +3763,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$12</c:f>
+              <c:f>Sheet1!$M$3:$M$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3714,16 +3795,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$N$3:$N$12</c:f>
+              <c:f>Sheet1!$N$3:$N$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>6</c:v>
                 </c:pt>
@@ -3753,6 +3837,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>43</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3847,9 +3934,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$12</c:f>
+              <c:f>Sheet1!$M$3:$M$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -3879,16 +3966,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$O$3:$O$12</c:f>
+              <c:f>Sheet1!$O$3:$O$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>5</c:v>
                 </c:pt>
@@ -3918,6 +4008,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4012,9 +4105,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$12</c:f>
+              <c:f>Sheet1!$M$3:$M$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4044,16 +4137,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$P$3:$P$12</c:f>
+              <c:f>Sheet1!$P$3:$P$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -4083,6 +4179,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4177,9 +4276,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$12</c:f>
+              <c:f>Sheet1!$M$3:$M$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4209,16 +4308,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Q$3:$Q$12</c:f>
+              <c:f>Sheet1!$Q$3:$Q$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4248,6 +4350,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4342,9 +4447,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$M$3:$M$12</c:f>
+              <c:f>Sheet1!$M$3:$M$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4374,16 +4479,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$R$3:$R$12</c:f>
+              <c:f>Sheet1!$R$3:$R$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4413,6 +4521,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4787,9 +4898,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$12</c:f>
+              <c:f>Sheet1!$S$3:$S$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4819,16 +4930,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$T$3:$T$12</c:f>
+              <c:f>Sheet1!$T$3:$T$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4857,6 +4971,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4952,9 +5069,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$12</c:f>
+              <c:f>Sheet1!$S$3:$S$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -4984,16 +5101,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$U$3:$U$12</c:f>
+              <c:f>Sheet1!$U$3:$U$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5022,6 +5142,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5117,9 +5240,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$12</c:f>
+              <c:f>Sheet1!$S$3:$S$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5149,16 +5272,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$V$3:$V$12</c:f>
+              <c:f>Sheet1!$V$3:$V$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5187,6 +5313,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5282,9 +5411,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$12</c:f>
+              <c:f>Sheet1!$S$3:$S$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5314,16 +5443,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$W$3:$W$12</c:f>
+              <c:f>Sheet1!$W$3:$W$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5352,6 +5484,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5447,9 +5582,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$S$3:$S$12</c:f>
+              <c:f>Sheet1!$S$3:$S$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5479,16 +5614,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$X$3:$X$12</c:f>
+              <c:f>Sheet1!$X$3:$X$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5517,6 +5655,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5895,9 +6036,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$12</c:f>
+              <c:f>Sheet1!$Y$3:$Y$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -5927,16 +6068,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$Z$3:$Z$12</c:f>
+              <c:f>Sheet1!$Z$3:$Z$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>47</c:v>
                 </c:pt>
@@ -5966,6 +6110,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6060,9 +6207,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$12</c:f>
+              <c:f>Sheet1!$Y$3:$Y$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6092,16 +6239,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AA$3:$AA$12</c:f>
+              <c:f>Sheet1!$AA$3:$AA$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>43</c:v>
                 </c:pt>
@@ -6131,6 +6281,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6225,9 +6378,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$12</c:f>
+              <c:f>Sheet1!$Y$3:$Y$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6257,16 +6410,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AB$3:$AB$12</c:f>
+              <c:f>Sheet1!$AB$3:$AB$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>39</c:v>
                 </c:pt>
@@ -6296,6 +6452,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6390,9 +6549,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$12</c:f>
+              <c:f>Sheet1!$Y$3:$Y$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6422,16 +6581,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AC$3:$AC$12</c:f>
+              <c:f>Sheet1!$AC$3:$AC$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -6461,6 +6623,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6555,9 +6720,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$Y$3:$Y$12</c:f>
+              <c:f>Sheet1!$Y$3:$Y$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -6587,16 +6752,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AD$3:$AD$12</c:f>
+              <c:f>Sheet1!$AD$3:$AD$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -6626,6 +6794,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7003,9 +7174,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$12</c:f>
+              <c:f>Sheet1!$AE$3:$AE$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7035,16 +7206,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AF$3:$AF$12</c:f>
+              <c:f>Sheet1!$AF$3:$AF$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>27</c:v>
                 </c:pt>
@@ -7074,6 +7248,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7168,9 +7345,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$12</c:f>
+              <c:f>Sheet1!$AE$3:$AE$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7200,16 +7377,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AG$3:$AG$12</c:f>
+              <c:f>Sheet1!$AG$3:$AG$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>26</c:v>
                 </c:pt>
@@ -7239,6 +7419,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7333,9 +7516,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$12</c:f>
+              <c:f>Sheet1!$AE$3:$AE$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7365,16 +7548,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AH$3:$AH$12</c:f>
+              <c:f>Sheet1!$AH$3:$AH$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>22</c:v>
                 </c:pt>
@@ -7404,6 +7590,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7498,9 +7687,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$12</c:f>
+              <c:f>Sheet1!$AE$3:$AE$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7530,16 +7719,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AI$3:$AI$12</c:f>
+              <c:f>Sheet1!$AI$3:$AI$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -7568,6 +7760,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -7663,9 +7858,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AE$3:$AE$12</c:f>
+              <c:f>Sheet1!$AE$3:$AE$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -7695,16 +7890,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AJ$3:$AJ$12</c:f>
+              <c:f>Sheet1!$AJ$3:$AJ$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -7734,6 +7932,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8112,9 +8313,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$12</c:f>
+              <c:f>Sheet1!$AK$3:$AK$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8144,16 +8345,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AL$3:$AL$12</c:f>
+              <c:f>Sheet1!$AL$3:$AL$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>31</c:v>
                 </c:pt>
@@ -8183,6 +8387,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8277,9 +8484,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$12</c:f>
+              <c:f>Sheet1!$AK$3:$AK$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8309,16 +8516,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AM$3:$AM$12</c:f>
+              <c:f>Sheet1!$AM$3:$AM$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>30</c:v>
                 </c:pt>
@@ -8348,6 +8558,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8442,9 +8655,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$12</c:f>
+              <c:f>Sheet1!$AK$3:$AK$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8474,16 +8687,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AN$3:$AN$12</c:f>
+              <c:f>Sheet1!$AN$3:$AN$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>27</c:v>
                 </c:pt>
@@ -8513,6 +8729,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8607,9 +8826,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$12</c:f>
+              <c:f>Sheet1!$AK$3:$AK$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8639,16 +8858,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AO$3:$AO$12</c:f>
+              <c:f>Sheet1!$AO$3:$AO$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -8677,6 +8899,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -8772,9 +8997,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$AK$3:$AK$12</c:f>
+              <c:f>Sheet1!$AK$3:$AK$13</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1주차(5/15~26)</c:v>
                 </c:pt>
@@ -8804,16 +9029,19 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10주차(7/23~7/29)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11주차(7/30~8/5)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AP$3:$AP$12</c:f>
+              <c:f>Sheet1!$AP$3:$AP$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -8842,6 +9070,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -14110,153 +14341,153 @@
   <sheetData>
     <row r="1" spans="1:106" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14" t="s">
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14" t="s">
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14" t="s">
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14" t="s">
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14" t="s">
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="14"/>
-      <c r="AH1" s="14"/>
-      <c r="AI1" s="14"/>
-      <c r="AJ1" s="14"/>
-      <c r="AK1" s="14" t="s">
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="AL1" s="14"/>
-      <c r="AM1" s="14"/>
-      <c r="AN1" s="14"/>
-      <c r="AO1" s="14"/>
-      <c r="AP1" s="14" t="s">
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="AQ1" s="14"/>
-      <c r="AR1" s="14"/>
-      <c r="AS1" s="14"/>
-      <c r="AT1" s="14"/>
-      <c r="AU1" s="14" t="s">
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15"/>
+      <c r="AS1" s="15"/>
+      <c r="AT1" s="15"/>
+      <c r="AU1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="AV1" s="14"/>
-      <c r="AW1" s="14"/>
-      <c r="AX1" s="14"/>
-      <c r="AY1" s="14"/>
-      <c r="AZ1" s="14" t="s">
+      <c r="AV1" s="15"/>
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15"/>
+      <c r="AY1" s="15"/>
+      <c r="AZ1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="BA1" s="14"/>
-      <c r="BB1" s="14"/>
-      <c r="BC1" s="14"/>
-      <c r="BD1" s="14"/>
-      <c r="BE1" s="14" t="s">
+      <c r="BA1" s="15"/>
+      <c r="BB1" s="15"/>
+      <c r="BC1" s="15"/>
+      <c r="BD1" s="15"/>
+      <c r="BE1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="BF1" s="14"/>
-      <c r="BG1" s="14"/>
-      <c r="BH1" s="14"/>
-      <c r="BI1" s="14"/>
-      <c r="BJ1" s="14" t="s">
+      <c r="BF1" s="15"/>
+      <c r="BG1" s="15"/>
+      <c r="BH1" s="15"/>
+      <c r="BI1" s="15"/>
+      <c r="BJ1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="BK1" s="14"/>
-      <c r="BL1" s="14"/>
-      <c r="BM1" s="14"/>
-      <c r="BN1" s="14"/>
-      <c r="BO1" s="14" t="s">
+      <c r="BK1" s="15"/>
+      <c r="BL1" s="15"/>
+      <c r="BM1" s="15"/>
+      <c r="BN1" s="15"/>
+      <c r="BO1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="BP1" s="14"/>
-      <c r="BQ1" s="14"/>
-      <c r="BR1" s="14"/>
-      <c r="BS1" s="14"/>
-      <c r="BT1" s="14" t="s">
+      <c r="BP1" s="15"/>
+      <c r="BQ1" s="15"/>
+      <c r="BR1" s="15"/>
+      <c r="BS1" s="15"/>
+      <c r="BT1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="BU1" s="14"/>
-      <c r="BV1" s="14"/>
-      <c r="BW1" s="14"/>
-      <c r="BX1" s="14"/>
-      <c r="BY1" s="14" t="s">
+      <c r="BU1" s="15"/>
+      <c r="BV1" s="15"/>
+      <c r="BW1" s="15"/>
+      <c r="BX1" s="15"/>
+      <c r="BY1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="BZ1" s="14"/>
-      <c r="CA1" s="14"/>
-      <c r="CB1" s="14"/>
-      <c r="CC1" s="14"/>
-      <c r="CD1" s="14" t="s">
+      <c r="BZ1" s="15"/>
+      <c r="CA1" s="15"/>
+      <c r="CB1" s="15"/>
+      <c r="CC1" s="15"/>
+      <c r="CD1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="CE1" s="14"/>
-      <c r="CF1" s="14"/>
-      <c r="CG1" s="14"/>
-      <c r="CH1" s="14"/>
-      <c r="CI1" s="14" t="s">
+      <c r="CE1" s="15"/>
+      <c r="CF1" s="15"/>
+      <c r="CG1" s="15"/>
+      <c r="CH1" s="15"/>
+      <c r="CI1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="CJ1" s="14"/>
-      <c r="CK1" s="14"/>
-      <c r="CL1" s="14"/>
-      <c r="CM1" s="14"/>
-      <c r="CN1" s="14" t="s">
+      <c r="CJ1" s="15"/>
+      <c r="CK1" s="15"/>
+      <c r="CL1" s="15"/>
+      <c r="CM1" s="15"/>
+      <c r="CN1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="CO1" s="14"/>
-      <c r="CP1" s="14"/>
-      <c r="CQ1" s="14"/>
-      <c r="CR1" s="14"/>
-      <c r="CS1" s="14" t="s">
+      <c r="CO1" s="15"/>
+      <c r="CP1" s="15"/>
+      <c r="CQ1" s="15"/>
+      <c r="CR1" s="15"/>
+      <c r="CS1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="CT1" s="14"/>
-      <c r="CU1" s="14"/>
-      <c r="CV1" s="14"/>
-      <c r="CW1" s="14"/>
-      <c r="CX1" s="14" t="s">
+      <c r="CT1" s="15"/>
+      <c r="CU1" s="15"/>
+      <c r="CV1" s="15"/>
+      <c r="CW1" s="15"/>
+      <c r="CX1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="CY1" s="14"/>
-      <c r="CZ1" s="14"/>
-      <c r="DA1" s="14"/>
-      <c r="DB1" s="14"/>
+      <c r="CY1" s="15"/>
+      <c r="CZ1" s="15"/>
+      <c r="DA1" s="15"/>
+      <c r="DB1" s="15"/>
     </row>
     <row r="2" spans="1:106" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -16195,6 +16426,15 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="CN1:CR1"/>
+    <mergeCell ref="CS1:CW1"/>
+    <mergeCell ref="CX1:DB1"/>
+    <mergeCell ref="BJ1:BN1"/>
+    <mergeCell ref="BO1:BS1"/>
+    <mergeCell ref="BT1:BX1"/>
+    <mergeCell ref="BY1:CC1"/>
+    <mergeCell ref="CD1:CH1"/>
+    <mergeCell ref="CI1:CM1"/>
     <mergeCell ref="BE1:BI1"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:K1"/>
@@ -16207,15 +16447,6 @@
     <mergeCell ref="AP1:AT1"/>
     <mergeCell ref="AU1:AY1"/>
     <mergeCell ref="AZ1:BD1"/>
-    <mergeCell ref="CN1:CR1"/>
-    <mergeCell ref="CS1:CW1"/>
-    <mergeCell ref="CX1:DB1"/>
-    <mergeCell ref="BJ1:BN1"/>
-    <mergeCell ref="BO1:BS1"/>
-    <mergeCell ref="BT1:BX1"/>
-    <mergeCell ref="BY1:CC1"/>
-    <mergeCell ref="CD1:CH1"/>
-    <mergeCell ref="CI1:CM1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16348,7 +16579,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88AF971A-0C51-450E-BC56-9CBEC167DAAD}">
-  <dimension ref="A1:AP12"/>
+  <dimension ref="A1:AP13"/>
   <sheetFormatPr defaultColWidth="6" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" style="4" customWidth="1"/>
@@ -16398,61 +16629,61 @@
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A1" s="11"/>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="19"/>
       <c r="G1" s="11"/>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
       <c r="M1" s="11"/>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
       <c r="S1" s="11"/>
-      <c r="T1" s="15" t="s">
+      <c r="T1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
       <c r="Y1" s="11"/>
-      <c r="Z1" s="15" t="s">
+      <c r="Z1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
       <c r="AE1" s="11"/>
-      <c r="AF1" s="15" t="s">
+      <c r="AF1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15"/>
-      <c r="AI1" s="15"/>
-      <c r="AJ1" s="15"/>
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16"/>
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="16"/>
       <c r="AK1" s="11"/>
-      <c r="AL1" s="15" t="s">
+      <c r="AL1" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="AM1" s="15"/>
-      <c r="AN1" s="15"/>
-      <c r="AO1" s="15"/>
-      <c r="AP1" s="15"/>
+      <c r="AM1" s="16"/>
+      <c r="AN1" s="16"/>
+      <c r="AO1" s="16"/>
+      <c r="AP1" s="16"/>
     </row>
     <row r="2" spans="1:42" s="5" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -17859,6 +18090,134 @@
         <v>1</v>
       </c>
       <c r="AP12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="14">
+        <v>11</v>
+      </c>
+      <c r="C13" s="14">
+        <v>11</v>
+      </c>
+      <c r="D13" s="14">
+        <v>10</v>
+      </c>
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+      <c r="F13" s="14">
+        <v>2</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="14">
+        <v>12</v>
+      </c>
+      <c r="I13" s="14">
+        <v>12</v>
+      </c>
+      <c r="J13" s="14">
+        <v>11</v>
+      </c>
+      <c r="K13" s="14">
+        <v>1</v>
+      </c>
+      <c r="L13" s="14">
+        <v>2</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="14">
+        <v>43</v>
+      </c>
+      <c r="O13" s="14">
+        <v>40</v>
+      </c>
+      <c r="P13" s="14">
+        <v>39</v>
+      </c>
+      <c r="Q13" s="14">
+        <v>6</v>
+      </c>
+      <c r="R13" s="14">
+        <v>12</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="T13" s="14">
+        <v>0</v>
+      </c>
+      <c r="U13" s="14">
+        <v>0</v>
+      </c>
+      <c r="V13" s="14">
+        <v>0</v>
+      </c>
+      <c r="W13" s="14">
+        <v>0</v>
+      </c>
+      <c r="X13" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z13" s="14">
+        <v>22</v>
+      </c>
+      <c r="AA13" s="14">
+        <v>22</v>
+      </c>
+      <c r="AB13" s="14">
+        <v>20</v>
+      </c>
+      <c r="AC13" s="14">
+        <v>3</v>
+      </c>
+      <c r="AD13" s="14">
+        <v>4</v>
+      </c>
+      <c r="AE13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF13" s="14">
+        <v>15</v>
+      </c>
+      <c r="AG13" s="14">
+        <v>15</v>
+      </c>
+      <c r="AH13" s="14">
+        <v>14</v>
+      </c>
+      <c r="AI13" s="14">
+        <v>2</v>
+      </c>
+      <c r="AJ13" s="14">
+        <v>3</v>
+      </c>
+      <c r="AK13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AL13" s="14">
+        <v>9</v>
+      </c>
+      <c r="AM13" s="14">
+        <v>9</v>
+      </c>
+      <c r="AN13" s="14">
+        <v>9</v>
+      </c>
+      <c r="AO13" s="14">
+        <v>1</v>
+      </c>
+      <c r="AP13" s="14">
         <v>2</v>
       </c>
     </row>
